--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -523,16 +523,16 @@
         <v>0.4</v>
       </c>
       <c r="D2" t="n">
-        <v>1.166</v>
+        <v>1.24</v>
       </c>
       <c r="E2" t="n">
-        <v>12.2</v>
+        <v>30.9</v>
       </c>
       <c r="F2" t="n">
-        <v>25.4</v>
+        <v>52.4</v>
       </c>
       <c r="G2" t="n">
-        <v>38.6</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -551,13 +551,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>49.37</v>
+        <v>57.61</v>
       </c>
       <c r="M2" t="n">
-        <v>60.97</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>26.4</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
@@ -575,16 +575,16 @@
         <v>0.7</v>
       </c>
       <c r="D3" t="n">
-        <v>1.311</v>
+        <v>1.373</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.9</v>
+        <v>-3.3</v>
       </c>
       <c r="F3" t="n">
-        <v>10.8</v>
+        <v>13.1</v>
       </c>
       <c r="G3" t="n">
-        <v>24.4</v>
+        <v>29.4</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -597,25 +597,25 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>2725019</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>73.40000000000001</v>
+        <v>73.13</v>
       </c>
       <c r="M3" t="n">
-        <v>94.06999999999999</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>27.4</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -624,19 +624,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="D4" t="n">
-        <v>1.329</v>
+        <v>1.975</v>
       </c>
       <c r="E4" t="n">
-        <v>-9.4</v>
+        <v>-44.8</v>
       </c>
       <c r="F4" t="n">
-        <v>5.1</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>19.6</v>
+        <v>27.2</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -649,25 +649,25 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>38252</v>
+        <v>333611</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>14.5</v>
+        <v>2.87</v>
       </c>
       <c r="M4" t="n">
-        <v>19.13</v>
+        <v>6.61</v>
       </c>
       <c r="N4" t="n">
-        <v>29</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -676,19 +676,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="D5" t="n">
-        <v>1.194</v>
+        <v>1.331</v>
       </c>
       <c r="E5" t="n">
-        <v>-9.300000000000001</v>
+        <v>-5.9</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7</v>
+        <v>9.1</v>
       </c>
       <c r="G5" t="n">
-        <v>12.8</v>
+        <v>24.2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -701,19 +701,19 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>58812</v>
+        <v>38532</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>25.59</v>
+        <v>15.05</v>
       </c>
       <c r="M5" t="n">
-        <v>31.8</v>
+        <v>19.87</v>
       </c>
       <c r="N5" t="n">
-        <v>22</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="6">
@@ -731,16 +731,16 @@
         <v>0.76</v>
       </c>
       <c r="D6" t="n">
-        <v>1.19</v>
+        <v>1.341</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.1</v>
+        <v>4.1</v>
       </c>
       <c r="F6" t="n">
-        <v>2.9</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>23.9</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -759,19 +759,19 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>69.31</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>76.45</v>
+        <v>87.73</v>
       </c>
       <c r="N6" t="n">
-        <v>10.1</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -780,50 +780,50 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="D7" t="n">
-        <v>0.962</v>
+        <v>1.237</v>
       </c>
       <c r="E7" t="n">
-        <v>20.8</v>
+        <v>-5.4</v>
       </c>
       <c r="F7" t="n">
-        <v>13.1</v>
+        <v>8.1</v>
       </c>
       <c r="G7" t="n">
-        <v>5.3</v>
+        <v>21.7</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>BUY (undervalued)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>BUY (undervalued)</t>
-        </is>
-      </c>
       <c r="J7" t="n">
+        <v>68988</v>
+      </c>
+      <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="n">
-        <v>2977992</v>
-      </c>
       <c r="L7" t="n">
-        <v>26.45</v>
+        <v>26.68</v>
       </c>
       <c r="M7" t="n">
-        <v>23.07</v>
+        <v>34.31</v>
       </c>
       <c r="N7" t="n">
-        <v>-15.4</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -832,50 +832,50 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="D8" t="n">
-        <v>1.408</v>
+        <v>0.962</v>
       </c>
       <c r="E8" t="n">
-        <v>-29.7</v>
+        <v>35.3</v>
       </c>
       <c r="F8" t="n">
-        <v>-14.4</v>
+        <v>27.3</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>19.2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>123511</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>28991</v>
+        <v>2977992</v>
       </c>
       <c r="L8" t="n">
-        <v>5.41</v>
+        <v>29.63</v>
       </c>
       <c r="M8" t="n">
-        <v>7.78</v>
+        <v>26.11</v>
       </c>
       <c r="N8" t="n">
-        <v>30.7</v>
+        <v>-16.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -884,19 +884,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="D9" t="n">
-        <v>1.743</v>
+        <v>1.214</v>
       </c>
       <c r="E9" t="n">
-        <v>-56.1</v>
+        <v>-5.7</v>
       </c>
       <c r="F9" t="n">
-        <v>-30.6</v>
+        <v>5.5</v>
       </c>
       <c r="G9" t="n">
-        <v>-5</v>
+        <v>16.8</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -905,23 +905,23 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>287175</v>
+        <v>28969</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2.28</v>
+        <v>25.64</v>
       </c>
       <c r="M9" t="n">
-        <v>4.94</v>
+        <v>31.76</v>
       </c>
       <c r="N9" t="n">
-        <v>51.1</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="10">
@@ -939,16 +939,16 @@
         <v>0.98</v>
       </c>
       <c r="D10" t="n">
-        <v>1.374</v>
+        <v>1.517</v>
       </c>
       <c r="E10" t="n">
-        <v>-33.2</v>
+        <v>-23.7</v>
       </c>
       <c r="F10" t="n">
-        <v>-22.1</v>
+        <v>-7</v>
       </c>
       <c r="G10" t="n">
-        <v>-11.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -957,29 +957,29 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>303978</v>
+        <v>341877</v>
       </c>
       <c r="K10" t="n">
-        <v>72181</v>
+        <v>67877</v>
       </c>
       <c r="L10" t="n">
-        <v>52.08</v>
+        <v>59.5</v>
       </c>
       <c r="M10" t="n">
-        <v>69.37</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>22.2</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.09</v>
+        <v>0.95</v>
       </c>
       <c r="D11" t="n">
-        <v>0.986</v>
+        <v>1.433</v>
       </c>
       <c r="E11" t="n">
-        <v>-18.7</v>
+        <v>-25.1</v>
       </c>
       <c r="F11" t="n">
-        <v>-19.2</v>
+        <v>-8.4</v>
       </c>
       <c r="G11" t="n">
-        <v>-19.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1009,29 +1009,29 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>148415</v>
+        <v>126273</v>
       </c>
       <c r="K11" t="n">
-        <v>165372</v>
+        <v>28673</v>
       </c>
       <c r="L11" t="n">
-        <v>13.34</v>
+        <v>5.77</v>
       </c>
       <c r="M11" t="n">
-        <v>13.15</v>
+        <v>8.34</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1040,19 +1040,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.37</v>
+        <v>1.09</v>
       </c>
       <c r="D12" t="n">
-        <v>0.874</v>
+        <v>1.145</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.6</v>
+        <v>-8.1</v>
       </c>
       <c r="F12" t="n">
-        <v>-15.7</v>
+        <v>-2</v>
       </c>
       <c r="G12" t="n">
-        <v>-25.8</v>
+        <v>4</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1061,23 +1061,23 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>3162500</v>
+        <v>315444</v>
       </c>
       <c r="K12" t="n">
-        <v>3162500</v>
+        <v>168393</v>
       </c>
       <c r="L12" t="n">
-        <v>28.04</v>
+        <v>15.08</v>
       </c>
       <c r="M12" t="n">
-        <v>22.03</v>
+        <v>17.05</v>
       </c>
       <c r="N12" t="n">
-        <v>-20.2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -1095,16 +1095,16 @@
         <v>1.2</v>
       </c>
       <c r="D13" t="n">
-        <v>0.999</v>
+        <v>1.118</v>
       </c>
       <c r="E13" t="n">
-        <v>-30.8</v>
+        <v>-14.9</v>
       </c>
       <c r="F13" t="n">
-        <v>-30.8</v>
+        <v>-9</v>
       </c>
       <c r="G13" t="n">
-        <v>-30.9</v>
+        <v>-3</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1113,23 +1113,23 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>207932</v>
+        <v>311398</v>
       </c>
       <c r="K13" t="n">
-        <v>208756</v>
+        <v>214522</v>
       </c>
       <c r="L13" t="n">
-        <v>23.87</v>
+        <v>29.36</v>
       </c>
       <c r="M13" t="n">
-        <v>23.84</v>
+        <v>33.45</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="14">
@@ -1147,16 +1147,16 @@
         <v>1.21</v>
       </c>
       <c r="D14" t="n">
-        <v>0.991</v>
+        <v>1.118</v>
       </c>
       <c r="E14" t="n">
-        <v>-31.8</v>
+        <v>-17.6</v>
       </c>
       <c r="F14" t="n">
-        <v>-32.2</v>
+        <v>-11.9</v>
       </c>
       <c r="G14" t="n">
-        <v>-32.6</v>
+        <v>-6.2</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1169,19 +1169,71 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>207393</v>
+        <v>299841</v>
       </c>
       <c r="K14" t="n">
-        <v>215201</v>
+        <v>214608</v>
       </c>
       <c r="L14" t="n">
-        <v>32.53</v>
+        <v>39.32</v>
       </c>
       <c r="M14" t="n">
-        <v>32.14</v>
+        <v>44.72</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8</v>
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FLNG</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-21</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>HOLD (fairly valued)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>3162500</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3162500</v>
+      </c>
+      <c r="L15" t="n">
+        <v>29.73</v>
+      </c>
+      <c r="M15" t="n">
+        <v>23.47</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-21.1</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -887,7 +887,7 @@
         <v>0.82</v>
       </c>
       <c r="D9" t="n">
-        <v>1.214</v>
+        <v>1.215</v>
       </c>
       <c r="E9" t="n">
         <v>-5.7</v>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>28969</v>
+        <v>28968</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -918,41 +918,41 @@
         <v>25.64</v>
       </c>
       <c r="M9" t="n">
-        <v>31.76</v>
+        <v>31.77</v>
       </c>
       <c r="N9" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.98</v>
+        <v>0.87</v>
       </c>
       <c r="D10" t="n">
-        <v>1.517</v>
+        <v>1.045</v>
       </c>
       <c r="E10" t="n">
-        <v>-23.7</v>
+        <v>6.9</v>
       </c>
       <c r="F10" t="n">
-        <v>-7</v>
+        <v>9.5</v>
       </c>
       <c r="G10" t="n">
-        <v>9.699999999999999</v>
+        <v>12.1</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -961,46 +961,46 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>341877</v>
+        <v>18726</v>
       </c>
       <c r="K10" t="n">
-        <v>67877</v>
+        <v>12491</v>
       </c>
       <c r="L10" t="n">
-        <v>59.5</v>
+        <v>25.65</v>
       </c>
       <c r="M10" t="n">
-        <v>85.54000000000001</v>
+        <v>26.91</v>
       </c>
       <c r="N10" t="n">
-        <v>33.4</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="D11" t="n">
-        <v>1.433</v>
+        <v>1.517</v>
       </c>
       <c r="E11" t="n">
-        <v>-25.1</v>
+        <v>-23.7</v>
       </c>
       <c r="F11" t="n">
-        <v>-8.4</v>
+        <v>-7</v>
       </c>
       <c r="G11" t="n">
-        <v>8.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1013,16 +1013,16 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>126273</v>
+        <v>341877</v>
       </c>
       <c r="K11" t="n">
-        <v>28673</v>
+        <v>67877</v>
       </c>
       <c r="L11" t="n">
-        <v>5.77</v>
+        <v>59.5</v>
       </c>
       <c r="M11" t="n">
-        <v>8.34</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="N11" t="n">
         <v>33.4</v>
@@ -1031,7 +1031,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1040,19 +1040,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.09</v>
+        <v>0.95</v>
       </c>
       <c r="D12" t="n">
-        <v>1.145</v>
+        <v>1.433</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.1</v>
+        <v>-25.1</v>
       </c>
       <c r="F12" t="n">
-        <v>-2</v>
+        <v>-8.4</v>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1061,29 +1061,29 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>315444</v>
+        <v>126273</v>
       </c>
       <c r="K12" t="n">
-        <v>168393</v>
+        <v>28673</v>
       </c>
       <c r="L12" t="n">
-        <v>15.08</v>
+        <v>5.77</v>
       </c>
       <c r="M12" t="n">
-        <v>17.05</v>
+        <v>8.34</v>
       </c>
       <c r="N12" t="n">
-        <v>12</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1092,19 +1092,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="D13" t="n">
-        <v>1.118</v>
+        <v>1.145</v>
       </c>
       <c r="E13" t="n">
-        <v>-14.9</v>
+        <v>-8.1</v>
       </c>
       <c r="F13" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="G13" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1117,25 +1117,25 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>311398</v>
+        <v>315444</v>
       </c>
       <c r="K13" t="n">
-        <v>214522</v>
+        <v>168393</v>
       </c>
       <c r="L13" t="n">
-        <v>29.36</v>
+        <v>15.08</v>
       </c>
       <c r="M13" t="n">
-        <v>33.45</v>
+        <v>17.05</v>
       </c>
       <c r="N13" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="D14" t="n">
         <v>1.118</v>
       </c>
       <c r="E14" t="n">
-        <v>-17.6</v>
+        <v>-14.9</v>
       </c>
       <c r="F14" t="n">
-        <v>-11.9</v>
+        <v>-9</v>
       </c>
       <c r="G14" t="n">
-        <v>-6.2</v>
+        <v>-3</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1165,74 +1165,126 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>299841</v>
+        <v>311398</v>
       </c>
       <c r="K14" t="n">
-        <v>214608</v>
+        <v>214522</v>
       </c>
       <c r="L14" t="n">
-        <v>39.32</v>
+        <v>29.36</v>
       </c>
       <c r="M14" t="n">
-        <v>44.72</v>
+        <v>33.45</v>
       </c>
       <c r="N14" t="n">
-        <v>11.3</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>ECO</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.118</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-17.6</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-11.9</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>299841</v>
+      </c>
+      <c r="K15" t="n">
+        <v>214608</v>
+      </c>
+      <c r="L15" t="n">
+        <v>39.32</v>
+      </c>
+      <c r="M15" t="n">
+        <v>44.72</v>
+      </c>
+      <c r="N15" t="n">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>FLNG</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>whole-company</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
         <v>1.37</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D16" t="n">
         <v>0.874</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E16" t="n">
         <v>0.1</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F16" t="n">
         <v>-10.4</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G16" t="n">
         <v>-21</v>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="J16" t="n">
         <v>3162500</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K16" t="n">
         <v>3162500</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L16" t="n">
         <v>29.73</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M16" t="n">
         <v>23.47</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N16" t="n">
         <v>-21.1</v>
       </c>
     </row>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -557,7 +557,7 @@
         <v>76.51000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="3">
@@ -627,13 +627,13 @@
         <v>0.85</v>
       </c>
       <c r="D4" t="n">
-        <v>1.975</v>
+        <v>1.979</v>
       </c>
       <c r="E4" t="n">
-        <v>-44.8</v>
+        <v>-44.9</v>
       </c>
       <c r="F4" t="n">
-        <v>-8.800000000000001</v>
+        <v>-8.9</v>
       </c>
       <c r="G4" t="n">
         <v>27.2</v>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>333611</v>
+        <v>334239</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="M4" t="n">
         <v>6.61</v>
       </c>
       <c r="N4" t="n">
-        <v>72</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -731,7 +731,7 @@
         <v>0.76</v>
       </c>
       <c r="D6" t="n">
-        <v>1.341</v>
+        <v>1.342</v>
       </c>
       <c r="E6" t="n">
         <v>4.1</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>73.73999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="M6" t="n">
         <v>87.73</v>
@@ -991,10 +991,10 @@
         <v>0.98</v>
       </c>
       <c r="D11" t="n">
-        <v>1.517</v>
+        <v>1.518</v>
       </c>
       <c r="E11" t="n">
-        <v>-23.7</v>
+        <v>-23.8</v>
       </c>
       <c r="F11" t="n">
         <v>-7</v>
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>341877</v>
+        <v>342121</v>
       </c>
       <c r="K11" t="n">
-        <v>67877</v>
+        <v>67887</v>
       </c>
       <c r="L11" t="n">
-        <v>59.5</v>
+        <v>59.47</v>
       </c>
       <c r="M11" t="n">
         <v>85.54000000000001</v>
@@ -1169,10 +1169,10 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>311398</v>
+        <v>311332</v>
       </c>
       <c r="K14" t="n">
-        <v>214522</v>
+        <v>214599</v>
       </c>
       <c r="L14" t="n">
         <v>29.36</v>
@@ -1202,7 +1202,7 @@
         <v>1.118</v>
       </c>
       <c r="E15" t="n">
-        <v>-17.6</v>
+        <v>-17.5</v>
       </c>
       <c r="F15" t="n">
         <v>-11.9</v>
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>299841</v>
+        <v>299660</v>
       </c>
       <c r="K15" t="n">
-        <v>214608</v>
+        <v>214617</v>
       </c>
       <c r="L15" t="n">
-        <v>39.32</v>
+        <v>39.33</v>
       </c>
       <c r="M15" t="n">
         <v>44.72</v>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -887,13 +887,13 @@
         <v>0.82</v>
       </c>
       <c r="D9" t="n">
-        <v>1.215</v>
+        <v>1.211</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.7</v>
+        <v>-5.4</v>
       </c>
       <c r="F9" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="G9" t="n">
         <v>16.8</v>
@@ -909,19 +909,19 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>28968</v>
+        <v>28583</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>25.64</v>
+        <v>25.72</v>
       </c>
       <c r="M9" t="n">
         <v>31.77</v>
       </c>
       <c r="N9" t="n">
-        <v>22.6</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="10">
@@ -939,13 +939,13 @@
         <v>0.87</v>
       </c>
       <c r="D10" t="n">
-        <v>1.045</v>
+        <v>1.042</v>
       </c>
       <c r="E10" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="F10" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G10" t="n">
         <v>12.1</v>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>18726</v>
+        <v>18314</v>
       </c>
       <c r="K10" t="n">
-        <v>12491</v>
+        <v>12474</v>
       </c>
       <c r="L10" t="n">
-        <v>25.65</v>
+        <v>25.73</v>
       </c>
       <c r="M10" t="n">
         <v>26.91</v>
       </c>
       <c r="N10" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="11">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -563,7 +563,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -572,23 +572,23 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.7</v>
+        <v>0.62</v>
       </c>
       <c r="D3" t="n">
-        <v>1.373</v>
+        <v>0.843</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.3</v>
+        <v>64.2</v>
       </c>
       <c r="F3" t="n">
-        <v>13.1</v>
+        <v>53</v>
       </c>
       <c r="G3" t="n">
-        <v>29.4</v>
+        <v>41.9</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -597,25 +597,25 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2725019</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>73.13</v>
+        <v>28.32</v>
       </c>
       <c r="M3" t="n">
-        <v>97.81999999999999</v>
+        <v>24.47</v>
       </c>
       <c r="N3" t="n">
-        <v>32.7</v>
+        <v>-22.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -624,23 +624,23 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="D4" t="n">
-        <v>1.979</v>
+        <v>1.373</v>
       </c>
       <c r="E4" t="n">
-        <v>-44.9</v>
+        <v>-3.3</v>
       </c>
       <c r="F4" t="n">
-        <v>-8.9</v>
+        <v>13.1</v>
       </c>
       <c r="G4" t="n">
-        <v>27.2</v>
+        <v>29.4</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -649,25 +649,25 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>334239</v>
+        <v>2725019</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2.86</v>
+        <v>73.13</v>
       </c>
       <c r="M4" t="n">
-        <v>6.61</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>72.09999999999999</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -676,19 +676,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="D5" t="n">
-        <v>1.331</v>
+        <v>1.979</v>
       </c>
       <c r="E5" t="n">
-        <v>-5.9</v>
+        <v>-44.9</v>
       </c>
       <c r="F5" t="n">
-        <v>9.1</v>
+        <v>-8.9</v>
       </c>
       <c r="G5" t="n">
-        <v>24.2</v>
+        <v>27.2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -701,25 +701,25 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>38532</v>
+        <v>334239</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>15.05</v>
+        <v>2.86</v>
       </c>
       <c r="M5" t="n">
-        <v>19.87</v>
+        <v>6.61</v>
       </c>
       <c r="N5" t="n">
-        <v>30.1</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -728,23 +728,23 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="D6" t="n">
-        <v>1.342</v>
+        <v>1.331</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1</v>
+        <v>-5.9</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>9.1</v>
       </c>
       <c r="G6" t="n">
-        <v>23.9</v>
+        <v>24.2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -753,25 +753,25 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>38532</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>73.7</v>
+        <v>15.05</v>
       </c>
       <c r="M6" t="n">
-        <v>87.73</v>
+        <v>19.87</v>
       </c>
       <c r="N6" t="n">
-        <v>19.8</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -780,23 +780,23 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.83</v>
+        <v>0.76</v>
       </c>
       <c r="D7" t="n">
-        <v>1.237</v>
+        <v>1.342</v>
       </c>
       <c r="E7" t="n">
-        <v>-5.4</v>
+        <v>4.1</v>
       </c>
       <c r="F7" t="n">
-        <v>8.1</v>
+        <v>14</v>
       </c>
       <c r="G7" t="n">
-        <v>21.7</v>
+        <v>23.9</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -805,25 +805,25 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>68988</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>26.68</v>
+        <v>73.7</v>
       </c>
       <c r="M7" t="n">
-        <v>34.31</v>
+        <v>87.73</v>
       </c>
       <c r="N7" t="n">
-        <v>27.1</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -832,23 +832,23 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="D8" t="n">
-        <v>0.962</v>
+        <v>1.237</v>
       </c>
       <c r="E8" t="n">
-        <v>35.3</v>
+        <v>-5.4</v>
       </c>
       <c r="F8" t="n">
-        <v>27.3</v>
+        <v>8.1</v>
       </c>
       <c r="G8" t="n">
-        <v>19.2</v>
+        <v>21.7</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -857,25 +857,25 @@
         </is>
       </c>
       <c r="J8" t="n">
+        <v>68988</v>
+      </c>
+      <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="K8" t="n">
-        <v>2977992</v>
-      </c>
       <c r="L8" t="n">
-        <v>29.63</v>
+        <v>26.68</v>
       </c>
       <c r="M8" t="n">
-        <v>26.11</v>
+        <v>34.31</v>
       </c>
       <c r="N8" t="n">
-        <v>-16.1</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -884,23 +884,23 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.82</v>
+        <v>0.9</v>
       </c>
       <c r="D9" t="n">
-        <v>1.211</v>
+        <v>0.962</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.4</v>
+        <v>35.3</v>
       </c>
       <c r="F9" t="n">
-        <v>5.7</v>
+        <v>27.3</v>
       </c>
       <c r="G9" t="n">
-        <v>16.8</v>
+        <v>19.2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -909,25 +909,25 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>28583</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2977992</v>
       </c>
       <c r="L9" t="n">
-        <v>25.72</v>
+        <v>29.63</v>
       </c>
       <c r="M9" t="n">
-        <v>31.77</v>
+        <v>26.11</v>
       </c>
       <c r="N9" t="n">
-        <v>22.3</v>
+        <v>-16.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -936,23 +936,23 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="D10" t="n">
-        <v>1.042</v>
+        <v>1.211</v>
       </c>
       <c r="E10" t="n">
-        <v>7.2</v>
+        <v>-5.4</v>
       </c>
       <c r="F10" t="n">
-        <v>9.699999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="G10" t="n">
-        <v>12.1</v>
+        <v>16.8</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -961,50 +961,50 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>18314</v>
+        <v>28583</v>
       </c>
       <c r="K10" t="n">
-        <v>12474</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>25.73</v>
+        <v>25.72</v>
       </c>
       <c r="M10" t="n">
-        <v>26.91</v>
+        <v>31.77</v>
       </c>
       <c r="N10" t="n">
-        <v>4.9</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.98</v>
+        <v>0.87</v>
       </c>
       <c r="D11" t="n">
-        <v>1.518</v>
+        <v>1.042</v>
       </c>
       <c r="E11" t="n">
-        <v>-23.8</v>
+        <v>7.2</v>
       </c>
       <c r="F11" t="n">
-        <v>-7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>9.699999999999999</v>
+        <v>12.1</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1013,46 +1013,46 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>342121</v>
+        <v>18314</v>
       </c>
       <c r="K11" t="n">
-        <v>67887</v>
+        <v>12474</v>
       </c>
       <c r="L11" t="n">
-        <v>59.47</v>
+        <v>25.73</v>
       </c>
       <c r="M11" t="n">
-        <v>85.54000000000001</v>
+        <v>26.91</v>
       </c>
       <c r="N11" t="n">
-        <v>33.4</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="D12" t="n">
-        <v>1.433</v>
+        <v>1.518</v>
       </c>
       <c r="E12" t="n">
-        <v>-25.1</v>
+        <v>-23.8</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.4</v>
+        <v>-7</v>
       </c>
       <c r="G12" t="n">
-        <v>8.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1065,16 +1065,16 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>126273</v>
+        <v>342121</v>
       </c>
       <c r="K12" t="n">
-        <v>28673</v>
+        <v>67887</v>
       </c>
       <c r="L12" t="n">
-        <v>5.77</v>
+        <v>59.47</v>
       </c>
       <c r="M12" t="n">
-        <v>8.34</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="N12" t="n">
         <v>33.4</v>
@@ -1083,7 +1083,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1092,19 +1092,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.09</v>
+        <v>0.95</v>
       </c>
       <c r="D13" t="n">
-        <v>1.145</v>
+        <v>1.433</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.1</v>
+        <v>-25.1</v>
       </c>
       <c r="F13" t="n">
-        <v>-2</v>
+        <v>-8.4</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1113,29 +1113,29 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>315444</v>
+        <v>126273</v>
       </c>
       <c r="K13" t="n">
-        <v>168393</v>
+        <v>28673</v>
       </c>
       <c r="L13" t="n">
-        <v>15.08</v>
+        <v>5.77</v>
       </c>
       <c r="M13" t="n">
-        <v>17.05</v>
+        <v>8.34</v>
       </c>
       <c r="N13" t="n">
-        <v>12</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="D14" t="n">
-        <v>1.118</v>
+        <v>1.145</v>
       </c>
       <c r="E14" t="n">
-        <v>-14.9</v>
+        <v>-8.1</v>
       </c>
       <c r="F14" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="G14" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1169,25 +1169,25 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>311332</v>
+        <v>315444</v>
       </c>
       <c r="K14" t="n">
-        <v>214599</v>
+        <v>168393</v>
       </c>
       <c r="L14" t="n">
-        <v>29.36</v>
+        <v>15.08</v>
       </c>
       <c r="M14" t="n">
-        <v>33.45</v>
+        <v>17.05</v>
       </c>
       <c r="N14" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1196,19 +1196,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="D15" t="n">
         <v>1.118</v>
       </c>
       <c r="E15" t="n">
-        <v>-17.5</v>
+        <v>-14.9</v>
       </c>
       <c r="F15" t="n">
-        <v>-11.9</v>
+        <v>-9</v>
       </c>
       <c r="G15" t="n">
-        <v>-6.2</v>
+        <v>-3</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1217,74 +1217,126 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>299660</v>
+        <v>311332</v>
       </c>
       <c r="K15" t="n">
-        <v>214617</v>
+        <v>214599</v>
       </c>
       <c r="L15" t="n">
-        <v>39.33</v>
+        <v>29.36</v>
       </c>
       <c r="M15" t="n">
-        <v>44.72</v>
+        <v>33.45</v>
       </c>
       <c r="N15" t="n">
-        <v>11.3</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>ECO</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.118</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-17.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-11.9</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>299660</v>
+      </c>
+      <c r="K16" t="n">
+        <v>214617</v>
+      </c>
+      <c r="L16" t="n">
+        <v>39.33</v>
+      </c>
+      <c r="M16" t="n">
+        <v>44.72</v>
+      </c>
+      <c r="N16" t="n">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>FLNG</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>whole-company</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
         <v>1.37</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D17" t="n">
         <v>0.874</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E17" t="n">
         <v>0.1</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F17" t="n">
         <v>-10.4</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G17" t="n">
         <v>-21</v>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="J17" t="n">
         <v>3162500</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K17" t="n">
         <v>3162500</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L17" t="n">
         <v>29.73</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M17" t="n">
         <v>23.47</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N17" t="n">
         <v>-21.1</v>
       </c>
     </row>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -563,7 +563,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -572,23 +572,23 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.62</v>
+        <v>0.7</v>
       </c>
       <c r="D3" t="n">
-        <v>0.843</v>
+        <v>1.373</v>
       </c>
       <c r="E3" t="n">
-        <v>64.2</v>
+        <v>-3.3</v>
       </c>
       <c r="F3" t="n">
-        <v>53</v>
+        <v>13.1</v>
       </c>
       <c r="G3" t="n">
-        <v>41.9</v>
+        <v>29.4</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -597,25 +597,25 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>2725019</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>28.32</v>
+        <v>73.13</v>
       </c>
       <c r="M3" t="n">
-        <v>24.47</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>-22.3</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -624,23 +624,23 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="D4" t="n">
-        <v>1.373</v>
+        <v>1.979</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.3</v>
+        <v>-44.9</v>
       </c>
       <c r="F4" t="n">
-        <v>13.1</v>
+        <v>-8.9</v>
       </c>
       <c r="G4" t="n">
-        <v>29.4</v>
+        <v>27.2</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -649,25 +649,25 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2725019</v>
+        <v>334239</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>73.13</v>
+        <v>2.86</v>
       </c>
       <c r="M4" t="n">
-        <v>97.81999999999999</v>
+        <v>6.61</v>
       </c>
       <c r="N4" t="n">
-        <v>32.7</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -676,19 +676,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="D5" t="n">
-        <v>1.979</v>
+        <v>1.331</v>
       </c>
       <c r="E5" t="n">
-        <v>-44.9</v>
+        <v>-5.9</v>
       </c>
       <c r="F5" t="n">
-        <v>-8.9</v>
+        <v>9.1</v>
       </c>
       <c r="G5" t="n">
-        <v>27.2</v>
+        <v>24.2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -701,25 +701,25 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>334239</v>
+        <v>38532</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>2.86</v>
+        <v>15.05</v>
       </c>
       <c r="M5" t="n">
-        <v>6.61</v>
+        <v>19.87</v>
       </c>
       <c r="N5" t="n">
-        <v>72.09999999999999</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -728,23 +728,23 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="D6" t="n">
-        <v>1.331</v>
+        <v>1.342</v>
       </c>
       <c r="E6" t="n">
-        <v>-5.9</v>
+        <v>4.1</v>
       </c>
       <c r="F6" t="n">
-        <v>9.1</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>24.2</v>
+        <v>23.9</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -753,25 +753,25 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>38532</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>15.05</v>
+        <v>73.7</v>
       </c>
       <c r="M6" t="n">
-        <v>19.87</v>
+        <v>87.73</v>
       </c>
       <c r="N6" t="n">
-        <v>30.1</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -780,23 +780,23 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="D7" t="n">
-        <v>1.342</v>
+        <v>1.237</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1</v>
+        <v>-5.4</v>
       </c>
       <c r="F7" t="n">
-        <v>14</v>
+        <v>8.1</v>
       </c>
       <c r="G7" t="n">
-        <v>23.9</v>
+        <v>21.7</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -805,25 +805,25 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>68988</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>73.7</v>
+        <v>26.68</v>
       </c>
       <c r="M7" t="n">
-        <v>87.73</v>
+        <v>34.31</v>
       </c>
       <c r="N7" t="n">
-        <v>19.8</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -832,23 +832,23 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="D8" t="n">
-        <v>1.237</v>
+        <v>0.962</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.4</v>
+        <v>35.3</v>
       </c>
       <c r="F8" t="n">
-        <v>8.1</v>
+        <v>27.3</v>
       </c>
       <c r="G8" t="n">
-        <v>21.7</v>
+        <v>19.2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -857,25 +857,25 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>68988</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2977992</v>
       </c>
       <c r="L8" t="n">
-        <v>26.68</v>
+        <v>29.63</v>
       </c>
       <c r="M8" t="n">
-        <v>34.31</v>
+        <v>26.11</v>
       </c>
       <c r="N8" t="n">
-        <v>27.1</v>
+        <v>-16.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -884,23 +884,23 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="D9" t="n">
-        <v>0.962</v>
+        <v>1.211</v>
       </c>
       <c r="E9" t="n">
-        <v>35.3</v>
+        <v>-5.4</v>
       </c>
       <c r="F9" t="n">
-        <v>27.3</v>
+        <v>5.7</v>
       </c>
       <c r="G9" t="n">
-        <v>19.2</v>
+        <v>16.8</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -909,25 +909,25 @@
         </is>
       </c>
       <c r="J9" t="n">
+        <v>28583</v>
+      </c>
+      <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="K9" t="n">
-        <v>2977992</v>
-      </c>
       <c r="L9" t="n">
-        <v>29.63</v>
+        <v>25.72</v>
       </c>
       <c r="M9" t="n">
-        <v>26.11</v>
+        <v>31.77</v>
       </c>
       <c r="N9" t="n">
-        <v>-16.1</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -936,23 +936,23 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="D10" t="n">
-        <v>1.211</v>
+        <v>1.042</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.4</v>
+        <v>7.2</v>
       </c>
       <c r="F10" t="n">
-        <v>5.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>16.8</v>
+        <v>12.1</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -961,50 +961,50 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>28583</v>
+        <v>18314</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>12474</v>
       </c>
       <c r="L10" t="n">
-        <v>25.72</v>
+        <v>25.73</v>
       </c>
       <c r="M10" t="n">
-        <v>31.77</v>
+        <v>26.91</v>
       </c>
       <c r="N10" t="n">
-        <v>22.3</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.87</v>
+        <v>0.98</v>
       </c>
       <c r="D11" t="n">
-        <v>1.042</v>
+        <v>1.518</v>
       </c>
       <c r="E11" t="n">
-        <v>7.2</v>
+        <v>-23.8</v>
       </c>
       <c r="F11" t="n">
+        <v>-7</v>
+      </c>
+      <c r="G11" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="G11" t="n">
-        <v>12.1</v>
-      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1013,46 +1013,46 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>18314</v>
+        <v>342121</v>
       </c>
       <c r="K11" t="n">
-        <v>12474</v>
+        <v>67887</v>
       </c>
       <c r="L11" t="n">
-        <v>25.73</v>
+        <v>59.47</v>
       </c>
       <c r="M11" t="n">
-        <v>26.91</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>4.9</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="D12" t="n">
-        <v>1.518</v>
+        <v>1.433</v>
       </c>
       <c r="E12" t="n">
-        <v>-23.8</v>
+        <v>-25.1</v>
       </c>
       <c r="F12" t="n">
-        <v>-7</v>
+        <v>-8.4</v>
       </c>
       <c r="G12" t="n">
-        <v>9.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1065,16 +1065,16 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>342121</v>
+        <v>126273</v>
       </c>
       <c r="K12" t="n">
-        <v>67887</v>
+        <v>28673</v>
       </c>
       <c r="L12" t="n">
-        <v>59.47</v>
+        <v>5.77</v>
       </c>
       <c r="M12" t="n">
-        <v>85.54000000000001</v>
+        <v>8.34</v>
       </c>
       <c r="N12" t="n">
         <v>33.4</v>
@@ -1083,7 +1083,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1092,19 +1092,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.95</v>
+        <v>1.09</v>
       </c>
       <c r="D13" t="n">
-        <v>1.433</v>
+        <v>1.145</v>
       </c>
       <c r="E13" t="n">
-        <v>-25.1</v>
+        <v>-8.1</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.4</v>
+        <v>-2</v>
       </c>
       <c r="G13" t="n">
-        <v>8.300000000000001</v>
+        <v>4</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1113,29 +1113,29 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>126273</v>
+        <v>315444</v>
       </c>
       <c r="K13" t="n">
-        <v>28673</v>
+        <v>168393</v>
       </c>
       <c r="L13" t="n">
-        <v>5.77</v>
+        <v>15.08</v>
       </c>
       <c r="M13" t="n">
-        <v>8.34</v>
+        <v>17.05</v>
       </c>
       <c r="N13" t="n">
-        <v>33.4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1144,23 +1144,23 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.09</v>
+        <v>0.62</v>
       </c>
       <c r="D14" t="n">
-        <v>1.145</v>
+        <v>0.843</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.1</v>
+        <v>14.9</v>
       </c>
       <c r="F14" t="n">
-        <v>-2</v>
+        <v>7.1</v>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>-0.7</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1169,19 +1169,19 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>315444</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>168393</v>
+        <v>1070509</v>
       </c>
       <c r="L14" t="n">
-        <v>15.08</v>
+        <v>19.82</v>
       </c>
       <c r="M14" t="n">
-        <v>17.05</v>
+        <v>17.13</v>
       </c>
       <c r="N14" t="n">
-        <v>12</v>
+        <v>-15.6</v>
       </c>
     </row>
     <row r="15">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -520,19 +520,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="D2" t="n">
-        <v>1.24</v>
+        <v>1.234</v>
       </c>
       <c r="E2" t="n">
-        <v>30.9</v>
+        <v>55.1</v>
       </c>
       <c r="F2" t="n">
-        <v>52.4</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>73.90000000000001</v>
+        <v>104.7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -554,10 +554,10 @@
         <v>57.61</v>
       </c>
       <c r="M2" t="n">
-        <v>76.51000000000001</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>42.9</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="3">
@@ -575,13 +575,13 @@
         <v>0.7</v>
       </c>
       <c r="D3" t="n">
-        <v>1.373</v>
+        <v>1.39</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.3</v>
+        <v>-4.4</v>
       </c>
       <c r="F3" t="n">
-        <v>13.1</v>
+        <v>12.5</v>
       </c>
       <c r="G3" t="n">
         <v>29.4</v>
@@ -606,10 +606,10 @@
         <v>73.13</v>
       </c>
       <c r="M3" t="n">
-        <v>97.81999999999999</v>
+        <v>98.92</v>
       </c>
       <c r="N3" t="n">
-        <v>32.7</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="4">
@@ -627,13 +627,13 @@
         <v>0.85</v>
       </c>
       <c r="D4" t="n">
-        <v>1.979</v>
+        <v>1.973</v>
       </c>
       <c r="E4" t="n">
-        <v>-44.9</v>
+        <v>-44.7</v>
       </c>
       <c r="F4" t="n">
-        <v>-8.9</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>27.2</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>334239</v>
+        <v>332327</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>2.86</v>
       </c>
       <c r="M4" t="n">
-        <v>6.61</v>
+        <v>6.59</v>
       </c>
       <c r="N4" t="n">
-        <v>72.09999999999999</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5">
@@ -679,16 +679,16 @@
         <v>0.75</v>
       </c>
       <c r="D5" t="n">
-        <v>1.331</v>
+        <v>1.366</v>
       </c>
       <c r="E5" t="n">
-        <v>-5.9</v>
+        <v>-8.4</v>
       </c>
       <c r="F5" t="n">
-        <v>9.1</v>
+        <v>7.8</v>
       </c>
       <c r="G5" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>38532</v>
+        <v>43825</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -710,10 +710,10 @@
         <v>15.05</v>
       </c>
       <c r="M5" t="n">
-        <v>19.87</v>
+        <v>20.38</v>
       </c>
       <c r="N5" t="n">
-        <v>30.1</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="6">
@@ -731,16 +731,16 @@
         <v>0.76</v>
       </c>
       <c r="D6" t="n">
-        <v>1.342</v>
+        <v>1.398</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="G6" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>47855</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -762,10 +762,10 @@
         <v>73.7</v>
       </c>
       <c r="M6" t="n">
-        <v>87.73</v>
+        <v>90.04000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>19.8</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="7">
@@ -783,16 +783,16 @@
         <v>0.83</v>
       </c>
       <c r="D7" t="n">
-        <v>1.237</v>
+        <v>1.27</v>
       </c>
       <c r="E7" t="n">
-        <v>-5.4</v>
+        <v>-8.6</v>
       </c>
       <c r="F7" t="n">
-        <v>8.1</v>
+        <v>6.3</v>
       </c>
       <c r="G7" t="n">
-        <v>21.7</v>
+        <v>21.2</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>68988</v>
+        <v>78345</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -814,10 +814,10 @@
         <v>26.68</v>
       </c>
       <c r="M7" t="n">
-        <v>34.31</v>
+        <v>35.36</v>
       </c>
       <c r="N7" t="n">
-        <v>27.1</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="8">
@@ -835,16 +835,16 @@
         <v>0.9</v>
       </c>
       <c r="D8" t="n">
-        <v>0.962</v>
+        <v>0.957</v>
       </c>
       <c r="E8" t="n">
-        <v>35.3</v>
+        <v>38.1</v>
       </c>
       <c r="F8" t="n">
-        <v>27.3</v>
+        <v>28.8</v>
       </c>
       <c r="G8" t="n">
-        <v>19.2</v>
+        <v>19.5</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -866,10 +866,10 @@
         <v>29.63</v>
       </c>
       <c r="M8" t="n">
-        <v>26.11</v>
+        <v>25.65</v>
       </c>
       <c r="N8" t="n">
-        <v>-16.1</v>
+        <v>-18.5</v>
       </c>
     </row>
     <row r="9">
@@ -887,20 +887,20 @@
         <v>0.82</v>
       </c>
       <c r="D9" t="n">
-        <v>1.211</v>
+        <v>1.188</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.4</v>
+        <v>-3.2</v>
       </c>
       <c r="F9" t="n">
-        <v>5.7</v>
+        <v>6.9</v>
       </c>
       <c r="G9" t="n">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>28583</v>
+        <v>25856</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -918,10 +918,10 @@
         <v>25.72</v>
       </c>
       <c r="M9" t="n">
-        <v>31.77</v>
+        <v>31.1</v>
       </c>
       <c r="N9" t="n">
-        <v>22.3</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="10">
@@ -939,16 +939,16 @@
         <v>0.87</v>
       </c>
       <c r="D10" t="n">
-        <v>1.042</v>
+        <v>1.024</v>
       </c>
       <c r="E10" t="n">
-        <v>7.2</v>
+        <v>9.5</v>
       </c>
       <c r="F10" t="n">
-        <v>9.699999999999999</v>
+        <v>10.9</v>
       </c>
       <c r="G10" t="n">
-        <v>12.1</v>
+        <v>12.4</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>18314</v>
+        <v>15736</v>
       </c>
       <c r="K10" t="n">
-        <v>12474</v>
+        <v>12398</v>
       </c>
       <c r="L10" t="n">
         <v>25.73</v>
       </c>
       <c r="M10" t="n">
-        <v>26.91</v>
+        <v>26.41</v>
       </c>
       <c r="N10" t="n">
-        <v>4.9</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="11">
@@ -991,16 +991,16 @@
         <v>0.98</v>
       </c>
       <c r="D11" t="n">
-        <v>1.518</v>
+        <v>1.608</v>
       </c>
       <c r="E11" t="n">
-        <v>-23.8</v>
+        <v>-28</v>
       </c>
       <c r="F11" t="n">
-        <v>-7</v>
+        <v>-9.5</v>
       </c>
       <c r="G11" t="n">
-        <v>9.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>342121</v>
+        <v>393378</v>
       </c>
       <c r="K11" t="n">
-        <v>67887</v>
+        <v>71701</v>
       </c>
       <c r="L11" t="n">
         <v>59.47</v>
       </c>
       <c r="M11" t="n">
-        <v>85.54000000000001</v>
+        <v>90.05</v>
       </c>
       <c r="N11" t="n">
-        <v>33.4</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12">
@@ -1043,16 +1043,16 @@
         <v>0.95</v>
       </c>
       <c r="D12" t="n">
-        <v>1.433</v>
+        <v>1.38</v>
       </c>
       <c r="E12" t="n">
-        <v>-25.1</v>
+        <v>-21.7</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.4</v>
+        <v>-6.4</v>
       </c>
       <c r="G12" t="n">
-        <v>8.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1065,19 +1065,19 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>126273</v>
+        <v>113530</v>
       </c>
       <c r="K12" t="n">
-        <v>28673</v>
+        <v>28026</v>
       </c>
       <c r="L12" t="n">
         <v>5.77</v>
       </c>
       <c r="M12" t="n">
-        <v>8.34</v>
+        <v>8.02</v>
       </c>
       <c r="N12" t="n">
-        <v>33.4</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="13">
@@ -1095,16 +1095,16 @@
         <v>1.09</v>
       </c>
       <c r="D13" t="n">
-        <v>1.145</v>
+        <v>1.157</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.1</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-2</v>
+        <v>-2.7</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1117,19 +1117,19 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>315444</v>
+        <v>330771</v>
       </c>
       <c r="K13" t="n">
-        <v>168393</v>
+        <v>170951</v>
       </c>
       <c r="L13" t="n">
         <v>15.08</v>
       </c>
       <c r="M13" t="n">
-        <v>17.05</v>
+        <v>17.23</v>
       </c>
       <c r="N13" t="n">
-        <v>12</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="14">
@@ -1150,7 +1150,7 @@
         <v>0.843</v>
       </c>
       <c r="E14" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="F14" t="n">
         <v>7.1</v>
@@ -1178,10 +1178,10 @@
         <v>19.82</v>
       </c>
       <c r="M14" t="n">
-        <v>17.13</v>
+        <v>17.12</v>
       </c>
       <c r="N14" t="n">
-        <v>-15.6</v>
+        <v>-15.7</v>
       </c>
     </row>
     <row r="15">
@@ -1199,16 +1199,16 @@
         <v>1.2</v>
       </c>
       <c r="D15" t="n">
-        <v>1.118</v>
+        <v>1.158</v>
       </c>
       <c r="E15" t="n">
-        <v>-14.9</v>
+        <v>-19.1</v>
       </c>
       <c r="F15" t="n">
-        <v>-9</v>
+        <v>-11.5</v>
       </c>
       <c r="G15" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>311332</v>
+        <v>354881</v>
       </c>
       <c r="K15" t="n">
-        <v>214599</v>
+        <v>225188</v>
       </c>
       <c r="L15" t="n">
         <v>29.36</v>
       </c>
       <c r="M15" t="n">
-        <v>33.45</v>
+        <v>34.84</v>
       </c>
       <c r="N15" t="n">
-        <v>11.9</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="16">
@@ -1251,16 +1251,16 @@
         <v>1.21</v>
       </c>
       <c r="D16" t="n">
-        <v>1.118</v>
+        <v>1.143</v>
       </c>
       <c r="E16" t="n">
-        <v>-17.5</v>
+        <v>-20.1</v>
       </c>
       <c r="F16" t="n">
-        <v>-11.9</v>
+        <v>-13.4</v>
       </c>
       <c r="G16" t="n">
-        <v>-6.2</v>
+        <v>-6.7</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1273,19 +1273,19 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>299660</v>
+        <v>324117</v>
       </c>
       <c r="K16" t="n">
-        <v>214617</v>
+        <v>220611</v>
       </c>
       <c r="L16" t="n">
         <v>39.33</v>
       </c>
       <c r="M16" t="n">
-        <v>44.72</v>
+        <v>45.89</v>
       </c>
       <c r="N16" t="n">
-        <v>11.3</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="17">
@@ -1303,16 +1303,16 @@
         <v>1.37</v>
       </c>
       <c r="D17" t="n">
-        <v>0.874</v>
+        <v>0.883</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1</v>
+        <v>-2</v>
       </c>
       <c r="F17" t="n">
-        <v>-10.4</v>
+        <v>-11.6</v>
       </c>
       <c r="G17" t="n">
-        <v>-21</v>
+        <v>-21.2</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1334,10 +1334,10 @@
         <v>29.73</v>
       </c>
       <c r="M17" t="n">
-        <v>23.47</v>
+        <v>23.9</v>
       </c>
       <c r="N17" t="n">
-        <v>-21.1</v>
+        <v>-19.2</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -523,16 +523,16 @@
         <v>0.34</v>
       </c>
       <c r="D2" t="n">
-        <v>1.234</v>
+        <v>1.254</v>
       </c>
       <c r="E2" t="n">
-        <v>55.1</v>
+        <v>51.7</v>
       </c>
       <c r="F2" t="n">
-        <v>79.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="G2" t="n">
-        <v>104.7</v>
+        <v>104.3</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -554,16 +554,16 @@
         <v>57.61</v>
       </c>
       <c r="M2" t="n">
-        <v>76.01000000000001</v>
+        <v>77.63</v>
       </c>
       <c r="N2" t="n">
-        <v>49.5</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -572,23 +572,23 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="D3" t="n">
-        <v>1.39</v>
+        <v>1.042</v>
       </c>
       <c r="E3" t="n">
-        <v>-4.4</v>
+        <v>38.8</v>
       </c>
       <c r="F3" t="n">
-        <v>12.5</v>
+        <v>43.4</v>
       </c>
       <c r="G3" t="n">
-        <v>29.4</v>
+        <v>48.1</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -597,25 +597,25 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2725019</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>73.13</v>
+        <v>17.68</v>
       </c>
       <c r="M3" t="n">
-        <v>98.92</v>
+        <v>18.86</v>
       </c>
       <c r="N3" t="n">
-        <v>33.7</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -624,19 +624,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="D4" t="n">
-        <v>1.973</v>
+        <v>1.418</v>
       </c>
       <c r="E4" t="n">
-        <v>-44.7</v>
+        <v>-6.2</v>
       </c>
       <c r="F4" t="n">
-        <v>-8.699999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="G4" t="n">
-        <v>27.2</v>
+        <v>29.3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -649,25 +649,25 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>332327</v>
+        <v>2725019</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2.86</v>
+        <v>73.13</v>
       </c>
       <c r="M4" t="n">
-        <v>6.59</v>
+        <v>100.81</v>
       </c>
       <c r="N4" t="n">
-        <v>72</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -676,19 +676,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="D5" t="n">
-        <v>1.366</v>
+        <v>1.996</v>
       </c>
       <c r="E5" t="n">
-        <v>-8.4</v>
+        <v>-45.6</v>
       </c>
       <c r="F5" t="n">
-        <v>7.8</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>24.1</v>
+        <v>27</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -701,25 +701,25 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>43825</v>
+        <v>339977</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>15.05</v>
+        <v>2.86</v>
       </c>
       <c r="M5" t="n">
-        <v>20.38</v>
+        <v>6.68</v>
       </c>
       <c r="N5" t="n">
-        <v>32.5</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -728,23 +728,23 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="D6" t="n">
-        <v>1.398</v>
+        <v>1.404</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3</v>
+        <v>-10.9</v>
       </c>
       <c r="F6" t="n">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
       <c r="G6" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -753,25 +753,25 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>47855</v>
+        <v>49486</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>73.7</v>
+        <v>15.05</v>
       </c>
       <c r="M6" t="n">
-        <v>90.04000000000001</v>
+        <v>20.93</v>
       </c>
       <c r="N6" t="n">
-        <v>22.5</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -780,23 +780,23 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.83</v>
+        <v>0.76</v>
       </c>
       <c r="D7" t="n">
-        <v>1.27</v>
+        <v>1.436</v>
       </c>
       <c r="E7" t="n">
-        <v>-8.6</v>
+        <v>-0.5</v>
       </c>
       <c r="F7" t="n">
-        <v>6.3</v>
+        <v>11.6</v>
       </c>
       <c r="G7" t="n">
-        <v>21.2</v>
+        <v>23.6</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -805,25 +805,25 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>78345</v>
+        <v>88915</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>26.68</v>
+        <v>73.7</v>
       </c>
       <c r="M7" t="n">
-        <v>35.36</v>
+        <v>91.58</v>
       </c>
       <c r="N7" t="n">
-        <v>29.8</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -832,23 +832,23 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="D8" t="n">
-        <v>0.957</v>
+        <v>1.296</v>
       </c>
       <c r="E8" t="n">
-        <v>38.1</v>
+        <v>-11</v>
       </c>
       <c r="F8" t="n">
-        <v>28.8</v>
+        <v>4.9</v>
       </c>
       <c r="G8" t="n">
-        <v>19.5</v>
+        <v>20.8</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -857,25 +857,25 @@
         </is>
       </c>
       <c r="J8" t="n">
+        <v>85983</v>
+      </c>
+      <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="K8" t="n">
-        <v>2977992</v>
-      </c>
       <c r="L8" t="n">
-        <v>29.63</v>
+        <v>26.68</v>
       </c>
       <c r="M8" t="n">
-        <v>25.65</v>
+        <v>36.23</v>
       </c>
       <c r="N8" t="n">
-        <v>-18.5</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -884,23 +884,23 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.82</v>
+        <v>0.9</v>
       </c>
       <c r="D9" t="n">
-        <v>1.188</v>
+        <v>0.966</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.2</v>
+        <v>33.5</v>
       </c>
       <c r="F9" t="n">
-        <v>6.9</v>
+        <v>26.2</v>
       </c>
       <c r="G9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -909,25 +909,25 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>25856</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2977992</v>
       </c>
       <c r="L9" t="n">
-        <v>25.72</v>
+        <v>29.63</v>
       </c>
       <c r="M9" t="n">
-        <v>31.1</v>
+        <v>26.42</v>
       </c>
       <c r="N9" t="n">
-        <v>20.2</v>
+        <v>-14.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -936,23 +936,23 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="D10" t="n">
-        <v>1.024</v>
+        <v>1.206</v>
       </c>
       <c r="E10" t="n">
-        <v>9.5</v>
+        <v>-5</v>
       </c>
       <c r="F10" t="n">
-        <v>10.9</v>
+        <v>6</v>
       </c>
       <c r="G10" t="n">
-        <v>12.4</v>
+        <v>16.9</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -961,50 +961,50 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>15736</v>
+        <v>27977</v>
       </c>
       <c r="K10" t="n">
-        <v>12398</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>25.73</v>
+        <v>25.72</v>
       </c>
       <c r="M10" t="n">
-        <v>26.41</v>
+        <v>31.62</v>
       </c>
       <c r="N10" t="n">
-        <v>2.9</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.98</v>
+        <v>0.87</v>
       </c>
       <c r="D11" t="n">
-        <v>1.608</v>
+        <v>1.035</v>
       </c>
       <c r="E11" t="n">
-        <v>-28</v>
+        <v>8.1</v>
       </c>
       <c r="F11" t="n">
-        <v>-9.5</v>
+        <v>10.2</v>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>12.2</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>393378</v>
+        <v>17309</v>
       </c>
       <c r="K11" t="n">
-        <v>71701</v>
+        <v>12444</v>
       </c>
       <c r="L11" t="n">
-        <v>59.47</v>
+        <v>25.73</v>
       </c>
       <c r="M11" t="n">
-        <v>90.05</v>
+        <v>26.72</v>
       </c>
       <c r="N11" t="n">
-        <v>37</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="12">
@@ -1043,16 +1043,16 @@
         <v>0.95</v>
       </c>
       <c r="D12" t="n">
-        <v>1.38</v>
+        <v>1.392</v>
       </c>
       <c r="E12" t="n">
-        <v>-21.7</v>
+        <v>-22.5</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.4</v>
+        <v>-6.9</v>
       </c>
       <c r="G12" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1065,46 +1065,46 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>113530</v>
+        <v>116528</v>
       </c>
       <c r="K12" t="n">
-        <v>28026</v>
+        <v>28178</v>
       </c>
       <c r="L12" t="n">
         <v>5.77</v>
       </c>
       <c r="M12" t="n">
-        <v>8.02</v>
+        <v>8.09</v>
       </c>
       <c r="N12" t="n">
-        <v>30.6</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.09</v>
+        <v>0.98</v>
       </c>
       <c r="D13" t="n">
-        <v>1.157</v>
+        <v>1.641</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.199999999999999</v>
+        <v>-29.4</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.7</v>
+        <v>-10.3</v>
       </c>
       <c r="G13" t="n">
-        <v>3.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1113,29 +1113,29 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>330771</v>
+        <v>412112</v>
       </c>
       <c r="K13" t="n">
-        <v>170951</v>
+        <v>73095</v>
       </c>
       <c r="L13" t="n">
-        <v>15.08</v>
+        <v>59.47</v>
       </c>
       <c r="M13" t="n">
-        <v>17.23</v>
+        <v>91.7</v>
       </c>
       <c r="N13" t="n">
-        <v>12.9</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1144,23 +1144,23 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.62</v>
+        <v>1.09</v>
       </c>
       <c r="D14" t="n">
-        <v>0.843</v>
+        <v>1.178</v>
       </c>
       <c r="E14" t="n">
-        <v>15</v>
+        <v>-10.9</v>
       </c>
       <c r="F14" t="n">
-        <v>7.1</v>
+        <v>-3.7</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.7</v>
+        <v>3.4</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1169,25 +1169,25 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>355677</v>
       </c>
       <c r="K14" t="n">
-        <v>1070509</v>
+        <v>175108</v>
       </c>
       <c r="L14" t="n">
-        <v>19.82</v>
+        <v>15.08</v>
       </c>
       <c r="M14" t="n">
-        <v>17.12</v>
+        <v>17.5</v>
       </c>
       <c r="N14" t="n">
-        <v>-15.7</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1196,23 +1196,23 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.2</v>
+        <v>0.62</v>
       </c>
       <c r="D15" t="n">
-        <v>1.158</v>
+        <v>0.851</v>
       </c>
       <c r="E15" t="n">
-        <v>-19.1</v>
+        <v>14</v>
       </c>
       <c r="F15" t="n">
-        <v>-11.5</v>
+        <v>6.6</v>
       </c>
       <c r="G15" t="n">
-        <v>-4</v>
+        <v>-0.7</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1221,25 +1221,25 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>354881</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>225188</v>
+        <v>1070509</v>
       </c>
       <c r="L15" t="n">
-        <v>29.36</v>
+        <v>19.82</v>
       </c>
       <c r="M15" t="n">
-        <v>34.84</v>
+        <v>17.27</v>
       </c>
       <c r="N15" t="n">
-        <v>15.1</v>
+        <v>-14.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1248,19 +1248,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="D16" t="n">
-        <v>1.143</v>
+        <v>1.199</v>
       </c>
       <c r="E16" t="n">
-        <v>-20.1</v>
+        <v>-22.9</v>
       </c>
       <c r="F16" t="n">
-        <v>-13.4</v>
+        <v>-13.9</v>
       </c>
       <c r="G16" t="n">
-        <v>-6.7</v>
+        <v>-4.8</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1269,75 +1269,127 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>324117</v>
+        <v>398919</v>
       </c>
       <c r="K16" t="n">
-        <v>220611</v>
+        <v>235896</v>
       </c>
       <c r="L16" t="n">
-        <v>39.33</v>
+        <v>29.36</v>
       </c>
       <c r="M16" t="n">
-        <v>45.89</v>
+        <v>36.25</v>
       </c>
       <c r="N16" t="n">
-        <v>13.3</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>ECO</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-22.2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-14.7</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>346455</v>
+      </c>
+      <c r="K17" t="n">
+        <v>226085</v>
+      </c>
+      <c r="L17" t="n">
+        <v>39.33</v>
+      </c>
+      <c r="M17" t="n">
+        <v>46.96</v>
+      </c>
+      <c r="N17" t="n">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>FLNG</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>whole-company</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
         <v>1.37</v>
       </c>
-      <c r="D17" t="n">
-        <v>0.883</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-2</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-11.6</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-21.2</v>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="D18" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-12.9</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-21.5</v>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="J18" t="n">
         <v>3162500</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K18" t="n">
         <v>3162500</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L18" t="n">
         <v>29.73</v>
       </c>
-      <c r="M17" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-19.2</v>
+      <c r="M18" t="n">
+        <v>24.41</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-17.1</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -523,16 +523,16 @@
         <v>0.34</v>
       </c>
       <c r="D2" t="n">
-        <v>1.254</v>
+        <v>1.183</v>
       </c>
       <c r="E2" t="n">
-        <v>51.7</v>
+        <v>64.7</v>
       </c>
       <c r="F2" t="n">
-        <v>78</v>
+        <v>84.8</v>
       </c>
       <c r="G2" t="n">
-        <v>104.3</v>
+        <v>105</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -551,13 +551,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>57.61</v>
+        <v>62.56</v>
       </c>
       <c r="M2" t="n">
-        <v>77.63</v>
+        <v>77.87</v>
       </c>
       <c r="N2" t="n">
-        <v>52.7</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="3">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -523,16 +523,16 @@
         <v>0.34</v>
       </c>
       <c r="D2" t="n">
-        <v>1.183</v>
+        <v>1.163</v>
       </c>
       <c r="E2" t="n">
-        <v>64.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>84.8</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>105</v>
+        <v>105.3</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -554,10 +554,10 @@
         <v>62.56</v>
       </c>
       <c r="M2" t="n">
-        <v>77.87</v>
+        <v>76.19</v>
       </c>
       <c r="N2" t="n">
-        <v>40.3</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="3">
@@ -575,16 +575,16 @@
         <v>0.67</v>
       </c>
       <c r="D3" t="n">
-        <v>1.042</v>
+        <v>1.044</v>
       </c>
       <c r="E3" t="n">
-        <v>38.8</v>
+        <v>38.2</v>
       </c>
       <c r="F3" t="n">
-        <v>43.4</v>
+        <v>43.1</v>
       </c>
       <c r="G3" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -606,10 +606,10 @@
         <v>17.68</v>
       </c>
       <c r="M3" t="n">
-        <v>18.86</v>
+        <v>18.93</v>
       </c>
       <c r="N3" t="n">
-        <v>9.300000000000001</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -627,20 +627,20 @@
         <v>0.7</v>
       </c>
       <c r="D4" t="n">
-        <v>1.418</v>
+        <v>1.384</v>
       </c>
       <c r="E4" t="n">
-        <v>-6.2</v>
+        <v>-4</v>
       </c>
       <c r="F4" t="n">
-        <v>11.6</v>
+        <v>12.7</v>
       </c>
       <c r="G4" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -658,10 +658,10 @@
         <v>73.13</v>
       </c>
       <c r="M4" t="n">
-        <v>100.81</v>
+        <v>98.55</v>
       </c>
       <c r="N4" t="n">
-        <v>35.5</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="5">
@@ -679,16 +679,16 @@
         <v>0.85</v>
       </c>
       <c r="D5" t="n">
-        <v>1.996</v>
+        <v>1.965</v>
       </c>
       <c r="E5" t="n">
-        <v>-45.6</v>
+        <v>-44.4</v>
       </c>
       <c r="F5" t="n">
-        <v>-9.300000000000001</v>
+        <v>-8.5</v>
       </c>
       <c r="G5" t="n">
-        <v>27</v>
+        <v>27.3</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>339977</v>
+        <v>329458</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -710,10 +710,10 @@
         <v>2.86</v>
       </c>
       <c r="M5" t="n">
-        <v>6.68</v>
+        <v>6.56</v>
       </c>
       <c r="N5" t="n">
-        <v>72.5</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="6">
@@ -731,16 +731,16 @@
         <v>0.75</v>
       </c>
       <c r="D6" t="n">
-        <v>1.404</v>
+        <v>1.362</v>
       </c>
       <c r="E6" t="n">
-        <v>-10.9</v>
+        <v>-8.1</v>
       </c>
       <c r="F6" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>49486</v>
+        <v>43209</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -762,10 +762,10 @@
         <v>15.05</v>
       </c>
       <c r="M6" t="n">
-        <v>20.93</v>
+        <v>20.32</v>
       </c>
       <c r="N6" t="n">
-        <v>34.8</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="7">
@@ -783,16 +783,16 @@
         <v>0.76</v>
       </c>
       <c r="D7" t="n">
-        <v>1.436</v>
+        <v>1.391</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5</v>
+        <v>1.7</v>
       </c>
       <c r="F7" t="n">
-        <v>11.6</v>
+        <v>12.7</v>
       </c>
       <c r="G7" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>88915</v>
+        <v>39706</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -814,10 +814,10 @@
         <v>73.7</v>
       </c>
       <c r="M7" t="n">
-        <v>91.58</v>
+        <v>89.73</v>
       </c>
       <c r="N7" t="n">
-        <v>24.1</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="8">
@@ -835,16 +835,16 @@
         <v>0.83</v>
       </c>
       <c r="D8" t="n">
-        <v>1.296</v>
+        <v>1.262</v>
       </c>
       <c r="E8" t="n">
-        <v>-11</v>
+        <v>-7.9</v>
       </c>
       <c r="F8" t="n">
-        <v>4.9</v>
+        <v>6.7</v>
       </c>
       <c r="G8" t="n">
-        <v>20.8</v>
+        <v>21.3</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>85983</v>
+        <v>76149</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -866,10 +866,10 @@
         <v>26.68</v>
       </c>
       <c r="M8" t="n">
-        <v>36.23</v>
+        <v>35.12</v>
       </c>
       <c r="N8" t="n">
-        <v>31.9</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="9">
@@ -887,16 +887,16 @@
         <v>0.9</v>
       </c>
       <c r="D9" t="n">
-        <v>0.966</v>
+        <v>0.958</v>
       </c>
       <c r="E9" t="n">
-        <v>33.5</v>
+        <v>37.7</v>
       </c>
       <c r="F9" t="n">
-        <v>26.2</v>
+        <v>28.6</v>
       </c>
       <c r="G9" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -918,10 +918,10 @@
         <v>29.63</v>
       </c>
       <c r="M9" t="n">
-        <v>26.42</v>
+        <v>25.71</v>
       </c>
       <c r="N9" t="n">
-        <v>-14.4</v>
+        <v>-18.2</v>
       </c>
     </row>
     <row r="10">
@@ -939,20 +939,20 @@
         <v>0.82</v>
       </c>
       <c r="D10" t="n">
-        <v>1.206</v>
+        <v>1.21</v>
       </c>
       <c r="E10" t="n">
-        <v>-5</v>
+        <v>-5.3</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="G10" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>27977</v>
+        <v>28367</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -970,10 +970,10 @@
         <v>25.72</v>
       </c>
       <c r="M10" t="n">
-        <v>31.62</v>
+        <v>31.72</v>
       </c>
       <c r="N10" t="n">
-        <v>21.8</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="11">
@@ -991,16 +991,16 @@
         <v>0.87</v>
       </c>
       <c r="D11" t="n">
-        <v>1.035</v>
+        <v>1.031</v>
       </c>
       <c r="E11" t="n">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="F11" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="G11" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>17309</v>
+        <v>16716</v>
       </c>
       <c r="K11" t="n">
-        <v>12444</v>
+        <v>12427</v>
       </c>
       <c r="L11" t="n">
         <v>25.73</v>
       </c>
       <c r="M11" t="n">
-        <v>26.72</v>
+        <v>26.6</v>
       </c>
       <c r="N11" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="12">
@@ -1043,16 +1043,16 @@
         <v>0.95</v>
       </c>
       <c r="D12" t="n">
-        <v>1.392</v>
+        <v>1.367</v>
       </c>
       <c r="E12" t="n">
-        <v>-22.5</v>
+        <v>-20.8</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.9</v>
+        <v>-5.8</v>
       </c>
       <c r="G12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1065,19 +1065,19 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>116528</v>
+        <v>110531</v>
       </c>
       <c r="K12" t="n">
-        <v>28178</v>
+        <v>27874</v>
       </c>
       <c r="L12" t="n">
         <v>5.77</v>
       </c>
       <c r="M12" t="n">
-        <v>8.09</v>
+        <v>7.94</v>
       </c>
       <c r="N12" t="n">
-        <v>31.3</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="13">
@@ -1095,16 +1095,16 @@
         <v>0.98</v>
       </c>
       <c r="D13" t="n">
-        <v>1.641</v>
+        <v>1.607</v>
       </c>
       <c r="E13" t="n">
-        <v>-29.4</v>
+        <v>-28</v>
       </c>
       <c r="F13" t="n">
-        <v>-10.3</v>
+        <v>-9.5</v>
       </c>
       <c r="G13" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1117,19 +1117,19 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>412112</v>
+        <v>392822</v>
       </c>
       <c r="K13" t="n">
-        <v>73095</v>
+        <v>71660</v>
       </c>
       <c r="L13" t="n">
         <v>59.47</v>
       </c>
       <c r="M13" t="n">
-        <v>91.7</v>
+        <v>90</v>
       </c>
       <c r="N13" t="n">
-        <v>38.2</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -1147,16 +1147,16 @@
         <v>1.09</v>
       </c>
       <c r="D14" t="n">
-        <v>1.178</v>
+        <v>1.16</v>
       </c>
       <c r="E14" t="n">
-        <v>-10.9</v>
+        <v>-9.4</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.7</v>
+        <v>-2.9</v>
       </c>
       <c r="G14" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1169,19 +1169,19 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>355677</v>
+        <v>334603</v>
       </c>
       <c r="K14" t="n">
-        <v>175108</v>
+        <v>171590</v>
       </c>
       <c r="L14" t="n">
         <v>15.08</v>
       </c>
       <c r="M14" t="n">
-        <v>17.5</v>
+        <v>17.27</v>
       </c>
       <c r="N14" t="n">
-        <v>14.3</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="15">
@@ -1199,13 +1199,13 @@
         <v>0.62</v>
       </c>
       <c r="D15" t="n">
-        <v>0.851</v>
+        <v>0.863</v>
       </c>
       <c r="E15" t="n">
-        <v>14</v>
+        <v>12.6</v>
       </c>
       <c r="F15" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="G15" t="n">
         <v>-0.7</v>
@@ -1230,10 +1230,10 @@
         <v>19.82</v>
       </c>
       <c r="M15" t="n">
-        <v>17.27</v>
+        <v>17.47</v>
       </c>
       <c r="N15" t="n">
-        <v>-14.7</v>
+        <v>-13.3</v>
       </c>
     </row>
     <row r="16">
@@ -1251,16 +1251,16 @@
         <v>1.2</v>
       </c>
       <c r="D16" t="n">
-        <v>1.199</v>
+        <v>1.177</v>
       </c>
       <c r="E16" t="n">
-        <v>-22.9</v>
+        <v>-20.9</v>
       </c>
       <c r="F16" t="n">
-        <v>-13.9</v>
+        <v>-12.6</v>
       </c>
       <c r="G16" t="n">
-        <v>-4.8</v>
+        <v>-4.4</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1273,19 +1273,19 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>398919</v>
+        <v>375677</v>
       </c>
       <c r="K16" t="n">
-        <v>235896</v>
+        <v>230245</v>
       </c>
       <c r="L16" t="n">
         <v>29.36</v>
       </c>
       <c r="M16" t="n">
-        <v>36.25</v>
+        <v>35.51</v>
       </c>
       <c r="N16" t="n">
-        <v>18.1</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="17">
@@ -1303,16 +1303,16 @@
         <v>1.21</v>
       </c>
       <c r="D17" t="n">
-        <v>1.167</v>
+        <v>1.153</v>
       </c>
       <c r="E17" t="n">
-        <v>-22.2</v>
+        <v>-21</v>
       </c>
       <c r="F17" t="n">
-        <v>-14.7</v>
+        <v>-13.9</v>
       </c>
       <c r="G17" t="n">
-        <v>-7.1</v>
+        <v>-6.9</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1325,19 +1325,19 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>346455</v>
+        <v>333248</v>
       </c>
       <c r="K17" t="n">
-        <v>226085</v>
+        <v>222848</v>
       </c>
       <c r="L17" t="n">
         <v>39.33</v>
       </c>
       <c r="M17" t="n">
-        <v>46.96</v>
+        <v>46.33</v>
       </c>
       <c r="N17" t="n">
-        <v>15.1</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="18">
@@ -1355,16 +1355,16 @@
         <v>1.37</v>
       </c>
       <c r="D18" t="n">
-        <v>0.893</v>
+        <v>0.885</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.4</v>
+        <v>-2.5</v>
       </c>
       <c r="F18" t="n">
-        <v>-12.9</v>
+        <v>-11.9</v>
       </c>
       <c r="G18" t="n">
-        <v>-21.5</v>
+        <v>-21.3</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1386,10 +1386,10 @@
         <v>29.73</v>
       </c>
       <c r="M18" t="n">
-        <v>24.41</v>
+        <v>24.01</v>
       </c>
       <c r="N18" t="n">
-        <v>-17.1</v>
+        <v>-18.8</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1135,7 +1135,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.09</v>
+        <v>0.75</v>
       </c>
       <c r="D14" t="n">
-        <v>1.16</v>
+        <v>1.276</v>
       </c>
       <c r="E14" t="n">
-        <v>-9.4</v>
+        <v>-18.5</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.9</v>
+        <v>-4.9</v>
       </c>
       <c r="G14" t="n">
-        <v>3.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1165,29 +1165,29 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>334603</v>
+        <v>2757173</v>
       </c>
       <c r="K14" t="n">
-        <v>171590</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>15.08</v>
+        <v>31.76</v>
       </c>
       <c r="M14" t="n">
-        <v>17.27</v>
+        <v>42.4</v>
       </c>
       <c r="N14" t="n">
-        <v>13.2</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1196,23 +1196,23 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.62</v>
+        <v>1.09</v>
       </c>
       <c r="D15" t="n">
-        <v>0.863</v>
+        <v>1.16</v>
       </c>
       <c r="E15" t="n">
-        <v>12.6</v>
+        <v>-9.4</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>-2.9</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7</v>
+        <v>3.7</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1221,25 +1221,25 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>334603</v>
       </c>
       <c r="K15" t="n">
-        <v>1070509</v>
+        <v>171590</v>
       </c>
       <c r="L15" t="n">
-        <v>19.82</v>
+        <v>15.08</v>
       </c>
       <c r="M15" t="n">
-        <v>17.47</v>
+        <v>17.27</v>
       </c>
       <c r="N15" t="n">
-        <v>-13.3</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1248,23 +1248,23 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.2</v>
+        <v>0.62</v>
       </c>
       <c r="D16" t="n">
-        <v>1.177</v>
+        <v>0.863</v>
       </c>
       <c r="E16" t="n">
-        <v>-20.9</v>
+        <v>12.6</v>
       </c>
       <c r="F16" t="n">
-        <v>-12.6</v>
+        <v>6</v>
       </c>
       <c r="G16" t="n">
-        <v>-4.4</v>
+        <v>-0.7</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1273,25 +1273,25 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>375677</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>230245</v>
+        <v>1070509</v>
       </c>
       <c r="L16" t="n">
-        <v>29.36</v>
+        <v>19.82</v>
       </c>
       <c r="M16" t="n">
-        <v>35.51</v>
+        <v>17.47</v>
       </c>
       <c r="N16" t="n">
-        <v>16.6</v>
+        <v>-13.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1300,19 +1300,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="D17" t="n">
-        <v>1.153</v>
+        <v>1.177</v>
       </c>
       <c r="E17" t="n">
-        <v>-21</v>
+        <v>-20.9</v>
       </c>
       <c r="F17" t="n">
-        <v>-13.9</v>
+        <v>-12.6</v>
       </c>
       <c r="G17" t="n">
-        <v>-6.9</v>
+        <v>-4.4</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1321,74 +1321,178 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>333248</v>
+        <v>375677</v>
       </c>
       <c r="K17" t="n">
-        <v>222848</v>
+        <v>230245</v>
       </c>
       <c r="L17" t="n">
-        <v>39.33</v>
+        <v>29.36</v>
       </c>
       <c r="M17" t="n">
-        <v>46.33</v>
+        <v>35.51</v>
       </c>
       <c r="N17" t="n">
-        <v>14.1</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>ECO</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.153</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-21</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-13.9</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-6.9</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>333248</v>
+      </c>
+      <c r="K18" t="n">
+        <v>222848</v>
+      </c>
+      <c r="L18" t="n">
+        <v>39.33</v>
+      </c>
+      <c r="M18" t="n">
+        <v>46.33</v>
+      </c>
+      <c r="N18" t="n">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MPCC</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.109</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-29.6</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-23.9</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-18.2</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>350590</v>
+      </c>
+      <c r="K19" t="n">
+        <v>180943</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="N19" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>FLNG</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>whole-company</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
         <v>1.37</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D20" t="n">
         <v>0.885</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E20" t="n">
         <v>-2.5</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F20" t="n">
         <v>-11.9</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G20" t="n">
         <v>-21.3</v>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="J20" t="n">
         <v>3162500</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K20" t="n">
         <v>3162500</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L20" t="n">
         <v>29.73</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M20" t="n">
         <v>24.01</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N20" t="n">
         <v>-18.8</v>
       </c>
     </row>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -523,16 +523,16 @@
         <v>0.34</v>
       </c>
       <c r="D2" t="n">
-        <v>1.163</v>
+        <v>1.168</v>
       </c>
       <c r="E2" t="n">
-        <v>68.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="F2" t="n">
-        <v>86.90000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>105.3</v>
+        <v>105.4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -551,13 +551,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>62.56</v>
+        <v>62.23</v>
       </c>
       <c r="M2" t="n">
-        <v>76.19</v>
+        <v>76.23</v>
       </c>
       <c r="N2" t="n">
-        <v>36.7</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="3">
@@ -783,7 +783,7 @@
         <v>0.76</v>
       </c>
       <c r="D7" t="n">
-        <v>1.391</v>
+        <v>1.39</v>
       </c>
       <c r="E7" t="n">
         <v>1.7</v>
@@ -805,13 +805,13 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>39706</v>
+        <v>39131</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>73.7</v>
+        <v>73.72</v>
       </c>
       <c r="M7" t="n">
         <v>89.73</v>
@@ -939,20 +939,20 @@
         <v>0.82</v>
       </c>
       <c r="D10" t="n">
-        <v>1.21</v>
+        <v>1.198</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.3</v>
+        <v>-4.3</v>
       </c>
       <c r="F10" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="G10" t="n">
         <v>16.8</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>28367</v>
+        <v>27187</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>25.72</v>
+        <v>25.98</v>
       </c>
       <c r="M10" t="n">
-        <v>31.72</v>
+        <v>31.7</v>
       </c>
       <c r="N10" t="n">
-        <v>22.1</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="11">
@@ -991,13 +991,13 @@
         <v>0.87</v>
       </c>
       <c r="D11" t="n">
-        <v>1.031</v>
+        <v>1.03</v>
       </c>
       <c r="E11" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="G11" t="n">
         <v>12.3</v>
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>16716</v>
+        <v>16592</v>
       </c>
       <c r="K11" t="n">
-        <v>12427</v>
+        <v>12421</v>
       </c>
       <c r="L11" t="n">
-        <v>25.73</v>
+        <v>25.76</v>
       </c>
       <c r="M11" t="n">
         <v>26.6</v>
       </c>
       <c r="N11" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="12">
@@ -1117,16 +1117,16 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>392822</v>
+        <v>392865</v>
       </c>
       <c r="K13" t="n">
-        <v>71660</v>
+        <v>71592</v>
       </c>
       <c r="L13" t="n">
         <v>59.47</v>
       </c>
       <c r="M13" t="n">
-        <v>90</v>
+        <v>90.01000000000001</v>
       </c>
       <c r="N13" t="n">
         <v>37</v>
@@ -1251,13 +1251,13 @@
         <v>0.62</v>
       </c>
       <c r="D16" t="n">
-        <v>0.863</v>
+        <v>0.855</v>
       </c>
       <c r="E16" t="n">
-        <v>12.6</v>
+        <v>13.5</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="G16" t="n">
         <v>-0.7</v>
@@ -1276,16 +1276,16 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1070509</v>
+        <v>1068984</v>
       </c>
       <c r="L16" t="n">
-        <v>19.82</v>
+        <v>19.98</v>
       </c>
       <c r="M16" t="n">
         <v>17.47</v>
       </c>
       <c r="N16" t="n">
-        <v>-13.3</v>
+        <v>-14.2</v>
       </c>
     </row>
     <row r="17">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -523,16 +523,16 @@
         <v>0.34</v>
       </c>
       <c r="D2" t="n">
-        <v>1.168</v>
+        <v>1.195</v>
       </c>
       <c r="E2" t="n">
-        <v>67.7</v>
+        <v>62.5</v>
       </c>
       <c r="F2" t="n">
-        <v>86.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="G2" t="n">
-        <v>105.4</v>
+        <v>105</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -554,10 +554,10 @@
         <v>62.23</v>
       </c>
       <c r="M2" t="n">
-        <v>76.23</v>
+        <v>78.48999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>37.7</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="3">
@@ -575,16 +575,16 @@
         <v>0.67</v>
       </c>
       <c r="D3" t="n">
-        <v>1.044</v>
+        <v>1.171</v>
       </c>
       <c r="E3" t="n">
-        <v>38.2</v>
+        <v>22.4</v>
       </c>
       <c r="F3" t="n">
-        <v>43.1</v>
+        <v>39.6</v>
       </c>
       <c r="G3" t="n">
-        <v>48</v>
+        <v>56.9</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -603,19 +603,19 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>17.68</v>
+        <v>16.2</v>
       </c>
       <c r="M3" t="n">
-        <v>18.93</v>
+        <v>20.78</v>
       </c>
       <c r="N3" t="n">
-        <v>9.800000000000001</v>
+        <v>34.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -624,23 +624,23 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="D4" t="n">
-        <v>1.384</v>
+        <v>0.926</v>
       </c>
       <c r="E4" t="n">
-        <v>-4</v>
+        <v>97.3</v>
       </c>
       <c r="F4" t="n">
-        <v>12.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>29.4</v>
+        <v>56.6</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -649,25 +649,25 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2725019</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>73.13</v>
+        <v>10.65</v>
       </c>
       <c r="M4" t="n">
-        <v>98.55</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>33.4</v>
+        <v>-40.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -676,19 +676,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="D5" t="n">
-        <v>1.965</v>
+        <v>1.469</v>
       </c>
       <c r="E5" t="n">
-        <v>-44.4</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>-8.5</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>27.3</v>
+        <v>29.3</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -701,25 +701,25 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>329458</v>
+        <v>2725019</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>2.86</v>
+        <v>73.13</v>
       </c>
       <c r="M5" t="n">
-        <v>6.56</v>
+        <v>104.18</v>
       </c>
       <c r="N5" t="n">
-        <v>71.8</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -728,19 +728,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="D6" t="n">
-        <v>1.362</v>
+        <v>2.164</v>
       </c>
       <c r="E6" t="n">
-        <v>-8.1</v>
+        <v>-51.1</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>-12.9</v>
       </c>
       <c r="G6" t="n">
-        <v>24.1</v>
+        <v>25.2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -753,25 +753,25 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>43209</v>
+        <v>396401</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>15.05</v>
+        <v>2.86</v>
       </c>
       <c r="M6" t="n">
-        <v>20.32</v>
+        <v>7.32</v>
       </c>
       <c r="N6" t="n">
-        <v>32.2</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -780,23 +780,23 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="D7" t="n">
-        <v>1.39</v>
+        <v>1.419</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7</v>
+        <v>-11.8</v>
       </c>
       <c r="F7" t="n">
-        <v>12.7</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -805,25 +805,25 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>39131</v>
+        <v>51701</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>73.72</v>
+        <v>15.05</v>
       </c>
       <c r="M7" t="n">
-        <v>89.73</v>
+        <v>21.14</v>
       </c>
       <c r="N7" t="n">
-        <v>22.1</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -832,23 +832,23 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.83</v>
+        <v>0.76</v>
       </c>
       <c r="D8" t="n">
-        <v>1.262</v>
+        <v>1.446</v>
       </c>
       <c r="E8" t="n">
-        <v>-7.9</v>
+        <v>-1</v>
       </c>
       <c r="F8" t="n">
-        <v>6.7</v>
+        <v>11.3</v>
       </c>
       <c r="G8" t="n">
-        <v>21.3</v>
+        <v>23.6</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -857,25 +857,25 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>76149</v>
+        <v>100249</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>26.68</v>
+        <v>73.72</v>
       </c>
       <c r="M8" t="n">
-        <v>35.12</v>
+        <v>92.02</v>
       </c>
       <c r="N8" t="n">
-        <v>29.2</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -884,23 +884,23 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="D9" t="n">
-        <v>0.958</v>
+        <v>1.277</v>
       </c>
       <c r="E9" t="n">
-        <v>37.7</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>28.6</v>
+        <v>5.9</v>
       </c>
       <c r="G9" t="n">
-        <v>19.5</v>
+        <v>21.1</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -909,25 +909,25 @@
         </is>
       </c>
       <c r="J9" t="n">
+        <v>80541</v>
+      </c>
+      <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="K9" t="n">
-        <v>2977992</v>
-      </c>
       <c r="L9" t="n">
-        <v>29.63</v>
+        <v>26.68</v>
       </c>
       <c r="M9" t="n">
-        <v>25.71</v>
+        <v>35.61</v>
       </c>
       <c r="N9" t="n">
-        <v>-18.2</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -936,23 +936,23 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.82</v>
+        <v>0.9</v>
       </c>
       <c r="D10" t="n">
-        <v>1.198</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.3</v>
+        <v>47.9</v>
       </c>
       <c r="F10" t="n">
-        <v>6.2</v>
+        <v>34.3</v>
       </c>
       <c r="G10" t="n">
-        <v>16.8</v>
+        <v>20.7</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>27187</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2977992</v>
       </c>
       <c r="L10" t="n">
-        <v>25.98</v>
+        <v>29.63</v>
       </c>
       <c r="M10" t="n">
-        <v>31.7</v>
+        <v>24.17</v>
       </c>
       <c r="N10" t="n">
-        <v>21.1</v>
+        <v>-27.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -988,23 +988,23 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="D11" t="n">
-        <v>1.03</v>
+        <v>1.149</v>
       </c>
       <c r="E11" t="n">
-        <v>8.699999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="F11" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>12.3</v>
+        <v>17.3</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1013,25 +1013,25 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>16592</v>
+        <v>21396</v>
       </c>
       <c r="K11" t="n">
-        <v>12421</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>25.76</v>
+        <v>25.98</v>
       </c>
       <c r="M11" t="n">
-        <v>26.6</v>
+        <v>30.27</v>
       </c>
       <c r="N11" t="n">
-        <v>3.6</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1040,23 +1040,23 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="D12" t="n">
-        <v>1.367</v>
+        <v>1.029</v>
       </c>
       <c r="E12" t="n">
-        <v>-20.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.8</v>
+        <v>10.5</v>
       </c>
       <c r="G12" t="n">
-        <v>9.1</v>
+        <v>12.3</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1065,46 +1065,46 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>110531</v>
+        <v>16540</v>
       </c>
       <c r="K12" t="n">
-        <v>27874</v>
+        <v>12419</v>
       </c>
       <c r="L12" t="n">
-        <v>5.77</v>
+        <v>25.76</v>
       </c>
       <c r="M12" t="n">
-        <v>7.94</v>
+        <v>26.59</v>
       </c>
       <c r="N12" t="n">
-        <v>29.9</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="D13" t="n">
-        <v>1.607</v>
+        <v>1.359</v>
       </c>
       <c r="E13" t="n">
-        <v>-28</v>
+        <v>-20.3</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.5</v>
+        <v>-5.5</v>
       </c>
       <c r="G13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1117,19 +1117,19 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>392865</v>
+        <v>108657</v>
       </c>
       <c r="K13" t="n">
-        <v>71592</v>
+        <v>27779</v>
       </c>
       <c r="L13" t="n">
-        <v>59.47</v>
+        <v>5.77</v>
       </c>
       <c r="M13" t="n">
-        <v>90.01000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="N13" t="n">
-        <v>37</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="14">
@@ -1147,13 +1147,13 @@
         <v>0.75</v>
       </c>
       <c r="D14" t="n">
-        <v>1.276</v>
+        <v>1.245</v>
       </c>
       <c r="E14" t="n">
-        <v>-18.5</v>
+        <v>-16.2</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.9</v>
+        <v>-3.7</v>
       </c>
       <c r="G14" t="n">
         <v>8.800000000000001</v>
@@ -1178,37 +1178,37 @@
         <v>31.76</v>
       </c>
       <c r="M14" t="n">
-        <v>42.4</v>
+        <v>41.24</v>
       </c>
       <c r="N14" t="n">
-        <v>27.3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.09</v>
+        <v>0.98</v>
       </c>
       <c r="D15" t="n">
-        <v>1.16</v>
+        <v>1.645</v>
       </c>
       <c r="E15" t="n">
-        <v>-9.4</v>
+        <v>-29.6</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.9</v>
+        <v>-10.4</v>
       </c>
       <c r="G15" t="n">
-        <v>3.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1217,29 +1217,29 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>334603</v>
+        <v>414323</v>
       </c>
       <c r="K15" t="n">
-        <v>171590</v>
+        <v>73188</v>
       </c>
       <c r="L15" t="n">
-        <v>15.08</v>
+        <v>59.47</v>
       </c>
       <c r="M15" t="n">
-        <v>17.27</v>
+        <v>91.89</v>
       </c>
       <c r="N15" t="n">
-        <v>13.2</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1248,23 +1248,23 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.62</v>
+        <v>1.09</v>
       </c>
       <c r="D16" t="n">
-        <v>0.855</v>
+        <v>1.301</v>
       </c>
       <c r="E16" t="n">
-        <v>13.5</v>
+        <v>-20.2</v>
       </c>
       <c r="F16" t="n">
-        <v>6.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7</v>
+        <v>1.6</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1273,25 +1273,25 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>506266</v>
       </c>
       <c r="K16" t="n">
-        <v>1068984</v>
+        <v>200241</v>
       </c>
       <c r="L16" t="n">
-        <v>19.98</v>
+        <v>15.08</v>
       </c>
       <c r="M16" t="n">
-        <v>17.47</v>
+        <v>19.19</v>
       </c>
       <c r="N16" t="n">
-        <v>-14.2</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1300,23 +1300,23 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.2</v>
+        <v>0.62</v>
       </c>
       <c r="D17" t="n">
-        <v>1.177</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>-20.9</v>
+        <v>18.2</v>
       </c>
       <c r="F17" t="n">
-        <v>-12.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>-4.4</v>
+        <v>-0.7</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1325,25 +1325,25 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>375677</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>230245</v>
+        <v>1068984</v>
       </c>
       <c r="L17" t="n">
-        <v>29.36</v>
+        <v>19.98</v>
       </c>
       <c r="M17" t="n">
-        <v>35.51</v>
+        <v>16.78</v>
       </c>
       <c r="N17" t="n">
-        <v>16.6</v>
+        <v>-18.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1352,19 +1352,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="D18" t="n">
-        <v>1.153</v>
+        <v>1.274</v>
       </c>
       <c r="E18" t="n">
-        <v>-21</v>
+        <v>-28.7</v>
       </c>
       <c r="F18" t="n">
-        <v>-13.9</v>
+        <v>-17.1</v>
       </c>
       <c r="G18" t="n">
-        <v>-6.9</v>
+        <v>-5.6</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1377,25 +1377,25 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>333248</v>
+        <v>472015</v>
       </c>
       <c r="K18" t="n">
-        <v>222848</v>
+        <v>248780</v>
       </c>
       <c r="L18" t="n">
-        <v>39.33</v>
+        <v>29.18</v>
       </c>
       <c r="M18" t="n">
-        <v>46.33</v>
+        <v>38.64</v>
       </c>
       <c r="N18" t="n">
-        <v>14.1</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1404,19 +1404,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="D19" t="n">
-        <v>1.109</v>
+        <v>1.199</v>
       </c>
       <c r="E19" t="n">
-        <v>-29.6</v>
+        <v>-25.1</v>
       </c>
       <c r="F19" t="n">
-        <v>-23.9</v>
+        <v>-16.4</v>
       </c>
       <c r="G19" t="n">
-        <v>-18.2</v>
+        <v>-7.7</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1429,71 +1429,123 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>350590</v>
+        <v>377597</v>
       </c>
       <c r="K19" t="n">
-        <v>180943</v>
+        <v>233717</v>
       </c>
       <c r="L19" t="n">
-        <v>1.96</v>
+        <v>39.33</v>
       </c>
       <c r="M19" t="n">
-        <v>2.27</v>
+        <v>48.45</v>
       </c>
       <c r="N19" t="n">
-        <v>11.4</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>MPCC</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.122</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-27.3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-20.6</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-13.9</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>299648</v>
+      </c>
+      <c r="K20" t="n">
+        <v>120040</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="N20" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>FLNG</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>whole-company</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
         <v>1.37</v>
       </c>
-      <c r="D20" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-11.9</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-21.3</v>
-      </c>
-      <c r="H20" t="inlineStr">
+      <c r="D21" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-21</v>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
-      <c r="J20" t="n">
+      <c r="J21" t="n">
         <v>3162500</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K21" t="n">
         <v>3162500</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L21" t="n">
         <v>29.73</v>
       </c>
-      <c r="M20" t="n">
-        <v>24.01</v>
-      </c>
-      <c r="N20" t="n">
-        <v>-18.8</v>
+      <c r="M21" t="n">
+        <v>23.49</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-21</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -581,10 +581,10 @@
         <v>22.4</v>
       </c>
       <c r="F3" t="n">
-        <v>39.6</v>
+        <v>39.7</v>
       </c>
       <c r="G3" t="n">
-        <v>56.9</v>
+        <v>57.1</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -606,10 +606,10 @@
         <v>16.2</v>
       </c>
       <c r="M3" t="n">
-        <v>20.78</v>
+        <v>20.8</v>
       </c>
       <c r="N3" t="n">
-        <v>34.6</v>
+        <v>34.7</v>
       </c>
     </row>
     <row r="4">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -526,13 +526,13 @@
         <v>1.195</v>
       </c>
       <c r="E2" t="n">
-        <v>62.5</v>
+        <v>69.3</v>
       </c>
       <c r="F2" t="n">
-        <v>83.7</v>
+        <v>90.2</v>
       </c>
       <c r="G2" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -551,13 +551,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>62.23</v>
+        <v>64.84</v>
       </c>
       <c r="M2" t="n">
-        <v>78.48999999999999</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>42.5</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="3">
@@ -578,13 +578,13 @@
         <v>1.171</v>
       </c>
       <c r="E3" t="n">
-        <v>22.4</v>
+        <v>26.7</v>
       </c>
       <c r="F3" t="n">
-        <v>39.7</v>
+        <v>43.6</v>
       </c>
       <c r="G3" t="n">
-        <v>57.1</v>
+        <v>60.5</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>2791</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>16.2</v>
+        <v>16.77</v>
       </c>
       <c r="M3" t="n">
-        <v>20.8</v>
+        <v>21.25</v>
       </c>
       <c r="N3" t="n">
-        <v>34.7</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="4">
@@ -630,13 +630,13 @@
         <v>0.926</v>
       </c>
       <c r="E4" t="n">
-        <v>97.3</v>
+        <v>100.1</v>
       </c>
       <c r="F4" t="n">
-        <v>76.90000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="G4" t="n">
-        <v>56.6</v>
+        <v>60.5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -655,19 +655,19 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>10.65</v>
+        <v>10.8</v>
       </c>
       <c r="M4" t="n">
-        <v>8.449999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="N4" t="n">
-        <v>-40.7</v>
+        <v>-39.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -676,23 +676,23 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="D5" t="n">
-        <v>1.469</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-9.199999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>29.3</v>
+        <v>51.9</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -701,25 +701,25 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2725019</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>73.13</v>
+        <v>35.91</v>
       </c>
       <c r="M5" t="n">
-        <v>104.18</v>
+        <v>30.42</v>
       </c>
       <c r="N5" t="n">
-        <v>38.5</v>
+        <v>-27.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -728,23 +728,23 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="D6" t="n">
-        <v>2.164</v>
+        <v>1.469</v>
       </c>
       <c r="E6" t="n">
-        <v>-51.1</v>
+        <v>-0.7</v>
       </c>
       <c r="F6" t="n">
-        <v>-12.9</v>
+        <v>18.2</v>
       </c>
       <c r="G6" t="n">
-        <v>25.2</v>
+        <v>37.1</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -753,25 +753,25 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>396401</v>
+        <v>62640</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2.86</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>7.32</v>
+        <v>110.45</v>
       </c>
       <c r="N6" t="n">
-        <v>76.2</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -783,20 +783,20 @@
         <v>0.75</v>
       </c>
       <c r="D7" t="n">
-        <v>1.419</v>
+        <v>1.245</v>
       </c>
       <c r="E7" t="n">
-        <v>-11.8</v>
+        <v>7.1</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>19.5</v>
       </c>
       <c r="G7" t="n">
-        <v>23.9</v>
+        <v>31.8</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -805,19 +805,19 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>51701</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>15.05</v>
+        <v>40.59</v>
       </c>
       <c r="M7" t="n">
-        <v>21.14</v>
+        <v>49.94</v>
       </c>
       <c r="N7" t="n">
-        <v>35.7</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="8">
@@ -838,17 +838,17 @@
         <v>1.446</v>
       </c>
       <c r="E8" t="n">
-        <v>-1</v>
+        <v>6.9</v>
       </c>
       <c r="F8" t="n">
-        <v>11.3</v>
+        <v>18.9</v>
       </c>
       <c r="G8" t="n">
-        <v>23.6</v>
+        <v>30.9</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -857,25 +857,25 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>100249</v>
+        <v>41889</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>73.72</v>
+        <v>79.56</v>
       </c>
       <c r="M8" t="n">
-        <v>92.02</v>
+        <v>97.48</v>
       </c>
       <c r="N8" t="n">
-        <v>24.6</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -884,19 +884,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="D9" t="n">
-        <v>1.277</v>
+        <v>1.419</v>
       </c>
       <c r="E9" t="n">
-        <v>-9.300000000000001</v>
+        <v>-11.3</v>
       </c>
       <c r="F9" t="n">
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
       <c r="G9" t="n">
-        <v>21.1</v>
+        <v>23.8</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>80541</v>
+        <v>41676</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>26.68</v>
+        <v>15.15</v>
       </c>
       <c r="M9" t="n">
-        <v>35.61</v>
+        <v>21.13</v>
       </c>
       <c r="N9" t="n">
-        <v>30.4</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -936,23 +936,23 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9409999999999999</v>
+        <v>1.277</v>
       </c>
       <c r="E10" t="n">
-        <v>47.9</v>
+        <v>-7.1</v>
       </c>
       <c r="F10" t="n">
-        <v>34.3</v>
+        <v>7.8</v>
       </c>
       <c r="G10" t="n">
-        <v>20.7</v>
+        <v>22.7</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>71405</v>
       </c>
       <c r="K10" t="n">
-        <v>2977992</v>
+        <v>5383</v>
       </c>
       <c r="L10" t="n">
-        <v>29.63</v>
+        <v>27.32</v>
       </c>
       <c r="M10" t="n">
-        <v>24.17</v>
+        <v>36.09</v>
       </c>
       <c r="N10" t="n">
-        <v>-27.3</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -988,23 +988,23 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="D11" t="n">
-        <v>1.149</v>
+        <v>2.164</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6</v>
+        <v>-52.5</v>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>-15.2</v>
       </c>
       <c r="G11" t="n">
-        <v>17.3</v>
+        <v>22.1</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1013,25 +1013,25 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>21396</v>
+        <v>404139</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>607</v>
       </c>
       <c r="L11" t="n">
-        <v>25.98</v>
+        <v>2.78</v>
       </c>
       <c r="M11" t="n">
-        <v>30.27</v>
+        <v>7.15</v>
       </c>
       <c r="N11" t="n">
-        <v>16.6</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1040,23 +1040,23 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="D12" t="n">
-        <v>1.029</v>
+        <v>1.149</v>
       </c>
       <c r="E12" t="n">
-        <v>8.800000000000001</v>
+        <v>-0.2</v>
       </c>
       <c r="F12" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>12.3</v>
+        <v>16.3</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1065,25 +1065,25 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>16540</v>
+        <v>22755</v>
       </c>
       <c r="K12" t="n">
-        <v>12419</v>
+        <v>4809</v>
       </c>
       <c r="L12" t="n">
         <v>25.76</v>
       </c>
       <c r="M12" t="n">
-        <v>26.59</v>
+        <v>30.01</v>
       </c>
       <c r="N12" t="n">
-        <v>3.5</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1092,23 +1092,23 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="D13" t="n">
-        <v>1.359</v>
+        <v>1.029</v>
       </c>
       <c r="E13" t="n">
-        <v>-20.3</v>
+        <v>7.3</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.5</v>
+        <v>9.1</v>
       </c>
       <c r="G13" t="n">
-        <v>9.199999999999999</v>
+        <v>10.8</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1117,25 +1117,25 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>108657</v>
+        <v>16540</v>
       </c>
       <c r="K13" t="n">
-        <v>27779</v>
+        <v>12419</v>
       </c>
       <c r="L13" t="n">
-        <v>5.77</v>
+        <v>25.41</v>
       </c>
       <c r="M13" t="n">
-        <v>7.9</v>
+        <v>26.24</v>
       </c>
       <c r="N13" t="n">
-        <v>29.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="D14" t="n">
-        <v>1.245</v>
+        <v>1.359</v>
       </c>
       <c r="E14" t="n">
-        <v>-16.2</v>
+        <v>-18.2</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.7</v>
+        <v>-3.8</v>
       </c>
       <c r="G14" t="n">
-        <v>8.800000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1169,19 +1169,19 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>2757173</v>
+        <v>95336</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>30566</v>
       </c>
       <c r="L14" t="n">
-        <v>31.76</v>
+        <v>5.91</v>
       </c>
       <c r="M14" t="n">
-        <v>41.24</v>
+        <v>8</v>
       </c>
       <c r="N14" t="n">
-        <v>25</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="15">
@@ -1202,13 +1202,13 @@
         <v>1.645</v>
       </c>
       <c r="E15" t="n">
-        <v>-29.6</v>
+        <v>-27.6</v>
       </c>
       <c r="F15" t="n">
-        <v>-10.4</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1221,25 +1221,25 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>414323</v>
+        <v>316872</v>
       </c>
       <c r="K15" t="n">
-        <v>73188</v>
+        <v>74962</v>
       </c>
       <c r="L15" t="n">
-        <v>59.47</v>
+        <v>61.16</v>
       </c>
       <c r="M15" t="n">
-        <v>91.89</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>38.4</v>
+        <v>37.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1248,50 +1248,50 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.09</v>
+        <v>0.62</v>
       </c>
       <c r="D16" t="n">
-        <v>1.301</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>-20.2</v>
+        <v>25</v>
       </c>
       <c r="F16" t="n">
-        <v>-9.300000000000001</v>
+        <v>15.7</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6</v>
+        <v>6.3</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>506266</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>200241</v>
+        <v>14632</v>
       </c>
       <c r="L16" t="n">
-        <v>15.08</v>
+        <v>21.13</v>
       </c>
       <c r="M16" t="n">
-        <v>19.19</v>
+        <v>17.97</v>
       </c>
       <c r="N16" t="n">
-        <v>21.8</v>
+        <v>-18.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1300,23 +1300,23 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.62</v>
+        <v>1.09</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8159999999999999</v>
+        <v>1.301</v>
       </c>
       <c r="E17" t="n">
-        <v>18.2</v>
+        <v>-21.8</v>
       </c>
       <c r="F17" t="n">
-        <v>8.699999999999999</v>
+        <v>-11.2</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7</v>
+        <v>-0.6</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1325,25 +1325,25 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>529540</v>
       </c>
       <c r="K17" t="n">
-        <v>1068984</v>
+        <v>230527</v>
       </c>
       <c r="L17" t="n">
-        <v>19.98</v>
+        <v>14.77</v>
       </c>
       <c r="M17" t="n">
-        <v>16.78</v>
+        <v>18.78</v>
       </c>
       <c r="N17" t="n">
-        <v>-18.9</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1352,19 +1352,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="D18" t="n">
-        <v>1.274</v>
+        <v>1.122</v>
       </c>
       <c r="E18" t="n">
-        <v>-28.7</v>
+        <v>-17.1</v>
       </c>
       <c r="F18" t="n">
-        <v>-17.1</v>
+        <v>-10.4</v>
       </c>
       <c r="G18" t="n">
-        <v>-5.6</v>
+        <v>-3.8</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1373,29 +1373,29 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>472015</v>
+        <v>137799</v>
       </c>
       <c r="K18" t="n">
-        <v>248780</v>
+        <v>46477</v>
       </c>
       <c r="L18" t="n">
-        <v>29.18</v>
+        <v>2.11</v>
       </c>
       <c r="M18" t="n">
-        <v>38.64</v>
+        <v>2.44</v>
       </c>
       <c r="N18" t="n">
-        <v>23.1</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1404,19 +1404,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="D19" t="n">
-        <v>1.199</v>
+        <v>1.274</v>
       </c>
       <c r="E19" t="n">
-        <v>-25.1</v>
+        <v>-29.9</v>
       </c>
       <c r="F19" t="n">
-        <v>-16.4</v>
+        <v>-18.6</v>
       </c>
       <c r="G19" t="n">
-        <v>-7.7</v>
+        <v>-7.4</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>377597</v>
+        <v>469143</v>
       </c>
       <c r="K19" t="n">
-        <v>233717</v>
+        <v>260767</v>
       </c>
       <c r="L19" t="n">
-        <v>39.33</v>
+        <v>28.68</v>
       </c>
       <c r="M19" t="n">
-        <v>48.45</v>
+        <v>37.92</v>
       </c>
       <c r="N19" t="n">
-        <v>17.4</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1456,19 +1456,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="D20" t="n">
-        <v>1.122</v>
+        <v>1.199</v>
       </c>
       <c r="E20" t="n">
-        <v>-27.3</v>
+        <v>-24.9</v>
       </c>
       <c r="F20" t="n">
-        <v>-20.6</v>
+        <v>-16.4</v>
       </c>
       <c r="G20" t="n">
-        <v>-13.9</v>
+        <v>-7.9</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>299648</v>
+        <v>343849</v>
       </c>
       <c r="K20" t="n">
-        <v>120040</v>
+        <v>222252</v>
       </c>
       <c r="L20" t="n">
-        <v>1.85</v>
+        <v>39.41</v>
       </c>
       <c r="M20" t="n">
-        <v>2.19</v>
+        <v>48.31</v>
       </c>
       <c r="N20" t="n">
-        <v>13.4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1514,13 +1514,13 @@
         <v>0.875</v>
       </c>
       <c r="E21" t="n">
-        <v>-0</v>
+        <v>3.1</v>
       </c>
       <c r="F21" t="n">
-        <v>-10.5</v>
+        <v>-7.4</v>
       </c>
       <c r="G21" t="n">
-        <v>-21</v>
+        <v>-17.9</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>3162500</v>
+        <v>148289</v>
       </c>
       <c r="K21" t="n">
-        <v>3162500</v>
+        <v>462295</v>
       </c>
       <c r="L21" t="n">
-        <v>29.73</v>
+        <v>30.67</v>
       </c>
       <c r="M21" t="n">
-        <v>23.49</v>
+        <v>24.41</v>
       </c>
       <c r="N21" t="n">
-        <v>-21</v>
+        <v>-21.1</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -523,13 +523,13 @@
         <v>0.34</v>
       </c>
       <c r="D2" t="n">
-        <v>1.195</v>
+        <v>1.194</v>
       </c>
       <c r="E2" t="n">
-        <v>69.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>90.2</v>
+        <v>90.3</v>
       </c>
       <c r="G2" t="n">
         <v>111</v>
@@ -551,19 +551,19 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>64.84</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>80.79000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="N2" t="n">
-        <v>41.7</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -572,16 +572,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="D3" t="n">
-        <v>1.171</v>
+        <v>0.926</v>
       </c>
       <c r="E3" t="n">
-        <v>26.7</v>
+        <v>100.1</v>
       </c>
       <c r="F3" t="n">
-        <v>43.6</v>
+        <v>80.3</v>
       </c>
       <c r="G3" t="n">
         <v>60.5</v>
@@ -597,25 +597,25 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2791</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>16.77</v>
+        <v>10.81</v>
       </c>
       <c r="M3" t="n">
-        <v>21.25</v>
+        <v>8.67</v>
       </c>
       <c r="N3" t="n">
-        <v>33.8</v>
+        <v>-39.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -624,16 +624,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="D4" t="n">
-        <v>0.926</v>
+        <v>1.171</v>
       </c>
       <c r="E4" t="n">
-        <v>100.1</v>
+        <v>26.7</v>
       </c>
       <c r="F4" t="n">
-        <v>80.3</v>
+        <v>43.6</v>
       </c>
       <c r="G4" t="n">
         <v>60.5</v>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2701</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>10.8</v>
+        <v>16.77</v>
       </c>
       <c r="M4" t="n">
-        <v>8.67</v>
+        <v>21.25</v>
       </c>
       <c r="N4" t="n">
-        <v>-39.6</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="5">
@@ -835,7 +835,7 @@
         <v>0.76</v>
       </c>
       <c r="D8" t="n">
-        <v>1.446</v>
+        <v>1.445</v>
       </c>
       <c r="E8" t="n">
         <v>6.9</v>
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>41889</v>
+        <v>41652</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>79.56</v>
+        <v>79.59</v>
       </c>
       <c r="M8" t="n">
-        <v>97.48</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -1199,13 +1199,13 @@
         <v>0.98</v>
       </c>
       <c r="D15" t="n">
-        <v>1.645</v>
+        <v>1.638</v>
       </c>
       <c r="E15" t="n">
-        <v>-27.6</v>
+        <v>-27.4</v>
       </c>
       <c r="F15" t="n">
-        <v>-8.800000000000001</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>9.9</v>
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>316872</v>
+        <v>316781</v>
       </c>
       <c r="K15" t="n">
-        <v>74962</v>
+        <v>75231</v>
       </c>
       <c r="L15" t="n">
-        <v>61.16</v>
+        <v>61.34</v>
       </c>
       <c r="M15" t="n">
-        <v>92.90000000000001</v>
+        <v>92.89</v>
       </c>
       <c r="N15" t="n">
-        <v>37.6</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="16">
@@ -1303,16 +1303,16 @@
         <v>1.09</v>
       </c>
       <c r="D17" t="n">
-        <v>1.301</v>
+        <v>1.287</v>
       </c>
       <c r="E17" t="n">
-        <v>-21.8</v>
+        <v>-21</v>
       </c>
       <c r="F17" t="n">
-        <v>-11.2</v>
+        <v>-10.8</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1325,19 +1325,19 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>529540</v>
+        <v>518123</v>
       </c>
       <c r="K17" t="n">
-        <v>230527</v>
+        <v>230052</v>
       </c>
       <c r="L17" t="n">
-        <v>14.77</v>
+        <v>14.92</v>
       </c>
       <c r="M17" t="n">
-        <v>18.78</v>
+        <v>18.79</v>
       </c>
       <c r="N17" t="n">
-        <v>21.3</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="18">
@@ -1407,16 +1407,16 @@
         <v>1.2</v>
       </c>
       <c r="D19" t="n">
-        <v>1.274</v>
+        <v>1.269</v>
       </c>
       <c r="E19" t="n">
-        <v>-29.9</v>
+        <v>-29.6</v>
       </c>
       <c r="F19" t="n">
-        <v>-18.6</v>
+        <v>-18.5</v>
       </c>
       <c r="G19" t="n">
-        <v>-7.4</v>
+        <v>-7.3</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1429,19 +1429,19 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>469143</v>
+        <v>466274</v>
       </c>
       <c r="K19" t="n">
-        <v>260767</v>
+        <v>260547</v>
       </c>
       <c r="L19" t="n">
-        <v>28.68</v>
+        <v>28.82</v>
       </c>
       <c r="M19" t="n">
-        <v>37.92</v>
+        <v>37.94</v>
       </c>
       <c r="N19" t="n">
-        <v>22.6</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="20">
@@ -1459,13 +1459,13 @@
         <v>1.21</v>
       </c>
       <c r="D20" t="n">
-        <v>1.199</v>
+        <v>1.195</v>
       </c>
       <c r="E20" t="n">
-        <v>-24.9</v>
+        <v>-24.6</v>
       </c>
       <c r="F20" t="n">
-        <v>-16.4</v>
+        <v>-16.2</v>
       </c>
       <c r="G20" t="n">
         <v>-7.9</v>
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>343849</v>
+        <v>341712</v>
       </c>
       <c r="K20" t="n">
-        <v>222252</v>
+        <v>222060</v>
       </c>
       <c r="L20" t="n">
-        <v>39.41</v>
+        <v>39.59</v>
       </c>
       <c r="M20" t="n">
-        <v>48.31</v>
+        <v>48.34</v>
       </c>
       <c r="N20" t="n">
-        <v>17</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="21">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -523,16 +523,16 @@
         <v>0.34</v>
       </c>
       <c r="D2" t="n">
-        <v>1.194</v>
+        <v>1.158</v>
       </c>
       <c r="E2" t="n">
-        <v>69.59999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="F2" t="n">
-        <v>90.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -554,16 +554,16 @@
         <v>64.93000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>80.8</v>
+        <v>77.86</v>
       </c>
       <c r="N2" t="n">
-        <v>41.5</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="D3" t="n">
-        <v>0.926</v>
+        <v>1.147</v>
       </c>
       <c r="E3" t="n">
-        <v>100.1</v>
+        <v>31.1</v>
       </c>
       <c r="F3" t="n">
-        <v>80.3</v>
+        <v>46.2</v>
       </c>
       <c r="G3" t="n">
-        <v>60.5</v>
+        <v>61.2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -603,19 +603,19 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>10.81</v>
+        <v>16.77</v>
       </c>
       <c r="M3" t="n">
-        <v>8.67</v>
+        <v>20.61</v>
       </c>
       <c r="N3" t="n">
-        <v>-39.6</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -624,19 +624,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="D4" t="n">
-        <v>1.171</v>
+        <v>0.924</v>
       </c>
       <c r="E4" t="n">
-        <v>26.7</v>
+        <v>102.4</v>
       </c>
       <c r="F4" t="n">
-        <v>43.6</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>60.5</v>
+        <v>60.9</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2701</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>16.77</v>
+        <v>10.81</v>
       </c>
       <c r="M4" t="n">
-        <v>21.25</v>
+        <v>8.59</v>
       </c>
       <c r="N4" t="n">
-        <v>33.8</v>
+        <v>-41.5</v>
       </c>
     </row>
     <row r="5">
@@ -679,16 +679,16 @@
         <v>0.9</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.949</v>
       </c>
       <c r="E5" t="n">
-        <v>79.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>65.59999999999999</v>
+        <v>61.8</v>
       </c>
       <c r="G5" t="n">
-        <v>51.9</v>
+        <v>50.3</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         <v>35.91</v>
       </c>
       <c r="M5" t="n">
-        <v>30.42</v>
+        <v>31.13</v>
       </c>
       <c r="N5" t="n">
-        <v>-27.4</v>
+        <v>-23</v>
       </c>
     </row>
     <row r="6">
@@ -731,20 +731,20 @@
         <v>0.7</v>
       </c>
       <c r="D6" t="n">
-        <v>1.469</v>
+        <v>1.315</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7</v>
+        <v>10.2</v>
       </c>
       <c r="F6" t="n">
-        <v>18.2</v>
+        <v>24.3</v>
       </c>
       <c r="G6" t="n">
-        <v>37.1</v>
+        <v>38.4</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>62640</v>
+        <v>23127</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -762,37 +762,37 @@
         <v>79.98999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>110.45</v>
+        <v>100.43</v>
       </c>
       <c r="N6" t="n">
-        <v>37.8</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="D7" t="n">
-        <v>1.245</v>
+        <v>1.143</v>
       </c>
       <c r="E7" t="n">
-        <v>7.1</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
-        <v>19.5</v>
+        <v>23.2</v>
       </c>
       <c r="G7" t="n">
-        <v>31.8</v>
+        <v>35.4</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -805,19 +805,19 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>54596</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>40.59</v>
+        <v>15.66</v>
       </c>
       <c r="M7" t="n">
-        <v>49.94</v>
+        <v>19.09</v>
       </c>
       <c r="N7" t="n">
-        <v>24.7</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="8">
@@ -835,16 +835,16 @@
         <v>0.76</v>
       </c>
       <c r="D8" t="n">
-        <v>1.445</v>
+        <v>1.26</v>
       </c>
       <c r="E8" t="n">
-        <v>6.9</v>
+        <v>17.1</v>
       </c>
       <c r="F8" t="n">
-        <v>18.9</v>
+        <v>24.8</v>
       </c>
       <c r="G8" t="n">
-        <v>30.9</v>
+        <v>32.4</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>41652</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -866,16 +866,16 @@
         <v>79.59</v>
       </c>
       <c r="M8" t="n">
-        <v>97.48999999999999</v>
+        <v>90.05</v>
       </c>
       <c r="N8" t="n">
-        <v>24</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -887,20 +887,20 @@
         <v>0.75</v>
       </c>
       <c r="D9" t="n">
-        <v>1.419</v>
+        <v>1.243</v>
       </c>
       <c r="E9" t="n">
-        <v>-11.3</v>
+        <v>7.4</v>
       </c>
       <c r="F9" t="n">
-        <v>6.3</v>
+        <v>19.6</v>
       </c>
       <c r="G9" t="n">
-        <v>23.8</v>
+        <v>31.9</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -909,25 +909,25 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>41676</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>15.15</v>
+        <v>40.59</v>
       </c>
       <c r="M9" t="n">
-        <v>21.13</v>
+        <v>49.84</v>
       </c>
       <c r="N9" t="n">
-        <v>35.1</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -936,23 +936,23 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="D10" t="n">
-        <v>1.277</v>
+        <v>1.259</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.1</v>
+        <v>0.2</v>
       </c>
       <c r="F10" t="n">
-        <v>7.8</v>
+        <v>12.4</v>
       </c>
       <c r="G10" t="n">
-        <v>22.7</v>
+        <v>24.7</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>71405</v>
+        <v>25023</v>
       </c>
       <c r="K10" t="n">
-        <v>5383</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>27.32</v>
+        <v>15.15</v>
       </c>
       <c r="M10" t="n">
-        <v>36.09</v>
+        <v>18.85</v>
       </c>
       <c r="N10" t="n">
-        <v>29.8</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -988,23 +988,23 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="D11" t="n">
-        <v>2.164</v>
+        <v>1.19</v>
       </c>
       <c r="E11" t="n">
-        <v>-52.5</v>
+        <v>1.9</v>
       </c>
       <c r="F11" t="n">
-        <v>-15.2</v>
+        <v>13.1</v>
       </c>
       <c r="G11" t="n">
-        <v>22.1</v>
+        <v>24.4</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1013,25 +1013,25 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>404139</v>
+        <v>52226</v>
       </c>
       <c r="K11" t="n">
-        <v>607</v>
+        <v>6749</v>
       </c>
       <c r="L11" t="n">
-        <v>2.78</v>
+        <v>27.32</v>
       </c>
       <c r="M11" t="n">
-        <v>7.15</v>
+        <v>33.34</v>
       </c>
       <c r="N11" t="n">
-        <v>74.59999999999999</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1040,23 +1040,23 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="D12" t="n">
-        <v>1.149</v>
+        <v>2.164</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2</v>
+        <v>-52.5</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>-15.2</v>
       </c>
       <c r="G12" t="n">
-        <v>16.3</v>
+        <v>22.1</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1065,25 +1065,25 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>22755</v>
+        <v>404139</v>
       </c>
       <c r="K12" t="n">
-        <v>4809</v>
+        <v>607</v>
       </c>
       <c r="L12" t="n">
-        <v>25.76</v>
+        <v>2.78</v>
       </c>
       <c r="M12" t="n">
-        <v>30.01</v>
+        <v>7.15</v>
       </c>
       <c r="N12" t="n">
-        <v>16.4</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1092,19 +1092,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="D13" t="n">
-        <v>1.029</v>
+        <v>1.097</v>
       </c>
       <c r="E13" t="n">
-        <v>7.3</v>
+        <v>5.6</v>
       </c>
       <c r="F13" t="n">
-        <v>9.1</v>
+        <v>11.2</v>
       </c>
       <c r="G13" t="n">
-        <v>10.8</v>
+        <v>16.9</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1117,19 +1117,19 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>16540</v>
+        <v>16931</v>
       </c>
       <c r="K13" t="n">
-        <v>12419</v>
+        <v>5154</v>
       </c>
       <c r="L13" t="n">
-        <v>25.41</v>
+        <v>25.76</v>
       </c>
       <c r="M13" t="n">
-        <v>26.24</v>
+        <v>28.52</v>
       </c>
       <c r="N13" t="n">
-        <v>3.5</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="14">
@@ -1147,16 +1147,16 @@
         <v>0.95</v>
       </c>
       <c r="D14" t="n">
-        <v>1.359</v>
+        <v>1.318</v>
       </c>
       <c r="E14" t="n">
-        <v>-18.2</v>
+        <v>-15.2</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.8</v>
+        <v>-1.9</v>
       </c>
       <c r="G14" t="n">
-        <v>10.7</v>
+        <v>11.4</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1169,50 +1169,50 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>95336</v>
+        <v>87353</v>
       </c>
       <c r="K14" t="n">
-        <v>30566</v>
+        <v>29992</v>
       </c>
       <c r="L14" t="n">
         <v>5.91</v>
       </c>
       <c r="M14" t="n">
-        <v>8</v>
+        <v>7.76</v>
       </c>
       <c r="N14" t="n">
-        <v>28.9</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.98</v>
+        <v>0.87</v>
       </c>
       <c r="D15" t="n">
-        <v>1.638</v>
+        <v>1.025</v>
       </c>
       <c r="E15" t="n">
-        <v>-27.4</v>
+        <v>7.8</v>
       </c>
       <c r="F15" t="n">
-        <v>-8.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>9.9</v>
+        <v>10.8</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1221,50 +1221,50 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>316781</v>
+        <v>15973</v>
       </c>
       <c r="K15" t="n">
-        <v>75231</v>
+        <v>12402</v>
       </c>
       <c r="L15" t="n">
-        <v>61.34</v>
+        <v>25.41</v>
       </c>
       <c r="M15" t="n">
-        <v>92.89</v>
+        <v>26.13</v>
       </c>
       <c r="N15" t="n">
-        <v>37.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.62</v>
+        <v>0.98</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8159999999999999</v>
+        <v>1.542</v>
       </c>
       <c r="E16" t="n">
-        <v>25</v>
+        <v>-22.8</v>
       </c>
       <c r="F16" t="n">
-        <v>15.7</v>
+        <v>-6</v>
       </c>
       <c r="G16" t="n">
-        <v>6.3</v>
+        <v>10.8</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1273,25 +1273,25 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>276426</v>
       </c>
       <c r="K16" t="n">
-        <v>14632</v>
+        <v>71380</v>
       </c>
       <c r="L16" t="n">
-        <v>21.13</v>
+        <v>61.34</v>
       </c>
       <c r="M16" t="n">
-        <v>17.97</v>
+        <v>88.12</v>
       </c>
       <c r="N16" t="n">
-        <v>-18.7</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1300,50 +1300,50 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.09</v>
+        <v>0.62</v>
       </c>
       <c r="D17" t="n">
-        <v>1.287</v>
+        <v>0.848</v>
       </c>
       <c r="E17" t="n">
-        <v>-21</v>
+        <v>20.9</v>
       </c>
       <c r="F17" t="n">
-        <v>-10.8</v>
+        <v>13.5</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5</v>
+        <v>6</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>518123</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>230052</v>
+        <v>14735</v>
       </c>
       <c r="L17" t="n">
-        <v>14.92</v>
+        <v>21.13</v>
       </c>
       <c r="M17" t="n">
-        <v>18.79</v>
+        <v>18.52</v>
       </c>
       <c r="N17" t="n">
-        <v>20.5</v>
+        <v>-14.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1352,19 +1352,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="D18" t="n">
-        <v>1.122</v>
+        <v>1.21</v>
       </c>
       <c r="E18" t="n">
-        <v>-17.1</v>
+        <v>-15.5</v>
       </c>
       <c r="F18" t="n">
-        <v>-10.4</v>
+        <v>-7.5</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.8</v>
+        <v>0.6</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1377,25 +1377,25 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>137799</v>
+        <v>423096</v>
       </c>
       <c r="K18" t="n">
-        <v>46477</v>
+        <v>212406</v>
       </c>
       <c r="L18" t="n">
-        <v>2.11</v>
+        <v>14.92</v>
       </c>
       <c r="M18" t="n">
-        <v>2.44</v>
+        <v>17.75</v>
       </c>
       <c r="N18" t="n">
-        <v>13.3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1404,19 +1404,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="D19" t="n">
-        <v>1.269</v>
+        <v>1.142</v>
       </c>
       <c r="E19" t="n">
-        <v>-29.6</v>
+        <v>-19.3</v>
       </c>
       <c r="F19" t="n">
-        <v>-18.5</v>
+        <v>-11.8</v>
       </c>
       <c r="G19" t="n">
-        <v>-7.3</v>
+        <v>-4.3</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1425,29 +1425,29 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>466274</v>
+        <v>155119</v>
       </c>
       <c r="K19" t="n">
-        <v>260547</v>
+        <v>49153</v>
       </c>
       <c r="L19" t="n">
-        <v>28.82</v>
+        <v>2.11</v>
       </c>
       <c r="M19" t="n">
-        <v>37.94</v>
+        <v>2.5</v>
       </c>
       <c r="N19" t="n">
-        <v>22.3</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1456,19 +1456,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="D20" t="n">
-        <v>1.195</v>
+        <v>1.146</v>
       </c>
       <c r="E20" t="n">
-        <v>-24.6</v>
+        <v>-18.9</v>
       </c>
       <c r="F20" t="n">
-        <v>-16.2</v>
+        <v>-11.9</v>
       </c>
       <c r="G20" t="n">
-        <v>-7.9</v>
+        <v>-4.9</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1477,75 +1477,127 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>341712</v>
+        <v>339908</v>
       </c>
       <c r="K20" t="n">
-        <v>222060</v>
+        <v>227971</v>
       </c>
       <c r="L20" t="n">
-        <v>39.59</v>
+        <v>28.82</v>
       </c>
       <c r="M20" t="n">
-        <v>48.34</v>
+        <v>33.78</v>
       </c>
       <c r="N20" t="n">
-        <v>16.7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>ECO</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.151</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-20.6</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-13.8</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>304990</v>
+      </c>
+      <c r="K21" t="n">
+        <v>212429</v>
+      </c>
+      <c r="L21" t="n">
+        <v>39.59</v>
+      </c>
+      <c r="M21" t="n">
+        <v>46.36</v>
+      </c>
+      <c r="N21" t="n">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>FLNG</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>whole-company</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
         <v>1.37</v>
       </c>
-      <c r="D21" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="E21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-7.4</v>
-      </c>
-      <c r="G21" t="n">
-        <v>-17.9</v>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="D22" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-6.9</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-17.8</v>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
-      <c r="J21" t="n">
-        <v>148289</v>
-      </c>
-      <c r="K21" t="n">
-        <v>462295</v>
-      </c>
-      <c r="L21" t="n">
+      <c r="J22" t="n">
+        <v>134259</v>
+      </c>
+      <c r="K22" t="n">
+        <v>457099</v>
+      </c>
+      <c r="L22" t="n">
         <v>30.67</v>
       </c>
-      <c r="M21" t="n">
-        <v>24.41</v>
-      </c>
-      <c r="N21" t="n">
-        <v>-21.1</v>
+      <c r="M22" t="n">
+        <v>24.24</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-21.8</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -786,13 +786,13 @@
         <v>1.143</v>
       </c>
       <c r="E7" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="F7" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="G7" t="n">
-        <v>35.4</v>
+        <v>35.2</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -805,19 +805,19 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>54596</v>
+        <v>54299</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>15.66</v>
+        <v>15.64</v>
       </c>
       <c r="M7" t="n">
-        <v>19.09</v>
+        <v>19.06</v>
       </c>
       <c r="N7" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="8">
@@ -1095,16 +1095,16 @@
         <v>0.82</v>
       </c>
       <c r="D13" t="n">
-        <v>1.097</v>
+        <v>1.085</v>
       </c>
       <c r="E13" t="n">
-        <v>5.6</v>
+        <v>6.9</v>
       </c>
       <c r="F13" t="n">
-        <v>11.2</v>
+        <v>11.9</v>
       </c>
       <c r="G13" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1117,19 +1117,19 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>16931</v>
+        <v>15583</v>
       </c>
       <c r="K13" t="n">
-        <v>5154</v>
+        <v>5007</v>
       </c>
       <c r="L13" t="n">
-        <v>25.76</v>
+        <v>26.07</v>
       </c>
       <c r="M13" t="n">
-        <v>28.52</v>
+        <v>28.54</v>
       </c>
       <c r="N13" t="n">
-        <v>11.3</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="14">
@@ -1199,20 +1199,20 @@
         <v>0.87</v>
       </c>
       <c r="D15" t="n">
-        <v>1.025</v>
+        <v>1.08</v>
       </c>
       <c r="E15" t="n">
-        <v>7.8</v>
+        <v>1.9</v>
       </c>
       <c r="F15" t="n">
-        <v>9.300000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="G15" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>15973</v>
+        <v>22647</v>
       </c>
       <c r="K15" t="n">
-        <v>12402</v>
+        <v>12051</v>
       </c>
       <c r="L15" t="n">
-        <v>25.41</v>
+        <v>24.02</v>
       </c>
       <c r="M15" t="n">
-        <v>26.13</v>
+        <v>26.16</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="16">
@@ -1303,13 +1303,13 @@
         <v>0.62</v>
       </c>
       <c r="D17" t="n">
-        <v>0.848</v>
+        <v>0.884</v>
       </c>
       <c r="E17" t="n">
-        <v>20.9</v>
+        <v>16.9</v>
       </c>
       <c r="F17" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="G17" t="n">
         <v>6</v>
@@ -1325,19 +1325,19 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>2713</v>
       </c>
       <c r="K17" t="n">
-        <v>14735</v>
+        <v>14534</v>
       </c>
       <c r="L17" t="n">
-        <v>21.13</v>
+        <v>20.43</v>
       </c>
       <c r="M17" t="n">
         <v>18.52</v>
       </c>
       <c r="N17" t="n">
-        <v>-14.9</v>
+        <v>-10.9</v>
       </c>
     </row>
     <row r="18">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1291,7 +1291,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1300,19 +1300,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.62</v>
+        <v>0.88</v>
       </c>
       <c r="D17" t="n">
-        <v>0.884</v>
+        <v>0.783</v>
       </c>
       <c r="E17" t="n">
-        <v>16.9</v>
+        <v>49</v>
       </c>
       <c r="F17" t="n">
-        <v>11.5</v>
+        <v>29.5</v>
       </c>
       <c r="G17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1325,25 +1325,25 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>2713</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>14534</v>
+        <v>11482</v>
       </c>
       <c r="L17" t="n">
-        <v>20.43</v>
+        <v>9.52</v>
       </c>
       <c r="M17" t="n">
-        <v>18.52</v>
+        <v>7.03</v>
       </c>
       <c r="N17" t="n">
-        <v>-10.9</v>
+        <v>-39</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1352,50 +1352,50 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.09</v>
+        <v>0.62</v>
       </c>
       <c r="D18" t="n">
-        <v>1.21</v>
+        <v>0.884</v>
       </c>
       <c r="E18" t="n">
-        <v>-15.5</v>
+        <v>16.9</v>
       </c>
       <c r="F18" t="n">
-        <v>-7.5</v>
+        <v>11.5</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>423096</v>
+        <v>2713</v>
       </c>
       <c r="K18" t="n">
-        <v>212406</v>
+        <v>14534</v>
       </c>
       <c r="L18" t="n">
-        <v>14.92</v>
+        <v>20.43</v>
       </c>
       <c r="M18" t="n">
-        <v>17.75</v>
+        <v>18.52</v>
       </c>
       <c r="N18" t="n">
-        <v>16</v>
+        <v>-10.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1404,19 +1404,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="D19" t="n">
-        <v>1.142</v>
+        <v>1.21</v>
       </c>
       <c r="E19" t="n">
-        <v>-19.3</v>
+        <v>-15.5</v>
       </c>
       <c r="F19" t="n">
-        <v>-11.8</v>
+        <v>-7.5</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.3</v>
+        <v>0.6</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>155119</v>
+        <v>423096</v>
       </c>
       <c r="K19" t="n">
-        <v>49153</v>
+        <v>212406</v>
       </c>
       <c r="L19" t="n">
-        <v>2.11</v>
+        <v>14.92</v>
       </c>
       <c r="M19" t="n">
-        <v>2.5</v>
+        <v>17.75</v>
       </c>
       <c r="N19" t="n">
-        <v>15.1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1456,19 +1456,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="D20" t="n">
-        <v>1.146</v>
+        <v>1.142</v>
       </c>
       <c r="E20" t="n">
-        <v>-18.9</v>
+        <v>-19.3</v>
       </c>
       <c r="F20" t="n">
-        <v>-11.9</v>
+        <v>-11.8</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.9</v>
+        <v>-4.3</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1481,25 +1481,25 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>339908</v>
+        <v>155119</v>
       </c>
       <c r="K20" t="n">
-        <v>227971</v>
+        <v>49153</v>
       </c>
       <c r="L20" t="n">
-        <v>28.82</v>
+        <v>2.11</v>
       </c>
       <c r="M20" t="n">
-        <v>33.78</v>
+        <v>2.5</v>
       </c>
       <c r="N20" t="n">
-        <v>14</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1508,19 +1508,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="D21" t="n">
-        <v>1.151</v>
+        <v>1.146</v>
       </c>
       <c r="E21" t="n">
-        <v>-20.6</v>
+        <v>-18.9</v>
       </c>
       <c r="F21" t="n">
-        <v>-13.8</v>
+        <v>-11.9</v>
       </c>
       <c r="G21" t="n">
-        <v>-7.1</v>
+        <v>-4.9</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1529,74 +1529,126 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>304990</v>
+        <v>339908</v>
       </c>
       <c r="K21" t="n">
-        <v>212429</v>
+        <v>227971</v>
       </c>
       <c r="L21" t="n">
-        <v>39.59</v>
+        <v>28.82</v>
       </c>
       <c r="M21" t="n">
-        <v>46.36</v>
+        <v>33.78</v>
       </c>
       <c r="N21" t="n">
-        <v>13.6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>ECO</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.151</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-20.6</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-13.8</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>304990</v>
+      </c>
+      <c r="K22" t="n">
+        <v>212429</v>
+      </c>
+      <c r="L22" t="n">
+        <v>39.59</v>
+      </c>
+      <c r="M22" t="n">
+        <v>46.36</v>
+      </c>
+      <c r="N22" t="n">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>FLNG</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>whole-company</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
         <v>1.37</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D23" t="n">
         <v>0.871</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E23" t="n">
         <v>4.1</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F23" t="n">
         <v>-6.9</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G23" t="n">
         <v>-17.8</v>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>134259</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K23" t="n">
         <v>457099</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L23" t="n">
         <v>30.67</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M23" t="n">
         <v>24.24</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N23" t="n">
         <v>-21.8</v>
       </c>
     </row>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -1135,7 +1135,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1144,23 +1144,23 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
       <c r="D14" t="n">
-        <v>1.318</v>
+        <v>0.802</v>
       </c>
       <c r="E14" t="n">
-        <v>-15.2</v>
+        <v>46.3</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.9</v>
+        <v>29</v>
       </c>
       <c r="G14" t="n">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1169,25 +1169,25 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>87353</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>29992</v>
+        <v>2688</v>
       </c>
       <c r="L14" t="n">
-        <v>5.91</v>
+        <v>9.35</v>
       </c>
       <c r="M14" t="n">
-        <v>7.76</v>
+        <v>7.13</v>
       </c>
       <c r="N14" t="n">
-        <v>26.6</v>
+        <v>-34.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1196,23 +1196,23 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.87</v>
+        <v>0.95</v>
       </c>
       <c r="D15" t="n">
-        <v>1.08</v>
+        <v>1.318</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9</v>
+        <v>-15.2</v>
       </c>
       <c r="F15" t="n">
-        <v>6.5</v>
+        <v>-1.9</v>
       </c>
       <c r="G15" t="n">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1221,50 +1221,50 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>22647</v>
+        <v>87353</v>
       </c>
       <c r="K15" t="n">
-        <v>12051</v>
+        <v>29992</v>
       </c>
       <c r="L15" t="n">
-        <v>24.02</v>
+        <v>5.91</v>
       </c>
       <c r="M15" t="n">
-        <v>26.16</v>
+        <v>7.76</v>
       </c>
       <c r="N15" t="n">
-        <v>9.1</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.98</v>
+        <v>0.87</v>
       </c>
       <c r="D16" t="n">
-        <v>1.542</v>
+        <v>1.08</v>
       </c>
       <c r="E16" t="n">
-        <v>-22.8</v>
+        <v>1.9</v>
       </c>
       <c r="F16" t="n">
-        <v>-6</v>
+        <v>6.5</v>
       </c>
       <c r="G16" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1273,50 +1273,50 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>276426</v>
+        <v>22647</v>
       </c>
       <c r="K16" t="n">
-        <v>71380</v>
+        <v>12051</v>
       </c>
       <c r="L16" t="n">
-        <v>61.34</v>
+        <v>24.02</v>
       </c>
       <c r="M16" t="n">
-        <v>88.12</v>
+        <v>26.16</v>
       </c>
       <c r="N16" t="n">
-        <v>33.7</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.88</v>
+        <v>0.98</v>
       </c>
       <c r="D17" t="n">
-        <v>0.783</v>
+        <v>1.542</v>
       </c>
       <c r="E17" t="n">
-        <v>49</v>
+        <v>-22.8</v>
       </c>
       <c r="F17" t="n">
-        <v>29.5</v>
+        <v>-6</v>
       </c>
       <c r="G17" t="n">
-        <v>10</v>
+        <v>10.8</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1325,19 +1325,19 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>276426</v>
       </c>
       <c r="K17" t="n">
-        <v>11482</v>
+        <v>71380</v>
       </c>
       <c r="L17" t="n">
-        <v>9.52</v>
+        <v>61.34</v>
       </c>
       <c r="M17" t="n">
-        <v>7.03</v>
+        <v>88.12</v>
       </c>
       <c r="N17" t="n">
-        <v>-39</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="18">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -523,16 +523,16 @@
         <v>0.34</v>
       </c>
       <c r="D2" t="n">
-        <v>1.158</v>
+        <v>1.165</v>
       </c>
       <c r="E2" t="n">
-        <v>76.8</v>
+        <v>75.7</v>
       </c>
       <c r="F2" t="n">
-        <v>94.40000000000001</v>
+        <v>94</v>
       </c>
       <c r="G2" t="n">
-        <v>112</v>
+        <v>112.3</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -551,19 +551,19 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>64.93000000000001</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>77.86</v>
+        <v>77.95</v>
       </c>
       <c r="N2" t="n">
-        <v>35.2</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="D3" t="n">
-        <v>1.147</v>
+        <v>1.112</v>
       </c>
       <c r="E3" t="n">
-        <v>31.1</v>
+        <v>12.2</v>
       </c>
       <c r="F3" t="n">
-        <v>46.2</v>
+        <v>37.6</v>
       </c>
       <c r="G3" t="n">
-        <v>61.2</v>
+        <v>63</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -597,25 +597,25 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>181776</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>16.77</v>
+        <v>5.99</v>
       </c>
       <c r="M3" t="n">
-        <v>20.61</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>30</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -624,19 +624,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="D4" t="n">
-        <v>0.924</v>
+        <v>1.311</v>
       </c>
       <c r="E4" t="n">
-        <v>102.4</v>
+        <v>6.5</v>
       </c>
       <c r="F4" t="n">
-        <v>81.59999999999999</v>
+        <v>34.4</v>
       </c>
       <c r="G4" t="n">
-        <v>60.9</v>
+        <v>62.4</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>127839</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>10.81</v>
+        <v>13.62</v>
       </c>
       <c r="M4" t="n">
-        <v>8.59</v>
+        <v>20.77</v>
       </c>
       <c r="N4" t="n">
-        <v>-41.5</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="5">
@@ -783,16 +783,16 @@
         <v>0.74</v>
       </c>
       <c r="D7" t="n">
-        <v>1.143</v>
+        <v>1.137</v>
       </c>
       <c r="E7" t="n">
-        <v>10.9</v>
+        <v>11.3</v>
       </c>
       <c r="F7" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="G7" t="n">
-        <v>35.2</v>
+        <v>34.6</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -805,19 +805,19 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>54299</v>
+        <v>43759</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>15.64</v>
+        <v>15.69</v>
       </c>
       <c r="M7" t="n">
-        <v>19.06</v>
+        <v>18.98</v>
       </c>
       <c r="N7" t="n">
-        <v>24.2</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="8">
@@ -1135,7 +1135,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1144,23 +1144,23 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
       <c r="D14" t="n">
-        <v>0.802</v>
+        <v>1.318</v>
       </c>
       <c r="E14" t="n">
-        <v>46.3</v>
+        <v>-15.2</v>
       </c>
       <c r="F14" t="n">
-        <v>29</v>
+        <v>-1.9</v>
       </c>
       <c r="G14" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1169,25 +1169,25 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>87353</v>
       </c>
       <c r="K14" t="n">
-        <v>2688</v>
+        <v>29992</v>
       </c>
       <c r="L14" t="n">
-        <v>9.35</v>
+        <v>5.91</v>
       </c>
       <c r="M14" t="n">
-        <v>7.13</v>
+        <v>7.76</v>
       </c>
       <c r="N14" t="n">
-        <v>-34.7</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1196,23 +1196,23 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="D15" t="n">
-        <v>1.318</v>
+        <v>1.078</v>
       </c>
       <c r="E15" t="n">
-        <v>-15.2</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.9</v>
+        <v>6.5</v>
       </c>
       <c r="G15" t="n">
-        <v>11.4</v>
+        <v>10.9</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1221,50 +1221,50 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>87353</v>
+        <v>22511</v>
       </c>
       <c r="K15" t="n">
-        <v>29992</v>
+        <v>12137</v>
       </c>
       <c r="L15" t="n">
-        <v>5.91</v>
+        <v>24.05</v>
       </c>
       <c r="M15" t="n">
-        <v>7.76</v>
+        <v>26.15</v>
       </c>
       <c r="N15" t="n">
-        <v>26.6</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.87</v>
+        <v>0.98</v>
       </c>
       <c r="D16" t="n">
-        <v>1.08</v>
+        <v>1.542</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9</v>
+        <v>-22.8</v>
       </c>
       <c r="F16" t="n">
-        <v>6.5</v>
+        <v>-6</v>
       </c>
       <c r="G16" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1273,50 +1273,50 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>22647</v>
+        <v>276426</v>
       </c>
       <c r="K16" t="n">
-        <v>12051</v>
+        <v>71380</v>
       </c>
       <c r="L16" t="n">
-        <v>24.02</v>
+        <v>61.34</v>
       </c>
       <c r="M16" t="n">
-        <v>26.16</v>
+        <v>88.12</v>
       </c>
       <c r="N16" t="n">
-        <v>9.1</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.98</v>
+        <v>0.88</v>
       </c>
       <c r="D17" t="n">
-        <v>1.542</v>
+        <v>0.773</v>
       </c>
       <c r="E17" t="n">
-        <v>-22.8</v>
+        <v>51.3</v>
       </c>
       <c r="F17" t="n">
-        <v>-6</v>
+        <v>30.8</v>
       </c>
       <c r="G17" t="n">
-        <v>10.8</v>
+        <v>10.4</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1325,19 +1325,19 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>276426</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>71380</v>
+        <v>4340</v>
       </c>
       <c r="L17" t="n">
-        <v>61.34</v>
+        <v>9.67</v>
       </c>
       <c r="M17" t="n">
-        <v>88.12</v>
+        <v>7.05</v>
       </c>
       <c r="N17" t="n">
-        <v>33.7</v>
+        <v>-41</v>
       </c>
     </row>
     <row r="18">
@@ -1407,16 +1407,16 @@
         <v>1.09</v>
       </c>
       <c r="D19" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="E19" t="n">
-        <v>-15.5</v>
+        <v>-18.3</v>
       </c>
       <c r="F19" t="n">
-        <v>-7.5</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1429,19 +1429,19 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>423096</v>
+        <v>459855</v>
       </c>
       <c r="K19" t="n">
-        <v>212406</v>
+        <v>208430</v>
       </c>
       <c r="L19" t="n">
-        <v>14.92</v>
+        <v>14.42</v>
       </c>
       <c r="M19" t="n">
-        <v>17.75</v>
+        <v>17.8</v>
       </c>
       <c r="N19" t="n">
-        <v>16</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="20">
@@ -1511,16 +1511,16 @@
         <v>1.2</v>
       </c>
       <c r="D21" t="n">
-        <v>1.146</v>
+        <v>1.197</v>
       </c>
       <c r="E21" t="n">
-        <v>-18.9</v>
+        <v>-22.5</v>
       </c>
       <c r="F21" t="n">
-        <v>-11.9</v>
+        <v>-13.4</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.9</v>
+        <v>-4.4</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>339908</v>
+        <v>366009</v>
       </c>
       <c r="K21" t="n">
-        <v>227971</v>
+        <v>222394</v>
       </c>
       <c r="L21" t="n">
-        <v>28.82</v>
+        <v>27.53</v>
       </c>
       <c r="M21" t="n">
-        <v>33.78</v>
+        <v>33.95</v>
       </c>
       <c r="N21" t="n">
-        <v>14</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="22">
@@ -1563,16 +1563,16 @@
         <v>1.21</v>
       </c>
       <c r="D22" t="n">
-        <v>1.151</v>
+        <v>1.193</v>
       </c>
       <c r="E22" t="n">
-        <v>-20.6</v>
+        <v>-23.5</v>
       </c>
       <c r="F22" t="n">
-        <v>-13.8</v>
+        <v>-15.1</v>
       </c>
       <c r="G22" t="n">
-        <v>-7.1</v>
+        <v>-6.6</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>304990</v>
+        <v>326486</v>
       </c>
       <c r="K22" t="n">
-        <v>212429</v>
+        <v>211006</v>
       </c>
       <c r="L22" t="n">
-        <v>39.59</v>
+        <v>38.18</v>
       </c>
       <c r="M22" t="n">
-        <v>46.36</v>
+        <v>46.56</v>
       </c>
       <c r="N22" t="n">
-        <v>13.6</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="23">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -523,16 +523,16 @@
         <v>0.34</v>
       </c>
       <c r="D2" t="n">
-        <v>1.165</v>
+        <v>1.127</v>
       </c>
       <c r="E2" t="n">
-        <v>75.7</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>94</v>
+        <v>97.8</v>
       </c>
       <c r="G2" t="n">
-        <v>112.3</v>
+        <v>112.5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -551,13 +551,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>64.54000000000001</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>77.95</v>
+        <v>75.98</v>
       </c>
       <c r="N2" t="n">
-        <v>36.5</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="3">
@@ -575,16 +575,16 @@
         <v>0.75</v>
       </c>
       <c r="D3" t="n">
-        <v>1.112</v>
+        <v>0.918</v>
       </c>
       <c r="E3" t="n">
-        <v>12.2</v>
+        <v>107.4</v>
       </c>
       <c r="F3" t="n">
-        <v>37.6</v>
+        <v>84.5</v>
       </c>
       <c r="G3" t="n">
-        <v>63</v>
+        <v>61.7</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>181776</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>5.99</v>
+        <v>10.81</v>
       </c>
       <c r="M3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="N3" t="n">
-        <v>50.7</v>
+        <v>-45.8</v>
       </c>
     </row>
     <row r="4">
@@ -627,16 +627,16 @@
         <v>0.67</v>
       </c>
       <c r="D4" t="n">
-        <v>1.311</v>
+        <v>1.121</v>
       </c>
       <c r="E4" t="n">
-        <v>6.5</v>
+        <v>35.6</v>
       </c>
       <c r="F4" t="n">
-        <v>34.4</v>
+        <v>48.2</v>
       </c>
       <c r="G4" t="n">
-        <v>62.4</v>
+        <v>60.9</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>127839</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>13.62</v>
+        <v>17.26</v>
       </c>
       <c r="M4" t="n">
-        <v>20.77</v>
+        <v>20.48</v>
       </c>
       <c r="N4" t="n">
-        <v>55.9</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="5">
@@ -679,16 +679,16 @@
         <v>0.9</v>
       </c>
       <c r="D5" t="n">
-        <v>0.949</v>
+        <v>0.951</v>
       </c>
       <c r="E5" t="n">
-        <v>73.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="F5" t="n">
-        <v>61.8</v>
+        <v>61</v>
       </c>
       <c r="G5" t="n">
-        <v>50.3</v>
+        <v>50</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         <v>35.91</v>
       </c>
       <c r="M5" t="n">
-        <v>31.13</v>
+        <v>31.3</v>
       </c>
       <c r="N5" t="n">
-        <v>-23</v>
+        <v>-22.1</v>
       </c>
     </row>
     <row r="6">
@@ -731,16 +731,16 @@
         <v>0.7</v>
       </c>
       <c r="D6" t="n">
-        <v>1.315</v>
+        <v>1.267</v>
       </c>
       <c r="E6" t="n">
-        <v>10.2</v>
+        <v>14.1</v>
       </c>
       <c r="F6" t="n">
-        <v>24.3</v>
+        <v>26.5</v>
       </c>
       <c r="G6" t="n">
-        <v>38.4</v>
+        <v>38.8</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>23127</v>
+        <v>10829</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -762,10 +762,10 @@
         <v>79.98999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>100.43</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>28.2</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="7">
@@ -783,16 +783,16 @@
         <v>0.74</v>
       </c>
       <c r="D7" t="n">
-        <v>1.137</v>
+        <v>1.116</v>
       </c>
       <c r="E7" t="n">
-        <v>11.3</v>
+        <v>14.1</v>
       </c>
       <c r="F7" t="n">
-        <v>23</v>
+        <v>24.2</v>
       </c>
       <c r="G7" t="n">
-        <v>34.6</v>
+        <v>34.3</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -805,19 +805,19 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>43759</v>
+        <v>41510</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>15.69</v>
+        <v>16.07</v>
       </c>
       <c r="M7" t="n">
-        <v>18.98</v>
+        <v>18.91</v>
       </c>
       <c r="N7" t="n">
-        <v>23.3</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="8">
@@ -835,16 +835,16 @@
         <v>0.76</v>
       </c>
       <c r="D8" t="n">
-        <v>1.26</v>
+        <v>1.203</v>
       </c>
       <c r="E8" t="n">
-        <v>17.1</v>
+        <v>20.6</v>
       </c>
       <c r="F8" t="n">
-        <v>24.8</v>
+        <v>26.8</v>
       </c>
       <c r="G8" t="n">
-        <v>32.4</v>
+        <v>33</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -866,10 +866,10 @@
         <v>79.59</v>
       </c>
       <c r="M8" t="n">
-        <v>90.05</v>
+        <v>87.75</v>
       </c>
       <c r="N8" t="n">
-        <v>15.4</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="9">
@@ -887,13 +887,13 @@
         <v>0.75</v>
       </c>
       <c r="D9" t="n">
-        <v>1.243</v>
+        <v>1.241</v>
       </c>
       <c r="E9" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="F9" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="G9" t="n">
         <v>31.9</v>
@@ -918,16 +918,16 @@
         <v>40.59</v>
       </c>
       <c r="M9" t="n">
-        <v>49.84</v>
+        <v>49.78</v>
       </c>
       <c r="N9" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -936,16 +936,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="D10" t="n">
-        <v>1.259</v>
+        <v>1.174</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2</v>
+        <v>3.8</v>
       </c>
       <c r="F10" t="n">
-        <v>12.4</v>
+        <v>14.3</v>
       </c>
       <c r="G10" t="n">
         <v>24.7</v>
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>25023</v>
+        <v>48537</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>7012</v>
       </c>
       <c r="L10" t="n">
-        <v>15.15</v>
+        <v>27.32</v>
       </c>
       <c r="M10" t="n">
-        <v>18.85</v>
+        <v>32.81</v>
       </c>
       <c r="N10" t="n">
-        <v>24.5</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -988,23 +988,23 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.83</v>
+        <v>0.75</v>
       </c>
       <c r="D11" t="n">
-        <v>1.19</v>
+        <v>1.331</v>
       </c>
       <c r="E11" t="n">
-        <v>1.9</v>
+        <v>-5.3</v>
       </c>
       <c r="F11" t="n">
-        <v>13.1</v>
+        <v>9.5</v>
       </c>
       <c r="G11" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>52226</v>
+        <v>32539</v>
       </c>
       <c r="K11" t="n">
-        <v>6749</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>27.32</v>
+        <v>15.15</v>
       </c>
       <c r="M11" t="n">
-        <v>33.34</v>
+        <v>19.88</v>
       </c>
       <c r="N11" t="n">
-        <v>22.5</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="12">
@@ -1043,16 +1043,16 @@
         <v>0.85</v>
       </c>
       <c r="D12" t="n">
-        <v>2.164</v>
+        <v>2.144</v>
       </c>
       <c r="E12" t="n">
-        <v>-52.5</v>
+        <v>-51.9</v>
       </c>
       <c r="F12" t="n">
-        <v>-15.2</v>
+        <v>-14.8</v>
       </c>
       <c r="G12" t="n">
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1065,19 +1065,19 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>404139</v>
+        <v>397445</v>
       </c>
       <c r="K12" t="n">
-        <v>607</v>
+        <v>836</v>
       </c>
       <c r="L12" t="n">
         <v>2.78</v>
       </c>
       <c r="M12" t="n">
-        <v>7.15</v>
+        <v>7.07</v>
       </c>
       <c r="N12" t="n">
-        <v>74.59999999999999</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="13">
@@ -1095,16 +1095,16 @@
         <v>0.82</v>
       </c>
       <c r="D13" t="n">
-        <v>1.085</v>
+        <v>1.094</v>
       </c>
       <c r="E13" t="n">
-        <v>6.9</v>
+        <v>5.8</v>
       </c>
       <c r="F13" t="n">
-        <v>11.9</v>
+        <v>11.3</v>
       </c>
       <c r="G13" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1117,19 +1117,19 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>15583</v>
+        <v>16572</v>
       </c>
       <c r="K13" t="n">
-        <v>5007</v>
+        <v>4948</v>
       </c>
       <c r="L13" t="n">
         <v>26.07</v>
       </c>
       <c r="M13" t="n">
-        <v>28.54</v>
+        <v>28.79</v>
       </c>
       <c r="N13" t="n">
-        <v>10.1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
@@ -1147,16 +1147,16 @@
         <v>0.95</v>
       </c>
       <c r="D14" t="n">
-        <v>1.318</v>
+        <v>1.301</v>
       </c>
       <c r="E14" t="n">
-        <v>-15.2</v>
+        <v>-13.8</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.9</v>
+        <v>-1.1</v>
       </c>
       <c r="G14" t="n">
-        <v>11.4</v>
+        <v>11.7</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1169,50 +1169,50 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>87353</v>
+        <v>83976</v>
       </c>
       <c r="K14" t="n">
-        <v>29992</v>
+        <v>29748</v>
       </c>
       <c r="L14" t="n">
         <v>5.91</v>
       </c>
       <c r="M14" t="n">
-        <v>7.76</v>
+        <v>7.66</v>
       </c>
       <c r="N14" t="n">
-        <v>26.6</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.87</v>
+        <v>0.98</v>
       </c>
       <c r="D15" t="n">
-        <v>1.078</v>
+        <v>1.509</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>-21.2</v>
       </c>
       <c r="F15" t="n">
-        <v>6.5</v>
+        <v>-5</v>
       </c>
       <c r="G15" t="n">
-        <v>10.9</v>
+        <v>11.2</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1221,50 +1221,50 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>22511</v>
+        <v>262650</v>
       </c>
       <c r="K15" t="n">
-        <v>12137</v>
+        <v>70065</v>
       </c>
       <c r="L15" t="n">
-        <v>24.05</v>
+        <v>61.34</v>
       </c>
       <c r="M15" t="n">
-        <v>26.15</v>
+        <v>86.5</v>
       </c>
       <c r="N15" t="n">
-        <v>8.9</v>
+        <v>32.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.98</v>
+        <v>0.87</v>
       </c>
       <c r="D16" t="n">
-        <v>1.542</v>
+        <v>1.109</v>
       </c>
       <c r="E16" t="n">
-        <v>-22.8</v>
+        <v>-1.4</v>
       </c>
       <c r="F16" t="n">
-        <v>-6</v>
+        <v>4.6</v>
       </c>
       <c r="G16" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1273,19 +1273,19 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>276426</v>
+        <v>26698</v>
       </c>
       <c r="K16" t="n">
-        <v>71380</v>
+        <v>12255</v>
       </c>
       <c r="L16" t="n">
-        <v>61.34</v>
+        <v>24.05</v>
       </c>
       <c r="M16" t="n">
-        <v>88.12</v>
+        <v>26.97</v>
       </c>
       <c r="N16" t="n">
-        <v>33.7</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="17">
@@ -1303,13 +1303,13 @@
         <v>0.88</v>
       </c>
       <c r="D17" t="n">
-        <v>0.773</v>
+        <v>0.771</v>
       </c>
       <c r="E17" t="n">
-        <v>51.3</v>
+        <v>52</v>
       </c>
       <c r="F17" t="n">
-        <v>30.8</v>
+        <v>31.2</v>
       </c>
       <c r="G17" t="n">
         <v>10.4</v>
@@ -1328,16 +1328,16 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>4340</v>
+        <v>4329</v>
       </c>
       <c r="L17" t="n">
         <v>9.67</v>
       </c>
       <c r="M17" t="n">
-        <v>7.05</v>
+        <v>7.02</v>
       </c>
       <c r="N17" t="n">
-        <v>-41</v>
+        <v>-41.6</v>
       </c>
     </row>
     <row r="18">
@@ -1355,16 +1355,16 @@
         <v>0.62</v>
       </c>
       <c r="D18" t="n">
-        <v>0.884</v>
+        <v>0.915</v>
       </c>
       <c r="E18" t="n">
-        <v>16.9</v>
+        <v>13.6</v>
       </c>
       <c r="F18" t="n">
-        <v>11.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>2713</v>
+        <v>5949</v>
       </c>
       <c r="K18" t="n">
-        <v>14534</v>
+        <v>14626</v>
       </c>
       <c r="L18" t="n">
         <v>20.43</v>
       </c>
       <c r="M18" t="n">
-        <v>18.52</v>
+        <v>19.03</v>
       </c>
       <c r="N18" t="n">
-        <v>-10.9</v>
+        <v>-7.8</v>
       </c>
     </row>
     <row r="19">
@@ -1407,16 +1407,16 @@
         <v>1.09</v>
       </c>
       <c r="D19" t="n">
-        <v>1.26</v>
+        <v>1.174</v>
       </c>
       <c r="E19" t="n">
-        <v>-18.3</v>
+        <v>-12.7</v>
       </c>
       <c r="F19" t="n">
-        <v>-8.699999999999999</v>
+        <v>-5.8</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1429,19 +1429,19 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>459855</v>
+        <v>379413</v>
       </c>
       <c r="K19" t="n">
-        <v>208430</v>
+        <v>204295</v>
       </c>
       <c r="L19" t="n">
-        <v>14.42</v>
+        <v>14.92</v>
       </c>
       <c r="M19" t="n">
-        <v>17.8</v>
+        <v>17.27</v>
       </c>
       <c r="N19" t="n">
-        <v>19.1</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="20">
@@ -1459,13 +1459,13 @@
         <v>1.04</v>
       </c>
       <c r="D20" t="n">
-        <v>1.142</v>
+        <v>1.144</v>
       </c>
       <c r="E20" t="n">
-        <v>-19.3</v>
+        <v>-19.6</v>
       </c>
       <c r="F20" t="n">
-        <v>-11.8</v>
+        <v>-12</v>
       </c>
       <c r="G20" t="n">
         <v>-4.3</v>
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>155119</v>
+        <v>157594</v>
       </c>
       <c r="K20" t="n">
-        <v>49153</v>
+        <v>49535</v>
       </c>
       <c r="L20" t="n">
         <v>2.11</v>
       </c>
       <c r="M20" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="N20" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="21">
@@ -1511,16 +1511,16 @@
         <v>1.2</v>
       </c>
       <c r="D21" t="n">
-        <v>1.197</v>
+        <v>1.145</v>
       </c>
       <c r="E21" t="n">
-        <v>-22.5</v>
+        <v>-18.7</v>
       </c>
       <c r="F21" t="n">
-        <v>-13.4</v>
+        <v>-11.8</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.4</v>
+        <v>-4.9</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>366009</v>
+        <v>338039</v>
       </c>
       <c r="K21" t="n">
-        <v>222394</v>
+        <v>227490</v>
       </c>
       <c r="L21" t="n">
-        <v>27.53</v>
+        <v>28.82</v>
       </c>
       <c r="M21" t="n">
-        <v>33.95</v>
+        <v>33.72</v>
       </c>
       <c r="N21" t="n">
-        <v>18.1</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="22">
@@ -1563,16 +1563,16 @@
         <v>1.21</v>
       </c>
       <c r="D22" t="n">
-        <v>1.193</v>
+        <v>1.13</v>
       </c>
       <c r="E22" t="n">
-        <v>-23.5</v>
+        <v>-19</v>
       </c>
       <c r="F22" t="n">
-        <v>-15.1</v>
+        <v>-13</v>
       </c>
       <c r="G22" t="n">
-        <v>-6.6</v>
+        <v>-7.1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>326486</v>
+        <v>292039</v>
       </c>
       <c r="K22" t="n">
-        <v>211006</v>
+        <v>211357</v>
       </c>
       <c r="L22" t="n">
-        <v>38.18</v>
+        <v>40.17</v>
       </c>
       <c r="M22" t="n">
-        <v>46.56</v>
+        <v>46.09</v>
       </c>
       <c r="N22" t="n">
-        <v>16.8</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="23">
@@ -1615,16 +1615,16 @@
         <v>1.37</v>
       </c>
       <c r="D23" t="n">
-        <v>0.871</v>
+        <v>0.869</v>
       </c>
       <c r="E23" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.9</v>
+        <v>-6.5</v>
       </c>
       <c r="G23" t="n">
-        <v>-17.8</v>
+        <v>-17.7</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1637,19 +1637,19 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>134259</v>
+        <v>124006</v>
       </c>
       <c r="K23" t="n">
-        <v>457099</v>
+        <v>453302</v>
       </c>
       <c r="L23" t="n">
         <v>30.67</v>
       </c>
       <c r="M23" t="n">
-        <v>24.24</v>
+        <v>24.11</v>
       </c>
       <c r="N23" t="n">
-        <v>-21.8</v>
+        <v>-22.4</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -1095,16 +1095,16 @@
         <v>0.82</v>
       </c>
       <c r="D13" t="n">
-        <v>1.094</v>
+        <v>1.019</v>
       </c>
       <c r="E13" t="n">
-        <v>5.8</v>
+        <v>15.1</v>
       </c>
       <c r="F13" t="n">
-        <v>11.3</v>
+        <v>16.4</v>
       </c>
       <c r="G13" t="n">
-        <v>16.9</v>
+        <v>17.6</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1117,25 +1117,25 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>16572</v>
+        <v>7455</v>
       </c>
       <c r="K13" t="n">
-        <v>4948</v>
+        <v>4797</v>
       </c>
       <c r="L13" t="n">
-        <v>26.07</v>
+        <v>28.37</v>
       </c>
       <c r="M13" t="n">
-        <v>28.79</v>
+        <v>28.98</v>
       </c>
       <c r="N13" t="n">
-        <v>11</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1144,23 +1144,23 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
       <c r="D14" t="n">
-        <v>1.301</v>
+        <v>0.801</v>
       </c>
       <c r="E14" t="n">
-        <v>-13.8</v>
+        <v>58.8</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1</v>
+        <v>35.7</v>
       </c>
       <c r="G14" t="n">
-        <v>11.7</v>
+        <v>12.6</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1169,46 +1169,46 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>83976</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>29748</v>
+        <v>2379</v>
       </c>
       <c r="L14" t="n">
-        <v>5.91</v>
+        <v>10.1</v>
       </c>
       <c r="M14" t="n">
-        <v>7.66</v>
+        <v>7.16</v>
       </c>
       <c r="N14" t="n">
-        <v>25.5</v>
+        <v>-46.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="D15" t="n">
-        <v>1.509</v>
+        <v>1.301</v>
       </c>
       <c r="E15" t="n">
-        <v>-21.2</v>
+        <v>-13.8</v>
       </c>
       <c r="F15" t="n">
-        <v>-5</v>
+        <v>-1.1</v>
       </c>
       <c r="G15" t="n">
-        <v>11.2</v>
+        <v>11.7</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1221,50 +1221,50 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>262650</v>
+        <v>83976</v>
       </c>
       <c r="K15" t="n">
-        <v>70065</v>
+        <v>29748</v>
       </c>
       <c r="L15" t="n">
-        <v>61.34</v>
+        <v>5.91</v>
       </c>
       <c r="M15" t="n">
-        <v>86.5</v>
+        <v>7.66</v>
       </c>
       <c r="N15" t="n">
-        <v>32.3</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.87</v>
+        <v>0.98</v>
       </c>
       <c r="D16" t="n">
-        <v>1.109</v>
+        <v>1.509</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.4</v>
+        <v>-21.2</v>
       </c>
       <c r="F16" t="n">
-        <v>4.6</v>
+        <v>-5</v>
       </c>
       <c r="G16" t="n">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1273,25 +1273,25 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>26698</v>
+        <v>262650</v>
       </c>
       <c r="K16" t="n">
-        <v>12255</v>
+        <v>70065</v>
       </c>
       <c r="L16" t="n">
-        <v>24.05</v>
+        <v>61.34</v>
       </c>
       <c r="M16" t="n">
-        <v>26.97</v>
+        <v>86.5</v>
       </c>
       <c r="N16" t="n">
-        <v>11.9</v>
+        <v>32.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1300,23 +1300,23 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="D17" t="n">
-        <v>0.771</v>
+        <v>1.109</v>
       </c>
       <c r="E17" t="n">
-        <v>52</v>
+        <v>-1.4</v>
       </c>
       <c r="F17" t="n">
-        <v>31.2</v>
+        <v>4.6</v>
       </c>
       <c r="G17" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1325,19 +1325,19 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>26698</v>
       </c>
       <c r="K17" t="n">
-        <v>4329</v>
+        <v>12255</v>
       </c>
       <c r="L17" t="n">
-        <v>9.67</v>
+        <v>24.05</v>
       </c>
       <c r="M17" t="n">
-        <v>7.02</v>
+        <v>26.97</v>
       </c>
       <c r="N17" t="n">
-        <v>-41.6</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="18">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -1147,13 +1147,13 @@
         <v>0.88</v>
       </c>
       <c r="D14" t="n">
-        <v>0.801</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>58.8</v>
+        <v>56.8</v>
       </c>
       <c r="F14" t="n">
-        <v>35.7</v>
+        <v>34.7</v>
       </c>
       <c r="G14" t="n">
         <v>12.6</v>
@@ -1172,16 +1172,16 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>2379</v>
+        <v>2502</v>
       </c>
       <c r="L14" t="n">
-        <v>10.1</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M14" t="n">
         <v>7.16</v>
       </c>
       <c r="N14" t="n">
-        <v>-46.1</v>
+        <v>-44.2</v>
       </c>
     </row>
     <row r="15">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -627,16 +627,16 @@
         <v>0.67</v>
       </c>
       <c r="D4" t="n">
-        <v>1.121</v>
+        <v>1.125</v>
       </c>
       <c r="E4" t="n">
-        <v>35.6</v>
+        <v>34.8</v>
       </c>
       <c r="F4" t="n">
-        <v>48.2</v>
+        <v>47.8</v>
       </c>
       <c r="G4" t="n">
-        <v>60.9</v>
+        <v>60.8</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -655,13 +655,13 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>17.26</v>
+        <v>17.16</v>
       </c>
       <c r="M4" t="n">
-        <v>20.48</v>
+        <v>20.47</v>
       </c>
       <c r="N4" t="n">
-        <v>25.3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -1407,16 +1407,16 @@
         <v>1.09</v>
       </c>
       <c r="D19" t="n">
-        <v>1.174</v>
+        <v>1.113</v>
       </c>
       <c r="E19" t="n">
-        <v>-12.7</v>
+        <v>-7.7</v>
       </c>
       <c r="F19" t="n">
-        <v>-5.8</v>
+        <v>-2.9</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1429,19 +1429,19 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>379413</v>
+        <v>310818</v>
       </c>
       <c r="K19" t="n">
-        <v>204295</v>
+        <v>194121</v>
       </c>
       <c r="L19" t="n">
-        <v>14.92</v>
+        <v>15.77</v>
       </c>
       <c r="M19" t="n">
-        <v>17.27</v>
+        <v>17.41</v>
       </c>
       <c r="N19" t="n">
-        <v>13.8</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="20">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -523,16 +523,16 @@
         <v>0.34</v>
       </c>
       <c r="D2" t="n">
-        <v>1.127</v>
+        <v>1.118</v>
       </c>
       <c r="E2" t="n">
-        <v>83.09999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="F2" t="n">
-        <v>97.8</v>
+        <v>99</v>
       </c>
       <c r="G2" t="n">
-        <v>112.5</v>
+        <v>112.8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -554,10 +554,10 @@
         <v>65.48999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>75.98</v>
+        <v>75.25</v>
       </c>
       <c r="N2" t="n">
-        <v>29.3</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="3">
@@ -627,16 +627,16 @@
         <v>0.67</v>
       </c>
       <c r="D4" t="n">
-        <v>1.125</v>
+        <v>1.117</v>
       </c>
       <c r="E4" t="n">
-        <v>34.8</v>
+        <v>36.4</v>
       </c>
       <c r="F4" t="n">
-        <v>47.8</v>
+        <v>48.7</v>
       </c>
       <c r="G4" t="n">
-        <v>60.8</v>
+        <v>61.1</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -658,10 +658,10 @@
         <v>17.16</v>
       </c>
       <c r="M4" t="n">
-        <v>20.47</v>
+        <v>20.26</v>
       </c>
       <c r="N4" t="n">
-        <v>26</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="5">
@@ -679,16 +679,16 @@
         <v>0.9</v>
       </c>
       <c r="D5" t="n">
-        <v>0.951</v>
+        <v>0.956</v>
       </c>
       <c r="E5" t="n">
-        <v>72</v>
+        <v>68.2</v>
       </c>
       <c r="F5" t="n">
-        <v>61</v>
+        <v>58.6</v>
       </c>
       <c r="G5" t="n">
-        <v>50</v>
+        <v>48.9</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         <v>35.91</v>
       </c>
       <c r="M5" t="n">
-        <v>31.3</v>
+        <v>31.8</v>
       </c>
       <c r="N5" t="n">
-        <v>-22.1</v>
+        <v>-19.2</v>
       </c>
     </row>
     <row r="6">
@@ -731,16 +731,16 @@
         <v>0.7</v>
       </c>
       <c r="D6" t="n">
-        <v>1.267</v>
+        <v>1.373</v>
       </c>
       <c r="E6" t="n">
-        <v>14.1</v>
+        <v>5.8</v>
       </c>
       <c r="F6" t="n">
-        <v>26.5</v>
+        <v>21.8</v>
       </c>
       <c r="G6" t="n">
-        <v>38.8</v>
+        <v>37.9</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>10829</v>
+        <v>38043</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -762,10 +762,10 @@
         <v>79.98999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>97.31999999999999</v>
+        <v>104.22</v>
       </c>
       <c r="N6" t="n">
-        <v>24.7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
@@ -783,16 +783,16 @@
         <v>0.74</v>
       </c>
       <c r="D7" t="n">
-        <v>1.116</v>
+        <v>1.112</v>
       </c>
       <c r="E7" t="n">
-        <v>14.1</v>
+        <v>14.9</v>
       </c>
       <c r="F7" t="n">
-        <v>24.2</v>
+        <v>24.6</v>
       </c>
       <c r="G7" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>41510</v>
+        <v>39378</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -814,16 +814,16 @@
         <v>16.07</v>
       </c>
       <c r="M7" t="n">
-        <v>18.91</v>
+        <v>18.8</v>
       </c>
       <c r="N7" t="n">
-        <v>20.1</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -832,19 +832,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="D8" t="n">
-        <v>1.203</v>
+        <v>1.237</v>
       </c>
       <c r="E8" t="n">
-        <v>20.6</v>
+        <v>8</v>
       </c>
       <c r="F8" t="n">
-        <v>26.8</v>
+        <v>20</v>
       </c>
       <c r="G8" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -863,19 +863,19 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>79.59</v>
+        <v>40.59</v>
       </c>
       <c r="M8" t="n">
-        <v>87.75</v>
+        <v>49.64</v>
       </c>
       <c r="N8" t="n">
-        <v>12.4</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -884,19 +884,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="D9" t="n">
-        <v>1.241</v>
+        <v>1.341</v>
       </c>
       <c r="E9" t="n">
-        <v>7.6</v>
+        <v>12.4</v>
       </c>
       <c r="F9" t="n">
-        <v>19.7</v>
+        <v>22.1</v>
       </c>
       <c r="G9" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -909,19 +909,19 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>10261</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>40.59</v>
+        <v>79.59</v>
       </c>
       <c r="M9" t="n">
-        <v>49.78</v>
+        <v>93.28</v>
       </c>
       <c r="N9" t="n">
-        <v>24.4</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="10">
@@ -939,16 +939,16 @@
         <v>0.83</v>
       </c>
       <c r="D10" t="n">
-        <v>1.174</v>
+        <v>1.165</v>
       </c>
       <c r="E10" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="F10" t="n">
-        <v>14.3</v>
+        <v>14.9</v>
       </c>
       <c r="G10" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>48537</v>
+        <v>46693</v>
       </c>
       <c r="K10" t="n">
-        <v>7012</v>
+        <v>7144</v>
       </c>
       <c r="L10" t="n">
         <v>27.32</v>
       </c>
       <c r="M10" t="n">
-        <v>32.81</v>
+        <v>32.55</v>
       </c>
       <c r="N10" t="n">
-        <v>20.9</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="11">
@@ -1043,16 +1043,16 @@
         <v>0.85</v>
       </c>
       <c r="D12" t="n">
-        <v>2.144</v>
+        <v>1.977</v>
       </c>
       <c r="E12" t="n">
-        <v>-51.9</v>
+        <v>-39.9</v>
       </c>
       <c r="F12" t="n">
-        <v>-14.8</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>22.3</v>
+        <v>21.2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1065,19 +1065,19 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>397445</v>
+        <v>360646</v>
       </c>
       <c r="K12" t="n">
-        <v>836</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2.78</v>
+        <v>3.33</v>
       </c>
       <c r="M12" t="n">
-        <v>7.07</v>
+        <v>6.71</v>
       </c>
       <c r="N12" t="n">
-        <v>74.2</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="13">
@@ -1095,16 +1095,16 @@
         <v>0.82</v>
       </c>
       <c r="D13" t="n">
-        <v>1.019</v>
+        <v>1.03</v>
       </c>
       <c r="E13" t="n">
-        <v>15.1</v>
+        <v>13.6</v>
       </c>
       <c r="F13" t="n">
-        <v>16.4</v>
+        <v>15.5</v>
       </c>
       <c r="G13" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1117,19 +1117,19 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>7455</v>
+        <v>8819</v>
       </c>
       <c r="K13" t="n">
-        <v>4797</v>
+        <v>4716</v>
       </c>
       <c r="L13" t="n">
         <v>28.37</v>
       </c>
       <c r="M13" t="n">
-        <v>28.98</v>
+        <v>29.33</v>
       </c>
       <c r="N13" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="14">
@@ -1147,16 +1147,16 @@
         <v>0.88</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.804</v>
       </c>
       <c r="E14" t="n">
-        <v>56.8</v>
+        <v>58</v>
       </c>
       <c r="F14" t="n">
-        <v>34.7</v>
+        <v>35.3</v>
       </c>
       <c r="G14" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1172,16 +1172,16 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>2502</v>
+        <v>2497</v>
       </c>
       <c r="L14" t="n">
         <v>9.970000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>7.16</v>
+        <v>7.11</v>
       </c>
       <c r="N14" t="n">
-        <v>-44.2</v>
+        <v>-45.3</v>
       </c>
     </row>
     <row r="15">
@@ -1199,16 +1199,16 @@
         <v>0.95</v>
       </c>
       <c r="D15" t="n">
-        <v>1.301</v>
+        <v>1.266</v>
       </c>
       <c r="E15" t="n">
-        <v>-13.8</v>
+        <v>-11</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1</v>
+        <v>0.7</v>
       </c>
       <c r="G15" t="n">
-        <v>11.7</v>
+        <v>12.4</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>83976</v>
+        <v>77221</v>
       </c>
       <c r="K15" t="n">
-        <v>29748</v>
+        <v>29262</v>
       </c>
       <c r="L15" t="n">
         <v>5.91</v>
       </c>
       <c r="M15" t="n">
-        <v>7.66</v>
+        <v>7.46</v>
       </c>
       <c r="N15" t="n">
-        <v>25.5</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="16">
@@ -1251,16 +1251,16 @@
         <v>0.98</v>
       </c>
       <c r="D16" t="n">
-        <v>1.509</v>
+        <v>1.485</v>
       </c>
       <c r="E16" t="n">
-        <v>-21.2</v>
+        <v>-19.9</v>
       </c>
       <c r="F16" t="n">
-        <v>-5</v>
+        <v>-4.2</v>
       </c>
       <c r="G16" t="n">
-        <v>11.2</v>
+        <v>11.4</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1273,19 +1273,19 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>262650</v>
+        <v>252764</v>
       </c>
       <c r="K16" t="n">
-        <v>70065</v>
+        <v>69122</v>
       </c>
       <c r="L16" t="n">
         <v>61.34</v>
       </c>
       <c r="M16" t="n">
-        <v>86.5</v>
+        <v>85.33</v>
       </c>
       <c r="N16" t="n">
-        <v>32.3</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="17">
@@ -1303,16 +1303,16 @@
         <v>0.87</v>
       </c>
       <c r="D17" t="n">
-        <v>1.109</v>
+        <v>1.124</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.4</v>
+        <v>-2.9</v>
       </c>
       <c r="F17" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="G17" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1325,19 +1325,19 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>26698</v>
+        <v>28690</v>
       </c>
       <c r="K17" t="n">
-        <v>12255</v>
+        <v>12311</v>
       </c>
       <c r="L17" t="n">
         <v>24.05</v>
       </c>
       <c r="M17" t="n">
-        <v>26.97</v>
+        <v>27.36</v>
       </c>
       <c r="N17" t="n">
-        <v>11.9</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="18">
@@ -1355,16 +1355,16 @@
         <v>0.62</v>
       </c>
       <c r="D18" t="n">
-        <v>0.915</v>
+        <v>0.889</v>
       </c>
       <c r="E18" t="n">
-        <v>13.6</v>
+        <v>16.3</v>
       </c>
       <c r="F18" t="n">
-        <v>9.699999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="G18" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>5949</v>
+        <v>3273</v>
       </c>
       <c r="K18" t="n">
-        <v>14626</v>
+        <v>14550</v>
       </c>
       <c r="L18" t="n">
         <v>20.43</v>
       </c>
       <c r="M18" t="n">
-        <v>19.03</v>
+        <v>18.61</v>
       </c>
       <c r="N18" t="n">
-        <v>-7.8</v>
+        <v>-10.3</v>
       </c>
     </row>
     <row r="19">
@@ -1407,20 +1407,20 @@
         <v>1.09</v>
       </c>
       <c r="D19" t="n">
-        <v>1.113</v>
+        <v>1.074</v>
       </c>
       <c r="E19" t="n">
-        <v>-7.7</v>
+        <v>-3.9</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.9</v>
+        <v>-0.6</v>
       </c>
       <c r="G19" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1429,19 +1429,19 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>310818</v>
+        <v>260972</v>
       </c>
       <c r="K19" t="n">
-        <v>194121</v>
+        <v>184868</v>
       </c>
       <c r="L19" t="n">
         <v>15.77</v>
       </c>
       <c r="M19" t="n">
-        <v>17.41</v>
+        <v>16.84</v>
       </c>
       <c r="N19" t="n">
-        <v>9.6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="20">
@@ -1459,16 +1459,16 @@
         <v>1.04</v>
       </c>
       <c r="D20" t="n">
-        <v>1.144</v>
+        <v>1.125</v>
       </c>
       <c r="E20" t="n">
-        <v>-19.6</v>
+        <v>-17.4</v>
       </c>
       <c r="F20" t="n">
-        <v>-12</v>
+        <v>-10.6</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.3</v>
+        <v>-3.8</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>157594</v>
+        <v>140273</v>
       </c>
       <c r="K20" t="n">
-        <v>49535</v>
+        <v>46859</v>
       </c>
       <c r="L20" t="n">
         <v>2.11</v>
       </c>
       <c r="M20" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="N20" t="n">
-        <v>15.3</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="21">
@@ -1511,16 +1511,16 @@
         <v>1.2</v>
       </c>
       <c r="D21" t="n">
-        <v>1.145</v>
+        <v>1.123</v>
       </c>
       <c r="E21" t="n">
-        <v>-18.7</v>
+        <v>-16.5</v>
       </c>
       <c r="F21" t="n">
-        <v>-11.8</v>
+        <v>-10.4</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.9</v>
+        <v>-4.4</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>338039</v>
+        <v>316083</v>
       </c>
       <c r="K21" t="n">
-        <v>227490</v>
+        <v>221830</v>
       </c>
       <c r="L21" t="n">
         <v>28.82</v>
       </c>
       <c r="M21" t="n">
-        <v>33.72</v>
+        <v>33</v>
       </c>
       <c r="N21" t="n">
-        <v>13.8</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="22">
@@ -1563,16 +1563,16 @@
         <v>1.21</v>
       </c>
       <c r="D22" t="n">
-        <v>1.13</v>
+        <v>1.139</v>
       </c>
       <c r="E22" t="n">
-        <v>-19</v>
+        <v>-19.9</v>
       </c>
       <c r="F22" t="n">
-        <v>-13</v>
+        <v>-13.5</v>
       </c>
       <c r="G22" t="n">
-        <v>-7.1</v>
+        <v>-7.2</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>292039</v>
+        <v>299354</v>
       </c>
       <c r="K22" t="n">
-        <v>211357</v>
+        <v>213281</v>
       </c>
       <c r="L22" t="n">
         <v>40.17</v>
       </c>
       <c r="M22" t="n">
-        <v>46.09</v>
+        <v>46.49</v>
       </c>
       <c r="N22" t="n">
-        <v>11.9</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="23">
@@ -1615,20 +1615,20 @@
         <v>1.37</v>
       </c>
       <c r="D23" t="n">
-        <v>0.869</v>
+        <v>0.852</v>
       </c>
       <c r="E23" t="n">
-        <v>4.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.5</v>
+        <v>-3.9</v>
       </c>
       <c r="G23" t="n">
-        <v>-17.7</v>
+        <v>-17.1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1637,19 +1637,19 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>124006</v>
+        <v>57631</v>
       </c>
       <c r="K23" t="n">
-        <v>453302</v>
+        <v>428722</v>
       </c>
       <c r="L23" t="n">
         <v>30.67</v>
       </c>
       <c r="M23" t="n">
-        <v>24.11</v>
+        <v>23.28</v>
       </c>
       <c r="N23" t="n">
-        <v>-22.4</v>
+        <v>-26.4</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -991,20 +991,20 @@
         <v>0.75</v>
       </c>
       <c r="D11" t="n">
-        <v>1.331</v>
+        <v>1.23</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.3</v>
+        <v>5.2</v>
       </c>
       <c r="F11" t="n">
-        <v>9.5</v>
+        <v>14.9</v>
       </c>
       <c r="G11" t="n">
-        <v>24.3</v>
+        <v>24.6</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>32539</v>
+        <v>18010</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>15.15</v>
+        <v>16.83</v>
       </c>
       <c r="M11" t="n">
-        <v>19.88</v>
+        <v>19.93</v>
       </c>
       <c r="N11" t="n">
-        <v>29.6</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="12">
@@ -1147,16 +1147,16 @@
         <v>0.88</v>
       </c>
       <c r="D14" t="n">
-        <v>0.804</v>
+        <v>0.821</v>
       </c>
       <c r="E14" t="n">
-        <v>58</v>
+        <v>53.4</v>
       </c>
       <c r="F14" t="n">
-        <v>35.3</v>
+        <v>33.1</v>
       </c>
       <c r="G14" t="n">
-        <v>12.7</v>
+        <v>12.9</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1172,16 +1172,16 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>2497</v>
+        <v>2750</v>
       </c>
       <c r="L14" t="n">
-        <v>9.970000000000001</v>
+        <v>9.68</v>
       </c>
       <c r="M14" t="n">
-        <v>7.11</v>
+        <v>7.12</v>
       </c>
       <c r="N14" t="n">
-        <v>-45.3</v>
+        <v>-40.5</v>
       </c>
     </row>
     <row r="15">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -575,16 +575,16 @@
         <v>0.75</v>
       </c>
       <c r="D3" t="n">
-        <v>0.918</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>107.4</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>84.5</v>
+        <v>79.3</v>
       </c>
       <c r="G3" t="n">
-        <v>61.7</v>
+        <v>62</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -603,13 +603,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>10.81</v>
+        <v>10.24</v>
       </c>
       <c r="M3" t="n">
-        <v>8.42</v>
+        <v>8.44</v>
       </c>
       <c r="N3" t="n">
-        <v>-45.8</v>
+        <v>-34.5</v>
       </c>
     </row>
     <row r="4">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -1563,13 +1563,13 @@
         <v>1.21</v>
       </c>
       <c r="D22" t="n">
-        <v>1.139</v>
+        <v>1.144</v>
       </c>
       <c r="E22" t="n">
-        <v>-19.9</v>
+        <v>-20.2</v>
       </c>
       <c r="F22" t="n">
-        <v>-13.5</v>
+        <v>-13.7</v>
       </c>
       <c r="G22" t="n">
         <v>-7.2</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>299354</v>
+        <v>301800</v>
       </c>
       <c r="K22" t="n">
-        <v>213281</v>
+        <v>212954</v>
       </c>
       <c r="L22" t="n">
-        <v>40.17</v>
+        <v>40.02</v>
       </c>
       <c r="M22" t="n">
-        <v>46.49</v>
+        <v>46.53</v>
       </c>
       <c r="N22" t="n">
-        <v>12.6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -1199,16 +1199,16 @@
         <v>0.95</v>
       </c>
       <c r="D15" t="n">
-        <v>1.266</v>
+        <v>1.215</v>
       </c>
       <c r="E15" t="n">
-        <v>-11</v>
+        <v>-6.2</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="G15" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>77221</v>
+        <v>67495</v>
       </c>
       <c r="K15" t="n">
-        <v>29262</v>
+        <v>28712</v>
       </c>
       <c r="L15" t="n">
-        <v>5.91</v>
+        <v>6.23</v>
       </c>
       <c r="M15" t="n">
-        <v>7.46</v>
+        <v>7.47</v>
       </c>
       <c r="N15" t="n">
-        <v>23.3</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -731,20 +731,20 @@
         <v>0.7</v>
       </c>
       <c r="D6" t="n">
-        <v>1.373</v>
+        <v>1.435</v>
       </c>
       <c r="E6" t="n">
-        <v>5.8</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>21.8</v>
+        <v>19.7</v>
       </c>
       <c r="G6" t="n">
-        <v>37.9</v>
+        <v>37.4</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -753,19 +753,19 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>38043</v>
+        <v>53301</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>79.98999999999999</v>
+        <v>77.13</v>
       </c>
       <c r="M6" t="n">
-        <v>104.22</v>
+        <v>103.88</v>
       </c>
       <c r="N6" t="n">
-        <v>32</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="7">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -939,20 +939,20 @@
         <v>0.83</v>
       </c>
       <c r="D10" t="n">
-        <v>1.165</v>
+        <v>1.029</v>
       </c>
       <c r="E10" t="n">
-        <v>4.8</v>
+        <v>22.4</v>
       </c>
       <c r="F10" t="n">
-        <v>14.9</v>
+        <v>24.2</v>
       </c>
       <c r="G10" t="n">
-        <v>24.9</v>
+        <v>26</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>46693</v>
+        <v>12733</v>
       </c>
       <c r="K10" t="n">
-        <v>7144</v>
+        <v>5434</v>
       </c>
       <c r="L10" t="n">
-        <v>27.32</v>
+        <v>31.9</v>
       </c>
       <c r="M10" t="n">
-        <v>32.55</v>
+        <v>32.82</v>
       </c>
       <c r="N10" t="n">
-        <v>20.1</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="11">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -575,16 +575,16 @@
         <v>0.75</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>96.59999999999999</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>79.3</v>
+        <v>80.2</v>
       </c>
       <c r="G3" t="n">
-        <v>62</v>
+        <v>62.3</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -606,10 +606,10 @@
         <v>10.24</v>
       </c>
       <c r="M3" t="n">
-        <v>8.44</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-34.5</v>
+        <v>-35.8</v>
       </c>
     </row>
     <row r="4">
@@ -627,16 +627,16 @@
         <v>0.67</v>
       </c>
       <c r="D4" t="n">
-        <v>1.117</v>
+        <v>1.112</v>
       </c>
       <c r="E4" t="n">
-        <v>36.4</v>
+        <v>37.4</v>
       </c>
       <c r="F4" t="n">
-        <v>48.7</v>
+        <v>49.3</v>
       </c>
       <c r="G4" t="n">
-        <v>61.1</v>
+        <v>61.2</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -658,10 +658,10 @@
         <v>17.16</v>
       </c>
       <c r="M4" t="n">
-        <v>20.26</v>
+        <v>20.13</v>
       </c>
       <c r="N4" t="n">
-        <v>24.7</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="5">
@@ -679,16 +679,16 @@
         <v>0.9</v>
       </c>
       <c r="D5" t="n">
-        <v>0.956</v>
+        <v>0.96</v>
       </c>
       <c r="E5" t="n">
-        <v>68.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>58.6</v>
+        <v>56.9</v>
       </c>
       <c r="G5" t="n">
-        <v>48.9</v>
+        <v>48.3</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         <v>35.91</v>
       </c>
       <c r="M5" t="n">
-        <v>31.8</v>
+        <v>32.14</v>
       </c>
       <c r="N5" t="n">
-        <v>-19.2</v>
+        <v>-17.4</v>
       </c>
     </row>
     <row r="6">
@@ -731,20 +731,20 @@
         <v>0.7</v>
       </c>
       <c r="D6" t="n">
-        <v>1.435</v>
+        <v>1.311</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>10.9</v>
       </c>
       <c r="F6" t="n">
-        <v>19.7</v>
+        <v>24.7</v>
       </c>
       <c r="G6" t="n">
-        <v>37.4</v>
+        <v>38.5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>53301</v>
+        <v>21075</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -762,10 +762,10 @@
         <v>77.13</v>
       </c>
       <c r="M6" t="n">
-        <v>103.88</v>
+        <v>96.28</v>
       </c>
       <c r="N6" t="n">
-        <v>35.4</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="7">
@@ -783,16 +783,16 @@
         <v>0.74</v>
       </c>
       <c r="D7" t="n">
-        <v>1.112</v>
+        <v>1.115</v>
       </c>
       <c r="E7" t="n">
-        <v>14.9</v>
+        <v>14.4</v>
       </c>
       <c r="F7" t="n">
-        <v>24.6</v>
+        <v>24.3</v>
       </c>
       <c r="G7" t="n">
-        <v>34.4</v>
+        <v>34.3</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>39378</v>
+        <v>40799</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -814,16 +814,16 @@
         <v>16.07</v>
       </c>
       <c r="M7" t="n">
-        <v>18.8</v>
+        <v>18.87</v>
       </c>
       <c r="N7" t="n">
-        <v>19.5</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -832,19 +832,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="D8" t="n">
-        <v>1.237</v>
+        <v>1.155</v>
       </c>
       <c r="E8" t="n">
-        <v>8</v>
+        <v>23.7</v>
       </c>
       <c r="F8" t="n">
-        <v>20</v>
+        <v>28.6</v>
       </c>
       <c r="G8" t="n">
-        <v>32</v>
+        <v>33.4</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -863,19 +863,19 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>40.59</v>
+        <v>79.59</v>
       </c>
       <c r="M8" t="n">
-        <v>49.64</v>
+        <v>85.83</v>
       </c>
       <c r="N8" t="n">
-        <v>24.1</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -884,19 +884,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="D9" t="n">
-        <v>1.341</v>
+        <v>1.242</v>
       </c>
       <c r="E9" t="n">
-        <v>12.4</v>
+        <v>7.4</v>
       </c>
       <c r="F9" t="n">
-        <v>22.1</v>
+        <v>19.7</v>
       </c>
       <c r="G9" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -909,19 +909,19 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>10261</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>79.59</v>
+        <v>40.59</v>
       </c>
       <c r="M9" t="n">
-        <v>93.28</v>
+        <v>49.83</v>
       </c>
       <c r="N9" t="n">
-        <v>19.3</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="10">
@@ -939,16 +939,16 @@
         <v>0.83</v>
       </c>
       <c r="D10" t="n">
-        <v>1.029</v>
+        <v>1.035</v>
       </c>
       <c r="E10" t="n">
-        <v>22.4</v>
+        <v>21.5</v>
       </c>
       <c r="F10" t="n">
-        <v>24.2</v>
+        <v>23.7</v>
       </c>
       <c r="G10" t="n">
-        <v>26</v>
+        <v>25.8</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>12733</v>
+        <v>14186</v>
       </c>
       <c r="K10" t="n">
-        <v>5434</v>
+        <v>5336</v>
       </c>
       <c r="L10" t="n">
         <v>31.9</v>
       </c>
       <c r="M10" t="n">
-        <v>32.82</v>
+        <v>33.02</v>
       </c>
       <c r="N10" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="11">
@@ -991,16 +991,16 @@
         <v>0.75</v>
       </c>
       <c r="D11" t="n">
-        <v>1.23</v>
+        <v>1.078</v>
       </c>
       <c r="E11" t="n">
-        <v>5.2</v>
+        <v>18.1</v>
       </c>
       <c r="F11" t="n">
-        <v>14.9</v>
+        <v>21.8</v>
       </c>
       <c r="G11" t="n">
-        <v>24.6</v>
+        <v>25.5</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>18010</v>
+        <v>1481</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1022,10 +1022,10 @@
         <v>16.83</v>
       </c>
       <c r="M11" t="n">
-        <v>19.93</v>
+        <v>17.89</v>
       </c>
       <c r="N11" t="n">
-        <v>19.4</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="12">
@@ -1043,13 +1043,13 @@
         <v>0.85</v>
       </c>
       <c r="D12" t="n">
-        <v>1.977</v>
+        <v>1.983</v>
       </c>
       <c r="E12" t="n">
-        <v>-39.9</v>
+        <v>-40.1</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.5</v>
       </c>
       <c r="G12" t="n">
         <v>21.2</v>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>360646</v>
+        <v>362899</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1074,10 +1074,10 @@
         <v>3.33</v>
       </c>
       <c r="M12" t="n">
-        <v>6.71</v>
+        <v>6.74</v>
       </c>
       <c r="N12" t="n">
-        <v>61.1</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="13">
@@ -1095,13 +1095,13 @@
         <v>0.82</v>
       </c>
       <c r="D13" t="n">
-        <v>1.03</v>
+        <v>1.025</v>
       </c>
       <c r="E13" t="n">
-        <v>13.6</v>
+        <v>14.3</v>
       </c>
       <c r="F13" t="n">
-        <v>15.5</v>
+        <v>15.9</v>
       </c>
       <c r="G13" t="n">
         <v>17.5</v>
@@ -1117,19 +1117,19 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>8819</v>
+        <v>8164</v>
       </c>
       <c r="K13" t="n">
-        <v>4716</v>
+        <v>4755</v>
       </c>
       <c r="L13" t="n">
         <v>28.37</v>
       </c>
       <c r="M13" t="n">
-        <v>29.33</v>
+        <v>29.16</v>
       </c>
       <c r="N13" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="14">
@@ -1199,16 +1199,16 @@
         <v>0.95</v>
       </c>
       <c r="D15" t="n">
-        <v>1.215</v>
+        <v>1.202</v>
       </c>
       <c r="E15" t="n">
-        <v>-6.2</v>
+        <v>-5.1</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="G15" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>67495</v>
+        <v>65013</v>
       </c>
       <c r="K15" t="n">
-        <v>28712</v>
+        <v>28534</v>
       </c>
       <c r="L15" t="n">
         <v>6.23</v>
       </c>
       <c r="M15" t="n">
-        <v>7.47</v>
+        <v>7.39</v>
       </c>
       <c r="N15" t="n">
-        <v>18.7</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="16">
@@ -1251,16 +1251,16 @@
         <v>0.98</v>
       </c>
       <c r="D16" t="n">
-        <v>1.485</v>
+        <v>1.508</v>
       </c>
       <c r="E16" t="n">
-        <v>-19.9</v>
+        <v>-21.1</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.2</v>
+        <v>-5</v>
       </c>
       <c r="G16" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1273,19 +1273,19 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>252764</v>
+        <v>262407</v>
       </c>
       <c r="K16" t="n">
-        <v>69122</v>
+        <v>70042</v>
       </c>
       <c r="L16" t="n">
         <v>61.34</v>
       </c>
       <c r="M16" t="n">
-        <v>85.33</v>
+        <v>86.47</v>
       </c>
       <c r="N16" t="n">
-        <v>31.3</v>
+        <v>32.3</v>
       </c>
     </row>
     <row r="17">
@@ -1303,13 +1303,13 @@
         <v>0.87</v>
       </c>
       <c r="D17" t="n">
-        <v>1.124</v>
+        <v>1.119</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.9</v>
+        <v>-2.5</v>
       </c>
       <c r="F17" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
         <v>10.4</v>
@@ -1325,19 +1325,19 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>28690</v>
+        <v>28077</v>
       </c>
       <c r="K17" t="n">
-        <v>12311</v>
+        <v>12294</v>
       </c>
       <c r="L17" t="n">
         <v>24.05</v>
       </c>
       <c r="M17" t="n">
-        <v>27.36</v>
+        <v>27.24</v>
       </c>
       <c r="N17" t="n">
-        <v>13.3</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="18">
@@ -1355,16 +1355,16 @@
         <v>0.62</v>
       </c>
       <c r="D18" t="n">
-        <v>0.889</v>
+        <v>0.928</v>
       </c>
       <c r="E18" t="n">
-        <v>16.3</v>
+        <v>12.2</v>
       </c>
       <c r="F18" t="n">
-        <v>11.2</v>
+        <v>8.9</v>
       </c>
       <c r="G18" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>3273</v>
+        <v>7318</v>
       </c>
       <c r="K18" t="n">
-        <v>14550</v>
+        <v>14664</v>
       </c>
       <c r="L18" t="n">
         <v>20.43</v>
       </c>
       <c r="M18" t="n">
-        <v>18.61</v>
+        <v>19.25</v>
       </c>
       <c r="N18" t="n">
-        <v>-10.3</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="19">
@@ -1407,16 +1407,16 @@
         <v>1.09</v>
       </c>
       <c r="D19" t="n">
-        <v>1.074</v>
+        <v>1.081</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.9</v>
+        <v>-4.6</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
       <c r="G19" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1429,19 +1429,19 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>260972</v>
+        <v>270502</v>
       </c>
       <c r="K19" t="n">
-        <v>184868</v>
+        <v>186637</v>
       </c>
       <c r="L19" t="n">
         <v>15.77</v>
       </c>
       <c r="M19" t="n">
-        <v>16.84</v>
+        <v>16.95</v>
       </c>
       <c r="N19" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="20">
@@ -1459,16 +1459,16 @@
         <v>1.04</v>
       </c>
       <c r="D20" t="n">
-        <v>1.125</v>
+        <v>1.088</v>
       </c>
       <c r="E20" t="n">
-        <v>-17.4</v>
+        <v>-13</v>
       </c>
       <c r="F20" t="n">
-        <v>-10.6</v>
+        <v>-7.9</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.8</v>
+        <v>-2.8</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>140273</v>
+        <v>108107</v>
       </c>
       <c r="K20" t="n">
-        <v>46859</v>
+        <v>41889</v>
       </c>
       <c r="L20" t="n">
         <v>2.11</v>
       </c>
       <c r="M20" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="N20" t="n">
-        <v>13.6</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="21">
@@ -1511,16 +1511,16 @@
         <v>1.2</v>
       </c>
       <c r="D21" t="n">
-        <v>1.123</v>
+        <v>1.128</v>
       </c>
       <c r="E21" t="n">
-        <v>-16.5</v>
+        <v>-16.9</v>
       </c>
       <c r="F21" t="n">
-        <v>-10.4</v>
+        <v>-10.7</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.4</v>
+        <v>-4.5</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>316083</v>
+        <v>320754</v>
       </c>
       <c r="K21" t="n">
-        <v>221830</v>
+        <v>223034</v>
       </c>
       <c r="L21" t="n">
         <v>28.82</v>
       </c>
       <c r="M21" t="n">
-        <v>33</v>
+        <v>33.15</v>
       </c>
       <c r="N21" t="n">
-        <v>12.1</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="22">
@@ -1563,16 +1563,16 @@
         <v>1.21</v>
       </c>
       <c r="D22" t="n">
-        <v>1.144</v>
+        <v>1.141</v>
       </c>
       <c r="E22" t="n">
-        <v>-20.2</v>
+        <v>-19.9</v>
       </c>
       <c r="F22" t="n">
-        <v>-13.7</v>
+        <v>-13.5</v>
       </c>
       <c r="G22" t="n">
-        <v>-7.2</v>
+        <v>-7.1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>301800</v>
+        <v>299265</v>
       </c>
       <c r="K22" t="n">
-        <v>212954</v>
+        <v>212288</v>
       </c>
       <c r="L22" t="n">
         <v>40.02</v>
       </c>
       <c r="M22" t="n">
-        <v>46.53</v>
+        <v>46.39</v>
       </c>
       <c r="N22" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="23">
@@ -1615,16 +1615,16 @@
         <v>1.37</v>
       </c>
       <c r="D23" t="n">
-        <v>0.852</v>
+        <v>0.86</v>
       </c>
       <c r="E23" t="n">
-        <v>9.300000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.9</v>
+        <v>-5.1</v>
       </c>
       <c r="G23" t="n">
-        <v>-17.1</v>
+        <v>-17.3</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1637,19 +1637,19 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>57631</v>
+        <v>87851</v>
       </c>
       <c r="K23" t="n">
-        <v>428722</v>
+        <v>439913</v>
       </c>
       <c r="L23" t="n">
         <v>30.67</v>
       </c>
       <c r="M23" t="n">
-        <v>23.28</v>
+        <v>23.66</v>
       </c>
       <c r="N23" t="n">
-        <v>-26.4</v>
+        <v>-24.5</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -526,13 +526,13 @@
         <v>1.118</v>
       </c>
       <c r="E2" t="n">
-        <v>85.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>99</v>
+        <v>95.5</v>
       </c>
       <c r="G2" t="n">
-        <v>112.8</v>
+        <v>109.2</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -551,13 +551,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>65.48999999999999</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>75.25</v>
+        <v>73.98</v>
       </c>
       <c r="N2" t="n">
-        <v>27.6</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="3">
@@ -771,28 +771,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="D7" t="n">
-        <v>1.115</v>
+        <v>1.155</v>
       </c>
       <c r="E7" t="n">
-        <v>14.4</v>
+        <v>23.7</v>
       </c>
       <c r="F7" t="n">
-        <v>24.3</v>
+        <v>28.6</v>
       </c>
       <c r="G7" t="n">
-        <v>34.3</v>
+        <v>33.4</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -805,25 +805,25 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>40799</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>16.07</v>
+        <v>79.59</v>
       </c>
       <c r="M7" t="n">
-        <v>18.87</v>
+        <v>85.83</v>
       </c>
       <c r="N7" t="n">
-        <v>19.9</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -832,19 +832,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="D8" t="n">
-        <v>1.155</v>
+        <v>1.242</v>
       </c>
       <c r="E8" t="n">
-        <v>23.7</v>
+        <v>7.4</v>
       </c>
       <c r="F8" t="n">
-        <v>28.6</v>
+        <v>19.7</v>
       </c>
       <c r="G8" t="n">
-        <v>33.4</v>
+        <v>31.9</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -863,40 +863,40 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>79.59</v>
+        <v>40.59</v>
       </c>
       <c r="M8" t="n">
-        <v>85.83</v>
+        <v>49.83</v>
       </c>
       <c r="N8" t="n">
-        <v>9.699999999999999</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="D9" t="n">
-        <v>1.242</v>
+        <v>1.115</v>
       </c>
       <c r="E9" t="n">
-        <v>7.4</v>
+        <v>10.7</v>
       </c>
       <c r="F9" t="n">
-        <v>19.7</v>
+        <v>20.5</v>
       </c>
       <c r="G9" t="n">
-        <v>31.9</v>
+        <v>30.3</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -909,19 +909,19 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>40799</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>40.59</v>
+        <v>15.56</v>
       </c>
       <c r="M9" t="n">
-        <v>49.83</v>
+        <v>18.31</v>
       </c>
       <c r="N9" t="n">
-        <v>24.4</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="10">
@@ -1239,32 +1239,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.98</v>
+        <v>0.87</v>
       </c>
       <c r="D16" t="n">
-        <v>1.508</v>
+        <v>1.119</v>
       </c>
       <c r="E16" t="n">
-        <v>-21.1</v>
+        <v>-2.5</v>
       </c>
       <c r="F16" t="n">
-        <v>-5</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1273,50 +1273,50 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>262407</v>
+        <v>28077</v>
       </c>
       <c r="K16" t="n">
-        <v>70042</v>
+        <v>12294</v>
       </c>
       <c r="L16" t="n">
-        <v>61.34</v>
+        <v>24.05</v>
       </c>
       <c r="M16" t="n">
-        <v>86.47</v>
+        <v>27.24</v>
       </c>
       <c r="N16" t="n">
-        <v>32.3</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.87</v>
+        <v>0.98</v>
       </c>
       <c r="D17" t="n">
-        <v>1.119</v>
+        <v>1.508</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.5</v>
+        <v>-22.6</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>-6.8</v>
       </c>
       <c r="G17" t="n">
-        <v>10.4</v>
+        <v>9.1</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1325,19 +1325,19 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>28077</v>
+        <v>262407</v>
       </c>
       <c r="K17" t="n">
-        <v>12294</v>
+        <v>70042</v>
       </c>
       <c r="L17" t="n">
-        <v>24.05</v>
+        <v>60.19</v>
       </c>
       <c r="M17" t="n">
-        <v>27.24</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>12.9</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="18">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -526,13 +526,13 @@
         <v>1.118</v>
       </c>
       <c r="E2" t="n">
-        <v>81.90000000000001</v>
+        <v>44</v>
       </c>
       <c r="F2" t="n">
-        <v>95.5</v>
+        <v>55.3</v>
       </c>
       <c r="G2" t="n">
-        <v>109.2</v>
+        <v>66.7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -551,19 +551,19 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>64.34999999999999</v>
+        <v>50.92</v>
       </c>
       <c r="M2" t="n">
-        <v>73.98</v>
+        <v>58.97</v>
       </c>
       <c r="N2" t="n">
-        <v>27.2</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="E3" t="n">
-        <v>98.09999999999999</v>
+        <v>54.5</v>
       </c>
       <c r="F3" t="n">
-        <v>80.2</v>
+        <v>46.1</v>
       </c>
       <c r="G3" t="n">
-        <v>62.3</v>
+        <v>37.8</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -603,19 +603,19 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>10.24</v>
+        <v>33.5</v>
       </c>
       <c r="M3" t="n">
-        <v>8.390000000000001</v>
+        <v>29.87</v>
       </c>
       <c r="N3" t="n">
-        <v>-35.8</v>
+        <v>-16.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -624,19 +624,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="D4" t="n">
-        <v>1.112</v>
+        <v>1.242</v>
       </c>
       <c r="E4" t="n">
-        <v>37.4</v>
+        <v>7.4</v>
       </c>
       <c r="F4" t="n">
-        <v>49.3</v>
+        <v>19.7</v>
       </c>
       <c r="G4" t="n">
-        <v>61.2</v>
+        <v>31.9</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -655,19 +655,19 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>17.16</v>
+        <v>40.59</v>
       </c>
       <c r="M4" t="n">
-        <v>20.13</v>
+        <v>49.83</v>
       </c>
       <c r="N4" t="n">
-        <v>23.8</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -676,23 +676,23 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="D5" t="n">
-        <v>0.96</v>
+        <v>1.311</v>
       </c>
       <c r="E5" t="n">
-        <v>65.59999999999999</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>56.9</v>
+        <v>14.7</v>
       </c>
       <c r="G5" t="n">
-        <v>48.3</v>
+        <v>27.5</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -701,25 +701,25 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>21075</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>35.91</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>32.14</v>
+        <v>88.64</v>
       </c>
       <c r="N5" t="n">
-        <v>-17.4</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -728,19 +728,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="D6" t="n">
-        <v>1.311</v>
+        <v>1.078</v>
       </c>
       <c r="E6" t="n">
-        <v>10.9</v>
+        <v>14.2</v>
       </c>
       <c r="F6" t="n">
-        <v>24.7</v>
+        <v>17.8</v>
       </c>
       <c r="G6" t="n">
-        <v>38.5</v>
+        <v>21.4</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -753,25 +753,25 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>21075</v>
+        <v>1481</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>77.13</v>
+        <v>16.28</v>
       </c>
       <c r="M6" t="n">
-        <v>96.28</v>
+        <v>17.3</v>
       </c>
       <c r="N6" t="n">
-        <v>27.5</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -780,19 +780,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="D7" t="n">
-        <v>1.155</v>
+        <v>1.025</v>
       </c>
       <c r="E7" t="n">
-        <v>23.7</v>
+        <v>13.6</v>
       </c>
       <c r="F7" t="n">
-        <v>28.6</v>
+        <v>15.2</v>
       </c>
       <c r="G7" t="n">
-        <v>33.4</v>
+        <v>16.8</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -805,25 +805,25 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>8259</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>4806</v>
       </c>
       <c r="L7" t="n">
-        <v>79.59</v>
+        <v>28.19</v>
       </c>
       <c r="M7" t="n">
-        <v>85.83</v>
+        <v>28.98</v>
       </c>
       <c r="N7" t="n">
-        <v>9.699999999999999</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -832,19 +832,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="D8" t="n">
-        <v>1.242</v>
+        <v>0.821</v>
       </c>
       <c r="E8" t="n">
-        <v>7.4</v>
+        <v>55.6</v>
       </c>
       <c r="F8" t="n">
-        <v>19.7</v>
+        <v>35.2</v>
       </c>
       <c r="G8" t="n">
-        <v>31.9</v>
+        <v>14.8</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -860,16 +860,16 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="L8" t="n">
-        <v>40.59</v>
+        <v>9.82</v>
       </c>
       <c r="M8" t="n">
-        <v>49.83</v>
+        <v>7.24</v>
       </c>
       <c r="N8" t="n">
-        <v>24.4</v>
+        <v>-40.9</v>
       </c>
     </row>
     <row r="9">
@@ -890,17 +890,17 @@
         <v>1.115</v>
       </c>
       <c r="E9" t="n">
-        <v>10.7</v>
+        <v>-5</v>
       </c>
       <c r="F9" t="n">
-        <v>20.5</v>
+        <v>4.1</v>
       </c>
       <c r="G9" t="n">
-        <v>30.3</v>
+        <v>13.1</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -915,13 +915,13 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>15.56</v>
+        <v>13.34</v>
       </c>
       <c r="M9" t="n">
-        <v>18.31</v>
+        <v>15.9</v>
       </c>
       <c r="N9" t="n">
-        <v>19.5</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="10">
@@ -942,13 +942,13 @@
         <v>1.035</v>
       </c>
       <c r="E10" t="n">
-        <v>21.5</v>
+        <v>9.1</v>
       </c>
       <c r="F10" t="n">
-        <v>23.7</v>
+        <v>11.1</v>
       </c>
       <c r="G10" t="n">
-        <v>25.8</v>
+        <v>13.1</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -967,19 +967,19 @@
         <v>5336</v>
       </c>
       <c r="L10" t="n">
-        <v>31.9</v>
+        <v>28.65</v>
       </c>
       <c r="M10" t="n">
-        <v>33.02</v>
+        <v>29.7</v>
       </c>
       <c r="N10" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="D11" t="n">
-        <v>1.078</v>
+        <v>1.155</v>
       </c>
       <c r="E11" t="n">
-        <v>18.1</v>
+        <v>5.1</v>
       </c>
       <c r="F11" t="n">
-        <v>21.8</v>
+        <v>8.9</v>
       </c>
       <c r="G11" t="n">
-        <v>25.5</v>
+        <v>12.8</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1013,25 +1013,25 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1481</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>16.83</v>
+        <v>67.61</v>
       </c>
       <c r="M11" t="n">
-        <v>17.89</v>
+        <v>72.55</v>
       </c>
       <c r="N11" t="n">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1040,23 +1040,23 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="D12" t="n">
-        <v>1.983</v>
+        <v>1.119</v>
       </c>
       <c r="E12" t="n">
-        <v>-40.1</v>
+        <v>-4.5</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.5</v>
+        <v>1.9</v>
       </c>
       <c r="G12" t="n">
-        <v>21.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1065,25 +1065,25 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>362899</v>
+        <v>30712</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>10604</v>
       </c>
       <c r="L12" t="n">
-        <v>3.33</v>
+        <v>23.56</v>
       </c>
       <c r="M12" t="n">
-        <v>6.74</v>
+        <v>26.68</v>
       </c>
       <c r="N12" t="n">
-        <v>61.3</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1092,19 +1092,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.82</v>
+        <v>0.62</v>
       </c>
       <c r="D13" t="n">
-        <v>1.025</v>
+        <v>0.928</v>
       </c>
       <c r="E13" t="n">
-        <v>14.3</v>
+        <v>11.7</v>
       </c>
       <c r="F13" t="n">
-        <v>15.9</v>
+        <v>8.5</v>
       </c>
       <c r="G13" t="n">
-        <v>17.5</v>
+        <v>5.2</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1117,25 +1117,25 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>8164</v>
+        <v>7396</v>
       </c>
       <c r="K13" t="n">
-        <v>4755</v>
+        <v>14819</v>
       </c>
       <c r="L13" t="n">
-        <v>28.37</v>
+        <v>20.34</v>
       </c>
       <c r="M13" t="n">
-        <v>29.16</v>
+        <v>19.16</v>
       </c>
       <c r="N13" t="n">
-        <v>3.2</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1144,50 +1144,50 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
       <c r="D14" t="n">
-        <v>0.821</v>
+        <v>1.202</v>
       </c>
       <c r="E14" t="n">
-        <v>53.4</v>
+        <v>-14.5</v>
       </c>
       <c r="F14" t="n">
-        <v>33.1</v>
+        <v>-6.3</v>
       </c>
       <c r="G14" t="n">
-        <v>12.9</v>
+        <v>2</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>65013</v>
       </c>
       <c r="K14" t="n">
-        <v>2750</v>
+        <v>28534</v>
       </c>
       <c r="L14" t="n">
-        <v>9.68</v>
+        <v>5.61</v>
       </c>
       <c r="M14" t="n">
-        <v>7.12</v>
+        <v>6.69</v>
       </c>
       <c r="N14" t="n">
-        <v>-40.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1196,19 +1196,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.95</v>
+        <v>0.67</v>
       </c>
       <c r="D15" t="n">
-        <v>1.202</v>
+        <v>1.112</v>
       </c>
       <c r="E15" t="n">
-        <v>-5.1</v>
+        <v>-19.4</v>
       </c>
       <c r="F15" t="n">
-        <v>3.8</v>
+        <v>-10.1</v>
       </c>
       <c r="G15" t="n">
-        <v>12.7</v>
+        <v>-0.9</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1217,29 +1217,29 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>65013</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>28534</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>6.23</v>
+        <v>10.07</v>
       </c>
       <c r="M15" t="n">
-        <v>7.39</v>
+        <v>12.38</v>
       </c>
       <c r="N15" t="n">
-        <v>17.8</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1248,71 +1248,71 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.87</v>
+        <v>1.04</v>
       </c>
       <c r="D16" t="n">
-        <v>1.119</v>
+        <v>1.088</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.5</v>
+        <v>-13</v>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>-7.9</v>
       </c>
       <c r="G16" t="n">
-        <v>10.4</v>
+        <v>-2.8</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>BUY (undervalued)</t>
-        </is>
-      </c>
       <c r="J16" t="n">
-        <v>28077</v>
+        <v>108107</v>
       </c>
       <c r="K16" t="n">
-        <v>12294</v>
+        <v>41889</v>
       </c>
       <c r="L16" t="n">
-        <v>24.05</v>
+        <v>2.11</v>
       </c>
       <c r="M16" t="n">
-        <v>27.24</v>
+        <v>2.35</v>
       </c>
       <c r="N16" t="n">
-        <v>12.9</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.98</v>
+        <v>0.85</v>
       </c>
       <c r="D17" t="n">
-        <v>1.508</v>
+        <v>1.983</v>
       </c>
       <c r="E17" t="n">
-        <v>-22.6</v>
+        <v>-59.5</v>
       </c>
       <c r="F17" t="n">
-        <v>-6.8</v>
+        <v>-35.4</v>
       </c>
       <c r="G17" t="n">
-        <v>9.1</v>
+        <v>-11.3</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1321,81 +1321,81 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>262407</v>
+        <v>362899</v>
       </c>
       <c r="K17" t="n">
-        <v>70042</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>60.19</v>
+        <v>2.25</v>
       </c>
       <c r="M17" t="n">
-        <v>84.84999999999999</v>
+        <v>4.93</v>
       </c>
       <c r="N17" t="n">
-        <v>31.7</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.62</v>
+        <v>0.98</v>
       </c>
       <c r="D18" t="n">
-        <v>0.928</v>
+        <v>1.508</v>
       </c>
       <c r="E18" t="n">
-        <v>12.2</v>
+        <v>-38.3</v>
       </c>
       <c r="F18" t="n">
-        <v>8.9</v>
+        <v>-25</v>
       </c>
       <c r="G18" t="n">
-        <v>5.7</v>
+        <v>-11.6</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>7318</v>
+        <v>262407</v>
       </c>
       <c r="K18" t="n">
-        <v>14664</v>
+        <v>70042</v>
       </c>
       <c r="L18" t="n">
-        <v>20.43</v>
+        <v>48</v>
       </c>
       <c r="M18" t="n">
-        <v>19.25</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>-6.5</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1404,19 +1404,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.09</v>
+        <v>1.37</v>
       </c>
       <c r="D19" t="n">
-        <v>1.081</v>
+        <v>0.86</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.6</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
-        <v>-1</v>
+        <v>-9.9</v>
       </c>
       <c r="G19" t="n">
-        <v>2.5</v>
+        <v>-21.7</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1425,29 +1425,29 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>270502</v>
+        <v>87851</v>
       </c>
       <c r="K19" t="n">
-        <v>186637</v>
+        <v>439913</v>
       </c>
       <c r="L19" t="n">
-        <v>15.77</v>
+        <v>29.19</v>
       </c>
       <c r="M19" t="n">
-        <v>16.95</v>
+        <v>22.41</v>
       </c>
       <c r="N19" t="n">
-        <v>7.1</v>
+        <v>-23.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1456,19 +1456,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="D20" t="n">
-        <v>1.088</v>
+        <v>1.081</v>
       </c>
       <c r="E20" t="n">
-        <v>-13</v>
+        <v>-31.3</v>
       </c>
       <c r="F20" t="n">
-        <v>-7.9</v>
+        <v>-28.6</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.8</v>
+        <v>-25.8</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1477,23 +1477,23 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>108107</v>
+        <v>270502</v>
       </c>
       <c r="K20" t="n">
-        <v>41889</v>
+        <v>186637</v>
       </c>
       <c r="L20" t="n">
-        <v>2.11</v>
+        <v>11.35</v>
       </c>
       <c r="M20" t="n">
-        <v>2.35</v>
+        <v>12.26</v>
       </c>
       <c r="N20" t="n">
-        <v>10.1</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="21">
@@ -1514,13 +1514,13 @@
         <v>1.128</v>
       </c>
       <c r="E21" t="n">
-        <v>-16.9</v>
+        <v>-47.6</v>
       </c>
       <c r="F21" t="n">
-        <v>-10.7</v>
+        <v>-42.8</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.5</v>
+        <v>-38</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -1539,13 +1539,13 @@
         <v>223034</v>
       </c>
       <c r="L21" t="n">
-        <v>28.82</v>
+        <v>18.17</v>
       </c>
       <c r="M21" t="n">
-        <v>33.15</v>
+        <v>21.53</v>
       </c>
       <c r="N21" t="n">
-        <v>12.5</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1566,13 +1566,13 @@
         <v>1.141</v>
       </c>
       <c r="E22" t="n">
-        <v>-19.9</v>
+        <v>-48.5</v>
       </c>
       <c r="F22" t="n">
-        <v>-13.5</v>
+        <v>-43.5</v>
       </c>
       <c r="G22" t="n">
-        <v>-7.1</v>
+        <v>-38.5</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1591,19 +1591,19 @@
         <v>212288</v>
       </c>
       <c r="L22" t="n">
-        <v>40.02</v>
+        <v>25.73</v>
       </c>
       <c r="M22" t="n">
-        <v>46.39</v>
+        <v>30.7</v>
       </c>
       <c r="N22" t="n">
-        <v>12.8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1612,23 +1612,23 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.37</v>
+        <v>0.75</v>
       </c>
       <c r="D23" t="n">
-        <v>0.86</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>7.2</v>
+        <v>-39.7</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.1</v>
+        <v>-53.5</v>
       </c>
       <c r="G23" t="n">
-        <v>-17.3</v>
+        <v>-67.40000000000001</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1637,19 +1637,19 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>87851</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>439913</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>30.67</v>
+        <v>3.12</v>
       </c>
       <c r="M23" t="n">
-        <v>23.66</v>
+        <v>1.69</v>
       </c>
       <c r="N23" t="n">
-        <v>-24.5</v>
+        <v>-27.7</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -523,16 +523,16 @@
         <v>0.34</v>
       </c>
       <c r="D2" t="n">
-        <v>1.118</v>
+        <v>1.164</v>
       </c>
       <c r="E2" t="n">
-        <v>44</v>
+        <v>36.3</v>
       </c>
       <c r="F2" t="n">
-        <v>55.3</v>
+        <v>51.2</v>
       </c>
       <c r="G2" t="n">
-        <v>66.7</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -554,10 +554,10 @@
         <v>50.92</v>
       </c>
       <c r="M2" t="n">
-        <v>58.97</v>
+        <v>62.06</v>
       </c>
       <c r="N2" t="n">
-        <v>22.8</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="3">
@@ -575,16 +575,16 @@
         <v>0.9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.96</v>
+        <v>0.959</v>
       </c>
       <c r="E3" t="n">
-        <v>54.5</v>
+        <v>55.1</v>
       </c>
       <c r="F3" t="n">
-        <v>46.1</v>
+        <v>46.5</v>
       </c>
       <c r="G3" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -606,10 +606,10 @@
         <v>33.5</v>
       </c>
       <c r="M3" t="n">
-        <v>29.87</v>
+        <v>29.78</v>
       </c>
       <c r="N3" t="n">
-        <v>-16.8</v>
+        <v>-17.2</v>
       </c>
     </row>
     <row r="4">
@@ -627,16 +627,16 @@
         <v>0.75</v>
       </c>
       <c r="D4" t="n">
-        <v>1.242</v>
+        <v>1.251</v>
       </c>
       <c r="E4" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="F4" t="n">
-        <v>19.7</v>
+        <v>19.1</v>
       </c>
       <c r="G4" t="n">
-        <v>31.9</v>
+        <v>31.6</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -658,10 +658,10 @@
         <v>40.59</v>
       </c>
       <c r="M4" t="n">
-        <v>49.83</v>
+        <v>50.17</v>
       </c>
       <c r="N4" t="n">
-        <v>24.4</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="5">
@@ -679,16 +679,16 @@
         <v>0.7</v>
       </c>
       <c r="D5" t="n">
-        <v>1.311</v>
+        <v>1.382</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>-2.9</v>
       </c>
       <c r="F5" t="n">
-        <v>14.7</v>
+        <v>12</v>
       </c>
       <c r="G5" t="n">
-        <v>27.5</v>
+        <v>26.9</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>21075</v>
+        <v>39551</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -710,10 +710,10 @@
         <v>70.90000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>88.64</v>
+        <v>92.67</v>
       </c>
       <c r="N5" t="n">
-        <v>25.5</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="6">
@@ -731,16 +731,16 @@
         <v>0.75</v>
       </c>
       <c r="D6" t="n">
-        <v>1.078</v>
+        <v>1.131</v>
       </c>
       <c r="E6" t="n">
-        <v>14.2</v>
+        <v>9.6</v>
       </c>
       <c r="F6" t="n">
-        <v>17.8</v>
+        <v>15.3</v>
       </c>
       <c r="G6" t="n">
-        <v>21.4</v>
+        <v>21.1</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1481</v>
+        <v>7407</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -762,10 +762,10 @@
         <v>16.28</v>
       </c>
       <c r="M6" t="n">
-        <v>17.3</v>
+        <v>17.99</v>
       </c>
       <c r="N6" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="7">
@@ -835,16 +835,16 @@
         <v>0.88</v>
       </c>
       <c r="D8" t="n">
-        <v>0.821</v>
+        <v>0.827</v>
       </c>
       <c r="E8" t="n">
-        <v>55.6</v>
+        <v>53.4</v>
       </c>
       <c r="F8" t="n">
-        <v>35.2</v>
+        <v>34</v>
       </c>
       <c r="G8" t="n">
-        <v>14.8</v>
+        <v>14.5</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -860,16 +860,16 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1100</v>
+        <v>1065</v>
       </c>
       <c r="L8" t="n">
         <v>9.82</v>
       </c>
       <c r="M8" t="n">
-        <v>7.24</v>
+        <v>7.33</v>
       </c>
       <c r="N8" t="n">
-        <v>-40.9</v>
+        <v>-38.9</v>
       </c>
     </row>
     <row r="9">
@@ -887,13 +887,13 @@
         <v>0.74</v>
       </c>
       <c r="D9" t="n">
-        <v>1.115</v>
+        <v>1.14</v>
       </c>
       <c r="E9" t="n">
-        <v>-5</v>
+        <v>-8.4</v>
       </c>
       <c r="F9" t="n">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="G9" t="n">
         <v>13.1</v>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>40799</v>
+        <v>52880</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -918,10 +918,10 @@
         <v>13.34</v>
       </c>
       <c r="M9" t="n">
-        <v>15.9</v>
+        <v>16.46</v>
       </c>
       <c r="N9" t="n">
-        <v>18.2</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="10">
@@ -939,20 +939,20 @@
         <v>0.83</v>
       </c>
       <c r="D10" t="n">
-        <v>1.035</v>
+        <v>1.082</v>
       </c>
       <c r="E10" t="n">
-        <v>9.1</v>
+        <v>3.4</v>
       </c>
       <c r="F10" t="n">
-        <v>11.1</v>
+        <v>7.9</v>
       </c>
       <c r="G10" t="n">
-        <v>13.1</v>
+        <v>12.4</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>14186</v>
+        <v>24799</v>
       </c>
       <c r="K10" t="n">
-        <v>5336</v>
+        <v>4587</v>
       </c>
       <c r="L10" t="n">
         <v>28.65</v>
       </c>
       <c r="M10" t="n">
-        <v>29.7</v>
+        <v>31.12</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="11">
@@ -991,20 +991,20 @@
         <v>0.76</v>
       </c>
       <c r="D11" t="n">
-        <v>1.155</v>
+        <v>1.249</v>
       </c>
       <c r="E11" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>8.9</v>
+        <v>5.9</v>
       </c>
       <c r="G11" t="n">
-        <v>12.8</v>
+        <v>11.7</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1022,10 +1022,10 @@
         <v>67.61</v>
       </c>
       <c r="M11" t="n">
-        <v>72.55</v>
+        <v>75.53</v>
       </c>
       <c r="N11" t="n">
-        <v>7.7</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="12">
@@ -1043,16 +1043,16 @@
         <v>0.87</v>
       </c>
       <c r="D12" t="n">
-        <v>1.119</v>
+        <v>1.113</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.5</v>
+        <v>-3.9</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="G12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1065,19 +1065,19 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>30712</v>
+        <v>29692</v>
       </c>
       <c r="K12" t="n">
-        <v>10604</v>
+        <v>10595</v>
       </c>
       <c r="L12" t="n">
         <v>23.56</v>
       </c>
       <c r="M12" t="n">
-        <v>26.68</v>
+        <v>26.52</v>
       </c>
       <c r="N12" t="n">
-        <v>12.7</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="13">
@@ -1095,16 +1095,16 @@
         <v>0.62</v>
       </c>
       <c r="D13" t="n">
-        <v>0.928</v>
+        <v>0.926</v>
       </c>
       <c r="E13" t="n">
-        <v>11.7</v>
+        <v>11.9</v>
       </c>
       <c r="F13" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="G13" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1117,19 +1117,19 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>7396</v>
+        <v>7207</v>
       </c>
       <c r="K13" t="n">
-        <v>14819</v>
+        <v>14814</v>
       </c>
       <c r="L13" t="n">
         <v>20.34</v>
       </c>
       <c r="M13" t="n">
-        <v>19.16</v>
+        <v>19.14</v>
       </c>
       <c r="N13" t="n">
-        <v>-6.5</v>
+        <v>-6.6</v>
       </c>
     </row>
     <row r="14">
@@ -1147,16 +1147,16 @@
         <v>0.95</v>
       </c>
       <c r="D14" t="n">
-        <v>1.202</v>
+        <v>1.276</v>
       </c>
       <c r="E14" t="n">
-        <v>-14.5</v>
+        <v>-20.1</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.3</v>
+        <v>-9.6</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1169,19 +1169,19 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>65013</v>
+        <v>79286</v>
       </c>
       <c r="K14" t="n">
-        <v>28534</v>
+        <v>29561</v>
       </c>
       <c r="L14" t="n">
         <v>5.61</v>
       </c>
       <c r="M14" t="n">
-        <v>6.69</v>
+        <v>7.09</v>
       </c>
       <c r="N14" t="n">
-        <v>16.5</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="15">
@@ -1199,16 +1199,16 @@
         <v>0.67</v>
       </c>
       <c r="D15" t="n">
-        <v>1.112</v>
+        <v>1.154</v>
       </c>
       <c r="E15" t="n">
-        <v>-19.4</v>
+        <v>-24.2</v>
       </c>
       <c r="F15" t="n">
-        <v>-10.1</v>
+        <v>-12.2</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.9</v>
+        <v>-0.3</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1230,10 +1230,10 @@
         <v>10.07</v>
       </c>
       <c r="M15" t="n">
-        <v>12.38</v>
+        <v>13.25</v>
       </c>
       <c r="N15" t="n">
-        <v>18.5</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="16">
@@ -1251,16 +1251,16 @@
         <v>1.04</v>
       </c>
       <c r="D16" t="n">
-        <v>1.088</v>
+        <v>1.094</v>
       </c>
       <c r="E16" t="n">
-        <v>-13</v>
+        <v>-13.7</v>
       </c>
       <c r="F16" t="n">
-        <v>-7.9</v>
+        <v>-8.4</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.8</v>
+        <v>-3</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1273,19 +1273,19 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>108107</v>
+        <v>113055</v>
       </c>
       <c r="K16" t="n">
-        <v>41889</v>
+        <v>42654</v>
       </c>
       <c r="L16" t="n">
         <v>2.11</v>
       </c>
       <c r="M16" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="N16" t="n">
-        <v>10.1</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="17">
@@ -1303,16 +1303,16 @@
         <v>0.85</v>
       </c>
       <c r="D17" t="n">
-        <v>1.983</v>
+        <v>2.06</v>
       </c>
       <c r="E17" t="n">
-        <v>-59.5</v>
+        <v>-61.2</v>
       </c>
       <c r="F17" t="n">
-        <v>-35.4</v>
+        <v>-36.3</v>
       </c>
       <c r="G17" t="n">
-        <v>-11.3</v>
+        <v>-11.5</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>362899</v>
+        <v>391067</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1334,10 +1334,10 @@
         <v>2.25</v>
       </c>
       <c r="M17" t="n">
-        <v>4.93</v>
+        <v>5.14</v>
       </c>
       <c r="N17" t="n">
-        <v>48.2</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="18">
@@ -1355,16 +1355,16 @@
         <v>0.98</v>
       </c>
       <c r="D18" t="n">
-        <v>1.508</v>
+        <v>1.598</v>
       </c>
       <c r="E18" t="n">
-        <v>-38.3</v>
+        <v>-41.8</v>
       </c>
       <c r="F18" t="n">
-        <v>-25</v>
+        <v>-26.9</v>
       </c>
       <c r="G18" t="n">
-        <v>-11.6</v>
+        <v>-12.1</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>262407</v>
+        <v>299845</v>
       </c>
       <c r="K18" t="n">
-        <v>70042</v>
+        <v>73615</v>
       </c>
       <c r="L18" t="n">
         <v>48</v>
       </c>
       <c r="M18" t="n">
-        <v>68.73999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>26.7</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="19">
@@ -1407,16 +1407,16 @@
         <v>1.37</v>
       </c>
       <c r="D19" t="n">
-        <v>0.86</v>
+        <v>0.869</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>-0.4</v>
       </c>
       <c r="F19" t="n">
-        <v>-9.9</v>
+        <v>-11.2</v>
       </c>
       <c r="G19" t="n">
-        <v>-21.7</v>
+        <v>-22</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1429,19 +1429,19 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>87851</v>
+        <v>124006</v>
       </c>
       <c r="K19" t="n">
-        <v>439913</v>
+        <v>453302</v>
       </c>
       <c r="L19" t="n">
         <v>29.19</v>
       </c>
       <c r="M19" t="n">
-        <v>22.41</v>
+        <v>22.85</v>
       </c>
       <c r="N19" t="n">
-        <v>-23.7</v>
+        <v>-21.6</v>
       </c>
     </row>
     <row r="20">
@@ -1459,16 +1459,16 @@
         <v>1.09</v>
       </c>
       <c r="D20" t="n">
-        <v>1.081</v>
+        <v>1.119</v>
       </c>
       <c r="E20" t="n">
-        <v>-31.3</v>
+        <v>-33.9</v>
       </c>
       <c r="F20" t="n">
-        <v>-28.6</v>
+        <v>-30.1</v>
       </c>
       <c r="G20" t="n">
-        <v>-25.8</v>
+        <v>-26.2</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>270502</v>
+        <v>318149</v>
       </c>
       <c r="K20" t="n">
-        <v>186637</v>
+        <v>195482</v>
       </c>
       <c r="L20" t="n">
         <v>11.35</v>
       </c>
       <c r="M20" t="n">
-        <v>12.26</v>
+        <v>12.68</v>
       </c>
       <c r="N20" t="n">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="21">
@@ -1511,16 +1511,16 @@
         <v>1.2</v>
       </c>
       <c r="D21" t="n">
-        <v>1.128</v>
+        <v>1.174</v>
       </c>
       <c r="E21" t="n">
-        <v>-47.6</v>
+        <v>-50.6</v>
       </c>
       <c r="F21" t="n">
-        <v>-42.8</v>
+        <v>-44.3</v>
       </c>
       <c r="G21" t="n">
-        <v>-38</v>
+        <v>-38.1</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>320754</v>
+        <v>368638</v>
       </c>
       <c r="K21" t="n">
-        <v>223034</v>
+        <v>235378</v>
       </c>
       <c r="L21" t="n">
         <v>18.17</v>
       </c>
       <c r="M21" t="n">
-        <v>21.53</v>
+        <v>22.75</v>
       </c>
       <c r="N21" t="n">
-        <v>9.699999999999999</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="22">
@@ -1563,16 +1563,16 @@
         <v>1.21</v>
       </c>
       <c r="D22" t="n">
-        <v>1.141</v>
+        <v>1.194</v>
       </c>
       <c r="E22" t="n">
-        <v>-48.5</v>
+        <v>-51.6</v>
       </c>
       <c r="F22" t="n">
-        <v>-43.5</v>
+        <v>-45.1</v>
       </c>
       <c r="G22" t="n">
-        <v>-38.5</v>
+        <v>-38.6</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>299265</v>
+        <v>343913</v>
       </c>
       <c r="K22" t="n">
-        <v>212288</v>
+        <v>224009</v>
       </c>
       <c r="L22" t="n">
         <v>25.73</v>
       </c>
       <c r="M22" t="n">
-        <v>30.7</v>
+        <v>32.59</v>
       </c>
       <c r="N22" t="n">
-        <v>10</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="23">
@@ -1615,16 +1615,16 @@
         <v>0.75</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-39.7</v>
+        <v>-41</v>
       </c>
       <c r="F23" t="n">
-        <v>-53.5</v>
+        <v>-53.4</v>
       </c>
       <c r="G23" t="n">
-        <v>-67.40000000000001</v>
+        <v>-65.8</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1646,10 +1646,10 @@
         <v>3.12</v>
       </c>
       <c r="M23" t="n">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="N23" t="n">
-        <v>-27.7</v>
+        <v>-24.8</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -630,13 +630,13 @@
         <v>1.251</v>
       </c>
       <c r="E4" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="F4" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="G4" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -655,10 +655,10 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>40.59</v>
+        <v>40.54</v>
       </c>
       <c r="M4" t="n">
-        <v>50.17</v>
+        <v>50.1</v>
       </c>
       <c r="N4" t="n">
         <v>25.1</v>
@@ -783,16 +783,16 @@
         <v>0.82</v>
       </c>
       <c r="D7" t="n">
-        <v>1.025</v>
+        <v>1.036</v>
       </c>
       <c r="E7" t="n">
-        <v>13.6</v>
+        <v>12.1</v>
       </c>
       <c r="F7" t="n">
-        <v>15.2</v>
+        <v>14.4</v>
       </c>
       <c r="G7" t="n">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -805,19 +805,19 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>8259</v>
+        <v>9650</v>
       </c>
       <c r="K7" t="n">
-        <v>4806</v>
+        <v>4723</v>
       </c>
       <c r="L7" t="n">
         <v>28.19</v>
       </c>
       <c r="M7" t="n">
-        <v>28.98</v>
+        <v>29.33</v>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="8">
@@ -890,10 +890,10 @@
         <v>1.14</v>
       </c>
       <c r="E9" t="n">
-        <v>-8.4</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G9" t="n">
         <v>13.1</v>
@@ -915,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>13.34</v>
+        <v>13.35</v>
       </c>
       <c r="M9" t="n">
         <v>16.46</v>
@@ -1199,16 +1199,16 @@
         <v>0.67</v>
       </c>
       <c r="D15" t="n">
-        <v>1.154</v>
+        <v>1.176</v>
       </c>
       <c r="E15" t="n">
-        <v>-24.2</v>
+        <v>-26.4</v>
       </c>
       <c r="F15" t="n">
-        <v>-12.2</v>
+        <v>-13.2</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>6063</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1230,10 +1230,10 @@
         <v>10.07</v>
       </c>
       <c r="M15" t="n">
-        <v>13.25</v>
+        <v>13.69</v>
       </c>
       <c r="N15" t="n">
-        <v>23.9</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="16">
@@ -1251,16 +1251,16 @@
         <v>1.04</v>
       </c>
       <c r="D16" t="n">
-        <v>1.094</v>
+        <v>1.11</v>
       </c>
       <c r="E16" t="n">
-        <v>-13.7</v>
+        <v>-18.1</v>
       </c>
       <c r="F16" t="n">
-        <v>-8.4</v>
+        <v>-12.1</v>
       </c>
       <c r="G16" t="n">
-        <v>-3</v>
+        <v>-6.1</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1269,23 +1269,23 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>113055</v>
+        <v>132543</v>
       </c>
       <c r="K16" t="n">
-        <v>42654</v>
+        <v>47330</v>
       </c>
       <c r="L16" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="M16" t="n">
         <v>2.37</v>
       </c>
       <c r="N16" t="n">
-        <v>10.7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
@@ -1615,16 +1615,16 @@
         <v>0.75</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-41</v>
+        <v>-41.4</v>
       </c>
       <c r="F23" t="n">
         <v>-53.4</v>
       </c>
       <c r="G23" t="n">
-        <v>-65.8</v>
+        <v>-65.5</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1646,10 +1646,10 @@
         <v>3.12</v>
       </c>
       <c r="M23" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="N23" t="n">
-        <v>-24.8</v>
+        <v>-24.1</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -676,19 +676,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>1.382</v>
+        <v>1.403</v>
       </c>
       <c r="E5" t="n">
         <v>-2.9</v>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>12.9</v>
       </c>
       <c r="G5" t="n">
-        <v>26.9</v>
+        <v>28.6</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -710,16 +710,16 @@
         <v>70.90000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>92.67</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>29.8</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -728,19 +728,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="D6" t="n">
-        <v>1.131</v>
+        <v>1.079</v>
       </c>
       <c r="E6" t="n">
-        <v>9.6</v>
+        <v>12.1</v>
       </c>
       <c r="F6" t="n">
-        <v>15.3</v>
+        <v>17.1</v>
       </c>
       <c r="G6" t="n">
-        <v>21.1</v>
+        <v>22</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -753,25 +753,25 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>7407</v>
+        <v>9650</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>16.28</v>
+        <v>28.19</v>
       </c>
       <c r="M6" t="n">
-        <v>17.99</v>
+        <v>30.69</v>
       </c>
       <c r="N6" t="n">
-        <v>11.5</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -780,19 +780,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="D7" t="n">
-        <v>1.036</v>
+        <v>1.131</v>
       </c>
       <c r="E7" t="n">
-        <v>12.1</v>
+        <v>9.6</v>
       </c>
       <c r="F7" t="n">
-        <v>14.4</v>
+        <v>15.3</v>
       </c>
       <c r="G7" t="n">
-        <v>16.6</v>
+        <v>21.1</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -805,25 +805,25 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>9650</v>
+        <v>7407</v>
       </c>
       <c r="K7" t="n">
-        <v>4723</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>28.19</v>
+        <v>16.28</v>
       </c>
       <c r="M7" t="n">
-        <v>29.33</v>
+        <v>17.99</v>
       </c>
       <c r="N7" t="n">
-        <v>4.6</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -832,23 +832,23 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.88</v>
+        <v>0.73</v>
       </c>
       <c r="D8" t="n">
-        <v>0.827</v>
+        <v>1.328</v>
       </c>
       <c r="E8" t="n">
-        <v>53.4</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>34</v>
+        <v>7.8</v>
       </c>
       <c r="G8" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -860,16 +860,16 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1065</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>9.82</v>
+        <v>67.61</v>
       </c>
       <c r="M8" t="n">
-        <v>7.33</v>
+        <v>78.06</v>
       </c>
       <c r="N8" t="n">
-        <v>-38.9</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="9">
@@ -884,19 +884,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="D9" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="E9" t="n">
         <v>-8.300000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="G9" t="n">
-        <v>13.1</v>
+        <v>14.6</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -918,16 +918,16 @@
         <v>13.35</v>
       </c>
       <c r="M9" t="n">
-        <v>16.46</v>
+        <v>16.68</v>
       </c>
       <c r="N9" t="n">
-        <v>21.4</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -936,23 +936,23 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="D10" t="n">
-        <v>1.082</v>
+        <v>0.827</v>
       </c>
       <c r="E10" t="n">
-        <v>3.4</v>
+        <v>53.4</v>
       </c>
       <c r="F10" t="n">
-        <v>7.9</v>
+        <v>34</v>
       </c>
       <c r="G10" t="n">
-        <v>12.4</v>
+        <v>14.5</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>24799</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>4587</v>
+        <v>1065</v>
       </c>
       <c r="L10" t="n">
-        <v>28.65</v>
+        <v>9.82</v>
       </c>
       <c r="M10" t="n">
-        <v>31.12</v>
+        <v>7.33</v>
       </c>
       <c r="N10" t="n">
-        <v>8.9</v>
+        <v>-38.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="D11" t="n">
-        <v>1.249</v>
+        <v>1.094</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="F11" t="n">
-        <v>5.9</v>
+        <v>8.5</v>
       </c>
       <c r="G11" t="n">
-        <v>11.7</v>
+        <v>13.6</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1013,25 +1013,25 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>24799</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1767</v>
       </c>
       <c r="L11" t="n">
-        <v>67.61</v>
+        <v>28.65</v>
       </c>
       <c r="M11" t="n">
-        <v>75.53</v>
+        <v>31.45</v>
       </c>
       <c r="N11" t="n">
-        <v>11.7</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1040,23 +1040,23 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="D12" t="n">
-        <v>1.113</v>
+        <v>1.393</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9</v>
+        <v>-20.1</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2</v>
+        <v>-5.1</v>
       </c>
       <c r="G12" t="n">
-        <v>8.300000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1065,25 +1065,25 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>29692</v>
+        <v>79286</v>
       </c>
       <c r="K12" t="n">
-        <v>10595</v>
+        <v>8086</v>
       </c>
       <c r="L12" t="n">
-        <v>23.56</v>
+        <v>5.61</v>
       </c>
       <c r="M12" t="n">
-        <v>26.52</v>
+        <v>7.71</v>
       </c>
       <c r="N12" t="n">
-        <v>12.1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1092,23 +1092,23 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.62</v>
+        <v>0.89</v>
       </c>
       <c r="D13" t="n">
-        <v>0.926</v>
+        <v>1.093</v>
       </c>
       <c r="E13" t="n">
-        <v>11.9</v>
+        <v>-3.9</v>
       </c>
       <c r="F13" t="n">
-        <v>8.6</v>
+        <v>1.1</v>
       </c>
       <c r="G13" t="n">
-        <v>5.3</v>
+        <v>6.1</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1117,25 +1117,25 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>7207</v>
+        <v>29692</v>
       </c>
       <c r="K13" t="n">
-        <v>14814</v>
+        <v>14076</v>
       </c>
       <c r="L13" t="n">
-        <v>20.34</v>
+        <v>23.56</v>
       </c>
       <c r="M13" t="n">
-        <v>19.14</v>
+        <v>25.98</v>
       </c>
       <c r="N13" t="n">
-        <v>-6.6</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1144,44 +1144,44 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.95</v>
+        <v>0.62</v>
       </c>
       <c r="D14" t="n">
-        <v>1.276</v>
+        <v>0.926</v>
       </c>
       <c r="E14" t="n">
-        <v>-20.1</v>
+        <v>11.9</v>
       </c>
       <c r="F14" t="n">
-        <v>-9.6</v>
+        <v>8.6</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9</v>
+        <v>5.3</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>79286</v>
+        <v>7207</v>
       </c>
       <c r="K14" t="n">
-        <v>29561</v>
+        <v>14814</v>
       </c>
       <c r="L14" t="n">
-        <v>5.61</v>
+        <v>20.34</v>
       </c>
       <c r="M14" t="n">
-        <v>7.09</v>
+        <v>19.14</v>
       </c>
       <c r="N14" t="n">
-        <v>21.1</v>
+        <v>-6.6</v>
       </c>
     </row>
     <row r="15">
@@ -1196,19 +1196,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>1.176</v>
+        <v>1.154</v>
       </c>
       <c r="E15" t="n">
         <v>-26.4</v>
       </c>
       <c r="F15" t="n">
-        <v>-13.2</v>
+        <v>-14.8</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-3.1</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1230,10 +1230,10 @@
         <v>10.07</v>
       </c>
       <c r="M15" t="n">
-        <v>13.69</v>
+        <v>13.25</v>
       </c>
       <c r="N15" t="n">
-        <v>26.5</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="16">
@@ -1343,32 +1343,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.98</v>
+        <v>1.35</v>
       </c>
       <c r="D18" t="n">
-        <v>1.598</v>
+        <v>0.875</v>
       </c>
       <c r="E18" t="n">
-        <v>-41.8</v>
+        <v>-0.4</v>
       </c>
       <c r="F18" t="n">
-        <v>-26.9</v>
+        <v>-10.7</v>
       </c>
       <c r="G18" t="n">
-        <v>-12.1</v>
+        <v>-21</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1377,50 +1377,50 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>299845</v>
+        <v>124006</v>
       </c>
       <c r="K18" t="n">
-        <v>73615</v>
+        <v>438558</v>
       </c>
       <c r="L18" t="n">
-        <v>48</v>
+        <v>29.19</v>
       </c>
       <c r="M18" t="n">
-        <v>72.40000000000001</v>
+        <v>23.14</v>
       </c>
       <c r="N18" t="n">
-        <v>29.6</v>
+        <v>-20.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.37</v>
+        <v>1.11</v>
       </c>
       <c r="D19" t="n">
-        <v>0.869</v>
+        <v>1.411</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4</v>
+        <v>-41.8</v>
       </c>
       <c r="F19" t="n">
-        <v>-11.2</v>
+        <v>-31.6</v>
       </c>
       <c r="G19" t="n">
-        <v>-22</v>
+        <v>-21.4</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1429,19 +1429,19 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>124006</v>
+        <v>299845</v>
       </c>
       <c r="K19" t="n">
-        <v>453302</v>
+        <v>144354</v>
       </c>
       <c r="L19" t="n">
-        <v>29.19</v>
+        <v>48</v>
       </c>
       <c r="M19" t="n">
-        <v>22.85</v>
+        <v>64.77</v>
       </c>
       <c r="N19" t="n">
-        <v>-21.6</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="20">
@@ -1456,19 +1456,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="D20" t="n">
-        <v>1.119</v>
+        <v>1.075</v>
       </c>
       <c r="E20" t="n">
         <v>-33.9</v>
       </c>
       <c r="F20" t="n">
-        <v>-30.1</v>
+        <v>-31.5</v>
       </c>
       <c r="G20" t="n">
-        <v>-26.2</v>
+        <v>-29</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1484,22 +1484,22 @@
         <v>318149</v>
       </c>
       <c r="K20" t="n">
-        <v>195482</v>
+        <v>240463</v>
       </c>
       <c r="L20" t="n">
         <v>11.35</v>
       </c>
       <c r="M20" t="n">
-        <v>12.68</v>
+        <v>12.19</v>
       </c>
       <c r="N20" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1508,19 +1508,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="D21" t="n">
-        <v>1.174</v>
+        <v>1.101</v>
       </c>
       <c r="E21" t="n">
-        <v>-50.6</v>
+        <v>-51.6</v>
       </c>
       <c r="F21" t="n">
-        <v>-44.3</v>
+        <v>-48.2</v>
       </c>
       <c r="G21" t="n">
-        <v>-38.1</v>
+        <v>-44.8</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1533,25 +1533,25 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>368638</v>
+        <v>343913</v>
       </c>
       <c r="K21" t="n">
-        <v>235378</v>
+        <v>281217</v>
       </c>
       <c r="L21" t="n">
-        <v>18.17</v>
+        <v>25.73</v>
       </c>
       <c r="M21" t="n">
-        <v>22.75</v>
+        <v>29.31</v>
       </c>
       <c r="N21" t="n">
-        <v>12.4</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1560,19 +1560,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="D22" t="n">
-        <v>1.194</v>
+        <v>1.071</v>
       </c>
       <c r="E22" t="n">
-        <v>-51.6</v>
+        <v>-50.6</v>
       </c>
       <c r="F22" t="n">
-        <v>-45.1</v>
+        <v>-48</v>
       </c>
       <c r="G22" t="n">
-        <v>-38.6</v>
+        <v>-45.5</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>343913</v>
+        <v>368638</v>
       </c>
       <c r="K22" t="n">
-        <v>224009</v>
+        <v>314436</v>
       </c>
       <c r="L22" t="n">
-        <v>25.73</v>
+        <v>18.17</v>
       </c>
       <c r="M22" t="n">
-        <v>32.59</v>
+        <v>20.03</v>
       </c>
       <c r="N22" t="n">
-        <v>12.9</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="23">
@@ -1612,19 +1612,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.953</v>
       </c>
       <c r="E23" t="n">
         <v>-41.4</v>
       </c>
       <c r="F23" t="n">
-        <v>-53.4</v>
+        <v>-51.3</v>
       </c>
       <c r="G23" t="n">
-        <v>-65.5</v>
+        <v>-61.3</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1646,10 +1646,10 @@
         <v>3.12</v>
       </c>
       <c r="M23" t="n">
-        <v>1.84</v>
+        <v>2.06</v>
       </c>
       <c r="N23" t="n">
-        <v>-24.1</v>
+        <v>-19.9</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -523,16 +523,16 @@
         <v>0.34</v>
       </c>
       <c r="D2" t="n">
-        <v>1.164</v>
+        <v>1.183</v>
       </c>
       <c r="E2" t="n">
-        <v>36.3</v>
+        <v>33.2</v>
       </c>
       <c r="F2" t="n">
-        <v>51.2</v>
+        <v>49.5</v>
       </c>
       <c r="G2" t="n">
-        <v>66.09999999999999</v>
+        <v>65.8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -554,10 +554,10 @@
         <v>50.92</v>
       </c>
       <c r="M2" t="n">
-        <v>62.06</v>
+        <v>63.37</v>
       </c>
       <c r="N2" t="n">
-        <v>29.8</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="3">
@@ -575,16 +575,16 @@
         <v>0.9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.959</v>
+        <v>0.969</v>
       </c>
       <c r="E3" t="n">
-        <v>55.1</v>
+        <v>49</v>
       </c>
       <c r="F3" t="n">
-        <v>46.5</v>
+        <v>42.7</v>
       </c>
       <c r="G3" t="n">
-        <v>37.9</v>
+        <v>36.4</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -606,10 +606,10 @@
         <v>33.5</v>
       </c>
       <c r="M3" t="n">
-        <v>29.78</v>
+        <v>30.68</v>
       </c>
       <c r="N3" t="n">
-        <v>-17.2</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="4">
@@ -627,20 +627,20 @@
         <v>0.75</v>
       </c>
       <c r="D4" t="n">
-        <v>1.251</v>
+        <v>1.288</v>
       </c>
       <c r="E4" t="n">
-        <v>6.4</v>
+        <v>2.8</v>
       </c>
       <c r="F4" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="G4" t="n">
-        <v>31.5</v>
+        <v>30.6</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>4829</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>40.54</v>
       </c>
       <c r="M4" t="n">
-        <v>50.1</v>
+        <v>51.49</v>
       </c>
       <c r="N4" t="n">
-        <v>25.1</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="5">
@@ -679,20 +679,20 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>1.403</v>
+        <v>1.47</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.9</v>
+        <v>-7</v>
       </c>
       <c r="F5" t="n">
-        <v>12.9</v>
+        <v>10.6</v>
       </c>
       <c r="G5" t="n">
-        <v>28.6</v>
+        <v>28.1</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>39551</v>
+        <v>56752</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -710,10 +710,10 @@
         <v>70.90000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>93.90000000000001</v>
+        <v>97.70999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>31.5</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="6">
@@ -731,16 +731,16 @@
         <v>0.78</v>
       </c>
       <c r="D6" t="n">
-        <v>1.079</v>
+        <v>1.105</v>
       </c>
       <c r="E6" t="n">
-        <v>12.1</v>
+        <v>8.9</v>
       </c>
       <c r="F6" t="n">
-        <v>17.1</v>
+        <v>15.3</v>
       </c>
       <c r="G6" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>9650</v>
+        <v>12503</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -762,10 +762,10 @@
         <v>28.19</v>
       </c>
       <c r="M6" t="n">
-        <v>30.69</v>
+        <v>31.5</v>
       </c>
       <c r="N6" t="n">
-        <v>9.9</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="7">
@@ -783,16 +783,16 @@
         <v>0.75</v>
       </c>
       <c r="D7" t="n">
-        <v>1.131</v>
+        <v>1.171</v>
       </c>
       <c r="E7" t="n">
-        <v>9.6</v>
+        <v>6.3</v>
       </c>
       <c r="F7" t="n">
-        <v>15.3</v>
+        <v>13.5</v>
       </c>
       <c r="G7" t="n">
-        <v>21.1</v>
+        <v>20.8</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>7407</v>
+        <v>11815</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -814,10 +814,10 @@
         <v>16.28</v>
       </c>
       <c r="M7" t="n">
-        <v>17.99</v>
+        <v>18.51</v>
       </c>
       <c r="N7" t="n">
-        <v>11.5</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="8">
@@ -835,16 +835,16 @@
         <v>0.73</v>
       </c>
       <c r="D8" t="n">
-        <v>1.328</v>
+        <v>1.378</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>-2.4</v>
       </c>
       <c r="F8" t="n">
-        <v>7.8</v>
+        <v>6.3</v>
       </c>
       <c r="G8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -866,10 +866,10 @@
         <v>67.61</v>
       </c>
       <c r="M8" t="n">
-        <v>78.06</v>
+        <v>79.65000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>15.5</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="9">
@@ -887,16 +887,16 @@
         <v>0.73</v>
       </c>
       <c r="D9" t="n">
-        <v>1.15</v>
+        <v>1.169</v>
       </c>
       <c r="E9" t="n">
-        <v>-8.300000000000001</v>
+        <v>-10.6</v>
       </c>
       <c r="F9" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>52880</v>
+        <v>61644</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -918,10 +918,10 @@
         <v>13.35</v>
       </c>
       <c r="M9" t="n">
-        <v>16.68</v>
+        <v>17.1</v>
       </c>
       <c r="N9" t="n">
-        <v>22.9</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="10">
@@ -939,16 +939,16 @@
         <v>0.88</v>
       </c>
       <c r="D10" t="n">
-        <v>0.827</v>
+        <v>0.848</v>
       </c>
       <c r="E10" t="n">
-        <v>53.4</v>
+        <v>46.6</v>
       </c>
       <c r="F10" t="n">
-        <v>34</v>
+        <v>30.2</v>
       </c>
       <c r="G10" t="n">
-        <v>14.5</v>
+        <v>13.9</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -964,16 +964,16 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1065</v>
+        <v>948</v>
       </c>
       <c r="L10" t="n">
         <v>9.82</v>
       </c>
       <c r="M10" t="n">
-        <v>7.33</v>
+        <v>7.63</v>
       </c>
       <c r="N10" t="n">
-        <v>-38.9</v>
+        <v>-32.7</v>
       </c>
     </row>
     <row r="11">
@@ -991,16 +991,16 @@
         <v>0.82</v>
       </c>
       <c r="D11" t="n">
-        <v>1.094</v>
+        <v>1.105</v>
       </c>
       <c r="E11" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="F11" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="G11" t="n">
-        <v>13.6</v>
+        <v>13.4</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>24799</v>
+        <v>27403</v>
       </c>
       <c r="K11" t="n">
-        <v>1767</v>
+        <v>1545</v>
       </c>
       <c r="L11" t="n">
         <v>28.65</v>
       </c>
       <c r="M11" t="n">
-        <v>31.45</v>
+        <v>31.81</v>
       </c>
       <c r="N11" t="n">
-        <v>10.1</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="12">
@@ -1095,13 +1095,13 @@
         <v>0.89</v>
       </c>
       <c r="D13" t="n">
-        <v>1.093</v>
+        <v>1.086</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.9</v>
+        <v>-3.1</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="G13" t="n">
         <v>6.1</v>
@@ -1117,25 +1117,25 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>29692</v>
+        <v>28480</v>
       </c>
       <c r="K13" t="n">
-        <v>14076</v>
+        <v>14038</v>
       </c>
       <c r="L13" t="n">
         <v>23.56</v>
       </c>
       <c r="M13" t="n">
-        <v>25.98</v>
+        <v>25.8</v>
       </c>
       <c r="N13" t="n">
-        <v>9.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1144,23 +1144,23 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.62</v>
+        <v>0.84</v>
       </c>
       <c r="D14" t="n">
-        <v>0.926</v>
+        <v>1.214</v>
       </c>
       <c r="E14" t="n">
-        <v>11.9</v>
+        <v>-15.1</v>
       </c>
       <c r="F14" t="n">
-        <v>8.6</v>
+        <v>-5</v>
       </c>
       <c r="G14" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1169,25 +1169,25 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>7207</v>
+        <v>90798</v>
       </c>
       <c r="K14" t="n">
-        <v>14814</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>20.34</v>
+        <v>30.55</v>
       </c>
       <c r="M14" t="n">
-        <v>19.14</v>
+        <v>37.82</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.6</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1196,23 +1196,23 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="D15" t="n">
-        <v>1.154</v>
+        <v>0.98</v>
       </c>
       <c r="E15" t="n">
-        <v>-26.4</v>
+        <v>6.6</v>
       </c>
       <c r="F15" t="n">
-        <v>-14.8</v>
+        <v>5.7</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.1</v>
+        <v>4.9</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1221,25 +1221,25 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>6063</v>
+        <v>12866</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>14974</v>
       </c>
       <c r="L15" t="n">
-        <v>10.07</v>
+        <v>20.34</v>
       </c>
       <c r="M15" t="n">
-        <v>13.25</v>
+        <v>20.01</v>
       </c>
       <c r="N15" t="n">
-        <v>23.3</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1248,19 +1248,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.04</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>1.11</v>
+        <v>1.122</v>
       </c>
       <c r="E16" t="n">
-        <v>-18.1</v>
+        <v>-22.9</v>
       </c>
       <c r="F16" t="n">
-        <v>-12.1</v>
+        <v>-13.3</v>
       </c>
       <c r="G16" t="n">
-        <v>-6.1</v>
+        <v>-3.6</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1269,29 +1269,29 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>132543</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>47330</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2.06</v>
+        <v>10.07</v>
       </c>
       <c r="M16" t="n">
-        <v>2.37</v>
+        <v>12.59</v>
       </c>
       <c r="N16" t="n">
-        <v>12</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1300,50 +1300,50 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.85</v>
+        <v>1.04</v>
       </c>
       <c r="D17" t="n">
+        <v>1.102</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-17.1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>124928</v>
+      </c>
+      <c r="K17" t="n">
+        <v>46150</v>
+      </c>
+      <c r="L17" t="n">
         <v>2.06</v>
       </c>
-      <c r="E17" t="n">
-        <v>-61.2</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-36.3</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-11.5</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT (overvalued)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT (overvalued)</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>391067</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2.25</v>
-      </c>
       <c r="M17" t="n">
-        <v>5.14</v>
+        <v>2.34</v>
       </c>
       <c r="N17" t="n">
-        <v>49.7</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>BWLP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1352,23 +1352,23 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.35</v>
+        <v>0.97</v>
       </c>
       <c r="D18" t="n">
-        <v>0.875</v>
+        <v>1.164</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4</v>
+        <v>-21.9</v>
       </c>
       <c r="F18" t="n">
-        <v>-10.7</v>
+        <v>-14.5</v>
       </c>
       <c r="G18" t="n">
-        <v>-21</v>
+        <v>-7.1</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1377,46 +1377,46 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>124006</v>
+        <v>124605</v>
       </c>
       <c r="K18" t="n">
-        <v>438558</v>
+        <v>55676</v>
       </c>
       <c r="L18" t="n">
-        <v>29.19</v>
+        <v>14.46</v>
       </c>
       <c r="M18" t="n">
-        <v>23.14</v>
+        <v>17.2</v>
       </c>
       <c r="N18" t="n">
-        <v>-20.7</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.11</v>
+        <v>0.85</v>
       </c>
       <c r="D19" t="n">
-        <v>1.411</v>
+        <v>2.088</v>
       </c>
       <c r="E19" t="n">
-        <v>-41.8</v>
+        <v>-61.8</v>
       </c>
       <c r="F19" t="n">
-        <v>-31.6</v>
+        <v>-36.7</v>
       </c>
       <c r="G19" t="n">
-        <v>-21.4</v>
+        <v>-11.5</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>299845</v>
+        <v>401208</v>
       </c>
       <c r="K19" t="n">
-        <v>144354</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>48</v>
+        <v>2.25</v>
       </c>
       <c r="M19" t="n">
-        <v>64.77</v>
+        <v>5.22</v>
       </c>
       <c r="N19" t="n">
-        <v>20.4</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1456,23 +1456,23 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="D20" t="n">
-        <v>1.075</v>
+        <v>0.873</v>
       </c>
       <c r="E20" t="n">
-        <v>-33.9</v>
+        <v>0.1</v>
       </c>
       <c r="F20" t="n">
-        <v>-31.5</v>
+        <v>-10.5</v>
       </c>
       <c r="G20" t="n">
-        <v>-29</v>
+        <v>-21</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1481,46 +1481,46 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>318149</v>
+        <v>117530</v>
       </c>
       <c r="K20" t="n">
-        <v>240463</v>
+        <v>436220</v>
       </c>
       <c r="L20" t="n">
-        <v>11.35</v>
+        <v>29.19</v>
       </c>
       <c r="M20" t="n">
-        <v>12.19</v>
+        <v>23.06</v>
       </c>
       <c r="N20" t="n">
-        <v>4.9</v>
+        <v>-21</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="D21" t="n">
-        <v>1.101</v>
+        <v>1.421</v>
       </c>
       <c r="E21" t="n">
-        <v>-51.6</v>
+        <v>-42.2</v>
       </c>
       <c r="F21" t="n">
-        <v>-48.2</v>
+        <v>-31.8</v>
       </c>
       <c r="G21" t="n">
-        <v>-44.8</v>
+        <v>-21.5</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1533,25 +1533,25 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>343913</v>
+        <v>304545</v>
       </c>
       <c r="K21" t="n">
-        <v>281217</v>
+        <v>145301</v>
       </c>
       <c r="L21" t="n">
-        <v>25.73</v>
+        <v>48</v>
       </c>
       <c r="M21" t="n">
-        <v>29.31</v>
+        <v>65.17</v>
       </c>
       <c r="N21" t="n">
-        <v>6.8</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1560,19 +1560,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
       <c r="D22" t="n">
-        <v>1.071</v>
+        <v>1.061</v>
       </c>
       <c r="E22" t="n">
-        <v>-50.6</v>
+        <v>-33</v>
       </c>
       <c r="F22" t="n">
-        <v>-48</v>
+        <v>-30.9</v>
       </c>
       <c r="G22" t="n">
-        <v>-45.5</v>
+        <v>-28.9</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1585,71 +1585,175 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>368638</v>
+        <v>299823</v>
       </c>
       <c r="K22" t="n">
-        <v>314436</v>
+        <v>236407</v>
       </c>
       <c r="L22" t="n">
-        <v>18.17</v>
+        <v>11.35</v>
       </c>
       <c r="M22" t="n">
-        <v>20.03</v>
+        <v>12.04</v>
       </c>
       <c r="N22" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>ECO</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.088</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-50.7</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-47.8</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-44.8</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>331519</v>
+      </c>
+      <c r="K23" t="n">
+        <v>277016</v>
+      </c>
+      <c r="L23" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="M23" t="n">
+        <v>28.85</v>
+      </c>
+      <c r="N23" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>FRO</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.067</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-50.3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-47.9</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-45.5</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>364200</v>
+      </c>
+      <c r="K24" t="n">
+        <v>312883</v>
+      </c>
+      <c r="L24" t="n">
+        <v>18.17</v>
+      </c>
+      <c r="M24" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="N24" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>BRUT</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>whole-company</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
         <v>0.72</v>
       </c>
-      <c r="D23" t="n">
-        <v>0.953</v>
-      </c>
-      <c r="E23" t="n">
-        <v>-41.4</v>
-      </c>
-      <c r="F23" t="n">
-        <v>-51.3</v>
-      </c>
-      <c r="G23" t="n">
-        <v>-61.3</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT (overvalued)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT (overvalued)</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
+      <c r="D25" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-44.9</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-51.1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-57.3</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
         <v>0</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K25" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L25" t="n">
         <v>3.12</v>
       </c>
-      <c r="M23" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="N23" t="n">
-        <v>-19.9</v>
+      <c r="M25" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-12.4</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -523,16 +523,16 @@
         <v>0.34</v>
       </c>
       <c r="D2" t="n">
-        <v>1.183</v>
+        <v>1.216</v>
       </c>
       <c r="E2" t="n">
-        <v>33.2</v>
+        <v>42.1</v>
       </c>
       <c r="F2" t="n">
-        <v>49.5</v>
+        <v>62.2</v>
       </c>
       <c r="G2" t="n">
-        <v>65.8</v>
+        <v>82.3</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -551,13 +551,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>50.92</v>
+        <v>56.36</v>
       </c>
       <c r="M2" t="n">
-        <v>63.37</v>
+        <v>72.3</v>
       </c>
       <c r="N2" t="n">
-        <v>32.6</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="3">
@@ -575,16 +575,16 @@
         <v>0.9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.969</v>
+        <v>0.967</v>
       </c>
       <c r="E3" t="n">
-        <v>49</v>
+        <v>50.2</v>
       </c>
       <c r="F3" t="n">
-        <v>42.7</v>
+        <v>43.4</v>
       </c>
       <c r="G3" t="n">
-        <v>36.4</v>
+        <v>36.7</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -606,10 +606,10 @@
         <v>33.5</v>
       </c>
       <c r="M3" t="n">
-        <v>30.68</v>
+        <v>30.5</v>
       </c>
       <c r="N3" t="n">
-        <v>-12.5</v>
+        <v>-13.4</v>
       </c>
     </row>
     <row r="4">
@@ -627,16 +627,16 @@
         <v>0.75</v>
       </c>
       <c r="D4" t="n">
-        <v>1.288</v>
+        <v>1.305</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="F4" t="n">
-        <v>16.7</v>
+        <v>15.7</v>
       </c>
       <c r="G4" t="n">
-        <v>30.6</v>
+        <v>30.1</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>4829</v>
+        <v>19341</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>40.54</v>
       </c>
       <c r="M4" t="n">
-        <v>51.49</v>
+        <v>52.14</v>
       </c>
       <c r="N4" t="n">
-        <v>27.8</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="5">
@@ -679,16 +679,16 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>1.47</v>
+        <v>1.534</v>
       </c>
       <c r="E5" t="n">
-        <v>-7</v>
+        <v>-10.6</v>
       </c>
       <c r="F5" t="n">
-        <v>10.6</v>
+        <v>8.6</v>
       </c>
       <c r="G5" t="n">
-        <v>28.1</v>
+        <v>27.7</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>56752</v>
+        <v>73052</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -710,16 +710,16 @@
         <v>70.90000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>97.70999999999999</v>
+        <v>101.32</v>
       </c>
       <c r="N5" t="n">
-        <v>35.2</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -728,23 +728,23 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="D6" t="n">
-        <v>1.105</v>
+        <v>1.473</v>
       </c>
       <c r="E6" t="n">
-        <v>8.9</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>15.3</v>
+        <v>12.7</v>
       </c>
       <c r="G6" t="n">
-        <v>21.7</v>
+        <v>24.4</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -753,25 +753,25 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>12503</v>
+        <v>24452</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>28.19</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>31.5</v>
+        <v>90.15000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>12.8</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -780,23 +780,23 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>1.171</v>
+        <v>1.119</v>
       </c>
       <c r="E7" t="n">
-        <v>6.3</v>
+        <v>1.1</v>
       </c>
       <c r="F7" t="n">
-        <v>13.5</v>
+        <v>11.7</v>
       </c>
       <c r="G7" t="n">
-        <v>20.8</v>
+        <v>22.3</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -805,25 +805,25 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>11815</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>16.28</v>
+        <v>13.14</v>
       </c>
       <c r="M7" t="n">
-        <v>18.51</v>
+        <v>15.9</v>
       </c>
       <c r="N7" t="n">
-        <v>14.6</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -832,23 +832,23 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="D8" t="n">
-        <v>1.378</v>
+        <v>1.121</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4</v>
+        <v>7</v>
       </c>
       <c r="F8" t="n">
-        <v>6.3</v>
+        <v>14.2</v>
       </c>
       <c r="G8" t="n">
-        <v>15</v>
+        <v>21.5</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>14332</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>67.61</v>
+        <v>28.19</v>
       </c>
       <c r="M8" t="n">
-        <v>79.65000000000001</v>
+        <v>32.02</v>
       </c>
       <c r="N8" t="n">
-        <v>17.4</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="9">
@@ -887,16 +887,16 @@
         <v>0.73</v>
       </c>
       <c r="D9" t="n">
-        <v>1.169</v>
+        <v>1.201</v>
       </c>
       <c r="E9" t="n">
-        <v>-10.6</v>
+        <v>-9.1</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>5.6</v>
       </c>
       <c r="G9" t="n">
-        <v>14.5</v>
+        <v>20.3</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>61644</v>
+        <v>76803</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>13.35</v>
+        <v>14.15</v>
       </c>
       <c r="M9" t="n">
-        <v>17.1</v>
+        <v>18.74</v>
       </c>
       <c r="N9" t="n">
-        <v>25.1</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -936,23 +936,23 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="D10" t="n">
-        <v>0.848</v>
+        <v>1.263</v>
       </c>
       <c r="E10" t="n">
-        <v>46.6</v>
+        <v>-0.7</v>
       </c>
       <c r="F10" t="n">
-        <v>30.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>13.9</v>
+        <v>20.3</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="J10" t="n">
+        <v>21504</v>
+      </c>
+      <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="K10" t="n">
-        <v>948</v>
-      </c>
       <c r="L10" t="n">
-        <v>9.82</v>
+        <v>16.28</v>
       </c>
       <c r="M10" t="n">
-        <v>7.63</v>
+        <v>19.72</v>
       </c>
       <c r="N10" t="n">
-        <v>-32.7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -988,23 +988,23 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.82</v>
+        <v>0.88</v>
       </c>
       <c r="D11" t="n">
-        <v>1.105</v>
+        <v>0.862</v>
       </c>
       <c r="E11" t="n">
-        <v>2.1</v>
+        <v>42.3</v>
       </c>
       <c r="F11" t="n">
-        <v>7.7</v>
+        <v>27.9</v>
       </c>
       <c r="G11" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1013,25 +1013,25 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>27403</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1545</v>
+        <v>871</v>
       </c>
       <c r="L11" t="n">
-        <v>28.65</v>
+        <v>9.82</v>
       </c>
       <c r="M11" t="n">
-        <v>31.81</v>
+        <v>7.83</v>
       </c>
       <c r="N11" t="n">
-        <v>11.3</v>
+        <v>-28.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1040,23 +1040,23 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="D12" t="n">
-        <v>1.393</v>
+        <v>1.153</v>
       </c>
       <c r="E12" t="n">
-        <v>-20.1</v>
+        <v>-2.8</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.1</v>
+        <v>4.9</v>
       </c>
       <c r="G12" t="n">
-        <v>9.9</v>
+        <v>12.7</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1065,25 +1065,25 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>79286</v>
+        <v>37673</v>
       </c>
       <c r="K12" t="n">
-        <v>8086</v>
+        <v>667</v>
       </c>
       <c r="L12" t="n">
-        <v>5.61</v>
+        <v>28.65</v>
       </c>
       <c r="M12" t="n">
-        <v>7.71</v>
+        <v>33.23</v>
       </c>
       <c r="N12" t="n">
-        <v>30</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1092,23 +1092,23 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="D13" t="n">
-        <v>1.086</v>
+        <v>1.437</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.1</v>
+        <v>-22.9</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5</v>
+        <v>-6.8</v>
       </c>
       <c r="G13" t="n">
-        <v>6.1</v>
+        <v>9.4</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1117,25 +1117,25 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>28480</v>
+        <v>87044</v>
       </c>
       <c r="K13" t="n">
-        <v>14038</v>
+        <v>7871</v>
       </c>
       <c r="L13" t="n">
-        <v>23.56</v>
+        <v>5.61</v>
       </c>
       <c r="M13" t="n">
-        <v>25.8</v>
+        <v>7.95</v>
       </c>
       <c r="N13" t="n">
-        <v>9.199999999999999</v>
+        <v>32.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.84</v>
+        <v>0.89</v>
       </c>
       <c r="D14" t="n">
-        <v>1.214</v>
+        <v>1.13</v>
       </c>
       <c r="E14" t="n">
-        <v>-15.1</v>
+        <v>-7.7</v>
       </c>
       <c r="F14" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="G14" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1169,19 +1169,19 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>90798</v>
+        <v>36132</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>14275</v>
       </c>
       <c r="L14" t="n">
-        <v>30.55</v>
+        <v>23.56</v>
       </c>
       <c r="M14" t="n">
-        <v>37.82</v>
+        <v>26.95</v>
       </c>
       <c r="N14" t="n">
-        <v>20.2</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="15">
@@ -1199,13 +1199,13 @@
         <v>0.62</v>
       </c>
       <c r="D15" t="n">
-        <v>0.98</v>
+        <v>0.979</v>
       </c>
       <c r="E15" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="F15" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="G15" t="n">
         <v>4.9</v>
@@ -1221,16 +1221,16 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>12866</v>
+        <v>12804</v>
       </c>
       <c r="K15" t="n">
-        <v>14974</v>
+        <v>14972</v>
       </c>
       <c r="L15" t="n">
         <v>20.34</v>
       </c>
       <c r="M15" t="n">
-        <v>20.01</v>
+        <v>20</v>
       </c>
       <c r="N15" t="n">
         <v>-1.8</v>
@@ -1239,7 +1239,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1248,19 +1248,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="D16" t="n">
-        <v>1.122</v>
+        <v>1.333</v>
       </c>
       <c r="E16" t="n">
-        <v>-22.9</v>
+        <v>-23.7</v>
       </c>
       <c r="F16" t="n">
-        <v>-13.3</v>
+        <v>-9.6</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.6</v>
+        <v>4.4</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1273,25 +1273,25 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>138721</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>10.07</v>
+        <v>30.55</v>
       </c>
       <c r="M16" t="n">
-        <v>12.59</v>
+        <v>41.83</v>
       </c>
       <c r="N16" t="n">
-        <v>19.3</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1300,19 +1300,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.04</v>
+        <v>0.85</v>
       </c>
       <c r="D17" t="n">
-        <v>1.102</v>
+        <v>2.171</v>
       </c>
       <c r="E17" t="n">
-        <v>-17.1</v>
+        <v>-56</v>
       </c>
       <c r="F17" t="n">
-        <v>-11.5</v>
+        <v>-27.1</v>
       </c>
       <c r="G17" t="n">
-        <v>-5.9</v>
+        <v>1.8</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1321,29 +1321,29 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>124928</v>
+        <v>431629</v>
       </c>
       <c r="K17" t="n">
-        <v>46150</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>2.06</v>
+        <v>2.72</v>
       </c>
       <c r="M17" t="n">
-        <v>2.34</v>
+        <v>6.28</v>
       </c>
       <c r="N17" t="n">
-        <v>11.2</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BWLP</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1352,50 +1352,50 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.97</v>
+        <v>0.72</v>
       </c>
       <c r="D18" t="n">
-        <v>1.164</v>
+        <v>0.965</v>
       </c>
       <c r="E18" t="n">
-        <v>-21.9</v>
+        <v>11.2</v>
       </c>
       <c r="F18" t="n">
-        <v>-14.5</v>
+        <v>3.2</v>
       </c>
       <c r="G18" t="n">
-        <v>-7.1</v>
+        <v>-4.7</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>124605</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>55676</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>14.46</v>
+        <v>6.2</v>
       </c>
       <c r="M18" t="n">
-        <v>17.2</v>
+        <v>5.32</v>
       </c>
       <c r="N18" t="n">
-        <v>14.8</v>
+        <v>-15.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1404,19 +1404,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.85</v>
+        <v>1.04</v>
       </c>
       <c r="D19" t="n">
-        <v>2.088</v>
+        <v>1.088</v>
       </c>
       <c r="E19" t="n">
-        <v>-61.8</v>
+        <v>-15.4</v>
       </c>
       <c r="F19" t="n">
-        <v>-36.7</v>
+        <v>-10.5</v>
       </c>
       <c r="G19" t="n">
-        <v>-11.5</v>
+        <v>-5.5</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>401208</v>
+        <v>112236</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>44184</v>
       </c>
       <c r="L19" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="M19" t="n">
-        <v>5.22</v>
+        <v>2.31</v>
       </c>
       <c r="N19" t="n">
-        <v>50.3</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>BWLP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1456,23 +1456,23 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.35</v>
+        <v>0.97</v>
       </c>
       <c r="D20" t="n">
-        <v>0.873</v>
+        <v>1.212</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1</v>
+        <v>-25.6</v>
       </c>
       <c r="F20" t="n">
-        <v>-10.5</v>
+        <v>-16.6</v>
       </c>
       <c r="G20" t="n">
-        <v>-21</v>
+        <v>-7.5</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>117530</v>
+        <v>146334</v>
       </c>
       <c r="K20" t="n">
-        <v>436220</v>
+        <v>57312</v>
       </c>
       <c r="L20" t="n">
-        <v>29.19</v>
+        <v>14.46</v>
       </c>
       <c r="M20" t="n">
-        <v>23.06</v>
+        <v>18</v>
       </c>
       <c r="N20" t="n">
-        <v>-21</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="21">
@@ -1511,16 +1511,16 @@
         <v>1.11</v>
       </c>
       <c r="D21" t="n">
-        <v>1.421</v>
+        <v>1.515</v>
       </c>
       <c r="E21" t="n">
-        <v>-42.2</v>
+        <v>-40.2</v>
       </c>
       <c r="F21" t="n">
-        <v>-31.8</v>
+        <v>-27.4</v>
       </c>
       <c r="G21" t="n">
-        <v>-21.5</v>
+        <v>-14.7</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>304545</v>
+        <v>349114</v>
       </c>
       <c r="K21" t="n">
-        <v>145301</v>
+        <v>154276</v>
       </c>
       <c r="L21" t="n">
-        <v>48</v>
+        <v>52.93</v>
       </c>
       <c r="M21" t="n">
-        <v>65.17</v>
+        <v>75.48</v>
       </c>
       <c r="N21" t="n">
-        <v>20.7</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="22">
@@ -1563,16 +1563,16 @@
         <v>1.14</v>
       </c>
       <c r="D22" t="n">
-        <v>1.061</v>
+        <v>1.107</v>
       </c>
       <c r="E22" t="n">
-        <v>-33</v>
+        <v>-24.9</v>
       </c>
       <c r="F22" t="n">
-        <v>-30.9</v>
+        <v>-21.1</v>
       </c>
       <c r="G22" t="n">
-        <v>-28.9</v>
+        <v>-17.3</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1585,25 +1585,25 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>299823</v>
+        <v>360665</v>
       </c>
       <c r="K22" t="n">
-        <v>236407</v>
+        <v>249874</v>
       </c>
       <c r="L22" t="n">
-        <v>11.35</v>
+        <v>13.34</v>
       </c>
       <c r="M22" t="n">
-        <v>12.04</v>
+        <v>14.69</v>
       </c>
       <c r="N22" t="n">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1615,20 +1615,20 @@
         <v>1.35</v>
       </c>
       <c r="D23" t="n">
-        <v>1.088</v>
+        <v>0.885</v>
       </c>
       <c r="E23" t="n">
-        <v>-50.7</v>
+        <v>-2.7</v>
       </c>
       <c r="F23" t="n">
-        <v>-47.8</v>
+        <v>-12</v>
       </c>
       <c r="G23" t="n">
-        <v>-44.8</v>
+        <v>-21.3</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1637,25 +1637,25 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>331519</v>
+        <v>162859</v>
       </c>
       <c r="K23" t="n">
-        <v>277016</v>
+        <v>452584</v>
       </c>
       <c r="L23" t="n">
-        <v>25.73</v>
+        <v>29.19</v>
       </c>
       <c r="M23" t="n">
-        <v>28.85</v>
+        <v>23.61</v>
       </c>
       <c r="N23" t="n">
-        <v>6</v>
+        <v>-18.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="D24" t="n">
-        <v>1.067</v>
+        <v>1.129</v>
       </c>
       <c r="E24" t="n">
-        <v>-50.3</v>
+        <v>-41.6</v>
       </c>
       <c r="F24" t="n">
-        <v>-47.9</v>
+        <v>-36.9</v>
       </c>
       <c r="G24" t="n">
-        <v>-45.5</v>
+        <v>-32.3</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1689,25 +1689,25 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>364200</v>
+        <v>369687</v>
       </c>
       <c r="K24" t="n">
-        <v>312883</v>
+        <v>289955</v>
       </c>
       <c r="L24" t="n">
-        <v>18.17</v>
+        <v>32.09</v>
       </c>
       <c r="M24" t="n">
-        <v>19.93</v>
+        <v>37.2</v>
       </c>
       <c r="N24" t="n">
-        <v>4.8</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1716,19 +1716,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.72</v>
+        <v>1.37</v>
       </c>
       <c r="D25" t="n">
-        <v>0.969</v>
+        <v>1.098</v>
       </c>
       <c r="E25" t="n">
-        <v>-44.9</v>
+        <v>-39.9</v>
       </c>
       <c r="F25" t="n">
-        <v>-51.1</v>
+        <v>-36.1</v>
       </c>
       <c r="G25" t="n">
-        <v>-57.3</v>
+        <v>-32.3</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1741,19 +1741,19 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>400872</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>325714</v>
       </c>
       <c r="L25" t="n">
-        <v>3.12</v>
+        <v>22.91</v>
       </c>
       <c r="M25" t="n">
-        <v>2.41</v>
+        <v>25.81</v>
       </c>
       <c r="N25" t="n">
-        <v>-12.4</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -823,7 +823,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -832,75 +832,75 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="D8" t="n">
-        <v>1.121</v>
+        <v>1.263</v>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>-0.7</v>
       </c>
       <c r="F8" t="n">
-        <v>14.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>21.5</v>
+        <v>20.3</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>HOLD (fairly valued)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>BUY (undervalued)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>BUY (undervalued)</t>
-        </is>
-      </c>
       <c r="J8" t="n">
-        <v>14332</v>
+        <v>21504</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>28.19</v>
+        <v>16.28</v>
       </c>
       <c r="M8" t="n">
-        <v>32.02</v>
+        <v>19.72</v>
       </c>
       <c r="N8" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="D9" t="n">
-        <v>1.201</v>
+        <v>1.121</v>
       </c>
       <c r="E9" t="n">
-        <v>-9.1</v>
+        <v>5.1</v>
       </c>
       <c r="F9" t="n">
-        <v>5.6</v>
+        <v>12.2</v>
       </c>
       <c r="G9" t="n">
-        <v>20.3</v>
+        <v>19.4</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -909,50 +909,50 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>76803</v>
+        <v>14427</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>14.15</v>
+        <v>27.69</v>
       </c>
       <c r="M9" t="n">
-        <v>18.74</v>
+        <v>31.46</v>
       </c>
       <c r="N9" t="n">
-        <v>29.4</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="D10" t="n">
-        <v>1.263</v>
+        <v>1.201</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7</v>
+        <v>-10.9</v>
       </c>
       <c r="F10" t="n">
-        <v>9.800000000000001</v>
+        <v>3.6</v>
       </c>
       <c r="G10" t="n">
-        <v>20.3</v>
+        <v>18.1</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>21504</v>
+        <v>76803</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>16.28</v>
+        <v>13.87</v>
       </c>
       <c r="M10" t="n">
-        <v>19.72</v>
+        <v>18.39</v>
       </c>
       <c r="N10" t="n">
-        <v>21</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -988,50 +988,50 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="D11" t="n">
-        <v>0.862</v>
+        <v>1.153</v>
       </c>
       <c r="E11" t="n">
-        <v>42.3</v>
+        <v>-2.8</v>
       </c>
       <c r="F11" t="n">
-        <v>27.9</v>
+        <v>4.9</v>
       </c>
       <c r="G11" t="n">
-        <v>13.5</v>
+        <v>12.7</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>HOLD (fairly valued)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>BUY (undervalued)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>BUY (undervalued)</t>
-        </is>
-      </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>37673</v>
       </c>
       <c r="K11" t="n">
-        <v>871</v>
+        <v>667</v>
       </c>
       <c r="L11" t="n">
-        <v>9.82</v>
+        <v>28.65</v>
       </c>
       <c r="M11" t="n">
-        <v>7.83</v>
+        <v>33.23</v>
       </c>
       <c r="N11" t="n">
-        <v>-28.9</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1040,23 +1040,23 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.82</v>
+        <v>0.88</v>
       </c>
       <c r="D12" t="n">
-        <v>1.153</v>
+        <v>0.862</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8</v>
+        <v>38.6</v>
       </c>
       <c r="F12" t="n">
-        <v>4.9</v>
+        <v>24.4</v>
       </c>
       <c r="G12" t="n">
-        <v>12.7</v>
+        <v>10.3</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1065,19 +1065,19 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>37673</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>667</v>
+        <v>875</v>
       </c>
       <c r="L12" t="n">
-        <v>28.65</v>
+        <v>9.56</v>
       </c>
       <c r="M12" t="n">
-        <v>33.23</v>
+        <v>7.61</v>
       </c>
       <c r="N12" t="n">
-        <v>15.5</v>
+        <v>-28.4</v>
       </c>
     </row>
     <row r="13">
@@ -1135,7 +1135,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="D14" t="n">
-        <v>1.13</v>
+        <v>1.333</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.7</v>
+        <v>-23.7</v>
       </c>
       <c r="F14" t="n">
-        <v>-1</v>
+        <v>-9.6</v>
       </c>
       <c r="G14" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1165,29 +1165,29 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>36132</v>
+        <v>138721</v>
       </c>
       <c r="K14" t="n">
-        <v>14275</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>23.56</v>
+        <v>30.55</v>
       </c>
       <c r="M14" t="n">
-        <v>26.95</v>
+        <v>41.83</v>
       </c>
       <c r="N14" t="n">
-        <v>13.3</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1196,23 +1196,23 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.62</v>
+        <v>0.89</v>
       </c>
       <c r="D15" t="n">
-        <v>0.979</v>
+        <v>1.13</v>
       </c>
       <c r="E15" t="n">
-        <v>6.7</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>5.8</v>
+        <v>-2.7</v>
       </c>
       <c r="G15" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1221,25 +1221,25 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>12804</v>
+        <v>36393</v>
       </c>
       <c r="K15" t="n">
-        <v>14972</v>
+        <v>14378</v>
       </c>
       <c r="L15" t="n">
-        <v>20.34</v>
+        <v>23.15</v>
       </c>
       <c r="M15" t="n">
-        <v>20</v>
+        <v>26.5</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.8</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1248,23 +1248,23 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.84</v>
+        <v>0.62</v>
       </c>
       <c r="D16" t="n">
-        <v>1.333</v>
+        <v>0.979</v>
       </c>
       <c r="E16" t="n">
-        <v>-23.7</v>
+        <v>5.4</v>
       </c>
       <c r="F16" t="n">
-        <v>-9.6</v>
+        <v>4.5</v>
       </c>
       <c r="G16" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1273,19 +1273,19 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>138721</v>
+        <v>12888</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>15070</v>
       </c>
       <c r="L16" t="n">
-        <v>30.55</v>
+        <v>20.1</v>
       </c>
       <c r="M16" t="n">
-        <v>41.83</v>
+        <v>19.76</v>
       </c>
       <c r="N16" t="n">
-        <v>28.2</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="17">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -523,16 +523,16 @@
         <v>0.34</v>
       </c>
       <c r="D2" t="n">
-        <v>1.216</v>
+        <v>1.197</v>
       </c>
       <c r="E2" t="n">
-        <v>42.1</v>
+        <v>45.1</v>
       </c>
       <c r="F2" t="n">
-        <v>62.2</v>
+        <v>63.9</v>
       </c>
       <c r="G2" t="n">
-        <v>82.3</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -554,10 +554,10 @@
         <v>56.36</v>
       </c>
       <c r="M2" t="n">
-        <v>72.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>40.2</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="3">
@@ -575,16 +575,16 @@
         <v>0.9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.967</v>
+        <v>0.968</v>
       </c>
       <c r="E3" t="n">
-        <v>50.2</v>
+        <v>49.7</v>
       </c>
       <c r="F3" t="n">
-        <v>43.4</v>
+        <v>43.1</v>
       </c>
       <c r="G3" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -606,10 +606,10 @@
         <v>33.5</v>
       </c>
       <c r="M3" t="n">
-        <v>30.5</v>
+        <v>30.57</v>
       </c>
       <c r="N3" t="n">
-        <v>-13.4</v>
+        <v>-13.1</v>
       </c>
     </row>
     <row r="4">
@@ -627,16 +627,16 @@
         <v>0.75</v>
       </c>
       <c r="D4" t="n">
-        <v>1.305</v>
+        <v>1.325</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2</v>
+        <v>-0.7</v>
       </c>
       <c r="F4" t="n">
-        <v>15.7</v>
+        <v>14.5</v>
       </c>
       <c r="G4" t="n">
-        <v>30.1</v>
+        <v>29.7</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>19341</v>
+        <v>36896</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>40.54</v>
       </c>
       <c r="M4" t="n">
-        <v>52.14</v>
+        <v>52.92</v>
       </c>
       <c r="N4" t="n">
-        <v>28.9</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="5">
@@ -679,16 +679,16 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>1.534</v>
+        <v>1.491</v>
       </c>
       <c r="E5" t="n">
-        <v>-10.6</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>8.6</v>
+        <v>9.9</v>
       </c>
       <c r="G5" t="n">
-        <v>27.7</v>
+        <v>28</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>73052</v>
+        <v>62221</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -710,10 +710,10 @@
         <v>70.90000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>101.32</v>
+        <v>98.92</v>
       </c>
       <c r="N5" t="n">
-        <v>38.4</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="6">
@@ -731,16 +731,16 @@
         <v>0.73</v>
       </c>
       <c r="D6" t="n">
-        <v>1.473</v>
+        <v>1.422</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="F6" t="n">
-        <v>12.7</v>
+        <v>14.2</v>
       </c>
       <c r="G6" t="n">
-        <v>24.4</v>
+        <v>24.9</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>24452</v>
+        <v>9573</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -762,10 +762,10 @@
         <v>73.18000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>90.15000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="N6" t="n">
-        <v>23.4</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="7">
@@ -783,13 +783,13 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>1.119</v>
+        <v>1.134</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1</v>
+        <v>-1.1</v>
       </c>
       <c r="F7" t="n">
-        <v>11.7</v>
+        <v>10.6</v>
       </c>
       <c r="G7" t="n">
         <v>22.3</v>
@@ -814,10 +814,10 @@
         <v>13.14</v>
       </c>
       <c r="M7" t="n">
-        <v>15.9</v>
+        <v>16.24</v>
       </c>
       <c r="N7" t="n">
-        <v>21.3</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="8">
@@ -835,16 +835,16 @@
         <v>0.75</v>
       </c>
       <c r="D8" t="n">
-        <v>1.263</v>
+        <v>1.215</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7</v>
+        <v>2.8</v>
       </c>
       <c r="F8" t="n">
-        <v>9.800000000000001</v>
+        <v>11.7</v>
       </c>
       <c r="G8" t="n">
-        <v>20.3</v>
+        <v>20.6</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>21504</v>
+        <v>16487</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -866,10 +866,10 @@
         <v>16.28</v>
       </c>
       <c r="M8" t="n">
-        <v>19.72</v>
+        <v>19.09</v>
       </c>
       <c r="N8" t="n">
-        <v>21</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="9">
@@ -887,29 +887,29 @@
         <v>0.78</v>
       </c>
       <c r="D9" t="n">
-        <v>1.121</v>
+        <v>1.128</v>
       </c>
       <c r="E9" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="F9" t="n">
-        <v>12.2</v>
+        <v>11.8</v>
       </c>
       <c r="G9" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>HOLD (fairly valued)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>BUY (undervalued)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>BUY (undervalued)</t>
-        </is>
-      </c>
       <c r="J9" t="n">
-        <v>14427</v>
+        <v>15171</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -918,10 +918,10 @@
         <v>27.69</v>
       </c>
       <c r="M9" t="n">
-        <v>31.46</v>
+        <v>31.67</v>
       </c>
       <c r="N9" t="n">
-        <v>14.3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -939,16 +939,16 @@
         <v>0.73</v>
       </c>
       <c r="D10" t="n">
-        <v>1.201</v>
+        <v>1.195</v>
       </c>
       <c r="E10" t="n">
-        <v>-10.9</v>
+        <v>-10.2</v>
       </c>
       <c r="F10" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>76803</v>
+        <v>73724</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -970,10 +970,10 @@
         <v>13.87</v>
       </c>
       <c r="M10" t="n">
-        <v>18.39</v>
+        <v>18.25</v>
       </c>
       <c r="N10" t="n">
-        <v>29.1</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="11">
@@ -991,16 +991,16 @@
         <v>0.82</v>
       </c>
       <c r="D11" t="n">
-        <v>1.153</v>
+        <v>1.132</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8</v>
+        <v>-0.7</v>
       </c>
       <c r="F11" t="n">
-        <v>4.9</v>
+        <v>6.1</v>
       </c>
       <c r="G11" t="n">
-        <v>12.7</v>
+        <v>13</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>37673</v>
+        <v>33189</v>
       </c>
       <c r="K11" t="n">
-        <v>667</v>
+        <v>1050</v>
       </c>
       <c r="L11" t="n">
         <v>28.65</v>
       </c>
       <c r="M11" t="n">
-        <v>33.23</v>
+        <v>32.61</v>
       </c>
       <c r="N11" t="n">
-        <v>15.5</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="12">
@@ -1043,16 +1043,16 @@
         <v>0.88</v>
       </c>
       <c r="D12" t="n">
-        <v>0.862</v>
+        <v>0.866</v>
       </c>
       <c r="E12" t="n">
-        <v>38.6</v>
+        <v>37.4</v>
       </c>
       <c r="F12" t="n">
-        <v>24.4</v>
+        <v>23.8</v>
       </c>
       <c r="G12" t="n">
-        <v>10.3</v>
+        <v>10.1</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1068,16 +1068,16 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>875</v>
+        <v>851</v>
       </c>
       <c r="L12" t="n">
         <v>9.56</v>
       </c>
       <c r="M12" t="n">
-        <v>7.61</v>
+        <v>7.67</v>
       </c>
       <c r="N12" t="n">
-        <v>-28.4</v>
+        <v>-27.3</v>
       </c>
     </row>
     <row r="13">
@@ -1095,16 +1095,16 @@
         <v>0.86</v>
       </c>
       <c r="D13" t="n">
-        <v>1.437</v>
+        <v>1.446</v>
       </c>
       <c r="E13" t="n">
-        <v>-22.9</v>
+        <v>-23.4</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.8</v>
+        <v>-7.1</v>
       </c>
       <c r="G13" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1117,19 +1117,19 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>87044</v>
+        <v>88595</v>
       </c>
       <c r="K13" t="n">
-        <v>7871</v>
+        <v>7828</v>
       </c>
       <c r="L13" t="n">
         <v>5.61</v>
       </c>
       <c r="M13" t="n">
-        <v>7.95</v>
+        <v>8</v>
       </c>
       <c r="N13" t="n">
-        <v>32.3</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="14">
@@ -1147,13 +1147,13 @@
         <v>0.84</v>
       </c>
       <c r="D14" t="n">
-        <v>1.333</v>
+        <v>1.335</v>
       </c>
       <c r="E14" t="n">
-        <v>-23.7</v>
+        <v>-23.9</v>
       </c>
       <c r="F14" t="n">
-        <v>-9.6</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>4.4</v>
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>138721</v>
+        <v>139786</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1178,10 +1178,10 @@
         <v>30.55</v>
       </c>
       <c r="M14" t="n">
-        <v>41.83</v>
+        <v>41.92</v>
       </c>
       <c r="N14" t="n">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="15">
@@ -1199,13 +1199,13 @@
         <v>0.89</v>
       </c>
       <c r="D15" t="n">
-        <v>1.13</v>
+        <v>1.124</v>
       </c>
       <c r="E15" t="n">
-        <v>-9.199999999999999</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.7</v>
+        <v>-2.4</v>
       </c>
       <c r="G15" t="n">
         <v>3.9</v>
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>36393</v>
+        <v>35366</v>
       </c>
       <c r="K15" t="n">
-        <v>14378</v>
+        <v>14346</v>
       </c>
       <c r="L15" t="n">
         <v>23.15</v>
       </c>
       <c r="M15" t="n">
-        <v>26.5</v>
+        <v>26.35</v>
       </c>
       <c r="N15" t="n">
-        <v>13.1</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="16">
@@ -1251,20 +1251,20 @@
         <v>0.62</v>
       </c>
       <c r="D16" t="n">
-        <v>0.979</v>
+        <v>1.008</v>
       </c>
       <c r="E16" t="n">
-        <v>5.4</v>
+        <v>2.8</v>
       </c>
       <c r="F16" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="G16" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1273,19 +1273,19 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>12888</v>
+        <v>15989</v>
       </c>
       <c r="K16" t="n">
-        <v>15070</v>
+        <v>15158</v>
       </c>
       <c r="L16" t="n">
         <v>20.1</v>
       </c>
       <c r="M16" t="n">
-        <v>19.76</v>
+        <v>20.23</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="17">
@@ -1303,16 +1303,16 @@
         <v>0.85</v>
       </c>
       <c r="D17" t="n">
-        <v>2.171</v>
+        <v>2.146</v>
       </c>
       <c r="E17" t="n">
-        <v>-56</v>
+        <v>-55.4</v>
       </c>
       <c r="F17" t="n">
-        <v>-27.1</v>
+        <v>-26.8</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>431629</v>
+        <v>422616</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1334,16 +1334,16 @@
         <v>2.72</v>
       </c>
       <c r="M17" t="n">
-        <v>6.28</v>
+        <v>6.2</v>
       </c>
       <c r="N17" t="n">
-        <v>57.7</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1352,23 +1352,23 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.72</v>
+        <v>0.98</v>
       </c>
       <c r="D18" t="n">
-        <v>0.965</v>
+        <v>1.03</v>
       </c>
       <c r="E18" t="n">
-        <v>11.2</v>
+        <v>-3.2</v>
       </c>
       <c r="F18" t="n">
-        <v>3.2</v>
+        <v>-1.8</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.7</v>
+        <v>-0.4</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1377,25 +1377,25 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>18774</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>16594</v>
       </c>
       <c r="L18" t="n">
-        <v>6.2</v>
+        <v>0.38</v>
       </c>
       <c r="M18" t="n">
-        <v>5.32</v>
+        <v>0.39</v>
       </c>
       <c r="N18" t="n">
-        <v>-15.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1404,50 +1404,50 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.04</v>
+        <v>0.72</v>
       </c>
       <c r="D19" t="n">
-        <v>1.088</v>
+        <v>0.963</v>
       </c>
       <c r="E19" t="n">
-        <v>-15.4</v>
+        <v>12</v>
       </c>
       <c r="F19" t="n">
-        <v>-10.5</v>
+        <v>3.6</v>
       </c>
       <c r="G19" t="n">
-        <v>-5.5</v>
+        <v>-4.9</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>112236</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>44184</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>2.06</v>
+        <v>6.2</v>
       </c>
       <c r="M19" t="n">
-        <v>2.31</v>
+        <v>5.27</v>
       </c>
       <c r="N19" t="n">
-        <v>9.9</v>
+        <v>-16.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BWLP</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1456,19 +1456,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.97</v>
+        <v>1.04</v>
       </c>
       <c r="D20" t="n">
-        <v>1.212</v>
+        <v>1.108</v>
       </c>
       <c r="E20" t="n">
-        <v>-25.6</v>
+        <v>-17.8</v>
       </c>
       <c r="F20" t="n">
-        <v>-16.6</v>
+        <v>-11.9</v>
       </c>
       <c r="G20" t="n">
-        <v>-7.5</v>
+        <v>-6</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1481,46 +1481,46 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>146334</v>
+        <v>130005</v>
       </c>
       <c r="K20" t="n">
-        <v>57312</v>
+        <v>46936</v>
       </c>
       <c r="L20" t="n">
-        <v>14.46</v>
+        <v>2.06</v>
       </c>
       <c r="M20" t="n">
-        <v>18</v>
+        <v>2.36</v>
       </c>
       <c r="N20" t="n">
-        <v>18.2</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>BWLP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.11</v>
+        <v>0.97</v>
       </c>
       <c r="D21" t="n">
-        <v>1.515</v>
+        <v>1.245</v>
       </c>
       <c r="E21" t="n">
-        <v>-40.2</v>
+        <v>-28</v>
       </c>
       <c r="F21" t="n">
-        <v>-27.4</v>
+        <v>-17.9</v>
       </c>
       <c r="G21" t="n">
-        <v>-14.7</v>
+        <v>-7.7</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1533,46 +1533,46 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>349114</v>
+        <v>161521</v>
       </c>
       <c r="K21" t="n">
-        <v>154276</v>
+        <v>58456</v>
       </c>
       <c r="L21" t="n">
-        <v>52.93</v>
+        <v>14.46</v>
       </c>
       <c r="M21" t="n">
-        <v>75.48</v>
+        <v>18.55</v>
       </c>
       <c r="N21" t="n">
-        <v>25.5</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="D22" t="n">
-        <v>1.107</v>
+        <v>1.475</v>
       </c>
       <c r="E22" t="n">
-        <v>-24.9</v>
+        <v>-38.6</v>
       </c>
       <c r="F22" t="n">
-        <v>-21.1</v>
+        <v>-26.5</v>
       </c>
       <c r="G22" t="n">
-        <v>-17.3</v>
+        <v>-14.4</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1585,25 +1585,25 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>360665</v>
+        <v>330395</v>
       </c>
       <c r="K22" t="n">
-        <v>249874</v>
+        <v>150506</v>
       </c>
       <c r="L22" t="n">
-        <v>13.34</v>
+        <v>52.93</v>
       </c>
       <c r="M22" t="n">
-        <v>14.69</v>
+        <v>73.75</v>
       </c>
       <c r="N22" t="n">
-        <v>7.6</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1612,23 +1612,23 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="D23" t="n">
-        <v>0.885</v>
+        <v>1.082</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7</v>
+        <v>-22.9</v>
       </c>
       <c r="F23" t="n">
-        <v>-12</v>
+        <v>-19.9</v>
       </c>
       <c r="G23" t="n">
-        <v>-21.3</v>
+        <v>-16.9</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1637,25 +1637,25 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>162859</v>
+        <v>327678</v>
       </c>
       <c r="K23" t="n">
-        <v>452584</v>
+        <v>242573</v>
       </c>
       <c r="L23" t="n">
-        <v>29.19</v>
+        <v>13.34</v>
       </c>
       <c r="M23" t="n">
-        <v>23.61</v>
+        <v>14.38</v>
       </c>
       <c r="N23" t="n">
-        <v>-18.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1667,41 +1667,41 @@
         <v>1.35</v>
       </c>
       <c r="D24" t="n">
-        <v>1.129</v>
+        <v>0.886</v>
       </c>
       <c r="E24" t="n">
-        <v>-41.6</v>
+        <v>-3.2</v>
       </c>
       <c r="F24" t="n">
-        <v>-36.9</v>
+        <v>-12.3</v>
       </c>
       <c r="G24" t="n">
-        <v>-32.3</v>
+        <v>-21.4</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
+          <t>HOLD (fairly valued)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT (overvalued)</t>
-        </is>
-      </c>
       <c r="J24" t="n">
-        <v>369687</v>
+        <v>169874</v>
       </c>
       <c r="K24" t="n">
-        <v>289955</v>
+        <v>455116</v>
       </c>
       <c r="L24" t="n">
-        <v>32.09</v>
+        <v>29.19</v>
       </c>
       <c r="M24" t="n">
-        <v>37.2</v>
+        <v>23.7</v>
       </c>
       <c r="N24" t="n">
-        <v>9.300000000000001</v>
+        <v>-18.2</v>
       </c>
     </row>
     <row r="25">
@@ -1719,16 +1719,16 @@
         <v>1.37</v>
       </c>
       <c r="D25" t="n">
-        <v>1.098</v>
+        <v>1.074</v>
       </c>
       <c r="E25" t="n">
-        <v>-39.9</v>
+        <v>-37.9</v>
       </c>
       <c r="F25" t="n">
-        <v>-36.1</v>
+        <v>-35</v>
       </c>
       <c r="G25" t="n">
-        <v>-32.3</v>
+        <v>-32</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1741,19 +1741,71 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>400872</v>
+        <v>372609</v>
       </c>
       <c r="K25" t="n">
-        <v>325714</v>
+        <v>315826</v>
       </c>
       <c r="L25" t="n">
         <v>22.91</v>
       </c>
       <c r="M25" t="n">
-        <v>25.81</v>
+        <v>25.1</v>
       </c>
       <c r="N25" t="n">
-        <v>7.6</v>
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ECO</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>whole-company</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1.118</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-40.8</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-36.5</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-32.2</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>359265</v>
+      </c>
+      <c r="K26" t="n">
+        <v>286422</v>
+      </c>
+      <c r="L26" t="n">
+        <v>32.09</v>
+      </c>
+      <c r="M26" t="n">
+        <v>36.76</v>
+      </c>
+      <c r="N26" t="n">
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -523,16 +523,16 @@
         <v>0.34</v>
       </c>
       <c r="D2" t="n">
-        <v>1.197</v>
+        <v>1.218</v>
       </c>
       <c r="E2" t="n">
-        <v>45.1</v>
+        <v>44.9</v>
       </c>
       <c r="F2" t="n">
-        <v>63.9</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>82.59999999999999</v>
+        <v>86</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -551,13 +551,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>56.36</v>
+        <v>57.6</v>
       </c>
       <c r="M2" t="n">
-        <v>70.90000000000001</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>37.5</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="3">
@@ -575,16 +575,16 @@
         <v>0.9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.968</v>
+        <v>0.971</v>
       </c>
       <c r="E3" t="n">
-        <v>49.7</v>
+        <v>58.3</v>
       </c>
       <c r="F3" t="n">
-        <v>43.1</v>
+        <v>52.3</v>
       </c>
       <c r="G3" t="n">
-        <v>36.6</v>
+        <v>46.3</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -603,19 +603,19 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>33.5</v>
+        <v>35.91</v>
       </c>
       <c r="M3" t="n">
-        <v>30.57</v>
+        <v>33.19</v>
       </c>
       <c r="N3" t="n">
-        <v>-13.1</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -624,19 +624,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>1.325</v>
+        <v>1.504</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7</v>
+        <v>-1</v>
       </c>
       <c r="F4" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="G4" t="n">
-        <v>29.7</v>
+        <v>38.9</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -649,25 +649,25 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>36896</v>
+        <v>65353</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>40.54</v>
+        <v>77.13</v>
       </c>
       <c r="M4" t="n">
-        <v>52.92</v>
+        <v>108.13</v>
       </c>
       <c r="N4" t="n">
-        <v>30.3</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -676,23 +676,23 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="D5" t="n">
-        <v>1.491</v>
+        <v>1.337</v>
       </c>
       <c r="E5" t="n">
-        <v>-8.300000000000001</v>
+        <v>-1.7</v>
       </c>
       <c r="F5" t="n">
-        <v>9.9</v>
+        <v>13.9</v>
       </c>
       <c r="G5" t="n">
-        <v>28</v>
+        <v>29.4</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -701,25 +701,25 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>62221</v>
+        <v>46961</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>70.90000000000001</v>
+        <v>40.54</v>
       </c>
       <c r="M5" t="n">
-        <v>98.92</v>
+        <v>53.37</v>
       </c>
       <c r="N5" t="n">
-        <v>36.3</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -728,23 +728,23 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.73</v>
+        <v>0.82</v>
       </c>
       <c r="D6" t="n">
-        <v>1.422</v>
+        <v>1.151</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5</v>
+        <v>8.4</v>
       </c>
       <c r="F6" t="n">
-        <v>14.2</v>
+        <v>16.7</v>
       </c>
       <c r="G6" t="n">
         <v>24.9</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -753,25 +753,25 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>9573</v>
+        <v>37275</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>701</v>
       </c>
       <c r="L6" t="n">
-        <v>73.18000000000001</v>
+        <v>31.9</v>
       </c>
       <c r="M6" t="n">
-        <v>88.3</v>
+        <v>36.76</v>
       </c>
       <c r="N6" t="n">
-        <v>21.4</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -780,19 +780,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="D7" t="n">
-        <v>1.134</v>
+        <v>1.245</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>10.6</v>
+        <v>14.3</v>
       </c>
       <c r="G7" t="n">
-        <v>22.3</v>
+        <v>24.5</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -805,25 +805,25 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>19623</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>13.14</v>
+        <v>16.83</v>
       </c>
       <c r="M7" t="n">
-        <v>16.24</v>
+        <v>20.14</v>
       </c>
       <c r="N7" t="n">
-        <v>23.3</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -832,19 +832,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="D8" t="n">
-        <v>1.215</v>
+        <v>1.468</v>
       </c>
       <c r="E8" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="F8" t="n">
-        <v>11.7</v>
+        <v>12.9</v>
       </c>
       <c r="G8" t="n">
-        <v>20.6</v>
+        <v>24.5</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -857,25 +857,25 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>16487</v>
+        <v>22904</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>16.28</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>19.09</v>
+        <v>89.95999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>17.7</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -884,19 +884,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.78</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>1.128</v>
+        <v>1.14</v>
       </c>
       <c r="E9" t="n">
-        <v>4.3</v>
+        <v>-1.9</v>
       </c>
       <c r="F9" t="n">
-        <v>11.8</v>
+        <v>10.2</v>
       </c>
       <c r="G9" t="n">
-        <v>19.3</v>
+        <v>22.3</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -909,46 +909,46 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>15171</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>27.69</v>
+        <v>13.14</v>
       </c>
       <c r="M9" t="n">
-        <v>31.67</v>
+        <v>16.38</v>
       </c>
       <c r="N9" t="n">
-        <v>15</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.73</v>
+        <v>0.86</v>
       </c>
       <c r="D10" t="n">
-        <v>1.195</v>
+        <v>1.474</v>
       </c>
       <c r="E10" t="n">
-        <v>-10.2</v>
+        <v>-16.7</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="G10" t="n">
-        <v>18.2</v>
+        <v>19.8</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>73724</v>
+        <v>93560</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>7691</v>
       </c>
       <c r="L10" t="n">
-        <v>13.87</v>
+        <v>6.23</v>
       </c>
       <c r="M10" t="n">
-        <v>18.25</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>28.4</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="D11" t="n">
-        <v>1.132</v>
+        <v>1.129</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7</v>
+        <v>4.3</v>
       </c>
       <c r="F11" t="n">
-        <v>6.1</v>
+        <v>11.8</v>
       </c>
       <c r="G11" t="n">
-        <v>13</v>
+        <v>19.3</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1013,77 +1013,77 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>33189</v>
+        <v>15250</v>
       </c>
       <c r="K11" t="n">
-        <v>1050</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>28.65</v>
+        <v>27.69</v>
       </c>
       <c r="M11" t="n">
-        <v>32.61</v>
+        <v>31.69</v>
       </c>
       <c r="N11" t="n">
-        <v>13.7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.88</v>
+        <v>0.73</v>
       </c>
       <c r="D12" t="n">
-        <v>0.866</v>
+        <v>1.212</v>
       </c>
       <c r="E12" t="n">
-        <v>37.4</v>
+        <v>-12.1</v>
       </c>
       <c r="F12" t="n">
-        <v>23.8</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>10.1</v>
+        <v>18.1</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>BUY (undervalued)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>BUY (undervalued)</t>
-        </is>
-      </c>
       <c r="J12" t="n">
+        <v>81778</v>
+      </c>
+      <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="K12" t="n">
-        <v>851</v>
-      </c>
       <c r="L12" t="n">
-        <v>9.56</v>
+        <v>13.87</v>
       </c>
       <c r="M12" t="n">
-        <v>7.67</v>
+        <v>18.63</v>
       </c>
       <c r="N12" t="n">
-        <v>-27.3</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1092,23 +1092,23 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="D13" t="n">
-        <v>1.446</v>
+        <v>0.878</v>
       </c>
       <c r="E13" t="n">
-        <v>-23.4</v>
+        <v>34.1</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.1</v>
+        <v>22</v>
       </c>
       <c r="G13" t="n">
-        <v>9.300000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1117,19 +1117,19 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>88595</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>7828</v>
+        <v>785</v>
       </c>
       <c r="L13" t="n">
-        <v>5.61</v>
+        <v>9.56</v>
       </c>
       <c r="M13" t="n">
-        <v>8</v>
+        <v>7.83</v>
       </c>
       <c r="N13" t="n">
-        <v>32.7</v>
+        <v>-24.3</v>
       </c>
     </row>
     <row r="14">
@@ -1147,16 +1147,16 @@
         <v>0.84</v>
       </c>
       <c r="D14" t="n">
-        <v>1.335</v>
+        <v>1.379</v>
       </c>
       <c r="E14" t="n">
-        <v>-23.9</v>
+        <v>-26.6</v>
       </c>
       <c r="F14" t="n">
-        <v>-9.699999999999999</v>
+        <v>-11.2</v>
       </c>
       <c r="G14" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>139786</v>
+        <v>157417</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1178,10 +1178,10 @@
         <v>30.55</v>
       </c>
       <c r="M14" t="n">
-        <v>41.92</v>
+        <v>43.39</v>
       </c>
       <c r="N14" t="n">
-        <v>28.3</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="15">
@@ -1199,13 +1199,13 @@
         <v>0.89</v>
       </c>
       <c r="D15" t="n">
-        <v>1.124</v>
+        <v>1.128</v>
       </c>
       <c r="E15" t="n">
-        <v>-8.699999999999999</v>
+        <v>-9</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.4</v>
+        <v>-2.6</v>
       </c>
       <c r="G15" t="n">
         <v>3.9</v>
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>35366</v>
+        <v>36008</v>
       </c>
       <c r="K15" t="n">
-        <v>14346</v>
+        <v>14366</v>
       </c>
       <c r="L15" t="n">
         <v>23.15</v>
       </c>
       <c r="M15" t="n">
-        <v>26.35</v>
+        <v>26.44</v>
       </c>
       <c r="N15" t="n">
-        <v>12.6</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="16">
@@ -1251,16 +1251,16 @@
         <v>0.62</v>
       </c>
       <c r="D16" t="n">
-        <v>1.008</v>
+        <v>1.031</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="F16" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1273,19 +1273,19 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>15989</v>
+        <v>18395</v>
       </c>
       <c r="K16" t="n">
-        <v>15158</v>
+        <v>15226</v>
       </c>
       <c r="L16" t="n">
         <v>20.1</v>
       </c>
       <c r="M16" t="n">
-        <v>20.23</v>
+        <v>20.59</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="17">
@@ -1303,16 +1303,16 @@
         <v>0.85</v>
       </c>
       <c r="D17" t="n">
-        <v>2.146</v>
+        <v>2.208</v>
       </c>
       <c r="E17" t="n">
-        <v>-55.4</v>
+        <v>-56.8</v>
       </c>
       <c r="F17" t="n">
-        <v>-26.8</v>
+        <v>-27.6</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>422616</v>
+        <v>445150</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1334,10 +1334,10 @@
         <v>2.72</v>
       </c>
       <c r="M17" t="n">
-        <v>6.2</v>
+        <v>6.39</v>
       </c>
       <c r="N17" t="n">
-        <v>57.3</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="18">
@@ -1355,13 +1355,13 @@
         <v>0.98</v>
       </c>
       <c r="D18" t="n">
-        <v>1.03</v>
+        <v>1.031</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.2</v>
+        <v>-3.3</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8</v>
+        <v>-1.9</v>
       </c>
       <c r="G18" t="n">
         <v>-0.4</v>
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>18774</v>
+        <v>18872</v>
       </c>
       <c r="K18" t="n">
-        <v>16594</v>
+        <v>16604</v>
       </c>
       <c r="L18" t="n">
         <v>0.38</v>
@@ -1389,7 +1389,7 @@
         <v>0.39</v>
       </c>
       <c r="N18" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1407,16 +1407,16 @@
         <v>0.72</v>
       </c>
       <c r="D19" t="n">
-        <v>0.963</v>
+        <v>0.965</v>
       </c>
       <c r="E19" t="n">
-        <v>12</v>
+        <v>11.3</v>
       </c>
       <c r="F19" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.9</v>
+        <v>-4.7</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1438,10 +1438,10 @@
         <v>6.2</v>
       </c>
       <c r="M19" t="n">
-        <v>5.27</v>
+        <v>5.31</v>
       </c>
       <c r="N19" t="n">
-        <v>-16.9</v>
+        <v>-16.1</v>
       </c>
     </row>
     <row r="20">
@@ -1459,16 +1459,16 @@
         <v>1.04</v>
       </c>
       <c r="D20" t="n">
-        <v>1.108</v>
+        <v>1.115</v>
       </c>
       <c r="E20" t="n">
-        <v>-17.8</v>
+        <v>-18.7</v>
       </c>
       <c r="F20" t="n">
-        <v>-11.9</v>
+        <v>-12.5</v>
       </c>
       <c r="G20" t="n">
-        <v>-6</v>
+        <v>-6.2</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>130005</v>
+        <v>137011</v>
       </c>
       <c r="K20" t="n">
-        <v>46936</v>
+        <v>48022</v>
       </c>
       <c r="L20" t="n">
         <v>2.06</v>
       </c>
       <c r="M20" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="N20" t="n">
-        <v>11.7</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="21">
@@ -1511,16 +1511,16 @@
         <v>0.97</v>
       </c>
       <c r="D21" t="n">
-        <v>1.245</v>
+        <v>1.299</v>
       </c>
       <c r="E21" t="n">
-        <v>-28</v>
+        <v>-31.6</v>
       </c>
       <c r="F21" t="n">
-        <v>-17.9</v>
+        <v>-19.8</v>
       </c>
       <c r="G21" t="n">
-        <v>-7.7</v>
+        <v>-8</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>161521</v>
+        <v>186184</v>
       </c>
       <c r="K21" t="n">
-        <v>58456</v>
+        <v>60314</v>
       </c>
       <c r="L21" t="n">
         <v>14.46</v>
       </c>
       <c r="M21" t="n">
-        <v>18.55</v>
+        <v>19.46</v>
       </c>
       <c r="N21" t="n">
-        <v>20.3</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="22">
@@ -1563,16 +1563,16 @@
         <v>1.11</v>
       </c>
       <c r="D22" t="n">
-        <v>1.475</v>
+        <v>1.509</v>
       </c>
       <c r="E22" t="n">
-        <v>-38.6</v>
+        <v>-38.5</v>
       </c>
       <c r="F22" t="n">
-        <v>-26.5</v>
+        <v>-25.6</v>
       </c>
       <c r="G22" t="n">
-        <v>-14.4</v>
+        <v>-12.7</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1585,25 +1585,25 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>330395</v>
+        <v>346197</v>
       </c>
       <c r="K22" t="n">
-        <v>150506</v>
+        <v>153688</v>
       </c>
       <c r="L22" t="n">
-        <v>52.93</v>
+        <v>54.21</v>
       </c>
       <c r="M22" t="n">
-        <v>73.75</v>
+        <v>76.94</v>
       </c>
       <c r="N22" t="n">
-        <v>24.2</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1612,50 +1612,50 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="D23" t="n">
-        <v>1.082</v>
+        <v>0.896</v>
       </c>
       <c r="E23" t="n">
-        <v>-22.9</v>
+        <v>-0.4</v>
       </c>
       <c r="F23" t="n">
-        <v>-19.9</v>
+        <v>-8.9</v>
       </c>
       <c r="G23" t="n">
-        <v>-16.9</v>
+        <v>-17.4</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
+          <t>HOLD (fairly valued)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT (overvalued)</t>
-        </is>
-      </c>
       <c r="J23" t="n">
-        <v>327678</v>
+        <v>206030</v>
       </c>
       <c r="K23" t="n">
-        <v>242573</v>
+        <v>468168</v>
       </c>
       <c r="L23" t="n">
-        <v>13.34</v>
+        <v>30.67</v>
       </c>
       <c r="M23" t="n">
-        <v>14.38</v>
+        <v>25.45</v>
       </c>
       <c r="N23" t="n">
-        <v>6</v>
+        <v>-17</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1664,23 +1664,23 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="D24" t="n">
-        <v>0.886</v>
+        <v>1.13</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2</v>
+        <v>-26.6</v>
       </c>
       <c r="F24" t="n">
-        <v>-12.3</v>
+        <v>-22.1</v>
       </c>
       <c r="G24" t="n">
-        <v>-21.4</v>
+        <v>-17.6</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>169874</v>
+        <v>391452</v>
       </c>
       <c r="K24" t="n">
-        <v>455116</v>
+        <v>256689</v>
       </c>
       <c r="L24" t="n">
-        <v>29.19</v>
+        <v>13.34</v>
       </c>
       <c r="M24" t="n">
-        <v>23.7</v>
+        <v>14.99</v>
       </c>
       <c r="N24" t="n">
-        <v>-18.2</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="25">
@@ -1719,16 +1719,16 @@
         <v>1.37</v>
       </c>
       <c r="D25" t="n">
-        <v>1.074</v>
+        <v>1.103</v>
       </c>
       <c r="E25" t="n">
-        <v>-37.9</v>
+        <v>-40.3</v>
       </c>
       <c r="F25" t="n">
-        <v>-35</v>
+        <v>-36.3</v>
       </c>
       <c r="G25" t="n">
-        <v>-32</v>
+        <v>-32.4</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1741,19 +1741,19 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>372609</v>
+        <v>406711</v>
       </c>
       <c r="K25" t="n">
-        <v>315826</v>
+        <v>327758</v>
       </c>
       <c r="L25" t="n">
         <v>22.91</v>
       </c>
       <c r="M25" t="n">
-        <v>25.1</v>
+        <v>25.95</v>
       </c>
       <c r="N25" t="n">
-        <v>5.9</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="26">
@@ -1771,16 +1771,16 @@
         <v>1.35</v>
       </c>
       <c r="D26" t="n">
-        <v>1.118</v>
+        <v>1.156</v>
       </c>
       <c r="E26" t="n">
-        <v>-40.8</v>
+        <v>-43.4</v>
       </c>
       <c r="F26" t="n">
-        <v>-36.5</v>
+        <v>-38</v>
       </c>
       <c r="G26" t="n">
-        <v>-32.2</v>
+        <v>-32.5</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1793,19 +1793,19 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>359265</v>
+        <v>394899</v>
       </c>
       <c r="K26" t="n">
-        <v>286422</v>
+        <v>298502</v>
       </c>
       <c r="L26" t="n">
         <v>32.09</v>
       </c>
       <c r="M26" t="n">
-        <v>36.76</v>
+        <v>38.27</v>
       </c>
       <c r="N26" t="n">
-        <v>8.6</v>
+        <v>10.9</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -523,13 +523,13 @@
         <v>0.34</v>
       </c>
       <c r="D2" t="n">
-        <v>1.218</v>
+        <v>1.217</v>
       </c>
       <c r="E2" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="F2" t="n">
-        <v>65.40000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="G2" t="n">
         <v>86</v>
@@ -551,13 +551,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>57.6</v>
+        <v>57.64</v>
       </c>
       <c r="M2" t="n">
         <v>73.93000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -523,16 +523,16 @@
         <v>0.34</v>
       </c>
       <c r="D2" t="n">
-        <v>1.217</v>
+        <v>1.24</v>
       </c>
       <c r="E2" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F2" t="n">
-        <v>65.5</v>
+        <v>63.6</v>
       </c>
       <c r="G2" t="n">
-        <v>86</v>
+        <v>85.2</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -551,13 +551,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>57.64</v>
+        <v>56.46</v>
       </c>
       <c r="M2" t="n">
-        <v>73.93000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>41</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="3">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -523,16 +523,16 @@
         <v>0.34</v>
       </c>
       <c r="D2" t="n">
-        <v>1.24</v>
+        <v>1.189</v>
       </c>
       <c r="E2" t="n">
-        <v>42</v>
+        <v>50.1</v>
       </c>
       <c r="F2" t="n">
-        <v>63.6</v>
+        <v>68</v>
       </c>
       <c r="G2" t="n">
-        <v>85.2</v>
+        <v>86</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -554,10 +554,10 @@
         <v>56.46</v>
       </c>
       <c r="M2" t="n">
-        <v>73.59999999999999</v>
+        <v>69.97</v>
       </c>
       <c r="N2" t="n">
-        <v>43.1</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="3">
@@ -575,16 +575,16 @@
         <v>0.9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.971</v>
+        <v>0.965</v>
       </c>
       <c r="E3" t="n">
-        <v>58.3</v>
+        <v>61.8</v>
       </c>
       <c r="F3" t="n">
-        <v>52.3</v>
+        <v>54.5</v>
       </c>
       <c r="G3" t="n">
-        <v>46.3</v>
+        <v>47.3</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -606,10 +606,10 @@
         <v>35.91</v>
       </c>
       <c r="M3" t="n">
-        <v>33.19</v>
+        <v>32.68</v>
       </c>
       <c r="N3" t="n">
-        <v>-12</v>
+        <v>-14.6</v>
       </c>
     </row>
     <row r="4">
@@ -627,16 +627,16 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>1.504</v>
+        <v>1.475</v>
       </c>
       <c r="E4" t="n">
-        <v>-1</v>
+        <v>0.8</v>
       </c>
       <c r="F4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
-        <v>38.9</v>
+        <v>39.1</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>65353</v>
+        <v>58027</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>77.13</v>
       </c>
       <c r="M4" t="n">
-        <v>108.13</v>
+        <v>106.38</v>
       </c>
       <c r="N4" t="n">
-        <v>39.8</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="5">
@@ -679,16 +679,16 @@
         <v>0.75</v>
       </c>
       <c r="D5" t="n">
-        <v>1.337</v>
+        <v>1.308</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.7</v>
+        <v>0.9</v>
       </c>
       <c r="F5" t="n">
-        <v>13.9</v>
+        <v>15.5</v>
       </c>
       <c r="G5" t="n">
-        <v>29.4</v>
+        <v>30.1</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>46961</v>
+        <v>21682</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -710,10 +710,10 @@
         <v>40.54</v>
       </c>
       <c r="M5" t="n">
-        <v>53.37</v>
+        <v>52.24</v>
       </c>
       <c r="N5" t="n">
-        <v>31.1</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="6">
@@ -731,16 +731,16 @@
         <v>0.82</v>
       </c>
       <c r="D6" t="n">
-        <v>1.151</v>
+        <v>1.118</v>
       </c>
       <c r="E6" t="n">
-        <v>8.4</v>
+        <v>12.1</v>
       </c>
       <c r="F6" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="G6" t="n">
-        <v>24.9</v>
+        <v>25.5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -753,25 +753,25 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>37275</v>
+        <v>30223</v>
       </c>
       <c r="K6" t="n">
-        <v>701</v>
+        <v>1304</v>
       </c>
       <c r="L6" t="n">
         <v>31.9</v>
       </c>
       <c r="M6" t="n">
-        <v>36.76</v>
+        <v>35.72</v>
       </c>
       <c r="N6" t="n">
-        <v>16.5</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -780,19 +780,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="D7" t="n">
-        <v>1.245</v>
+        <v>1.402</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="F7" t="n">
-        <v>14.3</v>
+        <v>14.7</v>
       </c>
       <c r="G7" t="n">
-        <v>24.5</v>
+        <v>25</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -805,25 +805,25 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>19623</v>
+        <v>3984</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>16.83</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>20.14</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -832,23 +832,23 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="D8" t="n">
-        <v>1.468</v>
+        <v>1.178</v>
       </c>
       <c r="E8" t="n">
-        <v>1.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>12.9</v>
+        <v>17.1</v>
       </c>
       <c r="G8" t="n">
-        <v>24.5</v>
+        <v>24.9</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>22904</v>
+        <v>12560</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>73.18000000000001</v>
+        <v>16.83</v>
       </c>
       <c r="M8" t="n">
-        <v>89.95999999999999</v>
+        <v>19.23</v>
       </c>
       <c r="N8" t="n">
-        <v>23.2</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="9">
@@ -887,16 +887,16 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>1.14</v>
+        <v>1.105</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9</v>
+        <v>3.3</v>
       </c>
       <c r="F9" t="n">
-        <v>10.2</v>
+        <v>12.9</v>
       </c>
       <c r="G9" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -918,10 +918,10 @@
         <v>13.14</v>
       </c>
       <c r="M9" t="n">
-        <v>16.38</v>
+        <v>15.57</v>
       </c>
       <c r="N9" t="n">
-        <v>24.2</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="10">
@@ -939,16 +939,16 @@
         <v>0.86</v>
       </c>
       <c r="D10" t="n">
-        <v>1.474</v>
+        <v>1.434</v>
       </c>
       <c r="E10" t="n">
-        <v>-16.7</v>
+        <v>-14.1</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="G10" t="n">
-        <v>19.8</v>
+        <v>20.4</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>93560</v>
+        <v>86423</v>
       </c>
       <c r="K10" t="n">
-        <v>7691</v>
+        <v>7889</v>
       </c>
       <c r="L10" t="n">
         <v>6.23</v>
       </c>
       <c r="M10" t="n">
-        <v>8.960000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="N10" t="n">
-        <v>36.5</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="11">
@@ -991,20 +991,20 @@
         <v>0.78</v>
       </c>
       <c r="D11" t="n">
-        <v>1.129</v>
+        <v>1.071</v>
       </c>
       <c r="E11" t="n">
-        <v>4.3</v>
+        <v>11.2</v>
       </c>
       <c r="F11" t="n">
-        <v>11.8</v>
+        <v>15.6</v>
       </c>
       <c r="G11" t="n">
-        <v>19.3</v>
+        <v>20</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>15250</v>
+        <v>8685</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1022,10 +1022,10 @@
         <v>27.69</v>
       </c>
       <c r="M11" t="n">
-        <v>31.69</v>
+        <v>29.88</v>
       </c>
       <c r="N11" t="n">
-        <v>15</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1043,16 +1043,16 @@
         <v>0.73</v>
       </c>
       <c r="D12" t="n">
-        <v>1.212</v>
+        <v>1.17</v>
       </c>
       <c r="E12" t="n">
-        <v>-12.1</v>
+        <v>-7.3</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="G12" t="n">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>81778</v>
+        <v>62354</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1074,10 +1074,10 @@
         <v>13.87</v>
       </c>
       <c r="M12" t="n">
-        <v>18.63</v>
+        <v>17.7</v>
       </c>
       <c r="N12" t="n">
-        <v>30.2</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="13">
@@ -1095,16 +1095,16 @@
         <v>0.88</v>
       </c>
       <c r="D13" t="n">
-        <v>0.878</v>
+        <v>0.856</v>
       </c>
       <c r="E13" t="n">
-        <v>34.1</v>
+        <v>40.2</v>
       </c>
       <c r="F13" t="n">
-        <v>22</v>
+        <v>25.3</v>
       </c>
       <c r="G13" t="n">
-        <v>9.800000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1120,22 +1120,22 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>785</v>
+        <v>906</v>
       </c>
       <c r="L13" t="n">
         <v>9.56</v>
       </c>
       <c r="M13" t="n">
-        <v>7.83</v>
+        <v>7.53</v>
       </c>
       <c r="N13" t="n">
-        <v>-24.3</v>
+        <v>-29.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1144,23 +1144,23 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.84</v>
+        <v>0.89</v>
       </c>
       <c r="D14" t="n">
-        <v>1.379</v>
+        <v>1.079</v>
       </c>
       <c r="E14" t="n">
-        <v>-26.6</v>
+        <v>-4</v>
       </c>
       <c r="F14" t="n">
-        <v>-11.2</v>
+        <v>0.2</v>
       </c>
       <c r="G14" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1169,25 +1169,25 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>157417</v>
+        <v>27466</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>14102</v>
       </c>
       <c r="L14" t="n">
-        <v>30.55</v>
+        <v>23.15</v>
       </c>
       <c r="M14" t="n">
-        <v>43.39</v>
+        <v>25.19</v>
       </c>
       <c r="N14" t="n">
-        <v>30.9</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1196,19 +1196,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="D15" t="n">
-        <v>1.128</v>
+        <v>1.361</v>
       </c>
       <c r="E15" t="n">
-        <v>-9</v>
+        <v>-25.5</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.6</v>
+        <v>-10.6</v>
       </c>
       <c r="G15" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>36008</v>
+        <v>150318</v>
       </c>
       <c r="K15" t="n">
-        <v>14366</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>23.15</v>
+        <v>30.55</v>
       </c>
       <c r="M15" t="n">
-        <v>26.44</v>
+        <v>42.8</v>
       </c>
       <c r="N15" t="n">
-        <v>12.9</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="16">
@@ -1251,41 +1251,41 @@
         <v>0.62</v>
       </c>
       <c r="D16" t="n">
-        <v>1.031</v>
+        <v>0.964</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8</v>
+        <v>6.8</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>5.3</v>
       </c>
       <c r="G16" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
+          <t>BUY (undervalued)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>HOLD (fairly valued)</t>
-        </is>
-      </c>
       <c r="J16" t="n">
-        <v>18395</v>
+        <v>11242</v>
       </c>
       <c r="K16" t="n">
-        <v>15226</v>
+        <v>15024</v>
       </c>
       <c r="L16" t="n">
         <v>20.1</v>
       </c>
       <c r="M16" t="n">
-        <v>20.59</v>
+        <v>19.51</v>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="17">
@@ -1303,16 +1303,16 @@
         <v>0.85</v>
       </c>
       <c r="D17" t="n">
-        <v>2.208</v>
+        <v>2.134</v>
       </c>
       <c r="E17" t="n">
-        <v>-56.8</v>
+        <v>-55.1</v>
       </c>
       <c r="F17" t="n">
-        <v>-27.6</v>
+        <v>-26.6</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>445150</v>
+        <v>418109</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1334,10 +1334,10 @@
         <v>2.72</v>
       </c>
       <c r="M17" t="n">
-        <v>6.39</v>
+        <v>6.17</v>
       </c>
       <c r="N17" t="n">
-        <v>58.4</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18">
@@ -1355,16 +1355,16 @@
         <v>0.98</v>
       </c>
       <c r="D18" t="n">
-        <v>1.031</v>
+        <v>1.043</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.3</v>
+        <v>-4.6</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.9</v>
+        <v>-2.5</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>18872</v>
+        <v>19858</v>
       </c>
       <c r="K18" t="n">
-        <v>16604</v>
+        <v>16712</v>
       </c>
       <c r="L18" t="n">
         <v>0.38</v>
@@ -1389,7 +1389,7 @@
         <v>0.39</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1407,16 +1407,16 @@
         <v>0.72</v>
       </c>
       <c r="D19" t="n">
-        <v>0.965</v>
+        <v>0.961</v>
       </c>
       <c r="E19" t="n">
-        <v>11.3</v>
+        <v>12.8</v>
       </c>
       <c r="F19" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.7</v>
+        <v>-5</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1438,10 +1438,10 @@
         <v>6.2</v>
       </c>
       <c r="M19" t="n">
-        <v>5.31</v>
+        <v>5.23</v>
       </c>
       <c r="N19" t="n">
-        <v>-16.1</v>
+        <v>-17.8</v>
       </c>
     </row>
     <row r="20">
@@ -1459,16 +1459,16 @@
         <v>1.04</v>
       </c>
       <c r="D20" t="n">
-        <v>1.115</v>
+        <v>1.101</v>
       </c>
       <c r="E20" t="n">
-        <v>-18.7</v>
+        <v>-16.9</v>
       </c>
       <c r="F20" t="n">
-        <v>-12.5</v>
+        <v>-11.4</v>
       </c>
       <c r="G20" t="n">
-        <v>-6.2</v>
+        <v>-5.9</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>137011</v>
+        <v>123507</v>
       </c>
       <c r="K20" t="n">
-        <v>48022</v>
+        <v>45930</v>
       </c>
       <c r="L20" t="n">
         <v>2.06</v>
       </c>
       <c r="M20" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="N20" t="n">
-        <v>12.4</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="21">
@@ -1511,16 +1511,16 @@
         <v>0.97</v>
       </c>
       <c r="D21" t="n">
-        <v>1.299</v>
+        <v>1.258</v>
       </c>
       <c r="E21" t="n">
-        <v>-31.6</v>
+        <v>-28.9</v>
       </c>
       <c r="F21" t="n">
-        <v>-19.8</v>
+        <v>-18.3</v>
       </c>
       <c r="G21" t="n">
-        <v>-8</v>
+        <v>-7.8</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>186184</v>
+        <v>167334</v>
       </c>
       <c r="K21" t="n">
-        <v>60314</v>
+        <v>58894</v>
       </c>
       <c r="L21" t="n">
         <v>14.46</v>
       </c>
       <c r="M21" t="n">
-        <v>19.46</v>
+        <v>18.77</v>
       </c>
       <c r="N21" t="n">
-        <v>23.6</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="22">
@@ -1563,16 +1563,16 @@
         <v>1.11</v>
       </c>
       <c r="D22" t="n">
-        <v>1.509</v>
+        <v>1.486</v>
       </c>
       <c r="E22" t="n">
-        <v>-38.5</v>
+        <v>-37.5</v>
       </c>
       <c r="F22" t="n">
-        <v>-25.6</v>
+        <v>-25</v>
       </c>
       <c r="G22" t="n">
-        <v>-12.7</v>
+        <v>-12.5</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1585,25 +1585,25 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>346197</v>
+        <v>335176</v>
       </c>
       <c r="K22" t="n">
-        <v>153688</v>
+        <v>151469</v>
       </c>
       <c r="L22" t="n">
         <v>54.21</v>
       </c>
       <c r="M22" t="n">
-        <v>76.94</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>25.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1612,23 +1612,23 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="D23" t="n">
-        <v>0.896</v>
+        <v>1.088</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4</v>
+        <v>-23.4</v>
       </c>
       <c r="F23" t="n">
-        <v>-8.9</v>
+        <v>-20.2</v>
       </c>
       <c r="G23" t="n">
-        <v>-17.4</v>
+        <v>-17</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1637,25 +1637,25 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>206030</v>
+        <v>335008</v>
       </c>
       <c r="K23" t="n">
-        <v>468168</v>
+        <v>244195</v>
       </c>
       <c r="L23" t="n">
-        <v>30.67</v>
+        <v>13.34</v>
       </c>
       <c r="M23" t="n">
-        <v>25.45</v>
+        <v>14.45</v>
       </c>
       <c r="N23" t="n">
-        <v>-17</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1664,44 +1664,44 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="D24" t="n">
-        <v>1.13</v>
+        <v>0.894</v>
       </c>
       <c r="E24" t="n">
-        <v>-26.6</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>-22.1</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>-17.6</v>
+        <v>-17.3</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
+          <t>HOLD (fairly valued)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT (overvalued)</t>
-        </is>
-      </c>
       <c r="J24" t="n">
-        <v>391452</v>
+        <v>198475</v>
       </c>
       <c r="K24" t="n">
-        <v>256689</v>
+        <v>465441</v>
       </c>
       <c r="L24" t="n">
-        <v>13.34</v>
+        <v>30.67</v>
       </c>
       <c r="M24" t="n">
-        <v>14.99</v>
+        <v>25.35</v>
       </c>
       <c r="N24" t="n">
-        <v>9.1</v>
+        <v>-17.4</v>
       </c>
     </row>
     <row r="25">
@@ -1719,16 +1719,16 @@
         <v>1.37</v>
       </c>
       <c r="D25" t="n">
-        <v>1.103</v>
+        <v>1.066</v>
       </c>
       <c r="E25" t="n">
-        <v>-40.3</v>
+        <v>-37.2</v>
       </c>
       <c r="F25" t="n">
-        <v>-36.3</v>
+        <v>-34.6</v>
       </c>
       <c r="G25" t="n">
-        <v>-32.4</v>
+        <v>-31.9</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1741,19 +1741,19 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>406711</v>
+        <v>362565</v>
       </c>
       <c r="K25" t="n">
-        <v>327758</v>
+        <v>312311</v>
       </c>
       <c r="L25" t="n">
         <v>22.91</v>
       </c>
       <c r="M25" t="n">
-        <v>25.95</v>
+        <v>24.85</v>
       </c>
       <c r="N25" t="n">
-        <v>7.9</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="26">
@@ -1771,16 +1771,16 @@
         <v>1.35</v>
       </c>
       <c r="D26" t="n">
-        <v>1.156</v>
+        <v>1.113</v>
       </c>
       <c r="E26" t="n">
-        <v>-43.4</v>
+        <v>-40.4</v>
       </c>
       <c r="F26" t="n">
-        <v>-38</v>
+        <v>-36.3</v>
       </c>
       <c r="G26" t="n">
-        <v>-32.5</v>
+        <v>-32.1</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1793,19 +1793,19 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>394899</v>
+        <v>354758</v>
       </c>
       <c r="K26" t="n">
-        <v>298502</v>
+        <v>284894</v>
       </c>
       <c r="L26" t="n">
         <v>32.09</v>
       </c>
       <c r="M26" t="n">
-        <v>38.27</v>
+        <v>36.57</v>
       </c>
       <c r="N26" t="n">
-        <v>10.9</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -523,16 +523,16 @@
         <v>0.34</v>
       </c>
       <c r="D2" t="n">
-        <v>1.189</v>
+        <v>1.187</v>
       </c>
       <c r="E2" t="n">
-        <v>50.1</v>
+        <v>50.4</v>
       </c>
       <c r="F2" t="n">
-        <v>68</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>86</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -551,13 +551,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>56.46</v>
+        <v>56.56</v>
       </c>
       <c r="M2" t="n">
-        <v>69.97</v>
+        <v>69.94</v>
       </c>
       <c r="N2" t="n">
-        <v>35.9</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="3">
@@ -627,13 +627,13 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>1.475</v>
+        <v>1.482</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="F4" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="G4" t="n">
         <v>39.1</v>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>58027</v>
+        <v>59337</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>77.13</v>
+        <v>76.87</v>
       </c>
       <c r="M4" t="n">
-        <v>106.38</v>
+        <v>106.43</v>
       </c>
       <c r="N4" t="n">
-        <v>38.2</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="5">
@@ -731,16 +731,16 @@
         <v>0.82</v>
       </c>
       <c r="D6" t="n">
-        <v>1.118</v>
+        <v>1.12</v>
       </c>
       <c r="E6" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="F6" t="n">
         <v>18.8</v>
       </c>
       <c r="G6" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -753,19 +753,19 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>30223</v>
+        <v>30419</v>
       </c>
       <c r="K6" t="n">
-        <v>1304</v>
+        <v>1282</v>
       </c>
       <c r="L6" t="n">
-        <v>31.9</v>
+        <v>31.87</v>
       </c>
       <c r="M6" t="n">
         <v>35.72</v>
       </c>
       <c r="N6" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="7">
@@ -783,13 +783,13 @@
         <v>0.73</v>
       </c>
       <c r="D7" t="n">
-        <v>1.402</v>
+        <v>1.395</v>
       </c>
       <c r="E7" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="F7" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="G7" t="n">
         <v>25</v>
@@ -805,19 +805,19 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3984</v>
+        <v>2343</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>73.18000000000001</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>87.59999999999999</v>
+        <v>87.61</v>
       </c>
       <c r="N7" t="n">
-        <v>20.6</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="8">
@@ -835,13 +835,13 @@
         <v>0.75</v>
       </c>
       <c r="D8" t="n">
-        <v>1.178</v>
+        <v>1.176</v>
       </c>
       <c r="E8" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="F8" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="G8" t="n">
         <v>24.9</v>
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>12560</v>
+        <v>12385</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>16.83</v>
+        <v>16.85</v>
       </c>
       <c r="M8" t="n">
         <v>19.23</v>
       </c>
       <c r="N8" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="9">
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>86423</v>
+        <v>86362</v>
       </c>
       <c r="K10" t="n">
-        <v>7889</v>
+        <v>7871</v>
       </c>
       <c r="L10" t="n">
         <v>6.23</v>
@@ -991,13 +991,13 @@
         <v>0.78</v>
       </c>
       <c r="D11" t="n">
-        <v>1.071</v>
+        <v>1.048</v>
       </c>
       <c r="E11" t="n">
-        <v>11.2</v>
+        <v>13.8</v>
       </c>
       <c r="F11" t="n">
-        <v>15.6</v>
+        <v>16.9</v>
       </c>
       <c r="G11" t="n">
         <v>20</v>
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>8685</v>
+        <v>5782</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>27.69</v>
+        <v>28.35</v>
       </c>
       <c r="M11" t="n">
-        <v>29.88</v>
+        <v>29.87</v>
       </c>
       <c r="N11" t="n">
-        <v>8.800000000000001</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="12">
@@ -1043,16 +1043,16 @@
         <v>0.73</v>
       </c>
       <c r="D12" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.3</v>
+        <v>-5.8</v>
       </c>
       <c r="F12" t="n">
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="G12" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1065,19 +1065,19 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>62354</v>
+        <v>56513</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>13.87</v>
+        <v>14.09</v>
       </c>
       <c r="M12" t="n">
-        <v>17.7</v>
+        <v>17.72</v>
       </c>
       <c r="N12" t="n">
-        <v>25.6</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="13">
@@ -1095,16 +1095,16 @@
         <v>0.88</v>
       </c>
       <c r="D13" t="n">
-        <v>0.856</v>
+        <v>0.854</v>
       </c>
       <c r="E13" t="n">
-        <v>40.2</v>
+        <v>40.8</v>
       </c>
       <c r="F13" t="n">
-        <v>25.3</v>
+        <v>25.5</v>
       </c>
       <c r="G13" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>906</v>
+        <v>992</v>
       </c>
       <c r="L13" t="n">
-        <v>9.56</v>
+        <v>9.6</v>
       </c>
       <c r="M13" t="n">
-        <v>7.53</v>
+        <v>7.52</v>
       </c>
       <c r="N13" t="n">
-        <v>-29.8</v>
+        <v>-30.5</v>
       </c>
     </row>
     <row r="14">
@@ -1147,13 +1147,13 @@
         <v>0.89</v>
       </c>
       <c r="D14" t="n">
-        <v>1.079</v>
+        <v>1.051</v>
       </c>
       <c r="E14" t="n">
-        <v>-4</v>
+        <v>-1.2</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="G14" t="n">
         <v>4.4</v>
@@ -1169,19 +1169,19 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>27466</v>
+        <v>23026</v>
       </c>
       <c r="K14" t="n">
-        <v>14102</v>
+        <v>14099</v>
       </c>
       <c r="L14" t="n">
-        <v>23.15</v>
+        <v>23.82</v>
       </c>
       <c r="M14" t="n">
-        <v>25.19</v>
+        <v>25.18</v>
       </c>
       <c r="N14" t="n">
-        <v>8.4</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="15">
@@ -1251,13 +1251,13 @@
         <v>0.62</v>
       </c>
       <c r="D16" t="n">
-        <v>0.964</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>5.3</v>
+        <v>6.5</v>
       </c>
       <c r="G16" t="n">
         <v>3.7</v>
@@ -1273,19 +1273,19 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>11242</v>
+        <v>8328</v>
       </c>
       <c r="K16" t="n">
-        <v>15024</v>
+        <v>15034</v>
       </c>
       <c r="L16" t="n">
-        <v>20.1</v>
+        <v>20.55</v>
       </c>
       <c r="M16" t="n">
         <v>19.51</v>
       </c>
       <c r="N16" t="n">
-        <v>-3.1</v>
+        <v>-5.6</v>
       </c>
     </row>
     <row r="17">
@@ -1303,13 +1303,13 @@
         <v>0.85</v>
       </c>
       <c r="D17" t="n">
-        <v>2.134</v>
+        <v>2.105</v>
       </c>
       <c r="E17" t="n">
-        <v>-55.1</v>
+        <v>-54.4</v>
       </c>
       <c r="F17" t="n">
-        <v>-26.6</v>
+        <v>-26.3</v>
       </c>
       <c r="G17" t="n">
         <v>1.9</v>
@@ -1325,19 +1325,19 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>418109</v>
+        <v>413067</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="M17" t="n">
         <v>6.17</v>
       </c>
       <c r="N17" t="n">
-        <v>57</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="18">
@@ -1355,13 +1355,13 @@
         <v>0.98</v>
       </c>
       <c r="D18" t="n">
-        <v>1.043</v>
+        <v>1.024</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.6</v>
+        <v>-2.8</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.5</v>
+        <v>-1.7</v>
       </c>
       <c r="G18" t="n">
         <v>-0.5</v>
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>19858</v>
+        <v>18543</v>
       </c>
       <c r="K18" t="n">
-        <v>16712</v>
+        <v>16762</v>
       </c>
       <c r="L18" t="n">
         <v>0.38</v>
@@ -1389,7 +1389,7 @@
         <v>0.39</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="19">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1435,7 +1435,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>6.2</v>
+        <v>6.21</v>
       </c>
       <c r="M19" t="n">
         <v>5.23</v>
@@ -1563,13 +1563,13 @@
         <v>1.11</v>
       </c>
       <c r="D22" t="n">
-        <v>1.486</v>
+        <v>1.489</v>
       </c>
       <c r="E22" t="n">
-        <v>-37.5</v>
+        <v>-37.6</v>
       </c>
       <c r="F22" t="n">
-        <v>-25</v>
+        <v>-25.1</v>
       </c>
       <c r="G22" t="n">
         <v>-12.5</v>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>335176</v>
+        <v>333611</v>
       </c>
       <c r="K22" t="n">
-        <v>151469</v>
+        <v>150513</v>
       </c>
       <c r="L22" t="n">
-        <v>54.21</v>
+        <v>54.12</v>
       </c>
       <c r="M22" t="n">
-        <v>75.90000000000001</v>
+        <v>75.91</v>
       </c>
       <c r="N22" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="23">
@@ -1615,16 +1615,16 @@
         <v>1.14</v>
       </c>
       <c r="D23" t="n">
-        <v>1.088</v>
+        <v>1.108</v>
       </c>
       <c r="E23" t="n">
-        <v>-23.4</v>
+        <v>-24.8</v>
       </c>
       <c r="F23" t="n">
-        <v>-20.2</v>
+        <v>-20.9</v>
       </c>
       <c r="G23" t="n">
-        <v>-17</v>
+        <v>-17.1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1637,19 +1637,19 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>335008</v>
+        <v>354792</v>
       </c>
       <c r="K23" t="n">
-        <v>244195</v>
+        <v>245065</v>
       </c>
       <c r="L23" t="n">
-        <v>13.34</v>
+        <v>13.1</v>
       </c>
       <c r="M23" t="n">
-        <v>14.45</v>
+        <v>14.44</v>
       </c>
       <c r="N23" t="n">
-        <v>6.4</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="24">
@@ -1719,16 +1719,16 @@
         <v>1.37</v>
       </c>
       <c r="D25" t="n">
-        <v>1.066</v>
+        <v>1.069</v>
       </c>
       <c r="E25" t="n">
-        <v>-37.2</v>
+        <v>-37.5</v>
       </c>
       <c r="F25" t="n">
-        <v>-34.6</v>
+        <v>-34.7</v>
       </c>
       <c r="G25" t="n">
-        <v>-31.9</v>
+        <v>-32</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1741,19 +1741,19 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>362565</v>
+        <v>365027</v>
       </c>
       <c r="K25" t="n">
-        <v>312311</v>
+        <v>312546</v>
       </c>
       <c r="L25" t="n">
-        <v>22.91</v>
+        <v>22.8</v>
       </c>
       <c r="M25" t="n">
-        <v>24.85</v>
+        <v>24.82</v>
       </c>
       <c r="N25" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="26">
@@ -1771,7 +1771,7 @@
         <v>1.35</v>
       </c>
       <c r="D26" t="n">
-        <v>1.113</v>
+        <v>1.111</v>
       </c>
       <c r="E26" t="n">
         <v>-40.4</v>
@@ -1780,7 +1780,7 @@
         <v>-36.3</v>
       </c>
       <c r="G26" t="n">
-        <v>-32.1</v>
+        <v>-32.2</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1793,19 +1793,19 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>354758</v>
+        <v>353871</v>
       </c>
       <c r="K26" t="n">
-        <v>284894</v>
+        <v>285119</v>
       </c>
       <c r="L26" t="n">
-        <v>32.09</v>
+        <v>32.1</v>
       </c>
       <c r="M26" t="n">
-        <v>36.57</v>
+        <v>36.52</v>
       </c>
       <c r="N26" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -1095,13 +1095,13 @@
         <v>0.88</v>
       </c>
       <c r="D13" t="n">
-        <v>0.854</v>
+        <v>0.861</v>
       </c>
       <c r="E13" t="n">
-        <v>40.8</v>
+        <v>38.9</v>
       </c>
       <c r="F13" t="n">
-        <v>25.5</v>
+        <v>24.6</v>
       </c>
       <c r="G13" t="n">
         <v>10.3</v>
@@ -1120,16 +1120,16 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>992</v>
+        <v>978</v>
       </c>
       <c r="L13" t="n">
-        <v>9.6</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M13" t="n">
         <v>7.52</v>
       </c>
       <c r="N13" t="n">
-        <v>-30.5</v>
+        <v>-28.6</v>
       </c>
     </row>
     <row r="14">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -523,16 +523,16 @@
         <v>0.34</v>
       </c>
       <c r="D2" t="n">
-        <v>1.187</v>
+        <v>1.217</v>
       </c>
       <c r="E2" t="n">
-        <v>50.4</v>
+        <v>45.6</v>
       </c>
       <c r="F2" t="n">
-        <v>68.09999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="G2" t="n">
-        <v>85.90000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -554,10 +554,10 @@
         <v>56.56</v>
       </c>
       <c r="M2" t="n">
-        <v>69.94</v>
+        <v>72.05</v>
       </c>
       <c r="N2" t="n">
-        <v>35.6</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="3">
@@ -575,16 +575,16 @@
         <v>0.9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.965</v>
+        <v>0.968</v>
       </c>
       <c r="E3" t="n">
-        <v>61.8</v>
+        <v>59.9</v>
       </c>
       <c r="F3" t="n">
-        <v>54.5</v>
+        <v>53.3</v>
       </c>
       <c r="G3" t="n">
-        <v>47.3</v>
+        <v>46.7</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -606,10 +606,10 @@
         <v>35.91</v>
       </c>
       <c r="M3" t="n">
-        <v>32.68</v>
+        <v>32.96</v>
       </c>
       <c r="N3" t="n">
-        <v>-14.6</v>
+        <v>-13.1</v>
       </c>
     </row>
     <row r="4">
@@ -627,16 +627,16 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>1.482</v>
+        <v>1.513</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5</v>
+        <v>-1.4</v>
       </c>
       <c r="F4" t="n">
-        <v>19.8</v>
+        <v>18.7</v>
       </c>
       <c r="G4" t="n">
-        <v>39.1</v>
+        <v>38.9</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>59337</v>
+        <v>67231</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>76.87</v>
       </c>
       <c r="M4" t="n">
-        <v>106.43</v>
+        <v>108.32</v>
       </c>
       <c r="N4" t="n">
-        <v>38.6</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="5">
@@ -679,16 +679,16 @@
         <v>0.75</v>
       </c>
       <c r="D5" t="n">
-        <v>1.308</v>
+        <v>1.333</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9</v>
+        <v>-1.4</v>
       </c>
       <c r="F5" t="n">
-        <v>15.5</v>
+        <v>14.1</v>
       </c>
       <c r="G5" t="n">
-        <v>30.1</v>
+        <v>29.5</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>21682</v>
+        <v>43684</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -710,10 +710,10 @@
         <v>40.54</v>
       </c>
       <c r="M5" t="n">
-        <v>52.24</v>
+        <v>53.22</v>
       </c>
       <c r="N5" t="n">
-        <v>29.1</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="6">
@@ -731,16 +731,16 @@
         <v>0.82</v>
       </c>
       <c r="D6" t="n">
-        <v>1.12</v>
+        <v>1.141</v>
       </c>
       <c r="E6" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="F6" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="G6" t="n">
-        <v>25.6</v>
+        <v>25.2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -753,25 +753,25 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>30419</v>
+        <v>34968</v>
       </c>
       <c r="K6" t="n">
-        <v>1282</v>
+        <v>893</v>
       </c>
       <c r="L6" t="n">
         <v>31.87</v>
       </c>
       <c r="M6" t="n">
-        <v>35.72</v>
+        <v>36.39</v>
       </c>
       <c r="N6" t="n">
-        <v>13.5</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -780,23 +780,23 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="D7" t="n">
-        <v>1.395</v>
+        <v>1.212</v>
       </c>
       <c r="E7" t="n">
-        <v>4.7</v>
+        <v>6.5</v>
       </c>
       <c r="F7" t="n">
-        <v>14.9</v>
+        <v>15.6</v>
       </c>
       <c r="G7" t="n">
-        <v>25</v>
+        <v>24.7</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -805,25 +805,25 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2343</v>
+        <v>16227</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>73.34999999999999</v>
+        <v>16.85</v>
       </c>
       <c r="M7" t="n">
-        <v>87.61</v>
+        <v>19.72</v>
       </c>
       <c r="N7" t="n">
-        <v>20.3</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -832,23 +832,23 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="D8" t="n">
-        <v>1.176</v>
+        <v>1.45</v>
       </c>
       <c r="E8" t="n">
-        <v>9.4</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>17.2</v>
+        <v>13.3</v>
       </c>
       <c r="G8" t="n">
-        <v>24.9</v>
+        <v>24.6</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>12385</v>
+        <v>18151</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>16.85</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>19.23</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>15.5</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="9">
@@ -887,16 +887,16 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>1.105</v>
+        <v>1.099</v>
       </c>
       <c r="E9" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="F9" t="n">
-        <v>12.9</v>
+        <v>13.4</v>
       </c>
       <c r="G9" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -918,10 +918,10 @@
         <v>13.14</v>
       </c>
       <c r="M9" t="n">
-        <v>15.57</v>
+        <v>15.43</v>
       </c>
       <c r="N9" t="n">
-        <v>19.1</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="10">
@@ -939,16 +939,16 @@
         <v>0.86</v>
       </c>
       <c r="D10" t="n">
-        <v>1.434</v>
+        <v>1.448</v>
       </c>
       <c r="E10" t="n">
-        <v>-14.1</v>
+        <v>-15</v>
       </c>
       <c r="F10" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="G10" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>86362</v>
+        <v>88842</v>
       </c>
       <c r="K10" t="n">
-        <v>7871</v>
+        <v>7802</v>
       </c>
       <c r="L10" t="n">
         <v>6.23</v>
       </c>
       <c r="M10" t="n">
-        <v>8.73</v>
+        <v>8.81</v>
       </c>
       <c r="N10" t="n">
-        <v>34.5</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="11">
@@ -991,16 +991,16 @@
         <v>0.78</v>
       </c>
       <c r="D11" t="n">
-        <v>1.048</v>
+        <v>1.089</v>
       </c>
       <c r="E11" t="n">
-        <v>13.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>16.9</v>
+        <v>14.1</v>
       </c>
       <c r="G11" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>5782</v>
+        <v>10780</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1022,10 +1022,10 @@
         <v>28.35</v>
       </c>
       <c r="M11" t="n">
-        <v>29.87</v>
+        <v>31.17</v>
       </c>
       <c r="N11" t="n">
-        <v>6.1</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="12">
@@ -1043,16 +1043,16 @@
         <v>0.73</v>
       </c>
       <c r="D12" t="n">
-        <v>1.16</v>
+        <v>1.166</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.8</v>
+        <v>-6.5</v>
       </c>
       <c r="F12" t="n">
-        <v>6.3</v>
+        <v>5.9</v>
       </c>
       <c r="G12" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>56513</v>
+        <v>59342</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1074,10 +1074,10 @@
         <v>14.09</v>
       </c>
       <c r="M12" t="n">
-        <v>17.72</v>
+        <v>17.86</v>
       </c>
       <c r="N12" t="n">
-        <v>24.2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
@@ -1095,16 +1095,16 @@
         <v>0.88</v>
       </c>
       <c r="D13" t="n">
-        <v>0.861</v>
+        <v>0.885</v>
       </c>
       <c r="E13" t="n">
-        <v>38.9</v>
+        <v>32.3</v>
       </c>
       <c r="F13" t="n">
-        <v>24.6</v>
+        <v>21</v>
       </c>
       <c r="G13" t="n">
-        <v>10.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1120,22 +1120,22 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>978</v>
+        <v>847</v>
       </c>
       <c r="L13" t="n">
         <v>9.470000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>7.52</v>
+        <v>7.86</v>
       </c>
       <c r="N13" t="n">
-        <v>-28.6</v>
+        <v>-22.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1144,50 +1144,50 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="D14" t="n">
-        <v>1.051</v>
+        <v>1.421</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.2</v>
+        <v>-29.1</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6</v>
+        <v>-12.5</v>
       </c>
       <c r="G14" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>HOLD (fairly valued)</t>
-        </is>
-      </c>
       <c r="J14" t="n">
-        <v>23026</v>
+        <v>174694</v>
       </c>
       <c r="K14" t="n">
-        <v>14099</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>23.82</v>
+        <v>30.55</v>
       </c>
       <c r="M14" t="n">
-        <v>25.18</v>
+        <v>44.84</v>
       </c>
       <c r="N14" t="n">
-        <v>5.6</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1196,19 +1196,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.84</v>
+        <v>0.89</v>
       </c>
       <c r="D15" t="n">
-        <v>1.361</v>
+        <v>1.092</v>
       </c>
       <c r="E15" t="n">
-        <v>-25.5</v>
+        <v>-5.7</v>
       </c>
       <c r="F15" t="n">
-        <v>-10.6</v>
+        <v>-0.9</v>
       </c>
       <c r="G15" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>150318</v>
+        <v>30323</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>14326</v>
       </c>
       <c r="L15" t="n">
-        <v>30.55</v>
+        <v>23.82</v>
       </c>
       <c r="M15" t="n">
-        <v>42.8</v>
+        <v>26.26</v>
       </c>
       <c r="N15" t="n">
-        <v>29.9</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1251,16 +1251,16 @@
         <v>0.62</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.927</v>
       </c>
       <c r="E16" t="n">
-        <v>9.199999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="F16" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="G16" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1273,19 +1273,19 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>8328</v>
+        <v>7192</v>
       </c>
       <c r="K16" t="n">
-        <v>15034</v>
+        <v>15001</v>
       </c>
       <c r="L16" t="n">
         <v>20.55</v>
       </c>
       <c r="M16" t="n">
-        <v>19.51</v>
+        <v>19.33</v>
       </c>
       <c r="N16" t="n">
-        <v>-5.6</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="17">
@@ -1303,16 +1303,16 @@
         <v>0.85</v>
       </c>
       <c r="D17" t="n">
-        <v>2.105</v>
+        <v>2.139</v>
       </c>
       <c r="E17" t="n">
-        <v>-54.4</v>
+        <v>-55.2</v>
       </c>
       <c r="F17" t="n">
-        <v>-26.3</v>
+        <v>-26.7</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>413067</v>
+        <v>425461</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1334,10 +1334,10 @@
         <v>2.76</v>
       </c>
       <c r="M17" t="n">
-        <v>6.17</v>
+        <v>6.27</v>
       </c>
       <c r="N17" t="n">
-        <v>56.3</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18">
@@ -1355,13 +1355,13 @@
         <v>0.98</v>
       </c>
       <c r="D18" t="n">
-        <v>1.024</v>
+        <v>1.02</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.8</v>
+        <v>-2.5</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7</v>
+        <v>-1.5</v>
       </c>
       <c r="G18" t="n">
         <v>-0.5</v>
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>18543</v>
+        <v>18267</v>
       </c>
       <c r="K18" t="n">
-        <v>16762</v>
+        <v>16732</v>
       </c>
       <c r="L18" t="n">
         <v>0.38</v>
@@ -1389,7 +1389,7 @@
         <v>0.39</v>
       </c>
       <c r="N18" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1407,16 +1407,16 @@
         <v>0.72</v>
       </c>
       <c r="D19" t="n">
-        <v>0.961</v>
+        <v>0.957</v>
       </c>
       <c r="E19" t="n">
-        <v>12.8</v>
+        <v>14.6</v>
       </c>
       <c r="F19" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="G19" t="n">
-        <v>-5</v>
+        <v>-5.4</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1438,10 +1438,10 @@
         <v>6.21</v>
       </c>
       <c r="M19" t="n">
-        <v>5.23</v>
+        <v>5.13</v>
       </c>
       <c r="N19" t="n">
-        <v>-17.8</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="20">
@@ -1459,16 +1459,16 @@
         <v>1.04</v>
       </c>
       <c r="D20" t="n">
-        <v>1.101</v>
+        <v>1.095</v>
       </c>
       <c r="E20" t="n">
-        <v>-16.9</v>
+        <v>-16.3</v>
       </c>
       <c r="F20" t="n">
-        <v>-11.4</v>
+        <v>-11.1</v>
       </c>
       <c r="G20" t="n">
-        <v>-5.9</v>
+        <v>-5.8</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>123507</v>
+        <v>117818</v>
       </c>
       <c r="K20" t="n">
-        <v>45930</v>
+        <v>45007</v>
       </c>
       <c r="L20" t="n">
         <v>2.06</v>
       </c>
       <c r="M20" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="N20" t="n">
-        <v>11.1</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="21">
@@ -1511,16 +1511,16 @@
         <v>0.97</v>
       </c>
       <c r="D21" t="n">
-        <v>1.258</v>
+        <v>1.297</v>
       </c>
       <c r="E21" t="n">
-        <v>-28.9</v>
+        <v>-31.5</v>
       </c>
       <c r="F21" t="n">
-        <v>-18.3</v>
+        <v>-19.7</v>
       </c>
       <c r="G21" t="n">
-        <v>-7.8</v>
+        <v>-8</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>167334</v>
+        <v>184952</v>
       </c>
       <c r="K21" t="n">
-        <v>58894</v>
+        <v>60221</v>
       </c>
       <c r="L21" t="n">
         <v>14.46</v>
       </c>
       <c r="M21" t="n">
-        <v>18.77</v>
+        <v>19.41</v>
       </c>
       <c r="N21" t="n">
-        <v>21.1</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="22">
@@ -1563,16 +1563,16 @@
         <v>1.11</v>
       </c>
       <c r="D22" t="n">
-        <v>1.489</v>
+        <v>1.517</v>
       </c>
       <c r="E22" t="n">
-        <v>-37.6</v>
+        <v>-38.8</v>
       </c>
       <c r="F22" t="n">
-        <v>-25.1</v>
+        <v>-25.7</v>
       </c>
       <c r="G22" t="n">
-        <v>-12.5</v>
+        <v>-12.7</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1585,25 +1585,25 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>333611</v>
+        <v>346802</v>
       </c>
       <c r="K22" t="n">
-        <v>150513</v>
+        <v>153172</v>
       </c>
       <c r="L22" t="n">
         <v>54.12</v>
       </c>
       <c r="M22" t="n">
-        <v>75.91</v>
+        <v>77.16</v>
       </c>
       <c r="N22" t="n">
-        <v>25.1</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1612,50 +1612,50 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="D23" t="n">
-        <v>1.108</v>
+        <v>0.892</v>
       </c>
       <c r="E23" t="n">
-        <v>-24.8</v>
+        <v>0.4</v>
       </c>
       <c r="F23" t="n">
-        <v>-20.9</v>
+        <v>-8.5</v>
       </c>
       <c r="G23" t="n">
-        <v>-17.1</v>
+        <v>-17.3</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
+          <t>HOLD (fairly valued)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT (overvalued)</t>
-        </is>
-      </c>
       <c r="J23" t="n">
-        <v>354792</v>
+        <v>192539</v>
       </c>
       <c r="K23" t="n">
-        <v>245065</v>
+        <v>463298</v>
       </c>
       <c r="L23" t="n">
-        <v>13.1</v>
+        <v>30.67</v>
       </c>
       <c r="M23" t="n">
-        <v>14.44</v>
+        <v>25.28</v>
       </c>
       <c r="N23" t="n">
-        <v>7.7</v>
+        <v>-17.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1664,23 +1664,23 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="D24" t="n">
-        <v>0.894</v>
+        <v>1.135</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>-26.8</v>
       </c>
       <c r="F24" t="n">
-        <v>-8.699999999999999</v>
+        <v>-22.1</v>
       </c>
       <c r="G24" t="n">
-        <v>-17.3</v>
+        <v>-17.4</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>198475</v>
+        <v>389978</v>
       </c>
       <c r="K24" t="n">
-        <v>465441</v>
+        <v>252874</v>
       </c>
       <c r="L24" t="n">
-        <v>30.67</v>
+        <v>13.1</v>
       </c>
       <c r="M24" t="n">
-        <v>25.35</v>
+        <v>14.77</v>
       </c>
       <c r="N24" t="n">
-        <v>-17.4</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="25">
@@ -1719,16 +1719,16 @@
         <v>1.37</v>
       </c>
       <c r="D25" t="n">
-        <v>1.069</v>
+        <v>1.078</v>
       </c>
       <c r="E25" t="n">
-        <v>-37.5</v>
+        <v>-38.3</v>
       </c>
       <c r="F25" t="n">
-        <v>-34.7</v>
+        <v>-35.2</v>
       </c>
       <c r="G25" t="n">
-        <v>-32</v>
+        <v>-32.1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1741,19 +1741,19 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>365027</v>
+        <v>375292</v>
       </c>
       <c r="K25" t="n">
-        <v>312546</v>
+        <v>316143</v>
       </c>
       <c r="L25" t="n">
         <v>22.8</v>
       </c>
       <c r="M25" t="n">
-        <v>24.82</v>
+        <v>25.08</v>
       </c>
       <c r="N25" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="26">
@@ -1771,16 +1771,16 @@
         <v>1.35</v>
       </c>
       <c r="D26" t="n">
-        <v>1.111</v>
+        <v>1.117</v>
       </c>
       <c r="E26" t="n">
-        <v>-40.4</v>
+        <v>-40.8</v>
       </c>
       <c r="F26" t="n">
-        <v>-36.3</v>
+        <v>-36.5</v>
       </c>
       <c r="G26" t="n">
-        <v>-32.2</v>
+        <v>-32.3</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1793,19 +1793,19 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>353871</v>
+        <v>358931</v>
       </c>
       <c r="K26" t="n">
-        <v>285119</v>
+        <v>286838</v>
       </c>
       <c r="L26" t="n">
         <v>32.1</v>
       </c>
       <c r="M26" t="n">
-        <v>36.52</v>
+        <v>36.73</v>
       </c>
       <c r="N26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -994,13 +994,13 @@
         <v>1.089</v>
       </c>
       <c r="E11" t="n">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="F11" t="n">
-        <v>14.1</v>
+        <v>13.4</v>
       </c>
       <c r="G11" t="n">
-        <v>19.5</v>
+        <v>18.8</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>10780</v>
+        <v>10759</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>28.35</v>
+        <v>28.19</v>
       </c>
       <c r="M11" t="n">
-        <v>31.17</v>
+        <v>30.99</v>
       </c>
       <c r="N11" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="12">
@@ -1046,13 +1046,13 @@
         <v>1.166</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.5</v>
+        <v>-7.3</v>
       </c>
       <c r="F12" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="G12" t="n">
-        <v>18.4</v>
+        <v>17.6</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1071,13 +1071,13 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>14.09</v>
+        <v>13.99</v>
       </c>
       <c r="M12" t="n">
-        <v>17.86</v>
+        <v>17.73</v>
       </c>
       <c r="N12" t="n">
-        <v>25</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="13">
@@ -1098,13 +1098,13 @@
         <v>0.885</v>
       </c>
       <c r="E13" t="n">
-        <v>32.3</v>
+        <v>31.6</v>
       </c>
       <c r="F13" t="n">
-        <v>21</v>
+        <v>20.4</v>
       </c>
       <c r="G13" t="n">
-        <v>9.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>847</v>
+        <v>840</v>
       </c>
       <c r="L13" t="n">
-        <v>9.470000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="M13" t="n">
-        <v>7.86</v>
+        <v>7.81</v>
       </c>
       <c r="N13" t="n">
-        <v>-22.6</v>
+        <v>-22.5</v>
       </c>
     </row>
     <row r="14">
@@ -1187,7 +1187,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1196,23 +1196,23 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.89</v>
+        <v>0.62</v>
       </c>
       <c r="D15" t="n">
-        <v>1.092</v>
+        <v>0.927</v>
       </c>
       <c r="E15" t="n">
-        <v>-5.7</v>
+        <v>9.9</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9</v>
+        <v>6.6</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1221,25 +1221,25 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>30323</v>
+        <v>7186</v>
       </c>
       <c r="K15" t="n">
-        <v>14326</v>
+        <v>14988</v>
       </c>
       <c r="L15" t="n">
-        <v>23.82</v>
+        <v>20.47</v>
       </c>
       <c r="M15" t="n">
-        <v>26.26</v>
+        <v>19.26</v>
       </c>
       <c r="N15" t="n">
-        <v>9.699999999999999</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1248,23 +1248,23 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.62</v>
+        <v>0.89</v>
       </c>
       <c r="D16" t="n">
-        <v>0.927</v>
+        <v>1.092</v>
       </c>
       <c r="E16" t="n">
-        <v>10.3</v>
+        <v>-6.4</v>
       </c>
       <c r="F16" t="n">
-        <v>7</v>
+        <v>-1.6</v>
       </c>
       <c r="G16" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1273,19 +1273,19 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>7192</v>
+        <v>30248</v>
       </c>
       <c r="K16" t="n">
-        <v>15001</v>
+        <v>14290</v>
       </c>
       <c r="L16" t="n">
-        <v>20.55</v>
+        <v>23.66</v>
       </c>
       <c r="M16" t="n">
-        <v>19.33</v>
+        <v>26.08</v>
       </c>
       <c r="N16" t="n">
-        <v>-6.5</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="17">
@@ -1358,13 +1358,13 @@
         <v>1.02</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.5</v>
+        <v>-2.9</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5</v>
+        <v>-1.9</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5</v>
+        <v>-0.9</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>18267</v>
+        <v>18360</v>
       </c>
       <c r="K18" t="n">
-        <v>16732</v>
+        <v>16817</v>
       </c>
       <c r="L18" t="n">
         <v>0.38</v>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -523,16 +523,16 @@
         <v>0.34</v>
       </c>
       <c r="D2" t="n">
-        <v>1.217</v>
+        <v>1.23</v>
       </c>
       <c r="E2" t="n">
-        <v>45.6</v>
+        <v>43.6</v>
       </c>
       <c r="F2" t="n">
-        <v>65.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>85.40000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -554,10 +554,10 @@
         <v>56.56</v>
       </c>
       <c r="M2" t="n">
-        <v>72.05</v>
+        <v>72.97</v>
       </c>
       <c r="N2" t="n">
-        <v>39.9</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="3">
@@ -575,16 +575,16 @@
         <v>0.9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.968</v>
+        <v>0.978</v>
       </c>
       <c r="E3" t="n">
-        <v>59.9</v>
+        <v>53.8</v>
       </c>
       <c r="F3" t="n">
-        <v>53.3</v>
+        <v>49.4</v>
       </c>
       <c r="G3" t="n">
-        <v>46.7</v>
+        <v>45.1</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -606,10 +606,10 @@
         <v>35.91</v>
       </c>
       <c r="M3" t="n">
-        <v>32.96</v>
+        <v>33.88</v>
       </c>
       <c r="N3" t="n">
-        <v>-13.1</v>
+        <v>-8.699999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -627,16 +627,16 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>1.513</v>
+        <v>1.544</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.4</v>
+        <v>-3.3</v>
       </c>
       <c r="F4" t="n">
-        <v>18.7</v>
+        <v>17.7</v>
       </c>
       <c r="G4" t="n">
-        <v>38.9</v>
+        <v>38.7</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>67231</v>
+        <v>75231</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>76.87</v>
       </c>
       <c r="M4" t="n">
-        <v>108.32</v>
+        <v>110.24</v>
       </c>
       <c r="N4" t="n">
-        <v>40.3</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5">
@@ -679,20 +679,20 @@
         <v>0.75</v>
       </c>
       <c r="D5" t="n">
-        <v>1.333</v>
+        <v>1.402</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.4</v>
+        <v>-7</v>
       </c>
       <c r="F5" t="n">
-        <v>14.1</v>
+        <v>10.5</v>
       </c>
       <c r="G5" t="n">
-        <v>29.5</v>
+        <v>28</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>43684</v>
+        <v>102435</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -710,10 +710,10 @@
         <v>40.54</v>
       </c>
       <c r="M5" t="n">
-        <v>53.22</v>
+        <v>55.84</v>
       </c>
       <c r="N5" t="n">
-        <v>30.9</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="6">
@@ -731,16 +731,16 @@
         <v>0.82</v>
       </c>
       <c r="D6" t="n">
-        <v>1.141</v>
+        <v>1.18</v>
       </c>
       <c r="E6" t="n">
-        <v>9.6</v>
+        <v>5.2</v>
       </c>
       <c r="F6" t="n">
-        <v>17.4</v>
+        <v>14.8</v>
       </c>
       <c r="G6" t="n">
-        <v>25.2</v>
+        <v>24.4</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -753,19 +753,19 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>34968</v>
+        <v>43631</v>
       </c>
       <c r="K6" t="n">
-        <v>893</v>
+        <v>152</v>
       </c>
       <c r="L6" t="n">
         <v>31.87</v>
       </c>
       <c r="M6" t="n">
-        <v>36.39</v>
+        <v>37.68</v>
       </c>
       <c r="N6" t="n">
-        <v>15.6</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="7">
@@ -783,29 +783,29 @@
         <v>0.75</v>
       </c>
       <c r="D7" t="n">
-        <v>1.212</v>
+        <v>1.281</v>
       </c>
       <c r="E7" t="n">
-        <v>6.5</v>
+        <v>1.4</v>
       </c>
       <c r="F7" t="n">
-        <v>15.6</v>
+        <v>12.9</v>
       </c>
       <c r="G7" t="n">
-        <v>24.7</v>
+        <v>24.3</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>HOLD (fairly valued)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>BUY (undervalued)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>BUY (undervalued)</t>
-        </is>
-      </c>
       <c r="J7" t="n">
-        <v>16227</v>
+        <v>23306</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -814,10 +814,10 @@
         <v>16.85</v>
       </c>
       <c r="M7" t="n">
-        <v>19.72</v>
+        <v>20.65</v>
       </c>
       <c r="N7" t="n">
-        <v>18.2</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="8">
@@ -835,16 +835,16 @@
         <v>0.73</v>
       </c>
       <c r="D8" t="n">
-        <v>1.45</v>
+        <v>1.566</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>-3.2</v>
       </c>
       <c r="F8" t="n">
-        <v>13.3</v>
+        <v>10.2</v>
       </c>
       <c r="G8" t="n">
-        <v>24.6</v>
+        <v>23.7</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>18151</v>
+        <v>51652</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -866,10 +866,10 @@
         <v>73.34999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>89.56999999999999</v>
+        <v>93.75</v>
       </c>
       <c r="N8" t="n">
-        <v>22.6</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="9">
@@ -887,16 +887,16 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>1.099</v>
+        <v>1.12</v>
       </c>
       <c r="E9" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>13.4</v>
+        <v>11.7</v>
       </c>
       <c r="G9" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -918,10 +918,10 @@
         <v>13.14</v>
       </c>
       <c r="M9" t="n">
-        <v>15.43</v>
+        <v>15.92</v>
       </c>
       <c r="N9" t="n">
-        <v>18.2</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="10">
@@ -939,16 +939,16 @@
         <v>0.86</v>
       </c>
       <c r="D10" t="n">
-        <v>1.448</v>
+        <v>1.504</v>
       </c>
       <c r="E10" t="n">
-        <v>-15</v>
+        <v>-18.6</v>
       </c>
       <c r="F10" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="G10" t="n">
-        <v>20.2</v>
+        <v>19.4</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>88842</v>
+        <v>98762</v>
       </c>
       <c r="K10" t="n">
-        <v>7802</v>
+        <v>7528</v>
       </c>
       <c r="L10" t="n">
         <v>6.23</v>
       </c>
       <c r="M10" t="n">
-        <v>8.81</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>35.2</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">
@@ -991,29 +991,29 @@
         <v>0.78</v>
       </c>
       <c r="D11" t="n">
-        <v>1.089</v>
+        <v>1.159</v>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>0.2</v>
       </c>
       <c r="F11" t="n">
-        <v>13.4</v>
+        <v>9.1</v>
       </c>
       <c r="G11" t="n">
-        <v>18.8</v>
+        <v>18</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>HOLD (fairly valued)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>BUY (undervalued)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>BUY (undervalued)</t>
-        </is>
-      </c>
       <c r="J11" t="n">
-        <v>10759</v>
+        <v>18761</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1022,10 +1022,10 @@
         <v>28.19</v>
       </c>
       <c r="M11" t="n">
-        <v>30.99</v>
+        <v>33.21</v>
       </c>
       <c r="N11" t="n">
-        <v>10.7</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="12">
@@ -1043,16 +1043,16 @@
         <v>0.73</v>
       </c>
       <c r="D12" t="n">
-        <v>1.166</v>
+        <v>1.199</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.3</v>
+        <v>-11.1</v>
       </c>
       <c r="F12" t="n">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="G12" t="n">
-        <v>17.6</v>
+        <v>17.4</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>59342</v>
+        <v>74898</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1074,10 +1074,10 @@
         <v>13.99</v>
       </c>
       <c r="M12" t="n">
-        <v>17.73</v>
+        <v>18.48</v>
       </c>
       <c r="N12" t="n">
-        <v>24.8</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="13">
@@ -1095,16 +1095,16 @@
         <v>0.88</v>
       </c>
       <c r="D13" t="n">
-        <v>0.885</v>
+        <v>0.92</v>
       </c>
       <c r="E13" t="n">
-        <v>31.6</v>
+        <v>22.9</v>
       </c>
       <c r="F13" t="n">
-        <v>20.4</v>
+        <v>15.6</v>
       </c>
       <c r="G13" t="n">
-        <v>9.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>840</v>
+        <v>644</v>
       </c>
       <c r="L13" t="n">
         <v>9.42</v>
       </c>
       <c r="M13" t="n">
-        <v>7.81</v>
+        <v>8.31</v>
       </c>
       <c r="N13" t="n">
-        <v>-22.5</v>
+        <v>-14.6</v>
       </c>
     </row>
     <row r="14">
@@ -1147,16 +1147,16 @@
         <v>0.84</v>
       </c>
       <c r="D14" t="n">
-        <v>1.421</v>
+        <v>1.486</v>
       </c>
       <c r="E14" t="n">
-        <v>-29.1</v>
+        <v>-32.6</v>
       </c>
       <c r="F14" t="n">
-        <v>-12.5</v>
+        <v>-14.4</v>
       </c>
       <c r="G14" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>174694</v>
+        <v>201081</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1178,10 +1178,10 @@
         <v>30.55</v>
       </c>
       <c r="M14" t="n">
-        <v>44.84</v>
+        <v>47.04</v>
       </c>
       <c r="N14" t="n">
-        <v>33.2</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="15">
@@ -1199,16 +1199,16 @@
         <v>0.62</v>
       </c>
       <c r="D15" t="n">
-        <v>0.927</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>9.9</v>
+        <v>8.6</v>
       </c>
       <c r="F15" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="G15" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>7186</v>
+        <v>8510</v>
       </c>
       <c r="K15" t="n">
-        <v>14988</v>
+        <v>15026</v>
       </c>
       <c r="L15" t="n">
         <v>20.47</v>
       </c>
       <c r="M15" t="n">
-        <v>19.26</v>
+        <v>19.46</v>
       </c>
       <c r="N15" t="n">
-        <v>-6.5</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="16">
@@ -1251,16 +1251,16 @@
         <v>0.89</v>
       </c>
       <c r="D16" t="n">
-        <v>1.092</v>
+        <v>1.146</v>
       </c>
       <c r="E16" t="n">
-        <v>-6.4</v>
+        <v>-11.6</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.6</v>
+        <v>-4.5</v>
       </c>
       <c r="G16" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1273,19 +1273,19 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>30248</v>
+        <v>39889</v>
       </c>
       <c r="K16" t="n">
-        <v>14290</v>
+        <v>14591</v>
       </c>
       <c r="L16" t="n">
         <v>23.66</v>
       </c>
       <c r="M16" t="n">
-        <v>26.08</v>
+        <v>27.5</v>
       </c>
       <c r="N16" t="n">
-        <v>9.6</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="17">
@@ -1303,16 +1303,16 @@
         <v>0.85</v>
       </c>
       <c r="D17" t="n">
-        <v>2.139</v>
+        <v>2.227</v>
       </c>
       <c r="E17" t="n">
-        <v>-55.2</v>
+        <v>-57.3</v>
       </c>
       <c r="F17" t="n">
-        <v>-26.7</v>
+        <v>-27.9</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>425461</v>
+        <v>458136</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1334,10 +1334,10 @@
         <v>2.76</v>
       </c>
       <c r="M17" t="n">
-        <v>6.27</v>
+        <v>6.54</v>
       </c>
       <c r="N17" t="n">
-        <v>57</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="18">
@@ -1355,41 +1355,41 @@
         <v>0.98</v>
       </c>
       <c r="D18" t="n">
-        <v>1.02</v>
+        <v>1.083</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.9</v>
+        <v>-9</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.9</v>
+        <v>-5.3</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9</v>
+        <v>-1.5</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>HOLD (fairly valued)</t>
-        </is>
-      </c>
       <c r="J18" t="n">
-        <v>18360</v>
+        <v>23656</v>
       </c>
       <c r="K18" t="n">
-        <v>16817</v>
+        <v>17397</v>
       </c>
       <c r="L18" t="n">
         <v>0.38</v>
       </c>
       <c r="M18" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="19">
@@ -1407,16 +1407,16 @@
         <v>0.72</v>
       </c>
       <c r="D19" t="n">
-        <v>0.957</v>
+        <v>0.972</v>
       </c>
       <c r="E19" t="n">
-        <v>14.6</v>
+        <v>8.4</v>
       </c>
       <c r="F19" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="G19" t="n">
-        <v>-5.4</v>
+        <v>-4.1</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1438,10 +1438,10 @@
         <v>6.21</v>
       </c>
       <c r="M19" t="n">
-        <v>5.13</v>
+        <v>5.49</v>
       </c>
       <c r="N19" t="n">
-        <v>-20</v>
+        <v>-12.6</v>
       </c>
     </row>
     <row r="20">
@@ -1459,16 +1459,16 @@
         <v>1.04</v>
       </c>
       <c r="D20" t="n">
-        <v>1.095</v>
+        <v>1.132</v>
       </c>
       <c r="E20" t="n">
-        <v>-16.3</v>
+        <v>-20.6</v>
       </c>
       <c r="F20" t="n">
-        <v>-11.1</v>
+        <v>-13.7</v>
       </c>
       <c r="G20" t="n">
-        <v>-5.8</v>
+        <v>-6.8</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>117818</v>
+        <v>151957</v>
       </c>
       <c r="K20" t="n">
-        <v>45007</v>
+        <v>50296</v>
       </c>
       <c r="L20" t="n">
         <v>2.06</v>
       </c>
       <c r="M20" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="N20" t="n">
-        <v>10.5</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="21">
@@ -1511,16 +1511,16 @@
         <v>0.97</v>
       </c>
       <c r="D21" t="n">
-        <v>1.297</v>
+        <v>1.342</v>
       </c>
       <c r="E21" t="n">
-        <v>-31.5</v>
+        <v>-34.2</v>
       </c>
       <c r="F21" t="n">
-        <v>-19.7</v>
+        <v>-21.2</v>
       </c>
       <c r="G21" t="n">
-        <v>-8</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>184952</v>
+        <v>205800</v>
       </c>
       <c r="K21" t="n">
-        <v>60221</v>
+        <v>61791</v>
       </c>
       <c r="L21" t="n">
         <v>14.46</v>
       </c>
       <c r="M21" t="n">
-        <v>19.41</v>
+        <v>20.18</v>
       </c>
       <c r="N21" t="n">
-        <v>23.5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22">
@@ -1563,16 +1563,16 @@
         <v>1.11</v>
       </c>
       <c r="D22" t="n">
-        <v>1.517</v>
+        <v>1.583</v>
       </c>
       <c r="E22" t="n">
-        <v>-38.8</v>
+        <v>-41.4</v>
       </c>
       <c r="F22" t="n">
-        <v>-25.7</v>
+        <v>-27.3</v>
       </c>
       <c r="G22" t="n">
-        <v>-12.7</v>
+        <v>-13.2</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>346802</v>
+        <v>378011</v>
       </c>
       <c r="K22" t="n">
-        <v>153172</v>
+        <v>159463</v>
       </c>
       <c r="L22" t="n">
         <v>54.12</v>
       </c>
       <c r="M22" t="n">
-        <v>77.16</v>
+        <v>80.13</v>
       </c>
       <c r="N22" t="n">
-        <v>26.1</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="23">
@@ -1615,16 +1615,16 @@
         <v>1.35</v>
       </c>
       <c r="D23" t="n">
-        <v>0.892</v>
+        <v>0.896</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="F23" t="n">
-        <v>-8.5</v>
+        <v>-9</v>
       </c>
       <c r="G23" t="n">
-        <v>-17.3</v>
+        <v>-17.4</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1637,19 +1637,19 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>192539</v>
+        <v>208188</v>
       </c>
       <c r="K23" t="n">
-        <v>463298</v>
+        <v>468948</v>
       </c>
       <c r="L23" t="n">
         <v>30.67</v>
       </c>
       <c r="M23" t="n">
-        <v>25.28</v>
+        <v>25.48</v>
       </c>
       <c r="N23" t="n">
-        <v>-17.7</v>
+        <v>-16.9</v>
       </c>
     </row>
     <row r="24">
@@ -1667,16 +1667,16 @@
         <v>1.14</v>
       </c>
       <c r="D24" t="n">
-        <v>1.135</v>
+        <v>1.167</v>
       </c>
       <c r="E24" t="n">
-        <v>-26.8</v>
+        <v>-29</v>
       </c>
       <c r="F24" t="n">
-        <v>-22.1</v>
+        <v>-23.4</v>
       </c>
       <c r="G24" t="n">
-        <v>-17.4</v>
+        <v>-17.8</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>389978</v>
+        <v>431028</v>
       </c>
       <c r="K24" t="n">
-        <v>252874</v>
+        <v>261985</v>
       </c>
       <c r="L24" t="n">
         <v>13.1</v>
       </c>
       <c r="M24" t="n">
-        <v>14.77</v>
+        <v>15.17</v>
       </c>
       <c r="N24" t="n">
-        <v>9.4</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="25">
@@ -1719,16 +1719,16 @@
         <v>1.37</v>
       </c>
       <c r="D25" t="n">
-        <v>1.078</v>
+        <v>1.125</v>
       </c>
       <c r="E25" t="n">
-        <v>-38.3</v>
+        <v>-42</v>
       </c>
       <c r="F25" t="n">
-        <v>-35.2</v>
+        <v>-37.3</v>
       </c>
       <c r="G25" t="n">
-        <v>-32.1</v>
+        <v>-32.6</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1741,19 +1741,19 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>375292</v>
+        <v>430349</v>
       </c>
       <c r="K25" t="n">
-        <v>316143</v>
+        <v>335434</v>
       </c>
       <c r="L25" t="n">
         <v>22.8</v>
       </c>
       <c r="M25" t="n">
-        <v>25.08</v>
+        <v>26.46</v>
       </c>
       <c r="N25" t="n">
-        <v>6.2</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1771,16 +1771,16 @@
         <v>1.35</v>
       </c>
       <c r="D26" t="n">
-        <v>1.117</v>
+        <v>1.172</v>
       </c>
       <c r="E26" t="n">
-        <v>-40.8</v>
+        <v>-44.5</v>
       </c>
       <c r="F26" t="n">
-        <v>-36.5</v>
+        <v>-38.7</v>
       </c>
       <c r="G26" t="n">
-        <v>-32.3</v>
+        <v>-32.8</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1793,19 +1793,19 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>358931</v>
+        <v>410092</v>
       </c>
       <c r="K26" t="n">
-        <v>286838</v>
+        <v>304222</v>
       </c>
       <c r="L26" t="n">
         <v>32.1</v>
       </c>
       <c r="M26" t="n">
-        <v>36.73</v>
+        <v>38.9</v>
       </c>
       <c r="N26" t="n">
-        <v>8.5</v>
+        <v>11.7</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -991,13 +991,13 @@
         <v>0.78</v>
       </c>
       <c r="D11" t="n">
-        <v>1.159</v>
+        <v>1.144</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="F11" t="n">
-        <v>9.1</v>
+        <v>9.9</v>
       </c>
       <c r="G11" t="n">
         <v>18</v>
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>18761</v>
+        <v>16990</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>28.19</v>
+        <v>28.62</v>
       </c>
       <c r="M11" t="n">
-        <v>33.21</v>
+        <v>33.22</v>
       </c>
       <c r="N11" t="n">
-        <v>17.8</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="12">
@@ -1043,13 +1043,13 @@
         <v>0.73</v>
       </c>
       <c r="D12" t="n">
-        <v>1.199</v>
+        <v>1.196</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.1</v>
+        <v>-10.7</v>
       </c>
       <c r="F12" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="G12" t="n">
         <v>17.4</v>
@@ -1065,19 +1065,19 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>74898</v>
+        <v>73290</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>13.99</v>
+        <v>14.05</v>
       </c>
       <c r="M12" t="n">
-        <v>18.48</v>
+        <v>18.49</v>
       </c>
       <c r="N12" t="n">
-        <v>28.5</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="13">
@@ -1095,16 +1095,16 @@
         <v>0.88</v>
       </c>
       <c r="D13" t="n">
-        <v>0.92</v>
+        <v>0.917</v>
       </c>
       <c r="E13" t="n">
-        <v>22.9</v>
+        <v>23.5</v>
       </c>
       <c r="F13" t="n">
-        <v>15.6</v>
+        <v>15.9</v>
       </c>
       <c r="G13" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>644</v>
+        <v>583</v>
       </c>
       <c r="L13" t="n">
-        <v>9.42</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M13" t="n">
         <v>8.31</v>
       </c>
       <c r="N13" t="n">
-        <v>-14.6</v>
+        <v>-15.1</v>
       </c>
     </row>
     <row r="14">
@@ -1199,13 +1199,13 @@
         <v>0.62</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.921</v>
       </c>
       <c r="E15" t="n">
-        <v>8.6</v>
+        <v>10.3</v>
       </c>
       <c r="F15" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="G15" t="n">
         <v>3.3</v>
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>8510</v>
+        <v>6450</v>
       </c>
       <c r="K15" t="n">
-        <v>15026</v>
+        <v>15020</v>
       </c>
       <c r="L15" t="n">
-        <v>20.47</v>
+        <v>20.79</v>
       </c>
       <c r="M15" t="n">
-        <v>19.46</v>
+        <v>19.45</v>
       </c>
       <c r="N15" t="n">
-        <v>-5.4</v>
+        <v>-7.1</v>
       </c>
     </row>
     <row r="16">
@@ -1251,16 +1251,16 @@
         <v>0.89</v>
       </c>
       <c r="D16" t="n">
-        <v>1.146</v>
+        <v>1.128</v>
       </c>
       <c r="E16" t="n">
-        <v>-11.6</v>
+        <v>-10.1</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.5</v>
+        <v>-3.7</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1273,19 +1273,19 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>39889</v>
+        <v>37010</v>
       </c>
       <c r="K16" t="n">
-        <v>14591</v>
+        <v>14526</v>
       </c>
       <c r="L16" t="n">
-        <v>23.66</v>
+        <v>24.08</v>
       </c>
       <c r="M16" t="n">
-        <v>27.5</v>
+        <v>27.51</v>
       </c>
       <c r="N16" t="n">
-        <v>14.4</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="17">
@@ -1355,16 +1355,16 @@
         <v>0.98</v>
       </c>
       <c r="D18" t="n">
-        <v>1.083</v>
+        <v>1.068</v>
       </c>
       <c r="E18" t="n">
-        <v>-9</v>
+        <v>-7.8</v>
       </c>
       <c r="F18" t="n">
-        <v>-5.3</v>
+        <v>-4.7</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.5</v>
+        <v>-1.6</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>23656</v>
+        <v>22622</v>
       </c>
       <c r="K18" t="n">
-        <v>17397</v>
+        <v>17436</v>
       </c>
       <c r="L18" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="M18" t="n">
         <v>0.41</v>
       </c>
       <c r="N18" t="n">
-        <v>7.5</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="19">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -523,16 +523,16 @@
         <v>0.34</v>
       </c>
       <c r="D2" t="n">
-        <v>1.23</v>
+        <v>1.249</v>
       </c>
       <c r="E2" t="n">
-        <v>43.6</v>
+        <v>41.3</v>
       </c>
       <c r="F2" t="n">
-        <v>64.40000000000001</v>
+        <v>63.5</v>
       </c>
       <c r="G2" t="n">
-        <v>85.2</v>
+        <v>85.8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -551,13 +551,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>56.56</v>
+        <v>56.83</v>
       </c>
       <c r="M2" t="n">
-        <v>72.97</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>41.6</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="3">
@@ -575,16 +575,16 @@
         <v>0.9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.978</v>
+        <v>0.968</v>
       </c>
       <c r="E3" t="n">
-        <v>53.8</v>
+        <v>60.4</v>
       </c>
       <c r="F3" t="n">
-        <v>49.4</v>
+        <v>53.6</v>
       </c>
       <c r="G3" t="n">
-        <v>45.1</v>
+        <v>46.9</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -606,10 +606,10 @@
         <v>35.91</v>
       </c>
       <c r="M3" t="n">
-        <v>33.88</v>
+        <v>32.88</v>
       </c>
       <c r="N3" t="n">
-        <v>-8.699999999999999</v>
+        <v>-13.5</v>
       </c>
     </row>
     <row r="4">
@@ -627,16 +627,16 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>1.544</v>
+        <v>1.5</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.3</v>
+        <v>-0.6</v>
       </c>
       <c r="F4" t="n">
-        <v>17.7</v>
+        <v>19.2</v>
       </c>
       <c r="G4" t="n">
-        <v>38.7</v>
+        <v>39</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>75231</v>
+        <v>63973</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>76.87</v>
       </c>
       <c r="M4" t="n">
-        <v>110.24</v>
+        <v>107.54</v>
       </c>
       <c r="N4" t="n">
-        <v>42</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="5">
@@ -679,16 +679,16 @@
         <v>0.75</v>
       </c>
       <c r="D5" t="n">
-        <v>1.402</v>
+        <v>1.421</v>
       </c>
       <c r="E5" t="n">
-        <v>-7</v>
+        <v>-8.5</v>
       </c>
       <c r="F5" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="G5" t="n">
-        <v>28</v>
+        <v>27.7</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>102435</v>
+        <v>118655</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -710,10 +710,10 @@
         <v>40.54</v>
       </c>
       <c r="M5" t="n">
-        <v>55.84</v>
+        <v>56.56</v>
       </c>
       <c r="N5" t="n">
-        <v>35.1</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="6">
@@ -731,16 +731,16 @@
         <v>0.82</v>
       </c>
       <c r="D6" t="n">
-        <v>1.18</v>
+        <v>1.177</v>
       </c>
       <c r="E6" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="F6" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="G6" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -753,25 +753,25 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>43631</v>
+        <v>42981</v>
       </c>
       <c r="K6" t="n">
-        <v>152</v>
+        <v>208</v>
       </c>
       <c r="L6" t="n">
         <v>31.87</v>
       </c>
       <c r="M6" t="n">
-        <v>37.68</v>
+        <v>37.58</v>
       </c>
       <c r="N6" t="n">
-        <v>19.2</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -780,19 +780,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>1.281</v>
+        <v>1.146</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4</v>
+        <v>-1</v>
       </c>
       <c r="F7" t="n">
-        <v>12.9</v>
+        <v>11.6</v>
       </c>
       <c r="G7" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -805,25 +805,25 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>23306</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>16.85</v>
+        <v>13.38</v>
       </c>
       <c r="M7" t="n">
-        <v>20.65</v>
+        <v>16.78</v>
       </c>
       <c r="N7" t="n">
-        <v>22.9</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -832,19 +832,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="D8" t="n">
-        <v>1.566</v>
+        <v>1.349</v>
       </c>
       <c r="E8" t="n">
         <v>-3.2</v>
       </c>
       <c r="F8" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="G8" t="n">
-        <v>23.7</v>
+        <v>24</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -857,25 +857,25 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>51652</v>
+        <v>30382</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>73.34999999999999</v>
+        <v>16.85</v>
       </c>
       <c r="M8" t="n">
-        <v>93.75</v>
+        <v>21.57</v>
       </c>
       <c r="N8" t="n">
-        <v>26.9</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -884,23 +884,23 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="D9" t="n">
-        <v>1.12</v>
+        <v>1.689</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>-7.8</v>
       </c>
       <c r="F9" t="n">
-        <v>11.7</v>
+        <v>7.8</v>
       </c>
       <c r="G9" t="n">
-        <v>22.4</v>
+        <v>23.5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -909,19 +909,19 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>87258</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>13.14</v>
+        <v>73.69</v>
       </c>
       <c r="M9" t="n">
-        <v>15.92</v>
+        <v>98.75</v>
       </c>
       <c r="N9" t="n">
-        <v>21.4</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="10">
@@ -939,16 +939,16 @@
         <v>0.86</v>
       </c>
       <c r="D10" t="n">
-        <v>1.504</v>
+        <v>1.508</v>
       </c>
       <c r="E10" t="n">
-        <v>-18.6</v>
+        <v>-18.8</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G10" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>98762</v>
+        <v>99382</v>
       </c>
       <c r="K10" t="n">
-        <v>7528</v>
+        <v>7511</v>
       </c>
       <c r="L10" t="n">
         <v>6.23</v>
       </c>
       <c r="M10" t="n">
-        <v>9.130000000000001</v>
+        <v>9.15</v>
       </c>
       <c r="N10" t="n">
-        <v>38</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="11">
@@ -991,16 +991,16 @@
         <v>0.78</v>
       </c>
       <c r="D11" t="n">
-        <v>1.144</v>
+        <v>1.165</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7</v>
+        <v>-0.5</v>
       </c>
       <c r="F11" t="n">
-        <v>9.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>18</v>
+        <v>17.8</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>16990</v>
+        <v>19445</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1022,10 +1022,10 @@
         <v>28.62</v>
       </c>
       <c r="M11" t="n">
-        <v>33.22</v>
+        <v>33.9</v>
       </c>
       <c r="N11" t="n">
-        <v>16.3</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="12">
@@ -1043,16 +1043,16 @@
         <v>0.73</v>
       </c>
       <c r="D12" t="n">
-        <v>1.196</v>
+        <v>1.217</v>
       </c>
       <c r="E12" t="n">
-        <v>-10.7</v>
+        <v>-12.7</v>
       </c>
       <c r="F12" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="G12" t="n">
-        <v>17.4</v>
+        <v>17.7</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1065,19 +1065,19 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>73290</v>
+        <v>83165</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>14.05</v>
+        <v>14.11</v>
       </c>
       <c r="M12" t="n">
-        <v>18.49</v>
+        <v>19.03</v>
       </c>
       <c r="N12" t="n">
-        <v>28.2</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="13">
@@ -1095,16 +1095,16 @@
         <v>0.88</v>
       </c>
       <c r="D13" t="n">
-        <v>0.917</v>
+        <v>0.927</v>
       </c>
       <c r="E13" t="n">
-        <v>23.5</v>
+        <v>21.3</v>
       </c>
       <c r="F13" t="n">
-        <v>15.9</v>
+        <v>14.7</v>
       </c>
       <c r="G13" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>583</v>
+        <v>529</v>
       </c>
       <c r="L13" t="n">
         <v>9.470000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>8.31</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-15.1</v>
+        <v>-13.1</v>
       </c>
     </row>
     <row r="14">
@@ -1147,16 +1147,16 @@
         <v>0.84</v>
       </c>
       <c r="D14" t="n">
-        <v>1.486</v>
+        <v>1.522</v>
       </c>
       <c r="E14" t="n">
-        <v>-32.6</v>
+        <v>-34.4</v>
       </c>
       <c r="F14" t="n">
-        <v>-14.4</v>
+        <v>-15.3</v>
       </c>
       <c r="G14" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>201081</v>
+        <v>215517</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1178,16 +1178,16 @@
         <v>30.55</v>
       </c>
       <c r="M14" t="n">
-        <v>47.04</v>
+        <v>48.25</v>
       </c>
       <c r="N14" t="n">
-        <v>36.4</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1196,23 +1196,23 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.62</v>
+        <v>0.89</v>
       </c>
       <c r="D15" t="n">
-        <v>0.921</v>
+        <v>1.093</v>
       </c>
       <c r="E15" t="n">
-        <v>10.3</v>
+        <v>-6.5</v>
       </c>
       <c r="F15" t="n">
-        <v>6.8</v>
+        <v>-1.7</v>
       </c>
       <c r="G15" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1221,25 +1221,25 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>6450</v>
+        <v>30584</v>
       </c>
       <c r="K15" t="n">
-        <v>15020</v>
+        <v>14327</v>
       </c>
       <c r="L15" t="n">
-        <v>20.79</v>
+        <v>24.08</v>
       </c>
       <c r="M15" t="n">
-        <v>19.45</v>
+        <v>26.56</v>
       </c>
       <c r="N15" t="n">
-        <v>-7.1</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1248,23 +1248,23 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.89</v>
+        <v>0.62</v>
       </c>
       <c r="D16" t="n">
-        <v>1.128</v>
+        <v>0.947</v>
       </c>
       <c r="E16" t="n">
-        <v>-10.1</v>
+        <v>7.7</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.7</v>
+        <v>5.4</v>
       </c>
       <c r="G16" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1273,19 +1273,19 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>37010</v>
+        <v>9375</v>
       </c>
       <c r="K16" t="n">
-        <v>14526</v>
+        <v>15105</v>
       </c>
       <c r="L16" t="n">
-        <v>24.08</v>
+        <v>20.79</v>
       </c>
       <c r="M16" t="n">
-        <v>27.51</v>
+        <v>19.89</v>
       </c>
       <c r="N16" t="n">
-        <v>12.8</v>
+        <v>-4.6</v>
       </c>
     </row>
     <row r="17">
@@ -1303,16 +1303,16 @@
         <v>0.85</v>
       </c>
       <c r="D17" t="n">
-        <v>2.227</v>
+        <v>2.25</v>
       </c>
       <c r="E17" t="n">
-        <v>-57.3</v>
+        <v>-57.2</v>
       </c>
       <c r="F17" t="n">
-        <v>-27.9</v>
+        <v>-27.5</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1325,25 +1325,25 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>458136</v>
+        <v>466586</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="M17" t="n">
-        <v>6.54</v>
+        <v>6.67</v>
       </c>
       <c r="N17" t="n">
-        <v>58.7</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1352,23 +1352,23 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.98</v>
+        <v>0.72</v>
       </c>
       <c r="D18" t="n">
-        <v>1.068</v>
+        <v>0.983</v>
       </c>
       <c r="E18" t="n">
-        <v>-7.8</v>
+        <v>8.1</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.7</v>
+        <v>4.5</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.6</v>
+        <v>0.9</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1377,25 +1377,25 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>22622</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>17436</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.39</v>
+        <v>6.45</v>
       </c>
       <c r="M18" t="n">
-        <v>0.41</v>
+        <v>6.02</v>
       </c>
       <c r="N18" t="n">
-        <v>6.2</v>
+        <v>-7.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1404,23 +1404,23 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.72</v>
+        <v>0.98</v>
       </c>
       <c r="D19" t="n">
-        <v>0.972</v>
+        <v>1.062</v>
       </c>
       <c r="E19" t="n">
-        <v>8.4</v>
+        <v>-7.2</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2</v>
+        <v>-4.4</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.1</v>
+        <v>-1.5</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1429,19 +1429,19 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>22126</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>17382</v>
       </c>
       <c r="L19" t="n">
-        <v>6.21</v>
+        <v>0.39</v>
       </c>
       <c r="M19" t="n">
-        <v>5.49</v>
+        <v>0.41</v>
       </c>
       <c r="N19" t="n">
-        <v>-12.6</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="20">
@@ -1459,16 +1459,16 @@
         <v>1.04</v>
       </c>
       <c r="D20" t="n">
-        <v>1.132</v>
+        <v>1.124</v>
       </c>
       <c r="E20" t="n">
-        <v>-20.6</v>
+        <v>-19.8</v>
       </c>
       <c r="F20" t="n">
-        <v>-13.7</v>
+        <v>-13.2</v>
       </c>
       <c r="G20" t="n">
-        <v>-6.8</v>
+        <v>-6.6</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>151957</v>
+        <v>144987</v>
       </c>
       <c r="K20" t="n">
-        <v>50296</v>
+        <v>49217</v>
       </c>
       <c r="L20" t="n">
         <v>2.06</v>
       </c>
       <c r="M20" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="N20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="21">
@@ -1511,16 +1511,16 @@
         <v>0.97</v>
       </c>
       <c r="D21" t="n">
-        <v>1.342</v>
+        <v>1.379</v>
       </c>
       <c r="E21" t="n">
-        <v>-34.2</v>
+        <v>-36.3</v>
       </c>
       <c r="F21" t="n">
-        <v>-21.2</v>
+        <v>-22.4</v>
       </c>
       <c r="G21" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8.4</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>205800</v>
+        <v>222333</v>
       </c>
       <c r="K21" t="n">
-        <v>61791</v>
+        <v>63037</v>
       </c>
       <c r="L21" t="n">
         <v>14.46</v>
       </c>
       <c r="M21" t="n">
-        <v>20.18</v>
+        <v>20.79</v>
       </c>
       <c r="N21" t="n">
-        <v>26</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="22">
@@ -1563,16 +1563,16 @@
         <v>1.11</v>
       </c>
       <c r="D22" t="n">
-        <v>1.583</v>
+        <v>1.649</v>
       </c>
       <c r="E22" t="n">
-        <v>-41.4</v>
+        <v>-43.3</v>
       </c>
       <c r="F22" t="n">
-        <v>-27.3</v>
+        <v>-28.2</v>
       </c>
       <c r="G22" t="n">
-        <v>-13.2</v>
+        <v>-13.1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1585,25 +1585,25 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>378011</v>
+        <v>408978</v>
       </c>
       <c r="K22" t="n">
-        <v>159463</v>
+        <v>165706</v>
       </c>
       <c r="L22" t="n">
-        <v>54.12</v>
+        <v>54.46</v>
       </c>
       <c r="M22" t="n">
-        <v>80.13</v>
+        <v>83.55</v>
       </c>
       <c r="N22" t="n">
-        <v>28.2</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1612,23 +1612,23 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="D23" t="n">
-        <v>0.896</v>
+        <v>1.179</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6</v>
+        <v>-29</v>
       </c>
       <c r="F23" t="n">
-        <v>-9</v>
+        <v>-23</v>
       </c>
       <c r="G23" t="n">
-        <v>-17.4</v>
+        <v>-17</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1637,25 +1637,25 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>208188</v>
+        <v>446788</v>
       </c>
       <c r="K23" t="n">
-        <v>468948</v>
+        <v>265483</v>
       </c>
       <c r="L23" t="n">
-        <v>30.67</v>
+        <v>13.24</v>
       </c>
       <c r="M23" t="n">
-        <v>25.48</v>
+        <v>15.48</v>
       </c>
       <c r="N23" t="n">
-        <v>-16.9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1664,23 +1664,23 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="D24" t="n">
-        <v>1.167</v>
+        <v>0.9</v>
       </c>
       <c r="E24" t="n">
-        <v>-29</v>
+        <v>-1.5</v>
       </c>
       <c r="F24" t="n">
-        <v>-23.4</v>
+        <v>-9.5</v>
       </c>
       <c r="G24" t="n">
-        <v>-17.8</v>
+        <v>-17.6</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>431028</v>
+        <v>224647</v>
       </c>
       <c r="K24" t="n">
-        <v>261985</v>
+        <v>474889</v>
       </c>
       <c r="L24" t="n">
-        <v>13.1</v>
+        <v>30.67</v>
       </c>
       <c r="M24" t="n">
-        <v>15.17</v>
+        <v>25.69</v>
       </c>
       <c r="N24" t="n">
-        <v>11.2</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="25">
@@ -1719,16 +1719,16 @@
         <v>1.37</v>
       </c>
       <c r="D25" t="n">
-        <v>1.125</v>
+        <v>1.126</v>
       </c>
       <c r="E25" t="n">
-        <v>-42</v>
+        <v>-41.2</v>
       </c>
       <c r="F25" t="n">
-        <v>-37.3</v>
+        <v>-36.4</v>
       </c>
       <c r="G25" t="n">
-        <v>-32.6</v>
+        <v>-31.7</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1741,19 +1741,19 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>430349</v>
+        <v>431515</v>
       </c>
       <c r="K25" t="n">
-        <v>335434</v>
+        <v>335842</v>
       </c>
       <c r="L25" t="n">
-        <v>22.8</v>
+        <v>23.15</v>
       </c>
       <c r="M25" t="n">
-        <v>26.46</v>
+        <v>26.87</v>
       </c>
       <c r="N25" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="26">
@@ -1771,16 +1771,16 @@
         <v>1.35</v>
       </c>
       <c r="D26" t="n">
-        <v>1.172</v>
+        <v>1.211</v>
       </c>
       <c r="E26" t="n">
-        <v>-44.5</v>
+        <v>-46.2</v>
       </c>
       <c r="F26" t="n">
-        <v>-38.7</v>
+        <v>-39.2</v>
       </c>
       <c r="G26" t="n">
-        <v>-32.8</v>
+        <v>-32.2</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1793,19 +1793,19 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>410092</v>
+        <v>446636</v>
       </c>
       <c r="K26" t="n">
-        <v>304222</v>
+        <v>316639</v>
       </c>
       <c r="L26" t="n">
-        <v>32.1</v>
+        <v>32.57</v>
       </c>
       <c r="M26" t="n">
-        <v>38.9</v>
+        <v>40.98</v>
       </c>
       <c r="N26" t="n">
-        <v>11.7</v>
+        <v>13.9</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -1095,16 +1095,16 @@
         <v>0.88</v>
       </c>
       <c r="D13" t="n">
-        <v>0.927</v>
+        <v>0.891</v>
       </c>
       <c r="E13" t="n">
-        <v>21.3</v>
+        <v>29.4</v>
       </c>
       <c r="F13" t="n">
-        <v>14.7</v>
+        <v>19.1</v>
       </c>
       <c r="G13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>529</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>9.470000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="M13" t="n">
-        <v>8.449999999999999</v>
+        <v>8.51</v>
       </c>
       <c r="N13" t="n">
-        <v>-13.1</v>
+        <v>-20.4</v>
       </c>
     </row>
     <row r="14">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -823,7 +823,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -832,19 +832,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="D8" t="n">
-        <v>1.349</v>
+        <v>1.562</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.2</v>
+        <v>-3.8</v>
       </c>
       <c r="F8" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="G8" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -857,25 +857,25 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>30382</v>
+        <v>54688</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>16.85</v>
+        <v>76.95</v>
       </c>
       <c r="M8" t="n">
-        <v>21.57</v>
+        <v>99.23999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>27.1</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -884,23 +884,23 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="D9" t="n">
-        <v>1.689</v>
+        <v>1.349</v>
       </c>
       <c r="E9" t="n">
-        <v>-7.8</v>
+        <v>-3.2</v>
       </c>
       <c r="F9" t="n">
-        <v>7.8</v>
+        <v>10.4</v>
       </c>
       <c r="G9" t="n">
-        <v>23.5</v>
+        <v>24</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -909,19 +909,19 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>87258</v>
+        <v>30382</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>73.69</v>
+        <v>16.85</v>
       </c>
       <c r="M9" t="n">
-        <v>98.75</v>
+        <v>21.57</v>
       </c>
       <c r="N9" t="n">
-        <v>31.3</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="10">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -823,7 +823,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -832,19 +832,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="D8" t="n">
-        <v>1.562</v>
+        <v>1.349</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.8</v>
+        <v>-3.2</v>
       </c>
       <c r="F8" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="G8" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -857,25 +857,25 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>54688</v>
+        <v>30382</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>76.95</v>
+        <v>16.85</v>
       </c>
       <c r="M8" t="n">
-        <v>99.23999999999999</v>
+        <v>21.57</v>
       </c>
       <c r="N8" t="n">
-        <v>27.9</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -884,23 +884,23 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="D9" t="n">
-        <v>1.349</v>
+        <v>1.689</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.2</v>
+        <v>-7.8</v>
       </c>
       <c r="F9" t="n">
-        <v>10.4</v>
+        <v>7.8</v>
       </c>
       <c r="G9" t="n">
-        <v>24</v>
+        <v>23.5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -909,19 +909,19 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>30382</v>
+        <v>87258</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>16.85</v>
+        <v>73.69</v>
       </c>
       <c r="M9" t="n">
-        <v>21.57</v>
+        <v>98.75</v>
       </c>
       <c r="N9" t="n">
-        <v>27.1</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="10">
@@ -1095,16 +1095,16 @@
         <v>0.88</v>
       </c>
       <c r="D13" t="n">
-        <v>0.891</v>
+        <v>0.927</v>
       </c>
       <c r="E13" t="n">
-        <v>29.4</v>
+        <v>21.3</v>
       </c>
       <c r="F13" t="n">
-        <v>19.1</v>
+        <v>14.7</v>
       </c>
       <c r="G13" t="n">
-        <v>8.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>529</v>
       </c>
       <c r="L13" t="n">
-        <v>10.1</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>8.51</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-20.4</v>
+        <v>-13.1</v>
       </c>
     </row>
     <row r="14">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -523,16 +523,16 @@
         <v>0.34</v>
       </c>
       <c r="D2" t="n">
-        <v>1.249</v>
+        <v>1.223</v>
       </c>
       <c r="E2" t="n">
-        <v>41.3</v>
+        <v>45.2</v>
       </c>
       <c r="F2" t="n">
-        <v>63.5</v>
+        <v>65.7</v>
       </c>
       <c r="G2" t="n">
-        <v>85.8</v>
+        <v>86.2</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -554,10 +554,10 @@
         <v>56.83</v>
       </c>
       <c r="M2" t="n">
-        <v>74.76000000000001</v>
+        <v>72.89</v>
       </c>
       <c r="N2" t="n">
-        <v>44.6</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
@@ -575,13 +575,13 @@
         <v>0.9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.968</v>
+        <v>0.967</v>
       </c>
       <c r="E3" t="n">
-        <v>60.4</v>
+        <v>60.5</v>
       </c>
       <c r="F3" t="n">
-        <v>53.6</v>
+        <v>53.7</v>
       </c>
       <c r="G3" t="n">
         <v>46.9</v>
@@ -606,10 +606,10 @@
         <v>35.91</v>
       </c>
       <c r="M3" t="n">
-        <v>32.88</v>
+        <v>32.86</v>
       </c>
       <c r="N3" t="n">
-        <v>-13.5</v>
+        <v>-13.6</v>
       </c>
     </row>
     <row r="4">
@@ -627,16 +627,16 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5</v>
+        <v>1.474</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>19.2</v>
+        <v>20.1</v>
       </c>
       <c r="G4" t="n">
-        <v>39</v>
+        <v>39.2</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>63973</v>
+        <v>57165</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>76.87</v>
       </c>
       <c r="M4" t="n">
-        <v>107.54</v>
+        <v>105.9</v>
       </c>
       <c r="N4" t="n">
-        <v>39.6</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="5">
@@ -679,20 +679,20 @@
         <v>0.75</v>
       </c>
       <c r="D5" t="n">
-        <v>1.421</v>
+        <v>1.37</v>
       </c>
       <c r="E5" t="n">
-        <v>-8.5</v>
+        <v>-4.5</v>
       </c>
       <c r="F5" t="n">
-        <v>9.6</v>
+        <v>12.1</v>
       </c>
       <c r="G5" t="n">
-        <v>27.7</v>
+        <v>28.7</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>118655</v>
+        <v>75049</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -710,10 +710,10 @@
         <v>40.54</v>
       </c>
       <c r="M5" t="n">
-        <v>56.56</v>
+        <v>54.62</v>
       </c>
       <c r="N5" t="n">
-        <v>36.2</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="6">
@@ -731,16 +731,16 @@
         <v>0.82</v>
       </c>
       <c r="D6" t="n">
-        <v>1.177</v>
+        <v>1.154</v>
       </c>
       <c r="E6" t="n">
-        <v>5.6</v>
+        <v>8.1</v>
       </c>
       <c r="F6" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="G6" t="n">
-        <v>24.5</v>
+        <v>24.9</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -753,25 +753,25 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>42981</v>
+        <v>37928</v>
       </c>
       <c r="K6" t="n">
-        <v>208</v>
+        <v>640</v>
       </c>
       <c r="L6" t="n">
         <v>31.87</v>
       </c>
       <c r="M6" t="n">
-        <v>37.58</v>
+        <v>36.83</v>
       </c>
       <c r="N6" t="n">
-        <v>18.9</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -780,19 +780,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="D7" t="n">
-        <v>1.146</v>
+        <v>1.289</v>
       </c>
       <c r="E7" t="n">
-        <v>-1</v>
+        <v>0.8</v>
       </c>
       <c r="F7" t="n">
-        <v>11.6</v>
+        <v>12.6</v>
       </c>
       <c r="G7" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -805,25 +805,25 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>24202</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>13.38</v>
+        <v>16.85</v>
       </c>
       <c r="M7" t="n">
-        <v>16.78</v>
+        <v>20.77</v>
       </c>
       <c r="N7" t="n">
-        <v>25.2</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -832,19 +832,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>1.349</v>
+        <v>1.168</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.2</v>
+        <v>-4</v>
       </c>
       <c r="F8" t="n">
-        <v>10.4</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>30382</v>
+        <v>19107</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>16.85</v>
+        <v>13.38</v>
       </c>
       <c r="M8" t="n">
-        <v>21.57</v>
+        <v>17.3</v>
       </c>
       <c r="N8" t="n">
-        <v>27.1</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="9">
@@ -887,20 +887,20 @@
         <v>0.73</v>
       </c>
       <c r="D9" t="n">
-        <v>1.689</v>
+        <v>1.609</v>
       </c>
       <c r="E9" t="n">
-        <v>-7.8</v>
+        <v>-4.6</v>
       </c>
       <c r="F9" t="n">
-        <v>7.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>23.5</v>
+        <v>24</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>87258</v>
+        <v>64022</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -918,10 +918,10 @@
         <v>73.69</v>
       </c>
       <c r="M9" t="n">
-        <v>98.75</v>
+        <v>95.83</v>
       </c>
       <c r="N9" t="n">
-        <v>31.3</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="10">
@@ -939,16 +939,16 @@
         <v>0.86</v>
       </c>
       <c r="D10" t="n">
-        <v>1.508</v>
+        <v>1.48</v>
       </c>
       <c r="E10" t="n">
-        <v>-18.8</v>
+        <v>-17.1</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="G10" t="n">
-        <v>19.3</v>
+        <v>19.7</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>99382</v>
+        <v>94422</v>
       </c>
       <c r="K10" t="n">
-        <v>7511</v>
+        <v>7648</v>
       </c>
       <c r="L10" t="n">
         <v>6.23</v>
       </c>
       <c r="M10" t="n">
-        <v>9.15</v>
+        <v>8.99</v>
       </c>
       <c r="N10" t="n">
-        <v>38.2</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="11">
@@ -991,13 +991,13 @@
         <v>0.78</v>
       </c>
       <c r="D11" t="n">
-        <v>1.165</v>
+        <v>1.169</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
       <c r="F11" t="n">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="G11" t="n">
         <v>17.8</v>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>19445</v>
+        <v>19951</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1022,10 +1022,10 @@
         <v>28.62</v>
       </c>
       <c r="M11" t="n">
-        <v>33.9</v>
+        <v>34.04</v>
       </c>
       <c r="N11" t="n">
-        <v>18.3</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="12">
@@ -1043,13 +1043,13 @@
         <v>0.73</v>
       </c>
       <c r="D12" t="n">
-        <v>1.217</v>
+        <v>1.223</v>
       </c>
       <c r="E12" t="n">
-        <v>-12.7</v>
+        <v>-13.4</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="G12" t="n">
         <v>17.7</v>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>83165</v>
+        <v>86221</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1074,10 +1074,10 @@
         <v>14.11</v>
       </c>
       <c r="M12" t="n">
-        <v>19.03</v>
+        <v>19.18</v>
       </c>
       <c r="N12" t="n">
-        <v>30.5</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="13">
@@ -1095,16 +1095,16 @@
         <v>0.88</v>
       </c>
       <c r="D13" t="n">
-        <v>0.927</v>
+        <v>0.913</v>
       </c>
       <c r="E13" t="n">
-        <v>21.3</v>
+        <v>24.6</v>
       </c>
       <c r="F13" t="n">
-        <v>14.7</v>
+        <v>16.5</v>
       </c>
       <c r="G13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>529</v>
+        <v>610</v>
       </c>
       <c r="L13" t="n">
         <v>9.470000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>8.449999999999999</v>
+        <v>8.24</v>
       </c>
       <c r="N13" t="n">
-        <v>-13.1</v>
+        <v>-16.2</v>
       </c>
     </row>
     <row r="14">
@@ -1147,16 +1147,16 @@
         <v>0.84</v>
       </c>
       <c r="D14" t="n">
-        <v>1.522</v>
+        <v>1.499</v>
       </c>
       <c r="E14" t="n">
-        <v>-34.4</v>
+        <v>-33.2</v>
       </c>
       <c r="F14" t="n">
-        <v>-15.3</v>
+        <v>-14.7</v>
       </c>
       <c r="G14" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>215517</v>
+        <v>206288</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1178,16 +1178,16 @@
         <v>30.55</v>
       </c>
       <c r="M14" t="n">
-        <v>48.25</v>
+        <v>47.48</v>
       </c>
       <c r="N14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1196,23 +1196,23 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.89</v>
+        <v>0.62</v>
       </c>
       <c r="D15" t="n">
-        <v>1.093</v>
+        <v>0.862</v>
       </c>
       <c r="E15" t="n">
-        <v>-6.5</v>
+        <v>16.8</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7</v>
+        <v>10.3</v>
       </c>
       <c r="G15" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1221,25 +1221,25 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>30584</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>14327</v>
+        <v>14830</v>
       </c>
       <c r="L15" t="n">
-        <v>24.08</v>
+        <v>20.79</v>
       </c>
       <c r="M15" t="n">
-        <v>26.56</v>
+        <v>18.47</v>
       </c>
       <c r="N15" t="n">
-        <v>9.6</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1248,23 +1248,23 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.62</v>
+        <v>0.89</v>
       </c>
       <c r="D16" t="n">
-        <v>0.947</v>
+        <v>1.078</v>
       </c>
       <c r="E16" t="n">
-        <v>7.7</v>
+        <v>-4.9</v>
       </c>
       <c r="F16" t="n">
-        <v>5.4</v>
+        <v>-0.8</v>
       </c>
       <c r="G16" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1273,19 +1273,19 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>9375</v>
+        <v>27848</v>
       </c>
       <c r="K16" t="n">
-        <v>15105</v>
+        <v>14242</v>
       </c>
       <c r="L16" t="n">
-        <v>20.79</v>
+        <v>24.08</v>
       </c>
       <c r="M16" t="n">
-        <v>19.89</v>
+        <v>26.15</v>
       </c>
       <c r="N16" t="n">
-        <v>-4.6</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1303,16 +1303,16 @@
         <v>0.85</v>
       </c>
       <c r="D17" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="E17" t="n">
-        <v>-57.2</v>
+        <v>-56.8</v>
       </c>
       <c r="F17" t="n">
-        <v>-27.5</v>
+        <v>-27.2</v>
       </c>
       <c r="G17" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>466586</v>
+        <v>459263</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1334,10 +1334,10 @@
         <v>2.79</v>
       </c>
       <c r="M17" t="n">
-        <v>6.67</v>
+        <v>6.61</v>
       </c>
       <c r="N17" t="n">
-        <v>59.5</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="18">
@@ -1355,20 +1355,20 @@
         <v>0.72</v>
       </c>
       <c r="D18" t="n">
-        <v>0.983</v>
+        <v>1.003</v>
       </c>
       <c r="E18" t="n">
-        <v>8.1</v>
+        <v>0.7</v>
       </c>
       <c r="F18" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1386,10 +1386,10 @@
         <v>6.45</v>
       </c>
       <c r="M18" t="n">
-        <v>6.02</v>
+        <v>6.54</v>
       </c>
       <c r="N18" t="n">
-        <v>-7.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="19">
@@ -1407,16 +1407,16 @@
         <v>0.98</v>
       </c>
       <c r="D19" t="n">
-        <v>1.062</v>
+        <v>1.215</v>
       </c>
       <c r="E19" t="n">
-        <v>-7.2</v>
+        <v>-19.9</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.4</v>
+        <v>-11.3</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5</v>
+        <v>-2.8</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1429,19 +1429,19 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>22126</v>
+        <v>35266</v>
       </c>
       <c r="K19" t="n">
-        <v>17382</v>
+        <v>18824</v>
       </c>
       <c r="L19" t="n">
         <v>0.39</v>
       </c>
       <c r="M19" t="n">
-        <v>0.41</v>
+        <v>0.47</v>
       </c>
       <c r="N19" t="n">
-        <v>5.7</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="20">
@@ -1459,16 +1459,16 @@
         <v>1.04</v>
       </c>
       <c r="D20" t="n">
-        <v>1.124</v>
+        <v>1.121</v>
       </c>
       <c r="E20" t="n">
-        <v>-19.8</v>
+        <v>-19.4</v>
       </c>
       <c r="F20" t="n">
-        <v>-13.2</v>
+        <v>-12.9</v>
       </c>
       <c r="G20" t="n">
-        <v>-6.6</v>
+        <v>-6.5</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>144987</v>
+        <v>141591</v>
       </c>
       <c r="K20" t="n">
-        <v>49217</v>
+        <v>48690</v>
       </c>
       <c r="L20" t="n">
         <v>2.06</v>
       </c>
       <c r="M20" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="N20" t="n">
-        <v>13.2</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="21">
@@ -1511,16 +1511,16 @@
         <v>0.97</v>
       </c>
       <c r="D21" t="n">
-        <v>1.379</v>
+        <v>1.322</v>
       </c>
       <c r="E21" t="n">
-        <v>-36.3</v>
+        <v>-33</v>
       </c>
       <c r="F21" t="n">
-        <v>-22.4</v>
+        <v>-20.6</v>
       </c>
       <c r="G21" t="n">
-        <v>-8.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>222333</v>
+        <v>196627</v>
       </c>
       <c r="K21" t="n">
-        <v>63037</v>
+        <v>61101</v>
       </c>
       <c r="L21" t="n">
         <v>14.46</v>
       </c>
       <c r="M21" t="n">
-        <v>20.79</v>
+        <v>19.84</v>
       </c>
       <c r="N21" t="n">
-        <v>27.8</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="22">
@@ -1563,16 +1563,16 @@
         <v>1.11</v>
       </c>
       <c r="D22" t="n">
-        <v>1.649</v>
+        <v>1.586</v>
       </c>
       <c r="E22" t="n">
-        <v>-43.3</v>
+        <v>-41.1</v>
       </c>
       <c r="F22" t="n">
-        <v>-28.2</v>
+        <v>-26.9</v>
       </c>
       <c r="G22" t="n">
-        <v>-13.1</v>
+        <v>-12.7</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>408978</v>
+        <v>379056</v>
       </c>
       <c r="K22" t="n">
-        <v>165706</v>
+        <v>159674</v>
       </c>
       <c r="L22" t="n">
         <v>54.46</v>
       </c>
       <c r="M22" t="n">
-        <v>83.55</v>
+        <v>80.69</v>
       </c>
       <c r="N22" t="n">
-        <v>30.3</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="23">
@@ -1615,16 +1615,16 @@
         <v>1.14</v>
       </c>
       <c r="D23" t="n">
-        <v>1.179</v>
+        <v>1.184</v>
       </c>
       <c r="E23" t="n">
-        <v>-29</v>
+        <v>-29.4</v>
       </c>
       <c r="F23" t="n">
-        <v>-23</v>
+        <v>-23.3</v>
       </c>
       <c r="G23" t="n">
-        <v>-17</v>
+        <v>-17.1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1637,19 +1637,19 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>446788</v>
+        <v>453752</v>
       </c>
       <c r="K23" t="n">
-        <v>265483</v>
+        <v>267029</v>
       </c>
       <c r="L23" t="n">
         <v>13.24</v>
       </c>
       <c r="M23" t="n">
-        <v>15.48</v>
+        <v>15.55</v>
       </c>
       <c r="N23" t="n">
-        <v>12</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="24">
@@ -1667,16 +1667,16 @@
         <v>1.35</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9</v>
+        <v>0.896</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.5</v>
+        <v>-0.5</v>
       </c>
       <c r="F24" t="n">
-        <v>-9.5</v>
+        <v>-9</v>
       </c>
       <c r="G24" t="n">
-        <v>-17.6</v>
+        <v>-17.4</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>224647</v>
+        <v>207648</v>
       </c>
       <c r="K24" t="n">
-        <v>474889</v>
+        <v>468753</v>
       </c>
       <c r="L24" t="n">
         <v>30.67</v>
       </c>
       <c r="M24" t="n">
-        <v>25.69</v>
+        <v>25.47</v>
       </c>
       <c r="N24" t="n">
-        <v>-16</v>
+        <v>-16.9</v>
       </c>
     </row>
     <row r="25">
@@ -1719,16 +1719,16 @@
         <v>1.37</v>
       </c>
       <c r="D25" t="n">
-        <v>1.126</v>
+        <v>1.134</v>
       </c>
       <c r="E25" t="n">
-        <v>-41.2</v>
+        <v>-41.8</v>
       </c>
       <c r="F25" t="n">
-        <v>-36.4</v>
+        <v>-36.8</v>
       </c>
       <c r="G25" t="n">
-        <v>-31.7</v>
+        <v>-31.8</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1741,19 +1741,19 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>431515</v>
+        <v>440847</v>
       </c>
       <c r="K25" t="n">
-        <v>335842</v>
+        <v>339112</v>
       </c>
       <c r="L25" t="n">
         <v>23.15</v>
       </c>
       <c r="M25" t="n">
-        <v>26.87</v>
+        <v>27.11</v>
       </c>
       <c r="N25" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -1771,16 +1771,16 @@
         <v>1.35</v>
       </c>
       <c r="D26" t="n">
-        <v>1.211</v>
+        <v>1.232</v>
       </c>
       <c r="E26" t="n">
-        <v>-46.2</v>
+        <v>-47.4</v>
       </c>
       <c r="F26" t="n">
-        <v>-39.2</v>
+        <v>-39.9</v>
       </c>
       <c r="G26" t="n">
-        <v>-32.2</v>
+        <v>-32.4</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1793,19 +1793,19 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>446636</v>
+        <v>466032</v>
       </c>
       <c r="K26" t="n">
-        <v>316639</v>
+        <v>323230</v>
       </c>
       <c r="L26" t="n">
         <v>32.57</v>
       </c>
       <c r="M26" t="n">
-        <v>40.98</v>
+        <v>41.81</v>
       </c>
       <c r="N26" t="n">
-        <v>13.9</v>
+        <v>14.9</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -667,7 +667,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -679,13 +679,13 @@
         <v>0.75</v>
       </c>
       <c r="D5" t="n">
-        <v>1.37</v>
+        <v>1.266</v>
       </c>
       <c r="E5" t="n">
-        <v>-4.5</v>
+        <v>2.4</v>
       </c>
       <c r="F5" t="n">
-        <v>12.1</v>
+        <v>15.6</v>
       </c>
       <c r="G5" t="n">
         <v>28.7</v>
@@ -701,25 +701,25 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>75049</v>
+        <v>21597</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>40.54</v>
+        <v>17.11</v>
       </c>
       <c r="M5" t="n">
-        <v>54.62</v>
+        <v>21.51</v>
       </c>
       <c r="N5" t="n">
-        <v>33.2</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -728,50 +728,50 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="D6" t="n">
-        <v>1.154</v>
+        <v>1.37</v>
       </c>
       <c r="E6" t="n">
-        <v>8.1</v>
+        <v>-4.5</v>
       </c>
       <c r="F6" t="n">
-        <v>16.5</v>
+        <v>12.1</v>
       </c>
       <c r="G6" t="n">
-        <v>24.9</v>
+        <v>28.7</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>HOLD (fairly valued)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>BUY (undervalued)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>BUY (undervalued)</t>
-        </is>
-      </c>
       <c r="J6" t="n">
-        <v>37928</v>
+        <v>75049</v>
       </c>
       <c r="K6" t="n">
-        <v>640</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>31.87</v>
+        <v>40.54</v>
       </c>
       <c r="M6" t="n">
-        <v>36.83</v>
+        <v>54.62</v>
       </c>
       <c r="N6" t="n">
-        <v>16.8</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -780,19 +780,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="D7" t="n">
-        <v>1.289</v>
+        <v>1.426</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="F7" t="n">
-        <v>12.6</v>
+        <v>14.3</v>
       </c>
       <c r="G7" t="n">
-        <v>24.3</v>
+        <v>25.2</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -805,25 +805,25 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>24202</v>
+        <v>8968</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>16.85</v>
+        <v>79.87</v>
       </c>
       <c r="M7" t="n">
-        <v>20.77</v>
+        <v>96.73</v>
       </c>
       <c r="N7" t="n">
-        <v>23.4</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -832,23 +832,23 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="D8" t="n">
-        <v>1.168</v>
+        <v>1.154</v>
       </c>
       <c r="E8" t="n">
-        <v>-4</v>
+        <v>8.1</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="G8" t="n">
-        <v>24.1</v>
+        <v>24.9</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -857,25 +857,25 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>19107</v>
+        <v>37928</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="L8" t="n">
-        <v>13.38</v>
+        <v>31.87</v>
       </c>
       <c r="M8" t="n">
-        <v>17.3</v>
+        <v>36.83</v>
       </c>
       <c r="N8" t="n">
-        <v>28.2</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -884,19 +884,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>1.609</v>
+        <v>1.168</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.6</v>
+        <v>-4</v>
       </c>
       <c r="F9" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -909,19 +909,19 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>64022</v>
+        <v>19107</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>73.69</v>
+        <v>13.38</v>
       </c>
       <c r="M9" t="n">
-        <v>95.83</v>
+        <v>17.3</v>
       </c>
       <c r="N9" t="n">
-        <v>28.7</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="10">
@@ -1095,16 +1095,16 @@
         <v>0.88</v>
       </c>
       <c r="D13" t="n">
-        <v>0.913</v>
+        <v>0.918</v>
       </c>
       <c r="E13" t="n">
         <v>24.6</v>
       </c>
       <c r="F13" t="n">
-        <v>16.5</v>
+        <v>16.7</v>
       </c>
       <c r="G13" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>610</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>9.470000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>8.24</v>
+        <v>8.26</v>
       </c>
       <c r="N13" t="n">
-        <v>-16.2</v>
+        <v>-15.8</v>
       </c>
     </row>
     <row r="14">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -1707,7 +1707,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1716,19 +1716,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="D25" t="n">
-        <v>1.134</v>
+        <v>1.169</v>
       </c>
       <c r="E25" t="n">
-        <v>-41.8</v>
+        <v>-42.3</v>
       </c>
       <c r="F25" t="n">
-        <v>-36.8</v>
+        <v>-36.9</v>
       </c>
       <c r="G25" t="n">
-        <v>-31.8</v>
+        <v>-31.6</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1741,25 +1741,25 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>440847</v>
+        <v>421886</v>
       </c>
       <c r="K25" t="n">
-        <v>339112</v>
+        <v>319860</v>
       </c>
       <c r="L25" t="n">
-        <v>23.15</v>
+        <v>35.69</v>
       </c>
       <c r="M25" t="n">
-        <v>27.11</v>
+        <v>42.32</v>
       </c>
       <c r="N25" t="n">
-        <v>10</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1768,19 +1768,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="D26" t="n">
-        <v>1.232</v>
+        <v>1.134</v>
       </c>
       <c r="E26" t="n">
-        <v>-47.4</v>
+        <v>-41.8</v>
       </c>
       <c r="F26" t="n">
-        <v>-39.9</v>
+        <v>-36.8</v>
       </c>
       <c r="G26" t="n">
-        <v>-32.4</v>
+        <v>-31.8</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1793,19 +1793,19 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>466032</v>
+        <v>440847</v>
       </c>
       <c r="K26" t="n">
-        <v>323230</v>
+        <v>339112</v>
       </c>
       <c r="L26" t="n">
-        <v>32.57</v>
+        <v>23.15</v>
       </c>
       <c r="M26" t="n">
-        <v>41.81</v>
+        <v>27.11</v>
       </c>
       <c r="N26" t="n">
-        <v>14.9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -575,16 +575,16 @@
         <v>0.9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.967</v>
+        <v>0.991</v>
       </c>
       <c r="E3" t="n">
-        <v>60.5</v>
+        <v>50.7</v>
       </c>
       <c r="F3" t="n">
-        <v>53.7</v>
+        <v>48.9</v>
       </c>
       <c r="G3" t="n">
-        <v>46.9</v>
+        <v>47.1</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -603,13 +603,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>35.91</v>
+        <v>33.7</v>
       </c>
       <c r="M3" t="n">
-        <v>32.86</v>
+        <v>32.91</v>
       </c>
       <c r="N3" t="n">
-        <v>-13.6</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="4">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -627,16 +627,16 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>1.474</v>
+        <v>1.552</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>-3.1</v>
       </c>
       <c r="F4" t="n">
-        <v>20.1</v>
+        <v>16.4</v>
       </c>
       <c r="G4" t="n">
-        <v>39.2</v>
+        <v>35.9</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>57165</v>
+        <v>71456</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>76.87</v>
+        <v>73.73</v>
       </c>
       <c r="M4" t="n">
-        <v>105.9</v>
+        <v>103.41</v>
       </c>
       <c r="N4" t="n">
-        <v>38.2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -1135,7 +1135,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1144,23 +1144,23 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.84</v>
+        <v>0.62</v>
       </c>
       <c r="D14" t="n">
-        <v>1.499</v>
+        <v>0.862</v>
       </c>
       <c r="E14" t="n">
-        <v>-33.2</v>
+        <v>16.8</v>
       </c>
       <c r="F14" t="n">
-        <v>-14.7</v>
+        <v>10.3</v>
       </c>
       <c r="G14" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1169,25 +1169,25 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>206288</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>14830</v>
       </c>
       <c r="L14" t="n">
-        <v>30.55</v>
+        <v>20.79</v>
       </c>
       <c r="M14" t="n">
-        <v>47.48</v>
+        <v>18.47</v>
       </c>
       <c r="N14" t="n">
-        <v>37</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1196,23 +1196,23 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.62</v>
+        <v>0.84</v>
       </c>
       <c r="D15" t="n">
-        <v>0.862</v>
+        <v>1.569</v>
       </c>
       <c r="E15" t="n">
-        <v>16.8</v>
+        <v>-30.5</v>
       </c>
       <c r="F15" t="n">
-        <v>10.3</v>
+        <v>-13.4</v>
       </c>
       <c r="G15" t="n">
         <v>3.7</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="J15" t="n">
+        <v>223619</v>
+      </c>
+      <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="K15" t="n">
-        <v>14830</v>
-      </c>
       <c r="L15" t="n">
-        <v>20.79</v>
+        <v>31.82</v>
       </c>
       <c r="M15" t="n">
-        <v>18.47</v>
+        <v>47.43</v>
       </c>
       <c r="N15" t="n">
-        <v>-13</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -667,7 +667,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -679,16 +679,16 @@
         <v>0.75</v>
       </c>
       <c r="D5" t="n">
-        <v>1.266</v>
+        <v>1.324</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="F5" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="G5" t="n">
-        <v>28.7</v>
+        <v>29.7</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -701,25 +701,25 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>21597</v>
+        <v>16874</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>17.11</v>
+        <v>43.02</v>
       </c>
       <c r="M5" t="n">
-        <v>21.51</v>
+        <v>55.05</v>
       </c>
       <c r="N5" t="n">
-        <v>26.3</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -731,13 +731,13 @@
         <v>0.75</v>
       </c>
       <c r="D6" t="n">
-        <v>1.37</v>
+        <v>1.266</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.5</v>
+        <v>2.4</v>
       </c>
       <c r="F6" t="n">
-        <v>12.1</v>
+        <v>15.6</v>
       </c>
       <c r="G6" t="n">
         <v>28.7</v>
@@ -753,19 +753,19 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>75049</v>
+        <v>21597</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>40.54</v>
+        <v>17.11</v>
       </c>
       <c r="M6" t="n">
-        <v>54.62</v>
+        <v>21.51</v>
       </c>
       <c r="N6" t="n">
-        <v>33.2</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="7">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -1615,16 +1615,16 @@
         <v>1.14</v>
       </c>
       <c r="D23" t="n">
-        <v>1.184</v>
+        <v>1.174</v>
       </c>
       <c r="E23" t="n">
-        <v>-29.4</v>
+        <v>-28</v>
       </c>
       <c r="F23" t="n">
-        <v>-23.3</v>
+        <v>-22.4</v>
       </c>
       <c r="G23" t="n">
-        <v>-17.1</v>
+        <v>-16.7</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1637,19 +1637,19 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>453752</v>
+        <v>437369</v>
       </c>
       <c r="K23" t="n">
-        <v>267029</v>
+        <v>266381</v>
       </c>
       <c r="L23" t="n">
-        <v>13.24</v>
+        <v>13.51</v>
       </c>
       <c r="M23" t="n">
-        <v>15.55</v>
+        <v>15.62</v>
       </c>
       <c r="N23" t="n">
-        <v>12.3</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="24">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -1251,41 +1251,41 @@
         <v>0.89</v>
       </c>
       <c r="D16" t="n">
-        <v>1.078</v>
+        <v>1.1</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.9</v>
+        <v>-7.5</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8</v>
+        <v>-2.2</v>
       </c>
       <c r="G16" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>HOLD (fairly valued)</t>
-        </is>
-      </c>
       <c r="J16" t="n">
-        <v>27848</v>
+        <v>32091</v>
       </c>
       <c r="K16" t="n">
-        <v>14242</v>
+        <v>14737</v>
       </c>
       <c r="L16" t="n">
-        <v>24.08</v>
+        <v>23.42</v>
       </c>
       <c r="M16" t="n">
-        <v>26.15</v>
+        <v>26.1</v>
       </c>
       <c r="N16" t="n">
-        <v>8.199999999999999</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="17">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -1407,16 +1407,16 @@
         <v>0.98</v>
       </c>
       <c r="D19" t="n">
-        <v>1.215</v>
+        <v>1.187</v>
       </c>
       <c r="E19" t="n">
-        <v>-19.9</v>
+        <v>-17.5</v>
       </c>
       <c r="F19" t="n">
-        <v>-11.3</v>
+        <v>-9.9</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.8</v>
+        <v>-2.3</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1429,19 +1429,19 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>35266</v>
+        <v>32650</v>
       </c>
       <c r="K19" t="n">
-        <v>18824</v>
+        <v>18346</v>
       </c>
       <c r="L19" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="M19" t="n">
         <v>0.47</v>
       </c>
       <c r="N19" t="n">
-        <v>17.1</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="20">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -991,16 +991,16 @@
         <v>0.78</v>
       </c>
       <c r="D11" t="n">
-        <v>1.169</v>
+        <v>1.122</v>
       </c>
       <c r="E11" t="n">
-        <v>-1</v>
+        <v>4.6</v>
       </c>
       <c r="F11" t="n">
-        <v>8.4</v>
+        <v>11.3</v>
       </c>
       <c r="G11" t="n">
-        <v>17.8</v>
+        <v>18.1</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>19951</v>
+        <v>13931</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>28.62</v>
+        <v>30.22</v>
       </c>
       <c r="M11" t="n">
-        <v>34.04</v>
+        <v>34.14</v>
       </c>
       <c r="N11" t="n">
-        <v>18.7</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="12">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -1135,7 +1135,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1144,23 +1144,23 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.62</v>
+        <v>0.84</v>
       </c>
       <c r="D14" t="n">
-        <v>0.862</v>
+        <v>1.569</v>
       </c>
       <c r="E14" t="n">
-        <v>16.8</v>
+        <v>-30.5</v>
       </c>
       <c r="F14" t="n">
-        <v>10.3</v>
+        <v>-13.4</v>
       </c>
       <c r="G14" t="n">
         <v>3.7</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1169,25 +1169,25 @@
         </is>
       </c>
       <c r="J14" t="n">
+        <v>223619</v>
+      </c>
+      <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="K14" t="n">
-        <v>14830</v>
-      </c>
       <c r="L14" t="n">
-        <v>20.79</v>
+        <v>31.82</v>
       </c>
       <c r="M14" t="n">
-        <v>18.47</v>
+        <v>47.43</v>
       </c>
       <c r="N14" t="n">
-        <v>-13</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1196,23 +1196,23 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.84</v>
+        <v>0.62</v>
       </c>
       <c r="D15" t="n">
-        <v>1.569</v>
+        <v>0.886</v>
       </c>
       <c r="E15" t="n">
-        <v>-30.5</v>
+        <v>14.2</v>
       </c>
       <c r="F15" t="n">
-        <v>-13.4</v>
+        <v>8.9</v>
       </c>
       <c r="G15" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>223619</v>
+        <v>2798</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>14918</v>
       </c>
       <c r="L15" t="n">
-        <v>31.82</v>
+        <v>20.33</v>
       </c>
       <c r="M15" t="n">
-        <v>47.43</v>
+        <v>18.44</v>
       </c>
       <c r="N15" t="n">
-        <v>34.1</v>
+        <v>-10.6</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -523,13 +523,13 @@
         <v>0.34</v>
       </c>
       <c r="D2" t="n">
-        <v>1.223</v>
+        <v>1.218</v>
       </c>
       <c r="E2" t="n">
-        <v>45.2</v>
+        <v>46</v>
       </c>
       <c r="F2" t="n">
-        <v>65.7</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>86.2</v>
@@ -551,13 +551,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>56.83</v>
+        <v>57.16</v>
       </c>
       <c r="M2" t="n">
-        <v>72.89</v>
+        <v>72.87</v>
       </c>
       <c r="N2" t="n">
-        <v>41</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="3">
@@ -627,13 +627,13 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>1.552</v>
+        <v>1.557</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.1</v>
+        <v>-3.3</v>
       </c>
       <c r="F4" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="G4" t="n">
         <v>35.9</v>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>71456</v>
+        <v>72587</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>73.73</v>
+        <v>73.56</v>
       </c>
       <c r="M4" t="n">
-        <v>103.41</v>
+        <v>103.42</v>
       </c>
       <c r="N4" t="n">
-        <v>39</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="5">
@@ -835,13 +835,13 @@
         <v>0.82</v>
       </c>
       <c r="D8" t="n">
-        <v>1.154</v>
+        <v>1.157</v>
       </c>
       <c r="E8" t="n">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="F8" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="G8" t="n">
         <v>24.9</v>
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>37928</v>
+        <v>38395</v>
       </c>
       <c r="K8" t="n">
-        <v>640</v>
+        <v>618</v>
       </c>
       <c r="L8" t="n">
-        <v>31.87</v>
+        <v>31.8</v>
       </c>
       <c r="M8" t="n">
-        <v>36.83</v>
+        <v>36.84</v>
       </c>
       <c r="N8" t="n">
-        <v>16.8</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="9">
@@ -890,13 +890,13 @@
         <v>1.168</v>
       </c>
       <c r="E9" t="n">
-        <v>-4</v>
+        <v>-3.9</v>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="G9" t="n">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -909,16 +909,16 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>19107</v>
+        <v>18274</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>13.38</v>
+        <v>13.39</v>
       </c>
       <c r="M9" t="n">
-        <v>17.3</v>
+        <v>17.33</v>
       </c>
       <c r="N9" t="n">
         <v>28.2</v>
@@ -939,7 +939,7 @@
         <v>0.86</v>
       </c>
       <c r="D10" t="n">
-        <v>1.48</v>
+        <v>1.481</v>
       </c>
       <c r="E10" t="n">
         <v>-17.1</v>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>94422</v>
+        <v>94534</v>
       </c>
       <c r="K10" t="n">
-        <v>7648</v>
+        <v>7642</v>
       </c>
       <c r="L10" t="n">
-        <v>6.23</v>
+        <v>6.22</v>
       </c>
       <c r="M10" t="n">
         <v>8.99</v>
       </c>
       <c r="N10" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="11">
@@ -991,20 +991,20 @@
         <v>0.78</v>
       </c>
       <c r="D11" t="n">
-        <v>1.122</v>
+        <v>1.103</v>
       </c>
       <c r="E11" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="F11" t="n">
-        <v>11.3</v>
+        <v>12.3</v>
       </c>
       <c r="G11" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>13931</v>
+        <v>11773</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>30.22</v>
+        <v>30.76</v>
       </c>
       <c r="M11" t="n">
-        <v>34.14</v>
+        <v>34.15</v>
       </c>
       <c r="N11" t="n">
-        <v>13.6</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="12">
@@ -1043,16 +1043,16 @@
         <v>0.73</v>
       </c>
       <c r="D12" t="n">
-        <v>1.223</v>
+        <v>1.211</v>
       </c>
       <c r="E12" t="n">
-        <v>-13.4</v>
+        <v>-11.9</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1065,19 +1065,19 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>86221</v>
+        <v>79939</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>14.11</v>
+        <v>14.35</v>
       </c>
       <c r="M12" t="n">
-        <v>19.18</v>
+        <v>19.21</v>
       </c>
       <c r="N12" t="n">
-        <v>31.1</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="13">
@@ -1095,16 +1095,16 @@
         <v>0.88</v>
       </c>
       <c r="D13" t="n">
-        <v>0.918</v>
+        <v>0.89</v>
       </c>
       <c r="E13" t="n">
-        <v>24.6</v>
+        <v>31.1</v>
       </c>
       <c r="F13" t="n">
-        <v>16.7</v>
+        <v>20.1</v>
       </c>
       <c r="G13" t="n">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1123,13 +1123,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>9.470000000000001</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>8.26</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-15.8</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="14">
@@ -1199,16 +1199,16 @@
         <v>0.62</v>
       </c>
       <c r="D15" t="n">
-        <v>0.886</v>
+        <v>0.87</v>
       </c>
       <c r="E15" t="n">
-        <v>14.2</v>
+        <v>15.8</v>
       </c>
       <c r="F15" t="n">
-        <v>8.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>2798</v>
+        <v>949</v>
       </c>
       <c r="K15" t="n">
-        <v>14918</v>
+        <v>14941</v>
       </c>
       <c r="L15" t="n">
-        <v>20.33</v>
+        <v>20.61</v>
       </c>
       <c r="M15" t="n">
-        <v>18.44</v>
+        <v>18.43</v>
       </c>
       <c r="N15" t="n">
-        <v>-10.6</v>
+        <v>-12.3</v>
       </c>
     </row>
     <row r="16">
@@ -1251,16 +1251,16 @@
         <v>0.89</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1</v>
+        <v>1.096</v>
       </c>
       <c r="E16" t="n">
-        <v>-7.5</v>
+        <v>-7.1</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.2</v>
+        <v>-2</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1273,25 +1273,25 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>32091</v>
+        <v>31433</v>
       </c>
       <c r="K16" t="n">
-        <v>14737</v>
+        <v>14720</v>
       </c>
       <c r="L16" t="n">
-        <v>23.42</v>
+        <v>23.53</v>
       </c>
       <c r="M16" t="n">
         <v>26.1</v>
       </c>
       <c r="N16" t="n">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1300,23 +1300,23 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.85</v>
+        <v>0.72</v>
       </c>
       <c r="D17" t="n">
-        <v>2.23</v>
+        <v>1.003</v>
       </c>
       <c r="E17" t="n">
-        <v>-56.8</v>
+        <v>1.3</v>
       </c>
       <c r="F17" t="n">
-        <v>-27.2</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1325,25 +1325,25 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>459263</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>2.79</v>
+        <v>6.49</v>
       </c>
       <c r="M17" t="n">
-        <v>6.61</v>
+        <v>6.58</v>
       </c>
       <c r="N17" t="n">
-        <v>59.1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1352,44 +1352,44 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.72</v>
+        <v>0.85</v>
       </c>
       <c r="D18" t="n">
-        <v>1.003</v>
+        <v>2.23</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7</v>
+        <v>-56.8</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4</v>
+        <v>-27.2</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>HOLD (fairly valued)</t>
-        </is>
-      </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>459263</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>6.45</v>
+        <v>2.79</v>
       </c>
       <c r="M18" t="n">
-        <v>6.54</v>
+        <v>6.61</v>
       </c>
       <c r="N18" t="n">
-        <v>1.3</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="19">
@@ -1407,10 +1407,10 @@
         <v>0.98</v>
       </c>
       <c r="D19" t="n">
-        <v>1.187</v>
+        <v>1.186</v>
       </c>
       <c r="E19" t="n">
-        <v>-17.5</v>
+        <v>-17.4</v>
       </c>
       <c r="F19" t="n">
         <v>-9.9</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>32650</v>
+        <v>32599</v>
       </c>
       <c r="K19" t="n">
-        <v>18346</v>
+        <v>18349</v>
       </c>
       <c r="L19" t="n">
         <v>0.4</v>
@@ -1563,16 +1563,16 @@
         <v>1.11</v>
       </c>
       <c r="D22" t="n">
-        <v>1.586</v>
+        <v>1.544</v>
       </c>
       <c r="E22" t="n">
-        <v>-41.1</v>
+        <v>-39.8</v>
       </c>
       <c r="F22" t="n">
-        <v>-26.9</v>
+        <v>-26.3</v>
       </c>
       <c r="G22" t="n">
-        <v>-12.7</v>
+        <v>-12.8</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>379056</v>
+        <v>380065</v>
       </c>
       <c r="K22" t="n">
-        <v>159674</v>
+        <v>164298</v>
       </c>
       <c r="L22" t="n">
-        <v>54.46</v>
+        <v>55.59</v>
       </c>
       <c r="M22" t="n">
-        <v>80.69</v>
+        <v>80.58</v>
       </c>
       <c r="N22" t="n">
-        <v>28.4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23">
@@ -1615,16 +1615,16 @@
         <v>1.14</v>
       </c>
       <c r="D23" t="n">
-        <v>1.174</v>
+        <v>1.089</v>
       </c>
       <c r="E23" t="n">
-        <v>-28</v>
+        <v>-22.8</v>
       </c>
       <c r="F23" t="n">
-        <v>-22.4</v>
+        <v>-19.7</v>
       </c>
       <c r="G23" t="n">
-        <v>-16.7</v>
+        <v>-16.6</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1637,19 +1637,19 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>437369</v>
+        <v>358707</v>
       </c>
       <c r="K23" t="n">
-        <v>266381</v>
+        <v>264214</v>
       </c>
       <c r="L23" t="n">
-        <v>13.51</v>
+        <v>14.48</v>
       </c>
       <c r="M23" t="n">
-        <v>15.62</v>
+        <v>15.65</v>
       </c>
       <c r="N23" t="n">
-        <v>11.2</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="24">
@@ -1719,16 +1719,16 @@
         <v>1.35</v>
       </c>
       <c r="D25" t="n">
-        <v>1.169</v>
+        <v>1.125</v>
       </c>
       <c r="E25" t="n">
-        <v>-42.3</v>
+        <v>-39.7</v>
       </c>
       <c r="F25" t="n">
-        <v>-36.9</v>
+        <v>-35.6</v>
       </c>
       <c r="G25" t="n">
-        <v>-31.6</v>
+        <v>-31.4</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1741,19 +1741,19 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>421886</v>
+        <v>401319</v>
       </c>
       <c r="K25" t="n">
-        <v>319860</v>
+        <v>321782</v>
       </c>
       <c r="L25" t="n">
-        <v>35.69</v>
+        <v>37.31</v>
       </c>
       <c r="M25" t="n">
-        <v>42.32</v>
+        <v>42.42</v>
       </c>
       <c r="N25" t="n">
-        <v>10.7</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1771,16 +1771,16 @@
         <v>1.37</v>
       </c>
       <c r="D26" t="n">
-        <v>1.134</v>
+        <v>1.097</v>
       </c>
       <c r="E26" t="n">
-        <v>-41.8</v>
+        <v>-39</v>
       </c>
       <c r="F26" t="n">
-        <v>-36.8</v>
+        <v>-35.3</v>
       </c>
       <c r="G26" t="n">
-        <v>-31.8</v>
+        <v>-31.6</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1793,19 +1793,19 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>440847</v>
+        <v>416150</v>
       </c>
       <c r="K26" t="n">
-        <v>339112</v>
+        <v>339162</v>
       </c>
       <c r="L26" t="n">
-        <v>23.15</v>
+        <v>24.22</v>
       </c>
       <c r="M26" t="n">
-        <v>27.11</v>
+        <v>27.2</v>
       </c>
       <c r="N26" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -682,13 +682,13 @@
         <v>1.324</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>15.5</v>
+        <v>15.2</v>
       </c>
       <c r="G5" t="n">
-        <v>29.7</v>
+        <v>29.3</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -701,19 +701,19 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>16874</v>
+        <v>41213</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>43.02</v>
+        <v>42.88</v>
       </c>
       <c r="M5" t="n">
-        <v>55.05</v>
+        <v>54.86</v>
       </c>
       <c r="N5" t="n">
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="6">
@@ -994,38 +994,38 @@
         <v>1.103</v>
       </c>
       <c r="E11" t="n">
-        <v>6.4</v>
+        <v>3.8</v>
       </c>
       <c r="F11" t="n">
-        <v>12.3</v>
+        <v>9.5</v>
       </c>
       <c r="G11" t="n">
-        <v>18.2</v>
+        <v>15.2</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>HOLD (fairly valued)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>BUY (undervalued)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>BUY (undervalued)</t>
-        </is>
-      </c>
       <c r="J11" t="n">
-        <v>11773</v>
+        <v>11492</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>30.76</v>
+        <v>30</v>
       </c>
       <c r="M11" t="n">
-        <v>34.15</v>
+        <v>33.3</v>
       </c>
       <c r="N11" t="n">
-        <v>11.7</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="12">
@@ -1046,13 +1046,13 @@
         <v>1.211</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.9</v>
+        <v>-14.9</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>-0.3</v>
       </c>
       <c r="G12" t="n">
-        <v>17.9</v>
+        <v>14.2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1071,13 +1071,13 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>14.35</v>
+        <v>13.86</v>
       </c>
       <c r="M12" t="n">
-        <v>19.21</v>
+        <v>18.61</v>
       </c>
       <c r="N12" t="n">
-        <v>29.8</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="13">
@@ -1098,13 +1098,13 @@
         <v>0.89</v>
       </c>
       <c r="E13" t="n">
-        <v>31.1</v>
+        <v>25.4</v>
       </c>
       <c r="F13" t="n">
-        <v>20.1</v>
+        <v>14.7</v>
       </c>
       <c r="G13" t="n">
-        <v>9.1</v>
+        <v>4</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1123,13 +1123,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>9.970000000000001</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>8.289999999999999</v>
+        <v>7.91</v>
       </c>
       <c r="N13" t="n">
-        <v>-22</v>
+        <v>-21.4</v>
       </c>
     </row>
     <row r="14">
@@ -1187,7 +1187,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1196,23 +1196,23 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.62</v>
+        <v>0.72</v>
       </c>
       <c r="D15" t="n">
-        <v>0.87</v>
+        <v>1.003</v>
       </c>
       <c r="E15" t="n">
-        <v>15.8</v>
+        <v>1.3</v>
       </c>
       <c r="F15" t="n">
-        <v>9.699999999999999</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1221,25 +1221,25 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>949</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>14941</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>20.61</v>
+        <v>6.49</v>
       </c>
       <c r="M15" t="n">
-        <v>18.43</v>
+        <v>6.58</v>
       </c>
       <c r="N15" t="n">
-        <v>-12.3</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1248,19 +1248,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="D16" t="n">
-        <v>1.096</v>
+        <v>2.23</v>
       </c>
       <c r="E16" t="n">
-        <v>-7.1</v>
+        <v>-56.8</v>
       </c>
       <c r="F16" t="n">
-        <v>-2</v>
+        <v>-27.2</v>
       </c>
       <c r="G16" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1273,25 +1273,25 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>31433</v>
+        <v>459263</v>
       </c>
       <c r="K16" t="n">
-        <v>14720</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>23.53</v>
+        <v>2.79</v>
       </c>
       <c r="M16" t="n">
-        <v>26.1</v>
+        <v>6.61</v>
       </c>
       <c r="N16" t="n">
-        <v>10.2</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1300,50 +1300,50 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.72</v>
+        <v>0.62</v>
       </c>
       <c r="D17" t="n">
-        <v>1.003</v>
+        <v>0.87</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3</v>
+        <v>13.9</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>7.9</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
+          <t>BUY (undervalued)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>HOLD (fairly valued)</t>
-        </is>
-      </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>930</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>14638</v>
       </c>
       <c r="L17" t="n">
-        <v>6.49</v>
+        <v>20.27</v>
       </c>
       <c r="M17" t="n">
-        <v>6.58</v>
+        <v>18.13</v>
       </c>
       <c r="N17" t="n">
-        <v>1.3</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1352,19 +1352,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="D18" t="n">
-        <v>2.23</v>
+        <v>1.096</v>
       </c>
       <c r="E18" t="n">
-        <v>-56.8</v>
+        <v>-9.6</v>
       </c>
       <c r="F18" t="n">
-        <v>-27.2</v>
+        <v>-4.7</v>
       </c>
       <c r="G18" t="n">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>459263</v>
+        <v>30423</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>14247</v>
       </c>
       <c r="L18" t="n">
-        <v>2.79</v>
+        <v>22.89</v>
       </c>
       <c r="M18" t="n">
-        <v>6.61</v>
+        <v>25.4</v>
       </c>
       <c r="N18" t="n">
-        <v>59.1</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="19">
@@ -1410,13 +1410,13 @@
         <v>1.186</v>
       </c>
       <c r="E19" t="n">
-        <v>-17.4</v>
+        <v>-17.7</v>
       </c>
       <c r="F19" t="n">
-        <v>-9.9</v>
+        <v>-10.2</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.3</v>
+        <v>-2.7</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>32599</v>
+        <v>28574</v>
       </c>
       <c r="K19" t="n">
-        <v>18349</v>
+        <v>17304</v>
       </c>
       <c r="L19" t="n">
         <v>0.4</v>
@@ -1441,7 +1441,7 @@
         <v>0.47</v>
       </c>
       <c r="N19" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1459,13 +1459,13 @@
         <v>1.04</v>
       </c>
       <c r="D20" t="n">
-        <v>1.121</v>
+        <v>1.118</v>
       </c>
       <c r="E20" t="n">
-        <v>-19.4</v>
+        <v>-19.1</v>
       </c>
       <c r="F20" t="n">
-        <v>-12.9</v>
+        <v>-12.8</v>
       </c>
       <c r="G20" t="n">
         <v>-6.5</v>
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>141591</v>
+        <v>139574</v>
       </c>
       <c r="K20" t="n">
-        <v>48690</v>
+        <v>48856</v>
       </c>
       <c r="L20" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="M20" t="n">
         <v>2.39</v>
       </c>
       <c r="N20" t="n">
-        <v>12.9</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="21">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -991,13 +991,13 @@
         <v>0.78</v>
       </c>
       <c r="D11" t="n">
-        <v>1.103</v>
+        <v>1.11</v>
       </c>
       <c r="E11" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="F11" t="n">
-        <v>9.5</v>
+        <v>9.1</v>
       </c>
       <c r="G11" t="n">
         <v>15.2</v>
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>11492</v>
+        <v>12307</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>30</v>
+        <v>29.79</v>
       </c>
       <c r="M11" t="n">
         <v>33.3</v>
       </c>
       <c r="N11" t="n">
-        <v>11.4</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="12">
@@ -1303,13 +1303,13 @@
         <v>0.62</v>
       </c>
       <c r="D17" t="n">
-        <v>0.87</v>
+        <v>0.879</v>
       </c>
       <c r="E17" t="n">
-        <v>13.9</v>
+        <v>12.9</v>
       </c>
       <c r="F17" t="n">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="G17" t="n">
         <v>1.9</v>
@@ -1325,19 +1325,19 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>930</v>
+        <v>1982</v>
       </c>
       <c r="K17" t="n">
-        <v>14638</v>
+        <v>14648</v>
       </c>
       <c r="L17" t="n">
-        <v>20.27</v>
+        <v>20.11</v>
       </c>
       <c r="M17" t="n">
         <v>18.13</v>
       </c>
       <c r="N17" t="n">
-        <v>-12</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="18">
@@ -1355,13 +1355,13 @@
         <v>0.89</v>
       </c>
       <c r="D18" t="n">
-        <v>1.096</v>
+        <v>1.105</v>
       </c>
       <c r="E18" t="n">
-        <v>-9.6</v>
+        <v>-10.5</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.7</v>
+        <v>-5.1</v>
       </c>
       <c r="G18" t="n">
         <v>0.3</v>
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>30423</v>
+        <v>31845</v>
       </c>
       <c r="K18" t="n">
-        <v>14247</v>
+        <v>14263</v>
       </c>
       <c r="L18" t="n">
-        <v>22.89</v>
+        <v>22.67</v>
       </c>
       <c r="M18" t="n">
         <v>25.4</v>
       </c>
       <c r="N18" t="n">
-        <v>9.9</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="19">
@@ -1407,13 +1407,13 @@
         <v>0.98</v>
       </c>
       <c r="D19" t="n">
-        <v>1.186</v>
+        <v>1.197</v>
       </c>
       <c r="E19" t="n">
-        <v>-17.7</v>
+        <v>-18.4</v>
       </c>
       <c r="F19" t="n">
-        <v>-10.2</v>
+        <v>-10.5</v>
       </c>
       <c r="G19" t="n">
         <v>-2.7</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>28574</v>
+        <v>29068</v>
       </c>
       <c r="K19" t="n">
-        <v>17304</v>
+        <v>17269</v>
       </c>
       <c r="L19" t="n">
         <v>0.4</v>
@@ -1441,7 +1441,7 @@
         <v>0.47</v>
       </c>
       <c r="N19" t="n">
-        <v>15</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="20">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -526,13 +526,13 @@
         <v>1.218</v>
       </c>
       <c r="E2" t="n">
-        <v>46</v>
+        <v>59.6</v>
       </c>
       <c r="F2" t="n">
-        <v>66.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="G2" t="n">
-        <v>86.2</v>
+        <v>102.7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -551,19 +551,19 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>57.16</v>
+        <v>62.47</v>
       </c>
       <c r="M2" t="n">
-        <v>72.87</v>
+        <v>79.34</v>
       </c>
       <c r="N2" t="n">
-        <v>40.1</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -572,16 +572,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9</v>
+        <v>0.72</v>
       </c>
       <c r="D3" t="n">
-        <v>0.991</v>
+        <v>1.003</v>
       </c>
       <c r="E3" t="n">
-        <v>50.7</v>
+        <v>45.6</v>
       </c>
       <c r="F3" t="n">
-        <v>48.9</v>
+        <v>46.4</v>
       </c>
       <c r="G3" t="n">
         <v>47.1</v>
@@ -603,19 +603,19 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>33.7</v>
+        <v>9.33</v>
       </c>
       <c r="M3" t="n">
-        <v>32.91</v>
+        <v>9.43</v>
       </c>
       <c r="N3" t="n">
-        <v>-3.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -624,23 +624,23 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="D4" t="n">
-        <v>1.557</v>
+        <v>0.991</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.3</v>
+        <v>50.7</v>
       </c>
       <c r="F4" t="n">
-        <v>16.3</v>
+        <v>48.9</v>
       </c>
       <c r="G4" t="n">
-        <v>35.9</v>
+        <v>47.1</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -649,25 +649,25 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>72587</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>73.56</v>
+        <v>33.7</v>
       </c>
       <c r="M4" t="n">
-        <v>103.42</v>
+        <v>32.91</v>
       </c>
       <c r="N4" t="n">
-        <v>39.2</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -676,23 +676,23 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>1.324</v>
+        <v>1.168</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>13.9</v>
       </c>
       <c r="F5" t="n">
-        <v>15.2</v>
+        <v>29.5</v>
       </c>
       <c r="G5" t="n">
-        <v>29.3</v>
+        <v>45.1</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -701,25 +701,25 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>41213</v>
+        <v>27208</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>42.88</v>
+        <v>15.88</v>
       </c>
       <c r="M5" t="n">
-        <v>54.86</v>
+        <v>20.23</v>
       </c>
       <c r="N5" t="n">
-        <v>28.2</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -728,19 +728,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>1.266</v>
+        <v>1.557</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="F6" t="n">
-        <v>15.6</v>
+        <v>21.6</v>
       </c>
       <c r="G6" t="n">
-        <v>28.7</v>
+        <v>42.4</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -753,19 +753,19 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>21597</v>
+        <v>67990</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>17.11</v>
+        <v>76.73</v>
       </c>
       <c r="M6" t="n">
-        <v>21.51</v>
+        <v>108.36</v>
       </c>
       <c r="N6" t="n">
-        <v>26.3</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="7">
@@ -786,17 +786,17 @@
         <v>1.426</v>
       </c>
       <c r="E7" t="n">
-        <v>3.4</v>
+        <v>8.4</v>
       </c>
       <c r="F7" t="n">
-        <v>14.3</v>
+        <v>20.4</v>
       </c>
       <c r="G7" t="n">
-        <v>25.2</v>
+        <v>32.3</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -805,19 +805,19 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>8968</v>
+        <v>11451</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>79.87</v>
+        <v>83.72</v>
       </c>
       <c r="M7" t="n">
-        <v>96.73</v>
+        <v>102.22</v>
       </c>
       <c r="N7" t="n">
-        <v>21.8</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="8">
@@ -838,13 +838,13 @@
         <v>1.157</v>
       </c>
       <c r="E8" t="n">
-        <v>7.8</v>
+        <v>13.9</v>
       </c>
       <c r="F8" t="n">
-        <v>16.4</v>
+        <v>22.9</v>
       </c>
       <c r="G8" t="n">
-        <v>24.9</v>
+        <v>31.9</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -857,25 +857,25 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>38395</v>
+        <v>37671</v>
       </c>
       <c r="K8" t="n">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="L8" t="n">
-        <v>31.8</v>
+        <v>33.58</v>
       </c>
       <c r="M8" t="n">
-        <v>36.84</v>
+        <v>38.9</v>
       </c>
       <c r="N8" t="n">
-        <v>17.1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -884,19 +884,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="D9" t="n">
-        <v>1.168</v>
+        <v>1.324</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.9</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>10.2</v>
+        <v>15.2</v>
       </c>
       <c r="G9" t="n">
-        <v>24.3</v>
+        <v>29.3</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -909,16 +909,16 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>18274</v>
+        <v>41213</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>13.39</v>
+        <v>42.88</v>
       </c>
       <c r="M9" t="n">
-        <v>17.33</v>
+        <v>54.86</v>
       </c>
       <c r="N9" t="n">
         <v>28.2</v>
@@ -942,13 +942,13 @@
         <v>1.481</v>
       </c>
       <c r="E10" t="n">
-        <v>-17.1</v>
+        <v>-12.7</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3</v>
+        <v>6.8</v>
       </c>
       <c r="G10" t="n">
-        <v>19.7</v>
+        <v>26.3</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>94534</v>
+        <v>96485</v>
       </c>
       <c r="K10" t="n">
-        <v>7642</v>
+        <v>7814</v>
       </c>
       <c r="L10" t="n">
-        <v>6.22</v>
+        <v>6.56</v>
       </c>
       <c r="M10" t="n">
-        <v>8.99</v>
+        <v>9.49</v>
       </c>
       <c r="N10" t="n">
-        <v>36.9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="D11" t="n">
-        <v>1.11</v>
+        <v>1.266</v>
       </c>
       <c r="E11" t="n">
-        <v>3.1</v>
+        <v>-2</v>
       </c>
       <c r="F11" t="n">
-        <v>9.1</v>
+        <v>10.6</v>
       </c>
       <c r="G11" t="n">
-        <v>15.2</v>
+        <v>23.1</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>12307</v>
+        <v>22102</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>29.79</v>
+        <v>16.38</v>
       </c>
       <c r="M11" t="n">
-        <v>33.3</v>
+        <v>20.57</v>
       </c>
       <c r="N11" t="n">
-        <v>12.2</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="12">
@@ -1046,13 +1046,13 @@
         <v>1.211</v>
       </c>
       <c r="E12" t="n">
-        <v>-14.9</v>
+        <v>-11.7</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3</v>
+        <v>3.2</v>
       </c>
       <c r="G12" t="n">
-        <v>14.2</v>
+        <v>18.1</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1065,25 +1065,25 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>79939</v>
+        <v>106340</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>13.86</v>
+        <v>14.38</v>
       </c>
       <c r="M12" t="n">
-        <v>18.61</v>
+        <v>19.23</v>
       </c>
       <c r="N12" t="n">
-        <v>29.2</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1092,50 +1092,50 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="D13" t="n">
-        <v>0.89</v>
+        <v>1.11</v>
       </c>
       <c r="E13" t="n">
-        <v>25.4</v>
+        <v>3.1</v>
       </c>
       <c r="F13" t="n">
-        <v>14.7</v>
+        <v>9.1</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>15.2</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>12307</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>9.529999999999999</v>
+        <v>29.79</v>
       </c>
       <c r="M13" t="n">
-        <v>7.91</v>
+        <v>33.3</v>
       </c>
       <c r="N13" t="n">
-        <v>-21.4</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="D14" t="n">
-        <v>1.569</v>
+        <v>2.23</v>
       </c>
       <c r="E14" t="n">
-        <v>-30.5</v>
+        <v>-52.8</v>
       </c>
       <c r="F14" t="n">
-        <v>-13.4</v>
+        <v>-20.7</v>
       </c>
       <c r="G14" t="n">
-        <v>3.7</v>
+        <v>11.3</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1165,29 +1165,29 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>223619</v>
+        <v>620285</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>31.82</v>
+        <v>3.05</v>
       </c>
       <c r="M14" t="n">
-        <v>47.43</v>
+        <v>7.19</v>
       </c>
       <c r="N14" t="n">
-        <v>34.1</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1196,23 +1196,23 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.72</v>
+        <v>0.88</v>
       </c>
       <c r="D15" t="n">
-        <v>1.003</v>
+        <v>0.89</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3</v>
+        <v>25.4</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>14.7</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1227,19 +1227,19 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>6.49</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>6.58</v>
+        <v>7.91</v>
       </c>
       <c r="N15" t="n">
-        <v>1.3</v>
+        <v>-21.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1248,19 +1248,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="D16" t="n">
-        <v>2.23</v>
+        <v>1.569</v>
       </c>
       <c r="E16" t="n">
-        <v>-56.8</v>
+        <v>-30.5</v>
       </c>
       <c r="F16" t="n">
-        <v>-27.2</v>
+        <v>-13.4</v>
       </c>
       <c r="G16" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1273,19 +1273,19 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>459263</v>
+        <v>223619</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2.79</v>
+        <v>31.82</v>
       </c>
       <c r="M16" t="n">
-        <v>6.61</v>
+        <v>47.43</v>
       </c>
       <c r="N16" t="n">
-        <v>59.1</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="17">
@@ -1499,28 +1499,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BWLP</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.97</v>
+        <v>1.11</v>
       </c>
       <c r="D21" t="n">
-        <v>1.322</v>
+        <v>1.531</v>
       </c>
       <c r="E21" t="n">
-        <v>-33</v>
+        <v>-35.7</v>
       </c>
       <c r="F21" t="n">
-        <v>-20.6</v>
+        <v>-21.7</v>
       </c>
       <c r="G21" t="n">
-        <v>-8.199999999999999</v>
+        <v>-7.7</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1533,46 +1533,46 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>196627</v>
+        <v>469118</v>
       </c>
       <c r="K21" t="n">
-        <v>61101</v>
+        <v>201666</v>
       </c>
       <c r="L21" t="n">
-        <v>14.46</v>
+        <v>59.39</v>
       </c>
       <c r="M21" t="n">
-        <v>19.84</v>
+        <v>85.27</v>
       </c>
       <c r="N21" t="n">
-        <v>24.9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>BWLP</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.11</v>
+        <v>0.97</v>
       </c>
       <c r="D22" t="n">
-        <v>1.544</v>
+        <v>1.322</v>
       </c>
       <c r="E22" t="n">
-        <v>-39.8</v>
+        <v>-33</v>
       </c>
       <c r="F22" t="n">
-        <v>-26.3</v>
+        <v>-20.6</v>
       </c>
       <c r="G22" t="n">
-        <v>-12.8</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>380065</v>
+        <v>196627</v>
       </c>
       <c r="K22" t="n">
-        <v>164298</v>
+        <v>61101</v>
       </c>
       <c r="L22" t="n">
-        <v>55.59</v>
+        <v>14.46</v>
       </c>
       <c r="M22" t="n">
-        <v>80.58</v>
+        <v>19.84</v>
       </c>
       <c r="N22" t="n">
-        <v>27</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="23">
@@ -1618,13 +1618,13 @@
         <v>1.089</v>
       </c>
       <c r="E23" t="n">
-        <v>-22.8</v>
+        <v>-15.4</v>
       </c>
       <c r="F23" t="n">
-        <v>-19.7</v>
+        <v>-11.9</v>
       </c>
       <c r="G23" t="n">
-        <v>-16.6</v>
+        <v>-8.5</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1637,19 +1637,19 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>358707</v>
+        <v>494031</v>
       </c>
       <c r="K23" t="n">
-        <v>264214</v>
+        <v>362684</v>
       </c>
       <c r="L23" t="n">
-        <v>14.48</v>
+        <v>15.88</v>
       </c>
       <c r="M23" t="n">
-        <v>15.65</v>
+        <v>17.17</v>
       </c>
       <c r="N23" t="n">
-        <v>6.2</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="24">
@@ -1707,7 +1707,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1716,19 +1716,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="D25" t="n">
-        <v>1.125</v>
+        <v>1.097</v>
       </c>
       <c r="E25" t="n">
-        <v>-39.7</v>
+        <v>-30.6</v>
       </c>
       <c r="F25" t="n">
-        <v>-35.6</v>
+        <v>-26.5</v>
       </c>
       <c r="G25" t="n">
-        <v>-31.4</v>
+        <v>-22.3</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1741,16 +1741,16 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>401319</v>
+        <v>545468</v>
       </c>
       <c r="K25" t="n">
-        <v>321782</v>
+        <v>444556</v>
       </c>
       <c r="L25" t="n">
-        <v>37.31</v>
+        <v>27.57</v>
       </c>
       <c r="M25" t="n">
-        <v>42.42</v>
+        <v>30.88</v>
       </c>
       <c r="N25" t="n">
         <v>8.300000000000001</v>
@@ -1759,7 +1759,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1768,19 +1768,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="D26" t="n">
-        <v>1.097</v>
+        <v>1.125</v>
       </c>
       <c r="E26" t="n">
-        <v>-39</v>
+        <v>-33</v>
       </c>
       <c r="F26" t="n">
-        <v>-35.3</v>
+        <v>-28.5</v>
       </c>
       <c r="G26" t="n">
-        <v>-31.6</v>
+        <v>-23.9</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1793,19 +1793,19 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>416150</v>
+        <v>530104</v>
       </c>
       <c r="K26" t="n">
-        <v>339162</v>
+        <v>425044</v>
       </c>
       <c r="L26" t="n">
-        <v>24.22</v>
+        <v>41.44</v>
       </c>
       <c r="M26" t="n">
-        <v>27.2</v>
+        <v>47.07</v>
       </c>
       <c r="N26" t="n">
-        <v>7.5</v>
+        <v>9.1</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -523,16 +523,16 @@
         <v>0.34</v>
       </c>
       <c r="D2" t="n">
-        <v>1.218</v>
+        <v>1.222</v>
       </c>
       <c r="E2" t="n">
-        <v>59.6</v>
+        <v>58.9</v>
       </c>
       <c r="F2" t="n">
-        <v>81.2</v>
+        <v>80.8</v>
       </c>
       <c r="G2" t="n">
-        <v>102.7</v>
+        <v>102.6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -554,10 +554,10 @@
         <v>62.47</v>
       </c>
       <c r="M2" t="n">
-        <v>79.34</v>
+        <v>79.66</v>
       </c>
       <c r="N2" t="n">
-        <v>43.1</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="3">
@@ -575,16 +575,16 @@
         <v>0.72</v>
       </c>
       <c r="D3" t="n">
-        <v>1.003</v>
+        <v>0.969</v>
       </c>
       <c r="E3" t="n">
-        <v>45.6</v>
+        <v>61.8</v>
       </c>
       <c r="F3" t="n">
-        <v>46.4</v>
+        <v>54.8</v>
       </c>
       <c r="G3" t="n">
-        <v>47.1</v>
+        <v>47.7</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -603,13 +603,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>9.33</v>
+        <v>10.13</v>
       </c>
       <c r="M3" t="n">
-        <v>9.43</v>
+        <v>9.24</v>
       </c>
       <c r="N3" t="n">
-        <v>1.5</v>
+        <v>-14.1</v>
       </c>
     </row>
     <row r="4">
@@ -627,16 +627,16 @@
         <v>0.9</v>
       </c>
       <c r="D4" t="n">
-        <v>0.991</v>
+        <v>0.994</v>
       </c>
       <c r="E4" t="n">
-        <v>50.7</v>
+        <v>49.2</v>
       </c>
       <c r="F4" t="n">
-        <v>48.9</v>
+        <v>47.9</v>
       </c>
       <c r="G4" t="n">
-        <v>47.1</v>
+        <v>46.7</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -658,10 +658,10 @@
         <v>33.7</v>
       </c>
       <c r="M4" t="n">
-        <v>32.91</v>
+        <v>33.14</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.5</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="5">
@@ -679,16 +679,16 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>1.168</v>
+        <v>1.187</v>
       </c>
       <c r="E5" t="n">
-        <v>13.9</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
-        <v>29.5</v>
+        <v>27.9</v>
       </c>
       <c r="G5" t="n">
-        <v>45.1</v>
+        <v>44.8</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>27208</v>
+        <v>53520</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -710,10 +710,10 @@
         <v>15.88</v>
       </c>
       <c r="M5" t="n">
-        <v>20.23</v>
+        <v>20.72</v>
       </c>
       <c r="N5" t="n">
-        <v>31.2</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="6">
@@ -731,10 +731,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>1.557</v>
+        <v>1.559</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F6" t="n">
         <v>21.6</v>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>67990</v>
+        <v>68460</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -762,16 +762,16 @@
         <v>76.73</v>
       </c>
       <c r="M6" t="n">
-        <v>108.36</v>
+        <v>108.45</v>
       </c>
       <c r="N6" t="n">
-        <v>41.6</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -780,19 +780,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.73</v>
+        <v>0.82</v>
       </c>
       <c r="D7" t="n">
-        <v>1.426</v>
+        <v>1.14</v>
       </c>
       <c r="E7" t="n">
-        <v>8.4</v>
+        <v>15.9</v>
       </c>
       <c r="F7" t="n">
-        <v>20.4</v>
+        <v>24.1</v>
       </c>
       <c r="G7" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -805,25 +805,25 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>11451</v>
+        <v>33992</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>922</v>
       </c>
       <c r="L7" t="n">
-        <v>83.72</v>
+        <v>33.58</v>
       </c>
       <c r="M7" t="n">
-        <v>102.22</v>
+        <v>38.31</v>
       </c>
       <c r="N7" t="n">
-        <v>23.9</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -832,23 +832,23 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="D8" t="n">
-        <v>1.157</v>
+        <v>1.526</v>
       </c>
       <c r="E8" t="n">
-        <v>13.9</v>
+        <v>3.5</v>
       </c>
       <c r="F8" t="n">
-        <v>22.9</v>
+        <v>17.6</v>
       </c>
       <c r="G8" t="n">
-        <v>31.9</v>
+        <v>31.7</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>37671</v>
+        <v>49193</v>
       </c>
       <c r="K8" t="n">
-        <v>607</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>33.58</v>
+        <v>83.72</v>
       </c>
       <c r="M8" t="n">
-        <v>38.9</v>
+        <v>106.57</v>
       </c>
       <c r="N8" t="n">
-        <v>18</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="9">
@@ -887,16 +887,16 @@
         <v>0.75</v>
       </c>
       <c r="D9" t="n">
-        <v>1.324</v>
+        <v>1.29</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>15.2</v>
+        <v>17</v>
       </c>
       <c r="G9" t="n">
-        <v>29.3</v>
+        <v>30</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>41213</v>
+        <v>3362</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -918,10 +918,10 @@
         <v>42.88</v>
       </c>
       <c r="M9" t="n">
-        <v>54.86</v>
+        <v>53.62</v>
       </c>
       <c r="N9" t="n">
-        <v>28.2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">
@@ -939,16 +939,16 @@
         <v>0.86</v>
       </c>
       <c r="D10" t="n">
-        <v>1.481</v>
+        <v>1.477</v>
       </c>
       <c r="E10" t="n">
-        <v>-12.7</v>
+        <v>-12.5</v>
       </c>
       <c r="F10" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="G10" t="n">
-        <v>26.3</v>
+        <v>26.4</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>96485</v>
+        <v>95853</v>
       </c>
       <c r="K10" t="n">
-        <v>7814</v>
+        <v>7832</v>
       </c>
       <c r="L10" t="n">
         <v>6.56</v>
       </c>
       <c r="M10" t="n">
-        <v>9.49</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>39</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="11">
@@ -991,13 +991,13 @@
         <v>0.75</v>
       </c>
       <c r="D11" t="n">
-        <v>1.266</v>
+        <v>1.263</v>
       </c>
       <c r="E11" t="n">
-        <v>-2</v>
+        <v>-1.8</v>
       </c>
       <c r="F11" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="G11" t="n">
         <v>23.1</v>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>22102</v>
+        <v>21702</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1022,10 +1022,10 @@
         <v>16.38</v>
       </c>
       <c r="M11" t="n">
-        <v>20.57</v>
+        <v>20.53</v>
       </c>
       <c r="N11" t="n">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="12">
@@ -1043,16 +1043,16 @@
         <v>0.73</v>
       </c>
       <c r="D12" t="n">
-        <v>1.211</v>
+        <v>1.234</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.7</v>
+        <v>-14.2</v>
       </c>
       <c r="F12" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="G12" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>106340</v>
+        <v>120740</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1074,10 +1074,10 @@
         <v>14.38</v>
       </c>
       <c r="M12" t="n">
-        <v>19.23</v>
+        <v>19.76</v>
       </c>
       <c r="N12" t="n">
-        <v>29.8</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="13">
@@ -1095,20 +1095,20 @@
         <v>0.78</v>
       </c>
       <c r="D13" t="n">
-        <v>1.11</v>
+        <v>1.077</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1</v>
+        <v>6.8</v>
       </c>
       <c r="F13" t="n">
-        <v>9.1</v>
+        <v>11.2</v>
       </c>
       <c r="G13" t="n">
-        <v>15.2</v>
+        <v>15.6</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>12307</v>
+        <v>8480</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1126,10 +1126,10 @@
         <v>29.79</v>
       </c>
       <c r="M13" t="n">
-        <v>33.3</v>
+        <v>32.23</v>
       </c>
       <c r="N13" t="n">
-        <v>12.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1147,16 +1147,16 @@
         <v>0.85</v>
       </c>
       <c r="D14" t="n">
-        <v>2.23</v>
+        <v>2.224</v>
       </c>
       <c r="E14" t="n">
-        <v>-52.8</v>
+        <v>-52.6</v>
       </c>
       <c r="F14" t="n">
-        <v>-20.7</v>
+        <v>-20.6</v>
       </c>
       <c r="G14" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>620285</v>
+        <v>617242</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1178,10 +1178,10 @@
         <v>3.05</v>
       </c>
       <c r="M14" t="n">
-        <v>7.19</v>
+        <v>7.17</v>
       </c>
       <c r="N14" t="n">
-        <v>64.09999999999999</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15">
@@ -1199,16 +1199,16 @@
         <v>0.88</v>
       </c>
       <c r="D15" t="n">
-        <v>0.89</v>
+        <v>0.881</v>
       </c>
       <c r="E15" t="n">
-        <v>25.4</v>
+        <v>27.8</v>
       </c>
       <c r="F15" t="n">
-        <v>14.7</v>
+        <v>16</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1230,10 +1230,10 @@
         <v>9.529999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>7.91</v>
+        <v>7.77</v>
       </c>
       <c r="N15" t="n">
-        <v>-21.4</v>
+        <v>-23.6</v>
       </c>
     </row>
     <row r="16">
@@ -1251,16 +1251,16 @@
         <v>0.84</v>
       </c>
       <c r="D16" t="n">
-        <v>1.569</v>
+        <v>1.532</v>
       </c>
       <c r="E16" t="n">
-        <v>-30.5</v>
+        <v>-28.9</v>
       </c>
       <c r="F16" t="n">
-        <v>-13.4</v>
+        <v>-12.5</v>
       </c>
       <c r="G16" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>223619</v>
+        <v>208723</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1282,10 +1282,10 @@
         <v>31.82</v>
       </c>
       <c r="M16" t="n">
-        <v>47.43</v>
+        <v>46.42</v>
       </c>
       <c r="N16" t="n">
-        <v>34.1</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="17">
@@ -1303,13 +1303,13 @@
         <v>0.62</v>
       </c>
       <c r="D17" t="n">
-        <v>0.879</v>
+        <v>0.872</v>
       </c>
       <c r="E17" t="n">
-        <v>12.9</v>
+        <v>13.7</v>
       </c>
       <c r="F17" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="G17" t="n">
         <v>1.9</v>
@@ -1325,19 +1325,19 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>1982</v>
+        <v>1244</v>
       </c>
       <c r="K17" t="n">
-        <v>14648</v>
+        <v>14626</v>
       </c>
       <c r="L17" t="n">
         <v>20.11</v>
       </c>
       <c r="M17" t="n">
-        <v>18.13</v>
+        <v>18.02</v>
       </c>
       <c r="N17" t="n">
-        <v>-11.1</v>
+        <v>-11.8</v>
       </c>
     </row>
     <row r="18">
@@ -1355,13 +1355,13 @@
         <v>0.89</v>
       </c>
       <c r="D18" t="n">
-        <v>1.105</v>
+        <v>1.102</v>
       </c>
       <c r="E18" t="n">
-        <v>-10.5</v>
+        <v>-10.2</v>
       </c>
       <c r="F18" t="n">
-        <v>-5.1</v>
+        <v>-5</v>
       </c>
       <c r="G18" t="n">
         <v>0.3</v>
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>31845</v>
+        <v>31418</v>
       </c>
       <c r="K18" t="n">
-        <v>14263</v>
+        <v>14250</v>
       </c>
       <c r="L18" t="n">
         <v>22.67</v>
       </c>
       <c r="M18" t="n">
-        <v>25.4</v>
+        <v>25.34</v>
       </c>
       <c r="N18" t="n">
-        <v>10.8</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="19">
@@ -1407,20 +1407,20 @@
         <v>0.98</v>
       </c>
       <c r="D19" t="n">
-        <v>1.197</v>
+        <v>0.98</v>
       </c>
       <c r="E19" t="n">
-        <v>-18.4</v>
+        <v>1.4</v>
       </c>
       <c r="F19" t="n">
-        <v>-10.5</v>
+        <v>0.4</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.7</v>
+        <v>-0.7</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1429,19 +1429,19 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>29068</v>
+        <v>14262</v>
       </c>
       <c r="K19" t="n">
-        <v>17269</v>
+        <v>15478</v>
       </c>
       <c r="L19" t="n">
         <v>0.4</v>
       </c>
       <c r="M19" t="n">
-        <v>0.47</v>
+        <v>0.39</v>
       </c>
       <c r="N19" t="n">
-        <v>15.7</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="20">
@@ -1459,13 +1459,13 @@
         <v>1.04</v>
       </c>
       <c r="D20" t="n">
-        <v>1.118</v>
+        <v>1.115</v>
       </c>
       <c r="E20" t="n">
-        <v>-19.1</v>
+        <v>-18.8</v>
       </c>
       <c r="F20" t="n">
-        <v>-12.8</v>
+        <v>-12.6</v>
       </c>
       <c r="G20" t="n">
         <v>-6.5</v>
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>139574</v>
+        <v>136966</v>
       </c>
       <c r="K20" t="n">
-        <v>48856</v>
+        <v>48452</v>
       </c>
       <c r="L20" t="n">
         <v>2.07</v>
       </c>
       <c r="M20" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="N20" t="n">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="21">
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>469118</v>
+        <v>468801</v>
       </c>
       <c r="K21" t="n">
-        <v>201666</v>
+        <v>201602</v>
       </c>
       <c r="L21" t="n">
         <v>59.39</v>
       </c>
       <c r="M21" t="n">
-        <v>85.27</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="N21" t="n">
         <v>28</v>
@@ -1563,16 +1563,16 @@
         <v>0.97</v>
       </c>
       <c r="D22" t="n">
-        <v>1.322</v>
+        <v>1.347</v>
       </c>
       <c r="E22" t="n">
-        <v>-33</v>
+        <v>-34.5</v>
       </c>
       <c r="F22" t="n">
-        <v>-20.6</v>
+        <v>-21.4</v>
       </c>
       <c r="G22" t="n">
-        <v>-8.199999999999999</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>196627</v>
+        <v>207795</v>
       </c>
       <c r="K22" t="n">
-        <v>61101</v>
+        <v>61942</v>
       </c>
       <c r="L22" t="n">
         <v>14.46</v>
       </c>
       <c r="M22" t="n">
-        <v>19.84</v>
+        <v>20.25</v>
       </c>
       <c r="N22" t="n">
-        <v>24.9</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="23">
@@ -1615,16 +1615,16 @@
         <v>1.14</v>
       </c>
       <c r="D23" t="n">
-        <v>1.089</v>
+        <v>1.087</v>
       </c>
       <c r="E23" t="n">
-        <v>-15.4</v>
+        <v>-15.2</v>
       </c>
       <c r="F23" t="n">
-        <v>-11.9</v>
+        <v>-11.8</v>
       </c>
       <c r="G23" t="n">
-        <v>-8.5</v>
+        <v>-8.4</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1637,19 +1637,19 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>494031</v>
+        <v>489951</v>
       </c>
       <c r="K23" t="n">
-        <v>362684</v>
+        <v>361780</v>
       </c>
       <c r="L23" t="n">
         <v>15.88</v>
       </c>
       <c r="M23" t="n">
-        <v>17.17</v>
+        <v>17.14</v>
       </c>
       <c r="N23" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="24">
@@ -1667,16 +1667,16 @@
         <v>1.35</v>
       </c>
       <c r="D24" t="n">
-        <v>0.896</v>
+        <v>0.877</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.5</v>
+        <v>4</v>
       </c>
       <c r="F24" t="n">
-        <v>-9</v>
+        <v>-6.4</v>
       </c>
       <c r="G24" t="n">
-        <v>-17.4</v>
+        <v>-16.8</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>207648</v>
+        <v>135338</v>
       </c>
       <c r="K24" t="n">
-        <v>468753</v>
+        <v>442649</v>
       </c>
       <c r="L24" t="n">
         <v>30.67</v>
       </c>
       <c r="M24" t="n">
-        <v>25.47</v>
+        <v>24.55</v>
       </c>
       <c r="N24" t="n">
-        <v>-16.9</v>
+        <v>-20.8</v>
       </c>
     </row>
     <row r="25">
@@ -1719,13 +1719,13 @@
         <v>1.37</v>
       </c>
       <c r="D25" t="n">
-        <v>1.097</v>
+        <v>1.094</v>
       </c>
       <c r="E25" t="n">
-        <v>-30.6</v>
+        <v>-30.3</v>
       </c>
       <c r="F25" t="n">
-        <v>-26.5</v>
+        <v>-26.3</v>
       </c>
       <c r="G25" t="n">
         <v>-22.3</v>
@@ -1741,19 +1741,19 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>545468</v>
+        <v>540231</v>
       </c>
       <c r="K25" t="n">
-        <v>444556</v>
+        <v>442731</v>
       </c>
       <c r="L25" t="n">
         <v>27.57</v>
       </c>
       <c r="M25" t="n">
-        <v>30.88</v>
+        <v>30.76</v>
       </c>
       <c r="N25" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="26">
@@ -1771,16 +1771,16 @@
         <v>1.35</v>
       </c>
       <c r="D26" t="n">
-        <v>1.125</v>
+        <v>1.14</v>
       </c>
       <c r="E26" t="n">
-        <v>-33</v>
+        <v>-34.1</v>
       </c>
       <c r="F26" t="n">
-        <v>-28.5</v>
+        <v>-29.1</v>
       </c>
       <c r="G26" t="n">
-        <v>-23.9</v>
+        <v>-24.1</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1793,19 +1793,19 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>530104</v>
+        <v>549197</v>
       </c>
       <c r="K26" t="n">
-        <v>425044</v>
+        <v>431507</v>
       </c>
       <c r="L26" t="n">
         <v>41.44</v>
       </c>
       <c r="M26" t="n">
-        <v>47.07</v>
+        <v>47.74</v>
       </c>
       <c r="N26" t="n">
-        <v>9.1</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -563,7 +563,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>CCEC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.72</v>
+        <v>0.9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.969</v>
+        <v>0.994</v>
       </c>
       <c r="E3" t="n">
-        <v>61.8</v>
+        <v>49.2</v>
       </c>
       <c r="F3" t="n">
-        <v>54.8</v>
+        <v>47.9</v>
       </c>
       <c r="G3" t="n">
-        <v>47.7</v>
+        <v>46.7</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -603,19 +603,19 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>10.13</v>
+        <v>33.7</v>
       </c>
       <c r="M3" t="n">
-        <v>9.24</v>
+        <v>33.14</v>
       </c>
       <c r="N3" t="n">
-        <v>-14.1</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CCEC</t>
+          <t>CAPT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -624,19 +624,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9</v>
+        <v>0.71</v>
       </c>
       <c r="D4" t="n">
-        <v>0.994</v>
+        <v>1.166</v>
       </c>
       <c r="E4" t="n">
-        <v>49.2</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
-        <v>47.9</v>
+        <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>46.7</v>
+        <v>41.1</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -649,25 +649,25 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>53520</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>33.7</v>
+        <v>15.88</v>
       </c>
       <c r="M4" t="n">
-        <v>33.14</v>
+        <v>20.18</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.5</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CAPT</t>
+          <t>STNG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -676,23 +676,23 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="D5" t="n">
-        <v>1.187</v>
+        <v>1.508</v>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>0.8</v>
       </c>
       <c r="F5" t="n">
-        <v>27.9</v>
+        <v>19.7</v>
       </c>
       <c r="G5" t="n">
-        <v>44.8</v>
+        <v>38.6</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -701,25 +701,25 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>53520</v>
+        <v>68460</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>15.88</v>
+        <v>76.73</v>
       </c>
       <c r="M5" t="n">
-        <v>20.72</v>
+        <v>105.56</v>
       </c>
       <c r="N5" t="n">
-        <v>33.8</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -728,19 +728,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="D6" t="n">
-        <v>1.559</v>
+        <v>1.29</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>21.6</v>
+        <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>42.4</v>
+        <v>30</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -753,19 +753,19 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>68460</v>
+        <v>3362</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>76.73</v>
+        <v>42.88</v>
       </c>
       <c r="M6" t="n">
-        <v>108.45</v>
+        <v>53.62</v>
       </c>
       <c r="N6" t="n">
-        <v>41.7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
@@ -780,19 +780,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="D7" t="n">
-        <v>1.14</v>
+        <v>1.095</v>
       </c>
       <c r="E7" t="n">
         <v>15.9</v>
       </c>
       <c r="F7" t="n">
-        <v>24.1</v>
+        <v>21.4</v>
       </c>
       <c r="G7" t="n">
-        <v>32.2</v>
+        <v>27</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -808,22 +808,22 @@
         <v>33992</v>
       </c>
       <c r="K7" t="n">
-        <v>922</v>
+        <v>12078</v>
       </c>
       <c r="L7" t="n">
         <v>33.58</v>
       </c>
       <c r="M7" t="n">
-        <v>38.31</v>
+        <v>36.79</v>
       </c>
       <c r="N7" t="n">
-        <v>16.3</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -832,23 +832,23 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.73</v>
+        <v>0.86</v>
       </c>
       <c r="D8" t="n">
-        <v>1.526</v>
+        <v>0.922</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5</v>
+        <v>61.8</v>
       </c>
       <c r="F8" t="n">
-        <v>17.6</v>
+        <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>31.7</v>
+        <v>26.3</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -857,25 +857,25 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>49193</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>83.72</v>
+        <v>10.13</v>
       </c>
       <c r="M8" t="n">
-        <v>106.57</v>
+        <v>7.9</v>
       </c>
       <c r="N8" t="n">
-        <v>28.2</v>
+        <v>-35.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -887,16 +887,16 @@
         <v>0.75</v>
       </c>
       <c r="D9" t="n">
-        <v>1.29</v>
+        <v>1.263</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>-1.8</v>
       </c>
       <c r="F9" t="n">
-        <v>17</v>
+        <v>10.7</v>
       </c>
       <c r="G9" t="n">
-        <v>30</v>
+        <v>23.1</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>3362</v>
+        <v>21702</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>42.88</v>
+        <v>16.38</v>
       </c>
       <c r="M9" t="n">
-        <v>53.62</v>
+        <v>20.53</v>
       </c>
       <c r="N9" t="n">
-        <v>26</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -936,23 +936,23 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="D10" t="n">
-        <v>1.477</v>
+        <v>1.331</v>
       </c>
       <c r="E10" t="n">
-        <v>-12.5</v>
+        <v>3.5</v>
       </c>
       <c r="F10" t="n">
-        <v>6.9</v>
+        <v>12.4</v>
       </c>
       <c r="G10" t="n">
-        <v>26.4</v>
+        <v>21.3</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>95853</v>
+        <v>49193</v>
       </c>
       <c r="K10" t="n">
-        <v>7832</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>6.56</v>
+        <v>83.72</v>
       </c>
       <c r="M10" t="n">
-        <v>9.460000000000001</v>
+        <v>98.11</v>
       </c>
       <c r="N10" t="n">
-        <v>38.8</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -988,23 +988,23 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="D11" t="n">
-        <v>1.263</v>
+        <v>1.391</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8</v>
+        <v>-12.5</v>
       </c>
       <c r="F11" t="n">
-        <v>10.7</v>
+        <v>3.4</v>
       </c>
       <c r="G11" t="n">
-        <v>23.1</v>
+        <v>19.3</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1013,46 +1013,46 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>21702</v>
+        <v>95853</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>24018</v>
       </c>
       <c r="L11" t="n">
-        <v>16.38</v>
+        <v>6.56</v>
       </c>
       <c r="M11" t="n">
-        <v>20.53</v>
+        <v>8.94</v>
       </c>
       <c r="N11" t="n">
-        <v>24.9</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.73</v>
+        <v>0.85</v>
       </c>
       <c r="D12" t="n">
-        <v>1.234</v>
+        <v>2.224</v>
       </c>
       <c r="E12" t="n">
-        <v>-14.2</v>
+        <v>-52.6</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9</v>
+        <v>-20.6</v>
       </c>
       <c r="G12" t="n">
-        <v>18</v>
+        <v>11.4</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1065,25 +1065,25 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>120740</v>
+        <v>617242</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>14.38</v>
+        <v>3.05</v>
       </c>
       <c r="M12" t="n">
-        <v>19.76</v>
+        <v>7.17</v>
       </c>
       <c r="N12" t="n">
-        <v>32.1</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1092,23 +1092,23 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="D13" t="n">
-        <v>1.077</v>
+        <v>1.049</v>
       </c>
       <c r="E13" t="n">
-        <v>6.8</v>
+        <v>1.4</v>
       </c>
       <c r="F13" t="n">
-        <v>11.2</v>
+        <v>3.8</v>
       </c>
       <c r="G13" t="n">
-        <v>15.6</v>
+        <v>6.2</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1117,25 +1117,25 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>8480</v>
+        <v>14262</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>11346</v>
       </c>
       <c r="L13" t="n">
-        <v>29.79</v>
+        <v>0.4</v>
       </c>
       <c r="M13" t="n">
-        <v>32.23</v>
+        <v>0.41</v>
       </c>
       <c r="N13" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1144,50 +1144,50 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="D14" t="n">
-        <v>2.224</v>
+        <v>0.881</v>
       </c>
       <c r="E14" t="n">
-        <v>-52.6</v>
+        <v>27.8</v>
       </c>
       <c r="F14" t="n">
-        <v>-20.6</v>
+        <v>16</v>
       </c>
       <c r="G14" t="n">
-        <v>11.4</v>
+        <v>4.2</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>617242</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>3.05</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>7.17</v>
+        <v>7.77</v>
       </c>
       <c r="N14" t="n">
-        <v>64</v>
+        <v>-23.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1196,19 +1196,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="D15" t="n">
-        <v>0.881</v>
+        <v>0.963</v>
       </c>
       <c r="E15" t="n">
-        <v>27.8</v>
+        <v>6.8</v>
       </c>
       <c r="F15" t="n">
-        <v>16</v>
+        <v>4.7</v>
       </c>
       <c r="G15" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1221,25 +1221,25 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>8480</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>13204</v>
       </c>
       <c r="L15" t="n">
-        <v>9.529999999999999</v>
+        <v>29.79</v>
       </c>
       <c r="M15" t="n">
-        <v>7.77</v>
+        <v>28.6</v>
       </c>
       <c r="N15" t="n">
-        <v>-23.6</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1248,23 +1248,23 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.84</v>
+        <v>0.62</v>
       </c>
       <c r="D16" t="n">
-        <v>1.532</v>
+        <v>0.872</v>
       </c>
       <c r="E16" t="n">
-        <v>-28.9</v>
+        <v>13.7</v>
       </c>
       <c r="F16" t="n">
-        <v>-12.5</v>
+        <v>7.8</v>
       </c>
       <c r="G16" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1273,71 +1273,71 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>208723</v>
+        <v>1244</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>14626</v>
       </c>
       <c r="L16" t="n">
-        <v>31.82</v>
+        <v>20.11</v>
       </c>
       <c r="M16" t="n">
-        <v>46.42</v>
+        <v>18.02</v>
       </c>
       <c r="N16" t="n">
-        <v>32.6</v>
+        <v>-11.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="D17" t="n">
-        <v>0.872</v>
+        <v>1.117</v>
       </c>
       <c r="E17" t="n">
-        <v>13.7</v>
+        <v>-14.2</v>
       </c>
       <c r="F17" t="n">
-        <v>7.8</v>
+        <v>-6.1</v>
       </c>
       <c r="G17" t="n">
         <v>1.9</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>1244</v>
+        <v>120740</v>
       </c>
       <c r="K17" t="n">
-        <v>14626</v>
+        <v>30426</v>
       </c>
       <c r="L17" t="n">
-        <v>20.11</v>
+        <v>14.38</v>
       </c>
       <c r="M17" t="n">
-        <v>18.02</v>
+        <v>17.07</v>
       </c>
       <c r="N17" t="n">
-        <v>-11.8</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="18">
@@ -1352,19 +1352,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="D18" t="n">
-        <v>1.102</v>
+        <v>1.073</v>
       </c>
       <c r="E18" t="n">
         <v>-10.2</v>
       </c>
       <c r="F18" t="n">
-        <v>-5</v>
+        <v>-6.5</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3</v>
+        <v>-2.7</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1380,22 +1380,22 @@
         <v>31418</v>
       </c>
       <c r="K18" t="n">
-        <v>14250</v>
+        <v>19118</v>
       </c>
       <c r="L18" t="n">
         <v>22.67</v>
       </c>
       <c r="M18" t="n">
-        <v>25.34</v>
+        <v>24.58</v>
       </c>
       <c r="N18" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1404,44 +1404,44 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.98</v>
+        <v>1.08</v>
       </c>
       <c r="D19" t="n">
-        <v>0.98</v>
+        <v>1.143</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4</v>
+        <v>-15.2</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4</v>
+        <v>-9.6</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7</v>
+        <v>-4.1</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>HOLD (fairly valued)</t>
-        </is>
-      </c>
       <c r="J19" t="n">
-        <v>14262</v>
+        <v>489951</v>
       </c>
       <c r="K19" t="n">
-        <v>15478</v>
+        <v>279182</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4</v>
+        <v>15.88</v>
       </c>
       <c r="M19" t="n">
-        <v>0.39</v>
+        <v>17.95</v>
       </c>
       <c r="N19" t="n">
-        <v>-2</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="20">
@@ -1499,28 +1499,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.11</v>
+        <v>0.96</v>
       </c>
       <c r="D21" t="n">
-        <v>1.531</v>
+        <v>1.33</v>
       </c>
       <c r="E21" t="n">
-        <v>-35.7</v>
+        <v>-28.9</v>
       </c>
       <c r="F21" t="n">
-        <v>-21.7</v>
+        <v>-18.7</v>
       </c>
       <c r="G21" t="n">
-        <v>-7.7</v>
+        <v>-8.6</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1533,46 +1533,46 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>468801</v>
+        <v>208723</v>
       </c>
       <c r="K21" t="n">
-        <v>201602</v>
+        <v>67351</v>
       </c>
       <c r="L21" t="n">
-        <v>59.39</v>
+        <v>31.82</v>
       </c>
       <c r="M21" t="n">
-        <v>85.23999999999999</v>
+        <v>40.88</v>
       </c>
       <c r="N21" t="n">
-        <v>28</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BWLP</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.97</v>
+        <v>1.17</v>
       </c>
       <c r="D22" t="n">
-        <v>1.347</v>
+        <v>1.452</v>
       </c>
       <c r="E22" t="n">
-        <v>-34.5</v>
+        <v>-35.7</v>
       </c>
       <c r="F22" t="n">
-        <v>-21.4</v>
+        <v>-23.8</v>
       </c>
       <c r="G22" t="n">
-        <v>-8.300000000000001</v>
+        <v>-11.9</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1585,25 +1585,25 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>207795</v>
+        <v>468801</v>
       </c>
       <c r="K22" t="n">
-        <v>61942</v>
+        <v>241493</v>
       </c>
       <c r="L22" t="n">
-        <v>14.46</v>
+        <v>59.39</v>
       </c>
       <c r="M22" t="n">
-        <v>20.25</v>
+        <v>81.38</v>
       </c>
       <c r="N22" t="n">
-        <v>26.2</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1612,19 +1612,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="D23" t="n">
-        <v>1.087</v>
+        <v>1.129</v>
       </c>
       <c r="E23" t="n">
-        <v>-15.2</v>
+        <v>-30.3</v>
       </c>
       <c r="F23" t="n">
-        <v>-11.8</v>
+        <v>-24.8</v>
       </c>
       <c r="G23" t="n">
-        <v>-8.4</v>
+        <v>-19.2</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1637,25 +1637,25 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>489951</v>
+        <v>540231</v>
       </c>
       <c r="K23" t="n">
-        <v>361780</v>
+        <v>406359</v>
       </c>
       <c r="L23" t="n">
-        <v>15.88</v>
+        <v>27.57</v>
       </c>
       <c r="M23" t="n">
-        <v>17.14</v>
+        <v>31.95</v>
       </c>
       <c r="N23" t="n">
-        <v>6.8</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>BWLP</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1664,23 +1664,23 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="D24" t="n">
-        <v>0.877</v>
+        <v>1.186</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>-34.5</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.4</v>
+        <v>-27.5</v>
       </c>
       <c r="G24" t="n">
-        <v>-16.8</v>
+        <v>-20.4</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1689,25 +1689,25 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>135338</v>
+        <v>207795</v>
       </c>
       <c r="K24" t="n">
-        <v>442649</v>
+        <v>129486</v>
       </c>
       <c r="L24" t="n">
-        <v>30.67</v>
+        <v>14.46</v>
       </c>
       <c r="M24" t="n">
-        <v>24.55</v>
+        <v>17.57</v>
       </c>
       <c r="N24" t="n">
-        <v>-20.8</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1716,44 +1716,44 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="D25" t="n">
-        <v>1.094</v>
+        <v>0.855</v>
       </c>
       <c r="E25" t="n">
-        <v>-30.3</v>
+        <v>4</v>
       </c>
       <c r="F25" t="n">
-        <v>-26.3</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>-22.3</v>
+        <v>-20.6</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
+          <t>HOLD (fairly valued)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
           <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>TRIM/SHORT (overvalued)</t>
-        </is>
-      </c>
       <c r="J25" t="n">
-        <v>540231</v>
+        <v>135338</v>
       </c>
       <c r="K25" t="n">
-        <v>442731</v>
+        <v>499557</v>
       </c>
       <c r="L25" t="n">
-        <v>27.57</v>
+        <v>30.67</v>
       </c>
       <c r="M25" t="n">
-        <v>30.76</v>
+        <v>23.41</v>
       </c>
       <c r="N25" t="n">
-        <v>8.1</v>
+        <v>-24.6</v>
       </c>
     </row>
     <row r="26">
@@ -1768,19 +1768,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="D26" t="n">
-        <v>1.14</v>
+        <v>1.147</v>
       </c>
       <c r="E26" t="n">
         <v>-34.1</v>
       </c>
       <c r="F26" t="n">
-        <v>-29.1</v>
+        <v>-28.8</v>
       </c>
       <c r="G26" t="n">
-        <v>-24.1</v>
+        <v>-23.6</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1796,16 +1796,16 @@
         <v>549197</v>
       </c>
       <c r="K26" t="n">
-        <v>431507</v>
+        <v>425696</v>
       </c>
       <c r="L26" t="n">
         <v>41.44</v>
       </c>
       <c r="M26" t="n">
-        <v>47.74</v>
+        <v>48.05</v>
       </c>
       <c r="N26" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -523,16 +523,16 @@
         <v>0.34</v>
       </c>
       <c r="D2" t="n">
-        <v>1.222</v>
+        <v>1.272</v>
       </c>
       <c r="E2" t="n">
-        <v>58.9</v>
+        <v>51.2</v>
       </c>
       <c r="F2" t="n">
-        <v>80.8</v>
+        <v>76.7</v>
       </c>
       <c r="G2" t="n">
-        <v>102.6</v>
+        <v>102.3</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -551,13 +551,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>62.47</v>
+        <v>62.66</v>
       </c>
       <c r="M2" t="n">
-        <v>79.66</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>43.7</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="3">
@@ -578,13 +578,13 @@
         <v>0.994</v>
       </c>
       <c r="E3" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="F3" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
       <c r="G3" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -606,10 +606,10 @@
         <v>33.7</v>
       </c>
       <c r="M3" t="n">
-        <v>33.14</v>
+        <v>33.16</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.5</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="4">
@@ -627,16 +627,16 @@
         <v>0.71</v>
       </c>
       <c r="D4" t="n">
-        <v>1.166</v>
+        <v>1.185</v>
       </c>
       <c r="E4" t="n">
-        <v>11</v>
+        <v>9.1</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>25.5</v>
       </c>
       <c r="G4" t="n">
-        <v>41.1</v>
+        <v>41.9</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>53520</v>
+        <v>80462</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>15.88</v>
+        <v>16.02</v>
       </c>
       <c r="M4" t="n">
-        <v>20.18</v>
+        <v>20.84</v>
       </c>
       <c r="N4" t="n">
-        <v>30.1</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="5">
@@ -679,16 +679,16 @@
         <v>0.71</v>
       </c>
       <c r="D5" t="n">
-        <v>1.508</v>
+        <v>1.583</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8</v>
+        <v>-3.4</v>
       </c>
       <c r="F5" t="n">
-        <v>19.7</v>
+        <v>17.5</v>
       </c>
       <c r="G5" t="n">
-        <v>38.6</v>
+        <v>38.3</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>68460</v>
+        <v>90377</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -710,10 +710,10 @@
         <v>76.73</v>
       </c>
       <c r="M5" t="n">
-        <v>105.56</v>
+        <v>109.83</v>
       </c>
       <c r="N5" t="n">
-        <v>37.9</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="6">
@@ -731,16 +731,16 @@
         <v>0.75</v>
       </c>
       <c r="D6" t="n">
-        <v>1.29</v>
+        <v>1.316</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="F6" t="n">
-        <v>17</v>
+        <v>15.6</v>
       </c>
       <c r="G6" t="n">
-        <v>30</v>
+        <v>29.4</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3362</v>
+        <v>32696</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -762,16 +762,16 @@
         <v>42.88</v>
       </c>
       <c r="M6" t="n">
-        <v>53.62</v>
+        <v>54.58</v>
       </c>
       <c r="N6" t="n">
-        <v>26</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -783,16 +783,16 @@
         <v>0.86</v>
       </c>
       <c r="D7" t="n">
-        <v>1.095</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>15.9</v>
+        <v>52.5</v>
       </c>
       <c r="F7" t="n">
-        <v>21.4</v>
+        <v>39.9</v>
       </c>
       <c r="G7" t="n">
-        <v>27</v>
+        <v>27.3</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -805,25 +805,25 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>33992</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>12078</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>33.58</v>
+        <v>10.28</v>
       </c>
       <c r="M7" t="n">
-        <v>36.79</v>
+        <v>8.59</v>
       </c>
       <c r="N7" t="n">
-        <v>11.1</v>
+        <v>-25.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -835,13 +835,13 @@
         <v>0.86</v>
       </c>
       <c r="D8" t="n">
-        <v>0.922</v>
+        <v>1.13</v>
       </c>
       <c r="E8" t="n">
-        <v>61.8</v>
+        <v>11.6</v>
       </c>
       <c r="F8" t="n">
-        <v>44</v>
+        <v>18.9</v>
       </c>
       <c r="G8" t="n">
         <v>26.3</v>
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>41844</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>11832</v>
       </c>
       <c r="L8" t="n">
-        <v>10.13</v>
+        <v>33.58</v>
       </c>
       <c r="M8" t="n">
-        <v>7.9</v>
+        <v>37.98</v>
       </c>
       <c r="N8" t="n">
-        <v>-35.6</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="9">
@@ -887,20 +887,20 @@
         <v>0.75</v>
       </c>
       <c r="D9" t="n">
-        <v>1.263</v>
+        <v>1.331</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8</v>
+        <v>-7</v>
       </c>
       <c r="F9" t="n">
-        <v>10.7</v>
+        <v>7.8</v>
       </c>
       <c r="G9" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>21702</v>
+        <v>31108</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -918,10 +918,10 @@
         <v>16.38</v>
       </c>
       <c r="M9" t="n">
-        <v>20.53</v>
+        <v>21.6</v>
       </c>
       <c r="N9" t="n">
-        <v>24.9</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="10">
@@ -939,16 +939,16 @@
         <v>0.8</v>
       </c>
       <c r="D10" t="n">
-        <v>1.331</v>
+        <v>1.437</v>
       </c>
       <c r="E10" t="n">
-        <v>3.5</v>
+        <v>-1.4</v>
       </c>
       <c r="F10" t="n">
-        <v>12.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>21.3</v>
+        <v>21</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>49193</v>
+        <v>93157</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>83.72</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>98.11</v>
+        <v>103.03</v>
       </c>
       <c r="N10" t="n">
-        <v>17.8</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="11">
@@ -991,16 +991,16 @@
         <v>0.92</v>
       </c>
       <c r="D11" t="n">
-        <v>1.391</v>
+        <v>1.433</v>
       </c>
       <c r="E11" t="n">
-        <v>-12.5</v>
+        <v>-15.3</v>
       </c>
       <c r="F11" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="G11" t="n">
-        <v>19.3</v>
+        <v>18.7</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>95853</v>
+        <v>103758</v>
       </c>
       <c r="K11" t="n">
-        <v>24018</v>
+        <v>24347</v>
       </c>
       <c r="L11" t="n">
         <v>6.56</v>
       </c>
       <c r="M11" t="n">
-        <v>8.94</v>
+        <v>9.19</v>
       </c>
       <c r="N11" t="n">
-        <v>31.8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12">
@@ -1043,16 +1043,16 @@
         <v>0.85</v>
       </c>
       <c r="D12" t="n">
-        <v>2.224</v>
+        <v>2.306</v>
       </c>
       <c r="E12" t="n">
-        <v>-52.6</v>
+        <v>-54.3</v>
       </c>
       <c r="F12" t="n">
-        <v>-20.6</v>
+        <v>-21.4</v>
       </c>
       <c r="G12" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1065,19 +1065,19 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>617242</v>
+        <v>658330</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="M12" t="n">
-        <v>7.17</v>
+        <v>7.48</v>
       </c>
       <c r="N12" t="n">
-        <v>64</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="13">
@@ -1095,41 +1095,41 @@
         <v>0.91</v>
       </c>
       <c r="D13" t="n">
-        <v>1.049</v>
+        <v>1.308</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4</v>
+        <v>-20.2</v>
       </c>
       <c r="F13" t="n">
-        <v>3.8</v>
+        <v>-8.1</v>
       </c>
       <c r="G13" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>BUY (undervalued)</t>
-        </is>
-      </c>
       <c r="J13" t="n">
-        <v>14262</v>
+        <v>30729</v>
       </c>
       <c r="K13" t="n">
-        <v>11346</v>
+        <v>12225</v>
       </c>
       <c r="L13" t="n">
         <v>0.4</v>
       </c>
       <c r="M13" t="n">
-        <v>0.41</v>
+        <v>0.51</v>
       </c>
       <c r="N13" t="n">
-        <v>4.8</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="14">
@@ -1147,16 +1147,16 @@
         <v>0.88</v>
       </c>
       <c r="D14" t="n">
-        <v>0.881</v>
+        <v>0.899</v>
       </c>
       <c r="E14" t="n">
-        <v>27.8</v>
+        <v>23</v>
       </c>
       <c r="F14" t="n">
-        <v>16</v>
+        <v>13.4</v>
       </c>
       <c r="G14" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1178,10 +1178,10 @@
         <v>9.529999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>7.77</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-23.6</v>
+        <v>-19.2</v>
       </c>
     </row>
     <row r="15">
@@ -1199,20 +1199,20 @@
         <v>0.89</v>
       </c>
       <c r="D15" t="n">
-        <v>0.963</v>
+        <v>0.996</v>
       </c>
       <c r="E15" t="n">
-        <v>6.8</v>
+        <v>2.5</v>
       </c>
       <c r="F15" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="G15" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1221,123 +1221,123 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>8480</v>
+        <v>12864</v>
       </c>
       <c r="K15" t="n">
-        <v>13204</v>
+        <v>13327</v>
       </c>
       <c r="L15" t="n">
         <v>29.79</v>
       </c>
       <c r="M15" t="n">
-        <v>28.6</v>
+        <v>29.67</v>
       </c>
       <c r="N15" t="n">
-        <v>-4.3</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="D16" t="n">
-        <v>0.872</v>
+        <v>1.138</v>
       </c>
       <c r="E16" t="n">
-        <v>13.7</v>
+        <v>-16.4</v>
       </c>
       <c r="F16" t="n">
-        <v>7.8</v>
+        <v>-7.2</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>BUY (undervalued)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>HOLD (fairly valued)</t>
-        </is>
-      </c>
       <c r="J16" t="n">
-        <v>1244</v>
+        <v>136080</v>
       </c>
       <c r="K16" t="n">
-        <v>14626</v>
+        <v>29760</v>
       </c>
       <c r="L16" t="n">
-        <v>20.11</v>
+        <v>14.41</v>
       </c>
       <c r="M16" t="n">
-        <v>18.02</v>
+        <v>17.59</v>
       </c>
       <c r="N16" t="n">
-        <v>-11.8</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.85</v>
+        <v>0.62</v>
       </c>
       <c r="D17" t="n">
-        <v>1.117</v>
+        <v>0.904</v>
       </c>
       <c r="E17" t="n">
-        <v>-14.2</v>
+        <v>10.3</v>
       </c>
       <c r="F17" t="n">
-        <v>-6.1</v>
+        <v>6</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>120740</v>
+        <v>4628</v>
       </c>
       <c r="K17" t="n">
-        <v>30426</v>
+        <v>14728</v>
       </c>
       <c r="L17" t="n">
-        <v>14.38</v>
+        <v>20.11</v>
       </c>
       <c r="M17" t="n">
-        <v>17.07</v>
+        <v>18.53</v>
       </c>
       <c r="N17" t="n">
-        <v>16.1</v>
+        <v>-8.6</v>
       </c>
     </row>
     <row r="18">
@@ -1355,16 +1355,16 @@
         <v>0.92</v>
       </c>
       <c r="D18" t="n">
-        <v>1.073</v>
+        <v>1.11</v>
       </c>
       <c r="E18" t="n">
-        <v>-10.2</v>
+        <v>-13.9</v>
       </c>
       <c r="F18" t="n">
-        <v>-6.5</v>
+        <v>-8.5</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.7</v>
+        <v>-3</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>31418</v>
+        <v>38006</v>
       </c>
       <c r="K18" t="n">
-        <v>19118</v>
+        <v>19532</v>
       </c>
       <c r="L18" t="n">
         <v>22.67</v>
       </c>
       <c r="M18" t="n">
-        <v>24.58</v>
+        <v>25.54</v>
       </c>
       <c r="N18" t="n">
-        <v>7.6</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="19">
@@ -1407,13 +1407,13 @@
         <v>1.08</v>
       </c>
       <c r="D19" t="n">
-        <v>1.143</v>
+        <v>1.188</v>
       </c>
       <c r="E19" t="n">
-        <v>-15.2</v>
+        <v>-18.2</v>
       </c>
       <c r="F19" t="n">
-        <v>-9.6</v>
+        <v>-11.2</v>
       </c>
       <c r="G19" t="n">
         <v>-4.1</v>
@@ -1429,19 +1429,19 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>489951</v>
+        <v>571564</v>
       </c>
       <c r="K19" t="n">
-        <v>279182</v>
+        <v>293729</v>
       </c>
       <c r="L19" t="n">
-        <v>15.88</v>
+        <v>15.97</v>
       </c>
       <c r="M19" t="n">
-        <v>17.95</v>
+        <v>18.72</v>
       </c>
       <c r="N19" t="n">
-        <v>11.1</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="20">
@@ -1459,16 +1459,16 @@
         <v>1.04</v>
       </c>
       <c r="D20" t="n">
-        <v>1.115</v>
+        <v>1.162</v>
       </c>
       <c r="E20" t="n">
-        <v>-18.8</v>
+        <v>-23.9</v>
       </c>
       <c r="F20" t="n">
-        <v>-12.6</v>
+        <v>-15.7</v>
       </c>
       <c r="G20" t="n">
-        <v>-6.5</v>
+        <v>-7.6</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>136966</v>
+        <v>180285</v>
       </c>
       <c r="K20" t="n">
-        <v>48452</v>
+        <v>55172</v>
       </c>
       <c r="L20" t="n">
         <v>2.07</v>
       </c>
       <c r="M20" t="n">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="N20" t="n">
-        <v>12.3</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="21">
@@ -1511,16 +1511,16 @@
         <v>0.96</v>
       </c>
       <c r="D21" t="n">
-        <v>1.33</v>
+        <v>1.413</v>
       </c>
       <c r="E21" t="n">
-        <v>-28.9</v>
+        <v>-32.8</v>
       </c>
       <c r="F21" t="n">
-        <v>-18.7</v>
+        <v>-20.8</v>
       </c>
       <c r="G21" t="n">
-        <v>-8.6</v>
+        <v>-8.9</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>208723</v>
+        <v>246904</v>
       </c>
       <c r="K21" t="n">
-        <v>67351</v>
+        <v>69874</v>
       </c>
       <c r="L21" t="n">
         <v>31.82</v>
       </c>
       <c r="M21" t="n">
-        <v>40.88</v>
+        <v>43.17</v>
       </c>
       <c r="N21" t="n">
-        <v>20.3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22">
@@ -1563,16 +1563,16 @@
         <v>1.17</v>
       </c>
       <c r="D22" t="n">
-        <v>1.452</v>
+        <v>1.526</v>
       </c>
       <c r="E22" t="n">
-        <v>-35.7</v>
+        <v>-38.6</v>
       </c>
       <c r="F22" t="n">
-        <v>-23.8</v>
+        <v>-25.4</v>
       </c>
       <c r="G22" t="n">
-        <v>-11.9</v>
+        <v>-12.2</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>468801</v>
+        <v>518082</v>
       </c>
       <c r="K22" t="n">
-        <v>241493</v>
+        <v>253467</v>
       </c>
       <c r="L22" t="n">
-        <v>59.39</v>
+        <v>59.59</v>
       </c>
       <c r="M22" t="n">
-        <v>81.38</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>23.8</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="23">
@@ -1615,16 +1615,16 @@
         <v>1.31</v>
       </c>
       <c r="D23" t="n">
-        <v>1.129</v>
+        <v>1.162</v>
       </c>
       <c r="E23" t="n">
-        <v>-30.3</v>
+        <v>-32.6</v>
       </c>
       <c r="F23" t="n">
-        <v>-24.8</v>
+        <v>-25.9</v>
       </c>
       <c r="G23" t="n">
-        <v>-19.2</v>
+        <v>-19.1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1637,19 +1637,19 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>540231</v>
+        <v>590752</v>
       </c>
       <c r="K23" t="n">
-        <v>406359</v>
+        <v>422460</v>
       </c>
       <c r="L23" t="n">
-        <v>27.57</v>
+        <v>27.79</v>
       </c>
       <c r="M23" t="n">
-        <v>31.95</v>
+        <v>33.32</v>
       </c>
       <c r="N23" t="n">
-        <v>11.1</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="24">
@@ -1667,16 +1667,16 @@
         <v>1.13</v>
       </c>
       <c r="D24" t="n">
-        <v>1.186</v>
+        <v>1.216</v>
       </c>
       <c r="E24" t="n">
-        <v>-34.5</v>
+        <v>-36.4</v>
       </c>
       <c r="F24" t="n">
-        <v>-27.5</v>
+        <v>-28.5</v>
       </c>
       <c r="G24" t="n">
-        <v>-20.4</v>
+        <v>-20.6</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>207795</v>
+        <v>223480</v>
       </c>
       <c r="K24" t="n">
-        <v>129486</v>
+        <v>132721</v>
       </c>
       <c r="L24" t="n">
         <v>14.46</v>
       </c>
       <c r="M24" t="n">
-        <v>17.57</v>
+        <v>18.07</v>
       </c>
       <c r="N24" t="n">
-        <v>14.1</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="25">
@@ -1719,16 +1719,16 @@
         <v>1.43</v>
       </c>
       <c r="D25" t="n">
-        <v>0.855</v>
+        <v>0.872</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>-0.4</v>
       </c>
       <c r="F25" t="n">
-        <v>-8.300000000000001</v>
+        <v>-10.8</v>
       </c>
       <c r="G25" t="n">
-        <v>-20.6</v>
+        <v>-21.2</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1741,19 +1741,19 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>135338</v>
+        <v>205490</v>
       </c>
       <c r="K25" t="n">
-        <v>499557</v>
+        <v>527389</v>
       </c>
       <c r="L25" t="n">
         <v>30.67</v>
       </c>
       <c r="M25" t="n">
-        <v>23.41</v>
+        <v>24.26</v>
       </c>
       <c r="N25" t="n">
-        <v>-24.6</v>
+        <v>-20.8</v>
       </c>
     </row>
     <row r="26">
@@ -1771,16 +1771,16 @@
         <v>1.34</v>
       </c>
       <c r="D26" t="n">
-        <v>1.147</v>
+        <v>1.109</v>
       </c>
       <c r="E26" t="n">
-        <v>-34.1</v>
+        <v>-30.8</v>
       </c>
       <c r="F26" t="n">
-        <v>-28.8</v>
+        <v>-26.7</v>
       </c>
       <c r="G26" t="n">
-        <v>-23.6</v>
+        <v>-22.7</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1793,19 +1793,19 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>549197</v>
+        <v>500715</v>
       </c>
       <c r="K26" t="n">
-        <v>425696</v>
+        <v>409525</v>
       </c>
       <c r="L26" t="n">
-        <v>41.44</v>
+        <v>41.71</v>
       </c>
       <c r="M26" t="n">
-        <v>48.05</v>
+        <v>46.62</v>
       </c>
       <c r="N26" t="n">
-        <v>10.5</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -523,16 +523,16 @@
         <v>0.34</v>
       </c>
       <c r="D2" t="n">
-        <v>1.272</v>
+        <v>1.292</v>
       </c>
       <c r="E2" t="n">
-        <v>51.2</v>
+        <v>48.2</v>
       </c>
       <c r="F2" t="n">
-        <v>76.7</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>102.3</v>
+        <v>102</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -554,10 +554,10 @@
         <v>62.66</v>
       </c>
       <c r="M2" t="n">
-        <v>83.84999999999999</v>
+        <v>85.37</v>
       </c>
       <c r="N2" t="n">
-        <v>51.1</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="3">
@@ -578,7 +578,7 @@
         <v>0.994</v>
       </c>
       <c r="E3" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="F3" t="n">
         <v>47.8</v>
@@ -606,7 +606,7 @@
         <v>33.7</v>
       </c>
       <c r="M3" t="n">
-        <v>33.16</v>
+        <v>33.17</v>
       </c>
       <c r="N3" t="n">
         <v>-2.4</v>
@@ -627,29 +627,29 @@
         <v>0.71</v>
       </c>
       <c r="D4" t="n">
-        <v>1.185</v>
+        <v>1.278</v>
       </c>
       <c r="E4" t="n">
-        <v>9.1</v>
+        <v>-3.1</v>
       </c>
       <c r="F4" t="n">
-        <v>25.5</v>
+        <v>18.8</v>
       </c>
       <c r="G4" t="n">
-        <v>41.9</v>
+        <v>40.6</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>HOLD (fairly valued)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>BUY (undervalued)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>BUY (undervalued)</t>
-        </is>
-      </c>
       <c r="J4" t="n">
-        <v>80462</v>
+        <v>212404</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>16.02</v>
       </c>
       <c r="M4" t="n">
-        <v>20.84</v>
+        <v>23.25</v>
       </c>
       <c r="N4" t="n">
-        <v>32.8</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="5">
@@ -679,16 +679,16 @@
         <v>0.71</v>
       </c>
       <c r="D5" t="n">
-        <v>1.583</v>
+        <v>1.532</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.4</v>
+        <v>-0.6</v>
       </c>
       <c r="F5" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="G5" t="n">
-        <v>38.3</v>
+        <v>38.5</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>90377</v>
+        <v>75519</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -710,16 +710,16 @@
         <v>76.73</v>
       </c>
       <c r="M5" t="n">
-        <v>109.83</v>
+        <v>106.94</v>
       </c>
       <c r="N5" t="n">
-        <v>41.7</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -728,23 +728,23 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
       <c r="D6" t="n">
-        <v>1.316</v>
+        <v>0.924</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7</v>
+        <v>62.7</v>
       </c>
       <c r="F6" t="n">
-        <v>15.6</v>
+        <v>45.6</v>
       </c>
       <c r="G6" t="n">
-        <v>29.4</v>
+        <v>28.4</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -753,25 +753,25 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>32696</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>42.88</v>
+        <v>10.28</v>
       </c>
       <c r="M6" t="n">
-        <v>54.58</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>27.8</v>
+        <v>-34.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -780,44 +780,44 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9409999999999999</v>
+        <v>1.404</v>
       </c>
       <c r="E7" t="n">
-        <v>52.5</v>
+        <v>-5.3</v>
       </c>
       <c r="F7" t="n">
-        <v>39.9</v>
+        <v>11.2</v>
       </c>
       <c r="G7" t="n">
-        <v>27.3</v>
+        <v>27.7</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>BUY (undervalued)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>BUY (undervalued)</t>
-        </is>
-      </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>131422</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>10.28</v>
+        <v>42.88</v>
       </c>
       <c r="M7" t="n">
-        <v>8.59</v>
+        <v>57.83</v>
       </c>
       <c r="N7" t="n">
-        <v>-25.2</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8">
@@ -835,16 +835,16 @@
         <v>0.86</v>
       </c>
       <c r="D8" t="n">
-        <v>1.13</v>
+        <v>1.174</v>
       </c>
       <c r="E8" t="n">
-        <v>11.6</v>
+        <v>6.7</v>
       </c>
       <c r="F8" t="n">
-        <v>18.9</v>
+        <v>16.1</v>
       </c>
       <c r="G8" t="n">
-        <v>26.3</v>
+        <v>25.5</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>41844</v>
+        <v>51677</v>
       </c>
       <c r="K8" t="n">
-        <v>11832</v>
+        <v>11523</v>
       </c>
       <c r="L8" t="n">
         <v>33.58</v>
       </c>
       <c r="M8" t="n">
-        <v>37.98</v>
+        <v>39.48</v>
       </c>
       <c r="N8" t="n">
-        <v>14.6</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="9">
@@ -887,16 +887,16 @@
         <v>0.75</v>
       </c>
       <c r="D9" t="n">
-        <v>1.331</v>
+        <v>1.358</v>
       </c>
       <c r="E9" t="n">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="F9" t="n">
-        <v>7.8</v>
+        <v>6.7</v>
       </c>
       <c r="G9" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>31108</v>
+        <v>34911</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -918,10 +918,10 @@
         <v>16.38</v>
       </c>
       <c r="M9" t="n">
-        <v>21.6</v>
+        <v>22.03</v>
       </c>
       <c r="N9" t="n">
-        <v>29.7</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="10">
@@ -939,20 +939,20 @@
         <v>0.8</v>
       </c>
       <c r="D10" t="n">
-        <v>1.437</v>
+        <v>1.56</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4</v>
+        <v>-6.8</v>
       </c>
       <c r="F10" t="n">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="G10" t="n">
-        <v>21</v>
+        <v>20.4</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>93157</v>
+        <v>143965</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -970,10 +970,10 @@
         <v>83.93000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>103.03</v>
+        <v>108.4</v>
       </c>
       <c r="N10" t="n">
-        <v>22.4</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="11">
@@ -991,16 +991,16 @@
         <v>0.92</v>
       </c>
       <c r="D11" t="n">
-        <v>1.433</v>
+        <v>1.507</v>
       </c>
       <c r="E11" t="n">
-        <v>-15.3</v>
+        <v>-19.9</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7</v>
+        <v>-1.1</v>
       </c>
       <c r="G11" t="n">
-        <v>18.7</v>
+        <v>17.7</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>103758</v>
+        <v>117987</v>
       </c>
       <c r="K11" t="n">
-        <v>24347</v>
+        <v>24941</v>
       </c>
       <c r="L11" t="n">
         <v>6.56</v>
       </c>
       <c r="M11" t="n">
-        <v>9.19</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>34</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="12">
@@ -1043,16 +1043,16 @@
         <v>0.85</v>
       </c>
       <c r="D12" t="n">
-        <v>2.306</v>
+        <v>2.364</v>
       </c>
       <c r="E12" t="n">
-        <v>-54.3</v>
+        <v>-55.5</v>
       </c>
       <c r="F12" t="n">
-        <v>-21.4</v>
+        <v>-22.1</v>
       </c>
       <c r="G12" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>658330</v>
+        <v>687243</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1074,10 +1074,10 @@
         <v>3.07</v>
       </c>
       <c r="M12" t="n">
-        <v>7.48</v>
+        <v>7.68</v>
       </c>
       <c r="N12" t="n">
-        <v>65.8</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="13">
@@ -1095,41 +1095,41 @@
         <v>0.91</v>
       </c>
       <c r="D13" t="n">
-        <v>1.308</v>
+        <v>1.049</v>
       </c>
       <c r="E13" t="n">
-        <v>-20.2</v>
+        <v>1.4</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.1</v>
+        <v>3.8</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>30729</v>
+        <v>14262</v>
       </c>
       <c r="K13" t="n">
-        <v>12225</v>
+        <v>11346</v>
       </c>
       <c r="L13" t="n">
         <v>0.4</v>
       </c>
       <c r="M13" t="n">
-        <v>0.51</v>
+        <v>0.41</v>
       </c>
       <c r="N13" t="n">
-        <v>24.1</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="14">
@@ -1147,16 +1147,16 @@
         <v>0.88</v>
       </c>
       <c r="D14" t="n">
-        <v>0.899</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>23</v>
+        <v>49.2</v>
       </c>
       <c r="F14" t="n">
-        <v>13.4</v>
+        <v>27.4</v>
       </c>
       <c r="G14" t="n">
-        <v>3.9</v>
+        <v>5.7</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1178,114 +1178,114 @@
         <v>9.529999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>8.050000000000001</v>
+        <v>6.75</v>
       </c>
       <c r="N14" t="n">
-        <v>-19.2</v>
+        <v>-43.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="D15" t="n">
-        <v>0.996</v>
+        <v>1.177</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5</v>
+        <v>-20.7</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3</v>
+        <v>-9.5</v>
       </c>
       <c r="G15" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>12864</v>
+        <v>165194</v>
       </c>
       <c r="K15" t="n">
-        <v>13327</v>
+        <v>28497</v>
       </c>
       <c r="L15" t="n">
-        <v>29.79</v>
+        <v>14.41</v>
       </c>
       <c r="M15" t="n">
-        <v>29.67</v>
+        <v>18.49</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="D16" t="n">
-        <v>1.138</v>
+        <v>1.056</v>
       </c>
       <c r="E16" t="n">
-        <v>-16.4</v>
+        <v>-4.2</v>
       </c>
       <c r="F16" t="n">
-        <v>-7.2</v>
+        <v>-1.4</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>136080</v>
+        <v>20513</v>
       </c>
       <c r="K16" t="n">
-        <v>29760</v>
+        <v>13545</v>
       </c>
       <c r="L16" t="n">
-        <v>14.41</v>
+        <v>29.79</v>
       </c>
       <c r="M16" t="n">
-        <v>17.59</v>
+        <v>31.57</v>
       </c>
       <c r="N16" t="n">
-        <v>18.4</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="17">
@@ -1303,20 +1303,20 @@
         <v>0.62</v>
       </c>
       <c r="D17" t="n">
-        <v>0.904</v>
+        <v>1.039</v>
       </c>
       <c r="E17" t="n">
-        <v>10.3</v>
+        <v>-2.4</v>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>-0.9</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1325,19 +1325,19 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>4628</v>
+        <v>19208</v>
       </c>
       <c r="K17" t="n">
-        <v>14728</v>
+        <v>15166</v>
       </c>
       <c r="L17" t="n">
         <v>20.11</v>
       </c>
       <c r="M17" t="n">
-        <v>18.53</v>
+        <v>20.73</v>
       </c>
       <c r="N17" t="n">
-        <v>-8.6</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="18">
@@ -1355,16 +1355,16 @@
         <v>0.92</v>
       </c>
       <c r="D18" t="n">
-        <v>1.11</v>
+        <v>1.143</v>
       </c>
       <c r="E18" t="n">
-        <v>-13.9</v>
+        <v>-17</v>
       </c>
       <c r="F18" t="n">
-        <v>-8.5</v>
+        <v>-10.2</v>
       </c>
       <c r="G18" t="n">
-        <v>-3</v>
+        <v>-3.3</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>38006</v>
+        <v>43985</v>
       </c>
       <c r="K18" t="n">
-        <v>19532</v>
+        <v>19908</v>
       </c>
       <c r="L18" t="n">
         <v>22.67</v>
       </c>
       <c r="M18" t="n">
-        <v>25.54</v>
+        <v>26.41</v>
       </c>
       <c r="N18" t="n">
-        <v>10.9</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="19">
@@ -1407,16 +1407,16 @@
         <v>1.08</v>
       </c>
       <c r="D19" t="n">
-        <v>1.188</v>
+        <v>1.168</v>
       </c>
       <c r="E19" t="n">
-        <v>-18.2</v>
+        <v>-16.7</v>
       </c>
       <c r="F19" t="n">
-        <v>-11.2</v>
+        <v>-10.3</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.1</v>
+        <v>-3.9</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>571564</v>
+        <v>535858</v>
       </c>
       <c r="K19" t="n">
-        <v>293729</v>
+        <v>287365</v>
       </c>
       <c r="L19" t="n">
         <v>15.97</v>
       </c>
       <c r="M19" t="n">
-        <v>18.72</v>
+        <v>18.43</v>
       </c>
       <c r="N19" t="n">
-        <v>14.1</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1456,19 +1456,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.04</v>
+        <v>0.96</v>
       </c>
       <c r="D20" t="n">
-        <v>1.162</v>
+        <v>1.521</v>
       </c>
       <c r="E20" t="n">
-        <v>-23.9</v>
+        <v>-37.3</v>
       </c>
       <c r="F20" t="n">
-        <v>-15.7</v>
+        <v>-23.3</v>
       </c>
       <c r="G20" t="n">
-        <v>-7.6</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1481,25 +1481,25 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>180285</v>
+        <v>296366</v>
       </c>
       <c r="K20" t="n">
-        <v>55172</v>
+        <v>73144</v>
       </c>
       <c r="L20" t="n">
-        <v>2.07</v>
+        <v>31.82</v>
       </c>
       <c r="M20" t="n">
-        <v>2.51</v>
+        <v>46.13</v>
       </c>
       <c r="N20" t="n">
-        <v>16.3</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1508,19 +1508,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.96</v>
+        <v>1.04</v>
       </c>
       <c r="D21" t="n">
-        <v>1.413</v>
+        <v>1.245</v>
       </c>
       <c r="E21" t="n">
-        <v>-32.8</v>
+        <v>-31.4</v>
       </c>
       <c r="F21" t="n">
-        <v>-20.8</v>
+        <v>-20.3</v>
       </c>
       <c r="G21" t="n">
-        <v>-8.9</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>246904</v>
+        <v>255556</v>
       </c>
       <c r="K21" t="n">
-        <v>69874</v>
+        <v>66850</v>
       </c>
       <c r="L21" t="n">
-        <v>31.82</v>
+        <v>2.07</v>
       </c>
       <c r="M21" t="n">
-        <v>43.17</v>
+        <v>2.74</v>
       </c>
       <c r="N21" t="n">
-        <v>24</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="22">
@@ -1563,16 +1563,16 @@
         <v>1.17</v>
       </c>
       <c r="D22" t="n">
-        <v>1.526</v>
+        <v>1.557</v>
       </c>
       <c r="E22" t="n">
-        <v>-38.6</v>
+        <v>-39.8</v>
       </c>
       <c r="F22" t="n">
-        <v>-25.4</v>
+        <v>-26.1</v>
       </c>
       <c r="G22" t="n">
-        <v>-12.2</v>
+        <v>-12.4</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>518082</v>
+        <v>539187</v>
       </c>
       <c r="K22" t="n">
-        <v>253467</v>
+        <v>258594</v>
       </c>
       <c r="L22" t="n">
         <v>59.59</v>
       </c>
       <c r="M22" t="n">
-        <v>85.26000000000001</v>
+        <v>86.81</v>
       </c>
       <c r="N22" t="n">
-        <v>26.5</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="23">
@@ -1615,16 +1615,16 @@
         <v>1.31</v>
       </c>
       <c r="D23" t="n">
-        <v>1.162</v>
+        <v>1.207</v>
       </c>
       <c r="E23" t="n">
-        <v>-32.6</v>
+        <v>-36.1</v>
       </c>
       <c r="F23" t="n">
-        <v>-25.9</v>
+        <v>-27.9</v>
       </c>
       <c r="G23" t="n">
-        <v>-19.1</v>
+        <v>-19.8</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1637,19 +1637,19 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>590752</v>
+        <v>660065</v>
       </c>
       <c r="K23" t="n">
-        <v>422460</v>
+        <v>444550</v>
       </c>
       <c r="L23" t="n">
         <v>27.79</v>
       </c>
       <c r="M23" t="n">
-        <v>33.32</v>
+        <v>34.87</v>
       </c>
       <c r="N23" t="n">
-        <v>13.4</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="24">
@@ -1667,16 +1667,16 @@
         <v>1.13</v>
       </c>
       <c r="D24" t="n">
-        <v>1.216</v>
+        <v>1.319</v>
       </c>
       <c r="E24" t="n">
-        <v>-36.4</v>
+        <v>-42.3</v>
       </c>
       <c r="F24" t="n">
-        <v>-28.5</v>
+        <v>-31.7</v>
       </c>
       <c r="G24" t="n">
-        <v>-20.6</v>
+        <v>-21.1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>223480</v>
+        <v>277962</v>
       </c>
       <c r="K24" t="n">
-        <v>132721</v>
+        <v>143958</v>
       </c>
       <c r="L24" t="n">
         <v>14.46</v>
       </c>
       <c r="M24" t="n">
-        <v>18.07</v>
+        <v>19.78</v>
       </c>
       <c r="N24" t="n">
-        <v>15.8</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="25">
@@ -1719,20 +1719,20 @@
         <v>1.43</v>
       </c>
       <c r="D25" t="n">
-        <v>0.872</v>
+        <v>0.908</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.4</v>
+        <v>-7.7</v>
       </c>
       <c r="F25" t="n">
-        <v>-10.8</v>
+        <v>-14.8</v>
       </c>
       <c r="G25" t="n">
-        <v>-21.2</v>
+        <v>-21.9</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1741,19 +1741,19 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>205490</v>
+        <v>328633</v>
       </c>
       <c r="K25" t="n">
-        <v>527389</v>
+        <v>556000</v>
       </c>
       <c r="L25" t="n">
-        <v>30.67</v>
+        <v>29.47</v>
       </c>
       <c r="M25" t="n">
-        <v>24.26</v>
+        <v>24.94</v>
       </c>
       <c r="N25" t="n">
-        <v>-20.8</v>
+        <v>-14.2</v>
       </c>
     </row>
     <row r="26">
@@ -1771,16 +1771,16 @@
         <v>1.34</v>
       </c>
       <c r="D26" t="n">
-        <v>1.109</v>
+        <v>1.179</v>
       </c>
       <c r="E26" t="n">
-        <v>-30.8</v>
+        <v>-35.9</v>
       </c>
       <c r="F26" t="n">
-        <v>-26.7</v>
+        <v>-29.6</v>
       </c>
       <c r="G26" t="n">
-        <v>-22.7</v>
+        <v>-23.4</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1793,19 +1793,19 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>500715</v>
+        <v>589629</v>
       </c>
       <c r="K26" t="n">
-        <v>409525</v>
+        <v>439183</v>
       </c>
       <c r="L26" t="n">
         <v>41.71</v>
       </c>
       <c r="M26" t="n">
-        <v>46.62</v>
+        <v>49.8</v>
       </c>
       <c r="N26" t="n">
-        <v>8.1</v>
+        <v>12.4</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -523,16 +523,16 @@
         <v>0.34</v>
       </c>
       <c r="D2" t="n">
-        <v>1.292</v>
+        <v>1.298</v>
       </c>
       <c r="E2" t="n">
-        <v>48.2</v>
+        <v>47.4</v>
       </c>
       <c r="F2" t="n">
-        <v>75.09999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>102</v>
+        <v>101.9</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -554,10 +554,10 @@
         <v>62.66</v>
       </c>
       <c r="M2" t="n">
-        <v>85.37</v>
+        <v>85.83</v>
       </c>
       <c r="N2" t="n">
-        <v>53.7</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="3">
@@ -575,16 +575,16 @@
         <v>0.9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.994</v>
+        <v>0.995</v>
       </c>
       <c r="E3" t="n">
-        <v>49</v>
+        <v>48.3</v>
       </c>
       <c r="F3" t="n">
-        <v>47.8</v>
+        <v>47.4</v>
       </c>
       <c r="G3" t="n">
-        <v>46.6</v>
+        <v>46.4</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -606,10 +606,10 @@
         <v>33.7</v>
       </c>
       <c r="M3" t="n">
-        <v>33.17</v>
+        <v>33.27</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.4</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="4">
@@ -627,16 +627,16 @@
         <v>0.71</v>
       </c>
       <c r="D4" t="n">
-        <v>1.278</v>
+        <v>1.275</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.1</v>
+        <v>-2.7</v>
       </c>
       <c r="F4" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="G4" t="n">
-        <v>40.6</v>
+        <v>40.7</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>212404</v>
+        <v>207375</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>16.02</v>
       </c>
       <c r="M4" t="n">
-        <v>23.25</v>
+        <v>23.16</v>
       </c>
       <c r="N4" t="n">
-        <v>43.7</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="5">
@@ -679,16 +679,16 @@
         <v>0.71</v>
       </c>
       <c r="D5" t="n">
-        <v>1.532</v>
+        <v>1.552</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6</v>
+        <v>-1.7</v>
       </c>
       <c r="F5" t="n">
-        <v>19</v>
+        <v>18.4</v>
       </c>
       <c r="G5" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>75519</v>
+        <v>81099</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -710,10 +710,10 @@
         <v>76.73</v>
       </c>
       <c r="M5" t="n">
-        <v>106.94</v>
+        <v>108.02</v>
       </c>
       <c r="N5" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="6">
@@ -731,16 +731,16 @@
         <v>0.86</v>
       </c>
       <c r="D6" t="n">
-        <v>0.924</v>
+        <v>0.871</v>
       </c>
       <c r="E6" t="n">
-        <v>62.7</v>
+        <v>108</v>
       </c>
       <c r="F6" t="n">
-        <v>45.6</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>28.4</v>
+        <v>33.3</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -762,10 +762,10 @@
         <v>10.28</v>
       </c>
       <c r="M6" t="n">
-        <v>8.119999999999999</v>
+        <v>6.59</v>
       </c>
       <c r="N6" t="n">
-        <v>-34.3</v>
+        <v>-74.7</v>
       </c>
     </row>
     <row r="7">
@@ -783,20 +783,20 @@
         <v>0.75</v>
       </c>
       <c r="D7" t="n">
-        <v>1.404</v>
+        <v>1.382</v>
       </c>
       <c r="E7" t="n">
-        <v>-5.3</v>
+        <v>-3.7</v>
       </c>
       <c r="F7" t="n">
-        <v>11.2</v>
+        <v>12.2</v>
       </c>
       <c r="G7" t="n">
-        <v>27.7</v>
+        <v>28.1</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>131422</v>
+        <v>106820</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -814,10 +814,10 @@
         <v>42.88</v>
       </c>
       <c r="M7" t="n">
-        <v>57.83</v>
+        <v>57.02</v>
       </c>
       <c r="N7" t="n">
-        <v>33</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="8">
@@ -835,16 +835,16 @@
         <v>0.86</v>
       </c>
       <c r="D8" t="n">
-        <v>1.174</v>
+        <v>1.148</v>
       </c>
       <c r="E8" t="n">
-        <v>6.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>16.1</v>
+        <v>17.7</v>
       </c>
       <c r="G8" t="n">
-        <v>25.5</v>
+        <v>25.8</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>51677</v>
+        <v>43444</v>
       </c>
       <c r="K8" t="n">
-        <v>11523</v>
+        <v>9917</v>
       </c>
       <c r="L8" t="n">
-        <v>33.58</v>
+        <v>35.79</v>
       </c>
       <c r="M8" t="n">
-        <v>39.48</v>
+        <v>41.02</v>
       </c>
       <c r="N8" t="n">
-        <v>18.8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -887,16 +887,16 @@
         <v>0.75</v>
       </c>
       <c r="D9" t="n">
-        <v>1.358</v>
+        <v>1.313</v>
       </c>
       <c r="E9" t="n">
-        <v>-9</v>
+        <v>-5.7</v>
       </c>
       <c r="F9" t="n">
-        <v>6.7</v>
+        <v>8.6</v>
       </c>
       <c r="G9" t="n">
-        <v>22.5</v>
+        <v>22.8</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>34911</v>
+        <v>28607</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -918,10 +918,10 @@
         <v>16.38</v>
       </c>
       <c r="M9" t="n">
-        <v>22.03</v>
+        <v>21.31</v>
       </c>
       <c r="N9" t="n">
-        <v>31.4</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="10">
@@ -939,16 +939,16 @@
         <v>0.8</v>
       </c>
       <c r="D10" t="n">
-        <v>1.56</v>
+        <v>1.527</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.8</v>
+        <v>-5.4</v>
       </c>
       <c r="F10" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="G10" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>143965</v>
+        <v>130174</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -970,10 +970,10 @@
         <v>83.93000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>108.4</v>
+        <v>106.94</v>
       </c>
       <c r="N10" t="n">
-        <v>27.2</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="11">
@@ -991,16 +991,16 @@
         <v>0.92</v>
       </c>
       <c r="D11" t="n">
-        <v>1.507</v>
+        <v>1.553</v>
       </c>
       <c r="E11" t="n">
-        <v>-19.9</v>
+        <v>-22.6</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1</v>
+        <v>-2.7</v>
       </c>
       <c r="G11" t="n">
-        <v>17.7</v>
+        <v>17.2</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>117987</v>
+        <v>126841</v>
       </c>
       <c r="K11" t="n">
-        <v>24941</v>
+        <v>25310</v>
       </c>
       <c r="L11" t="n">
         <v>6.56</v>
       </c>
       <c r="M11" t="n">
-        <v>9.640000000000001</v>
+        <v>9.92</v>
       </c>
       <c r="N11" t="n">
-        <v>37.7</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="12">
@@ -1043,16 +1043,16 @@
         <v>0.85</v>
       </c>
       <c r="D12" t="n">
-        <v>2.364</v>
+        <v>2.325</v>
       </c>
       <c r="E12" t="n">
-        <v>-55.5</v>
+        <v>-54.7</v>
       </c>
       <c r="F12" t="n">
-        <v>-22.1</v>
+        <v>-21.6</v>
       </c>
       <c r="G12" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>687243</v>
+        <v>667460</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1074,10 +1074,10 @@
         <v>3.07</v>
       </c>
       <c r="M12" t="n">
-        <v>7.68</v>
+        <v>7.54</v>
       </c>
       <c r="N12" t="n">
-        <v>66.8</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1199,16 +1199,16 @@
         <v>0.85</v>
       </c>
       <c r="D15" t="n">
-        <v>1.177</v>
+        <v>1.185</v>
       </c>
       <c r="E15" t="n">
-        <v>-20.7</v>
+        <v>-21.5</v>
       </c>
       <c r="F15" t="n">
-        <v>-9.5</v>
+        <v>-9.9</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>165194</v>
+        <v>170829</v>
       </c>
       <c r="K15" t="n">
-        <v>28497</v>
+        <v>28253</v>
       </c>
       <c r="L15" t="n">
         <v>14.41</v>
       </c>
       <c r="M15" t="n">
-        <v>18.49</v>
+        <v>18.67</v>
       </c>
       <c r="N15" t="n">
-        <v>22.5</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="16">
@@ -1251,16 +1251,16 @@
         <v>0.89</v>
       </c>
       <c r="D16" t="n">
-        <v>1.056</v>
+        <v>1.038</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.2</v>
+        <v>-2.3</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4</v>
+        <v>-0.3</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1273,19 +1273,19 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>20513</v>
+        <v>18174</v>
       </c>
       <c r="K16" t="n">
-        <v>13545</v>
+        <v>13478</v>
       </c>
       <c r="L16" t="n">
         <v>29.79</v>
       </c>
       <c r="M16" t="n">
-        <v>31.57</v>
+        <v>30.99</v>
       </c>
       <c r="N16" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1303,13 +1303,13 @@
         <v>0.62</v>
       </c>
       <c r="D17" t="n">
-        <v>1.039</v>
+        <v>1.034</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.4</v>
+        <v>-2</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9</v>
+        <v>-0.7</v>
       </c>
       <c r="G17" t="n">
         <v>0.7</v>
@@ -1325,19 +1325,19 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>19208</v>
+        <v>18716</v>
       </c>
       <c r="K17" t="n">
-        <v>15166</v>
+        <v>15152</v>
       </c>
       <c r="L17" t="n">
         <v>20.11</v>
       </c>
       <c r="M17" t="n">
-        <v>20.73</v>
+        <v>20.66</v>
       </c>
       <c r="N17" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="18">
@@ -1355,16 +1355,16 @@
         <v>0.92</v>
       </c>
       <c r="D18" t="n">
-        <v>1.143</v>
+        <v>1.094</v>
       </c>
       <c r="E18" t="n">
-        <v>-17</v>
+        <v>-12.4</v>
       </c>
       <c r="F18" t="n">
-        <v>-10.2</v>
+        <v>-7.6</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.3</v>
+        <v>-2.9</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>43985</v>
+        <v>35200</v>
       </c>
       <c r="K18" t="n">
-        <v>19908</v>
+        <v>19356</v>
       </c>
       <c r="L18" t="n">
         <v>22.67</v>
       </c>
       <c r="M18" t="n">
-        <v>26.41</v>
+        <v>25.13</v>
       </c>
       <c r="N18" t="n">
-        <v>13.7</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="19">
@@ -1407,16 +1407,16 @@
         <v>1.08</v>
       </c>
       <c r="D19" t="n">
-        <v>1.168</v>
+        <v>1.196</v>
       </c>
       <c r="E19" t="n">
-        <v>-16.7</v>
+        <v>-18.8</v>
       </c>
       <c r="F19" t="n">
-        <v>-10.3</v>
+        <v>-11.5</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.9</v>
+        <v>-4.2</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>535858</v>
+        <v>585846</v>
       </c>
       <c r="K19" t="n">
-        <v>287365</v>
+        <v>296274</v>
       </c>
       <c r="L19" t="n">
         <v>15.97</v>
       </c>
       <c r="M19" t="n">
-        <v>18.43</v>
+        <v>18.84</v>
       </c>
       <c r="N19" t="n">
-        <v>12.8</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1456,19 +1456,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.96</v>
+        <v>1.04</v>
       </c>
       <c r="D20" t="n">
-        <v>1.521</v>
+        <v>1.2</v>
       </c>
       <c r="E20" t="n">
-        <v>-37.3</v>
+        <v>-27.5</v>
       </c>
       <c r="F20" t="n">
-        <v>-23.3</v>
+        <v>-17.9</v>
       </c>
       <c r="G20" t="n">
-        <v>-9.199999999999999</v>
+        <v>-8.4</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1481,25 +1481,25 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>296366</v>
+        <v>214768</v>
       </c>
       <c r="K20" t="n">
-        <v>73144</v>
+        <v>60522</v>
       </c>
       <c r="L20" t="n">
-        <v>31.82</v>
+        <v>2.07</v>
       </c>
       <c r="M20" t="n">
-        <v>46.13</v>
+        <v>2.61</v>
       </c>
       <c r="N20" t="n">
-        <v>28.2</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1508,19 +1508,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.04</v>
+        <v>0.96</v>
       </c>
       <c r="D21" t="n">
-        <v>1.245</v>
+        <v>1.489</v>
       </c>
       <c r="E21" t="n">
-        <v>-31.4</v>
+        <v>-36.1</v>
       </c>
       <c r="F21" t="n">
-        <v>-20.3</v>
+        <v>-22.6</v>
       </c>
       <c r="G21" t="n">
-        <v>-9.199999999999999</v>
+        <v>-9.1</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>255556</v>
+        <v>281759</v>
       </c>
       <c r="K21" t="n">
-        <v>66850</v>
+        <v>72178</v>
       </c>
       <c r="L21" t="n">
-        <v>2.07</v>
+        <v>31.82</v>
       </c>
       <c r="M21" t="n">
-        <v>2.74</v>
+        <v>45.26</v>
       </c>
       <c r="N21" t="n">
-        <v>22.2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22">
@@ -1563,16 +1563,16 @@
         <v>1.17</v>
       </c>
       <c r="D22" t="n">
-        <v>1.557</v>
+        <v>1.554</v>
       </c>
       <c r="E22" t="n">
-        <v>-39.8</v>
+        <v>-39.7</v>
       </c>
       <c r="F22" t="n">
-        <v>-26.1</v>
+        <v>-26</v>
       </c>
       <c r="G22" t="n">
-        <v>-12.4</v>
+        <v>-12.3</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1585,19 +1585,19 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>539187</v>
+        <v>536654</v>
       </c>
       <c r="K22" t="n">
-        <v>258594</v>
+        <v>257979</v>
       </c>
       <c r="L22" t="n">
         <v>59.59</v>
       </c>
       <c r="M22" t="n">
-        <v>86.81</v>
+        <v>86.62</v>
       </c>
       <c r="N22" t="n">
-        <v>27.5</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="23">
@@ -1615,16 +1615,16 @@
         <v>1.31</v>
       </c>
       <c r="D23" t="n">
-        <v>1.207</v>
+        <v>1.222</v>
       </c>
       <c r="E23" t="n">
-        <v>-36.1</v>
+        <v>-37.1</v>
       </c>
       <c r="F23" t="n">
-        <v>-27.9</v>
+        <v>-28.5</v>
       </c>
       <c r="G23" t="n">
-        <v>-19.8</v>
+        <v>-19.9</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1637,19 +1637,19 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>660065</v>
+        <v>682553</v>
       </c>
       <c r="K23" t="n">
-        <v>444550</v>
+        <v>451717</v>
       </c>
       <c r="L23" t="n">
         <v>27.79</v>
       </c>
       <c r="M23" t="n">
-        <v>34.87</v>
+        <v>35.38</v>
       </c>
       <c r="N23" t="n">
-        <v>16.3</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="24">
@@ -1667,16 +1667,16 @@
         <v>1.13</v>
       </c>
       <c r="D24" t="n">
-        <v>1.319</v>
+        <v>1.273</v>
       </c>
       <c r="E24" t="n">
-        <v>-42.3</v>
+        <v>-39.9</v>
       </c>
       <c r="F24" t="n">
-        <v>-31.7</v>
+        <v>-30.4</v>
       </c>
       <c r="G24" t="n">
-        <v>-21.1</v>
+        <v>-20.9</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>277962</v>
+        <v>253792</v>
       </c>
       <c r="K24" t="n">
-        <v>143958</v>
+        <v>138973</v>
       </c>
       <c r="L24" t="n">
         <v>14.46</v>
       </c>
       <c r="M24" t="n">
-        <v>19.78</v>
+        <v>19.02</v>
       </c>
       <c r="N24" t="n">
-        <v>21.2</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="25">
@@ -1719,16 +1719,16 @@
         <v>1.43</v>
       </c>
       <c r="D25" t="n">
-        <v>0.908</v>
+        <v>0.902</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.7</v>
+        <v>-6.4</v>
       </c>
       <c r="F25" t="n">
-        <v>-14.8</v>
+        <v>-14</v>
       </c>
       <c r="G25" t="n">
-        <v>-21.9</v>
+        <v>-21.7</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1741,19 +1741,19 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>328633</v>
+        <v>304350</v>
       </c>
       <c r="K25" t="n">
-        <v>556000</v>
+        <v>546338</v>
       </c>
       <c r="L25" t="n">
         <v>29.47</v>
       </c>
       <c r="M25" t="n">
-        <v>24.94</v>
+        <v>24.65</v>
       </c>
       <c r="N25" t="n">
-        <v>-14.2</v>
+        <v>-15.3</v>
       </c>
     </row>
     <row r="26">
@@ -1771,16 +1771,16 @@
         <v>1.34</v>
       </c>
       <c r="D26" t="n">
-        <v>1.179</v>
+        <v>1.206</v>
       </c>
       <c r="E26" t="n">
-        <v>-35.9</v>
+        <v>-37.6</v>
       </c>
       <c r="F26" t="n">
-        <v>-29.6</v>
+        <v>-30.6</v>
       </c>
       <c r="G26" t="n">
-        <v>-23.4</v>
+        <v>-23.7</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1793,19 +1793,19 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>589629</v>
+        <v>623698</v>
       </c>
       <c r="K26" t="n">
-        <v>439183</v>
+        <v>450546</v>
       </c>
       <c r="L26" t="n">
         <v>41.71</v>
       </c>
       <c r="M26" t="n">
-        <v>49.8</v>
+        <v>51.03</v>
       </c>
       <c r="N26" t="n">
-        <v>12.4</v>
+        <v>13.9</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -719,7 +719,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>GSL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -728,50 +728,50 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="D6" t="n">
-        <v>0.871</v>
+        <v>1.382</v>
       </c>
       <c r="E6" t="n">
-        <v>108</v>
+        <v>-3.7</v>
       </c>
       <c r="F6" t="n">
-        <v>70.59999999999999</v>
+        <v>12.2</v>
       </c>
       <c r="G6" t="n">
-        <v>33.3</v>
+        <v>28.1</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>HOLD (fairly valued)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>BUY (undervalued)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>BUY (undervalued)</t>
-        </is>
-      </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>106820</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>10.28</v>
+        <v>42.88</v>
       </c>
       <c r="M6" t="n">
-        <v>6.59</v>
+        <v>57.02</v>
       </c>
       <c r="N6" t="n">
-        <v>-74.7</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GSL</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -780,23 +780,23 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
       <c r="D7" t="n">
-        <v>1.382</v>
+        <v>1.148</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>12.2</v>
+        <v>17.7</v>
       </c>
       <c r="G7" t="n">
-        <v>28.1</v>
+        <v>25.8</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -805,25 +805,25 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>106820</v>
+        <v>43444</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>9917</v>
       </c>
       <c r="L7" t="n">
-        <v>42.88</v>
+        <v>35.79</v>
       </c>
       <c r="M7" t="n">
-        <v>57.02</v>
+        <v>41.02</v>
       </c>
       <c r="N7" t="n">
-        <v>31.8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -832,50 +832,50 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="D8" t="n">
-        <v>1.148</v>
+        <v>1.313</v>
       </c>
       <c r="E8" t="n">
-        <v>9.699999999999999</v>
+        <v>-5.7</v>
       </c>
       <c r="F8" t="n">
-        <v>17.7</v>
+        <v>8.6</v>
       </c>
       <c r="G8" t="n">
-        <v>25.8</v>
+        <v>22.8</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>BUY (undervalued)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>BUY (undervalued)</t>
-        </is>
-      </c>
       <c r="J8" t="n">
-        <v>43444</v>
+        <v>28607</v>
       </c>
       <c r="K8" t="n">
-        <v>9917</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>35.79</v>
+        <v>16.38</v>
       </c>
       <c r="M8" t="n">
-        <v>41.02</v>
+        <v>21.31</v>
       </c>
       <c r="N8" t="n">
-        <v>16</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -884,19 +884,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="D9" t="n">
-        <v>1.313</v>
+        <v>1.527</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.7</v>
+        <v>-5.4</v>
       </c>
       <c r="F9" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="G9" t="n">
-        <v>22.8</v>
+        <v>20.6</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>28607</v>
+        <v>130174</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>16.38</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>21.31</v>
+        <v>106.94</v>
       </c>
       <c r="N9" t="n">
-        <v>28.4</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -936,19 +936,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.8</v>
+        <v>0.92</v>
       </c>
       <c r="D10" t="n">
-        <v>1.527</v>
+        <v>1.553</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.4</v>
+        <v>-22.6</v>
       </c>
       <c r="F10" t="n">
-        <v>7.6</v>
+        <v>-2.7</v>
       </c>
       <c r="G10" t="n">
-        <v>20.6</v>
+        <v>17.2</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>130174</v>
+        <v>126841</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>25310</v>
       </c>
       <c r="L10" t="n">
-        <v>83.93000000000001</v>
+        <v>6.56</v>
       </c>
       <c r="M10" t="n">
-        <v>106.94</v>
+        <v>9.92</v>
       </c>
       <c r="N10" t="n">
-        <v>25.9</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="D11" t="n">
-        <v>1.553</v>
+        <v>2.325</v>
       </c>
       <c r="E11" t="n">
-        <v>-22.6</v>
+        <v>-54.7</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.7</v>
+        <v>-21.6</v>
       </c>
       <c r="G11" t="n">
-        <v>17.2</v>
+        <v>11.4</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1013,25 +1013,25 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>126841</v>
+        <v>667460</v>
       </c>
       <c r="K11" t="n">
-        <v>25310</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>6.56</v>
+        <v>3.07</v>
       </c>
       <c r="M11" t="n">
-        <v>9.92</v>
+        <v>7.54</v>
       </c>
       <c r="N11" t="n">
-        <v>39.8</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1040,23 +1040,23 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.85</v>
+        <v>0.91</v>
       </c>
       <c r="D12" t="n">
-        <v>2.325</v>
+        <v>1.049</v>
       </c>
       <c r="E12" t="n">
-        <v>-54.7</v>
+        <v>1.4</v>
       </c>
       <c r="F12" t="n">
-        <v>-21.6</v>
+        <v>3.8</v>
       </c>
       <c r="G12" t="n">
-        <v>11.4</v>
+        <v>6.2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1065,25 +1065,25 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>667460</v>
+        <v>14262</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>11346</v>
       </c>
       <c r="L12" t="n">
-        <v>3.07</v>
+        <v>0.4</v>
       </c>
       <c r="M12" t="n">
-        <v>7.54</v>
+        <v>0.41</v>
       </c>
       <c r="N12" t="n">
-        <v>66.09999999999999</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1092,23 +1092,23 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="D13" t="n">
-        <v>1.049</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4</v>
+        <v>49.2</v>
       </c>
       <c r="F13" t="n">
-        <v>3.8</v>
+        <v>27.4</v>
       </c>
       <c r="G13" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1117,129 +1117,129 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>14262</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>11346</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>0.41</v>
+        <v>6.75</v>
       </c>
       <c r="N13" t="n">
-        <v>4.8</v>
+        <v>-43.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8120000000000001</v>
+        <v>1.185</v>
       </c>
       <c r="E14" t="n">
-        <v>49.2</v>
+        <v>-21.5</v>
       </c>
       <c r="F14" t="n">
-        <v>27.4</v>
+        <v>-9.9</v>
       </c>
       <c r="G14" t="n">
-        <v>5.7</v>
+        <v>1.7</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>BUY (undervalued)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>BUY (undervalued)</t>
-        </is>
-      </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>170829</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>28253</v>
       </c>
       <c r="L14" t="n">
-        <v>9.529999999999999</v>
+        <v>14.41</v>
       </c>
       <c r="M14" t="n">
-        <v>6.75</v>
+        <v>18.67</v>
       </c>
       <c r="N14" t="n">
-        <v>-43.5</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="D15" t="n">
-        <v>1.185</v>
+        <v>1.038</v>
       </c>
       <c r="E15" t="n">
-        <v>-21.5</v>
+        <v>-2.3</v>
       </c>
       <c r="F15" t="n">
-        <v>-9.9</v>
+        <v>-0.3</v>
       </c>
       <c r="G15" t="n">
         <v>1.7</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>170829</v>
+        <v>18174</v>
       </c>
       <c r="K15" t="n">
-        <v>28253</v>
+        <v>13478</v>
       </c>
       <c r="L15" t="n">
-        <v>14.41</v>
+        <v>29.79</v>
       </c>
       <c r="M15" t="n">
-        <v>18.67</v>
+        <v>30.99</v>
       </c>
       <c r="N15" t="n">
-        <v>23.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1248,19 +1248,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.89</v>
+        <v>1.03</v>
       </c>
       <c r="D16" t="n">
-        <v>1.038</v>
+        <v>0.989</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.3</v>
+        <v>3.6</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3</v>
+        <v>2.5</v>
       </c>
       <c r="G16" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1273,19 +1273,19 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>18174</v>
+        <v>203013</v>
       </c>
       <c r="K16" t="n">
-        <v>13478</v>
+        <v>229936</v>
       </c>
       <c r="L16" t="n">
-        <v>29.79</v>
+        <v>5.12</v>
       </c>
       <c r="M16" t="n">
-        <v>30.99</v>
+        <v>5.01</v>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="17">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -624,19 +624,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="D4" t="n">
-        <v>1.275</v>
+        <v>1.263</v>
       </c>
       <c r="E4" t="n">
         <v>-2.7</v>
       </c>
       <c r="F4" t="n">
-        <v>19</v>
+        <v>18.1</v>
       </c>
       <c r="G4" t="n">
-        <v>40.7</v>
+        <v>38.9</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>207375</v>
+        <v>207425</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         <v>16.02</v>
       </c>
       <c r="M4" t="n">
-        <v>23.16</v>
+        <v>22.86</v>
       </c>
       <c r="N4" t="n">
-        <v>43.4</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="5">
@@ -676,19 +676,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="D5" t="n">
-        <v>1.552</v>
+        <v>1.502</v>
       </c>
       <c r="E5" t="n">
         <v>-1.7</v>
       </c>
       <c r="F5" t="n">
-        <v>18.4</v>
+        <v>16.6</v>
       </c>
       <c r="G5" t="n">
-        <v>38.4</v>
+        <v>34.9</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         <v>76.73</v>
       </c>
       <c r="M5" t="n">
-        <v>108.02</v>
+        <v>105.23</v>
       </c>
       <c r="N5" t="n">
-        <v>40.1</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="6">
@@ -771,7 +771,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>ASC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -780,50 +780,50 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="D7" t="n">
-        <v>1.148</v>
+        <v>1.313</v>
       </c>
       <c r="E7" t="n">
-        <v>9.699999999999999</v>
+        <v>-5.7</v>
       </c>
       <c r="F7" t="n">
-        <v>17.7</v>
+        <v>8.6</v>
       </c>
       <c r="G7" t="n">
-        <v>25.8</v>
+        <v>22.8</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>BUY (undervalued)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>BUY (undervalued)</t>
-        </is>
-      </c>
       <c r="J7" t="n">
-        <v>43444</v>
+        <v>28607</v>
       </c>
       <c r="K7" t="n">
-        <v>9917</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>35.79</v>
+        <v>16.38</v>
       </c>
       <c r="M7" t="n">
-        <v>41.02</v>
+        <v>21.31</v>
       </c>
       <c r="N7" t="n">
-        <v>16</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ASC</t>
+          <t>TRMD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -832,23 +832,23 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="D8" t="n">
-        <v>1.313</v>
+        <v>1.083</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>8.6</v>
+        <v>14.2</v>
       </c>
       <c r="G8" t="n">
-        <v>22.8</v>
+        <v>18.7</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -857,25 +857,25 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>28607</v>
+        <v>43444</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>24848</v>
       </c>
       <c r="L8" t="n">
-        <v>16.38</v>
+        <v>35.79</v>
       </c>
       <c r="M8" t="n">
-        <v>21.31</v>
+        <v>38.72</v>
       </c>
       <c r="N8" t="n">
-        <v>28.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TNK</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -884,19 +884,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="D9" t="n">
-        <v>1.527</v>
+        <v>2.325</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.4</v>
+        <v>-54.7</v>
       </c>
       <c r="F9" t="n">
-        <v>7.6</v>
+        <v>-21.6</v>
       </c>
       <c r="G9" t="n">
-        <v>20.6</v>
+        <v>11.4</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>130174</v>
+        <v>667460</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>83.93000000000001</v>
+        <v>3.07</v>
       </c>
       <c r="M9" t="n">
-        <v>106.94</v>
+        <v>7.54</v>
       </c>
       <c r="N9" t="n">
-        <v>25.9</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>TNK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -936,19 +936,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="D10" t="n">
-        <v>1.553</v>
+        <v>1.258</v>
       </c>
       <c r="E10" t="n">
-        <v>-22.6</v>
+        <v>-5.4</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.7</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>17.2</v>
+        <v>7.3</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>126841</v>
+        <v>130174</v>
       </c>
       <c r="K10" t="n">
-        <v>25310</v>
+        <v>12273</v>
       </c>
       <c r="L10" t="n">
-        <v>6.56</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>9.92</v>
+        <v>95.2</v>
       </c>
       <c r="N10" t="n">
-        <v>39.8</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.85</v>
+        <v>1.03</v>
       </c>
       <c r="D11" t="n">
-        <v>2.325</v>
+        <v>1.404</v>
       </c>
       <c r="E11" t="n">
-        <v>-54.7</v>
+        <v>-22.6</v>
       </c>
       <c r="F11" t="n">
-        <v>-21.6</v>
+        <v>-8.1</v>
       </c>
       <c r="G11" t="n">
-        <v>11.4</v>
+        <v>6.4</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1013,25 +1013,25 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>667460</v>
+        <v>126841</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>52720</v>
       </c>
       <c r="L11" t="n">
-        <v>3.07</v>
+        <v>6.56</v>
       </c>
       <c r="M11" t="n">
-        <v>7.54</v>
+        <v>9.02</v>
       </c>
       <c r="N11" t="n">
-        <v>66.09999999999999</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>BRUT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1040,19 +1040,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.91</v>
+        <v>1.03</v>
       </c>
       <c r="D12" t="n">
-        <v>1.049</v>
+        <v>0.989</v>
       </c>
       <c r="E12" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="F12" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="G12" t="n">
-        <v>6.2</v>
+        <v>1.3</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1061,29 +1061,29 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14262</v>
+        <v>203062</v>
       </c>
       <c r="K12" t="n">
-        <v>11346</v>
+        <v>229942</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4</v>
+        <v>5.12</v>
       </c>
       <c r="M12" t="n">
-        <v>0.41</v>
+        <v>5.01</v>
       </c>
       <c r="N12" t="n">
-        <v>4.8</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>CMDB</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1092,44 +1092,44 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.88</v>
+        <v>0.62</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8120000000000001</v>
+        <v>1.034</v>
       </c>
       <c r="E13" t="n">
-        <v>49.2</v>
+        <v>-2</v>
       </c>
       <c r="F13" t="n">
-        <v>27.4</v>
+        <v>-0.7</v>
       </c>
       <c r="G13" t="n">
-        <v>5.7</v>
+        <v>0.7</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>HOLD (fairly valued)</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>18716</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>15152</v>
       </c>
       <c r="L13" t="n">
-        <v>9.529999999999999</v>
+        <v>20.11</v>
       </c>
       <c r="M13" t="n">
-        <v>6.75</v>
+        <v>20.66</v>
       </c>
       <c r="N13" t="n">
-        <v>-43.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="14">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="D14" t="n">
-        <v>1.185</v>
+        <v>1.176</v>
       </c>
       <c r="E14" t="n">
         <v>-21.5</v>
       </c>
       <c r="F14" t="n">
-        <v>-9.9</v>
+        <v>-10.4</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1172,16 +1172,16 @@
         <v>170829</v>
       </c>
       <c r="K14" t="n">
-        <v>28253</v>
+        <v>35323</v>
       </c>
       <c r="L14" t="n">
         <v>14.41</v>
       </c>
       <c r="M14" t="n">
-        <v>18.67</v>
+        <v>18.46</v>
       </c>
       <c r="N14" t="n">
-        <v>23.2</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="15">
@@ -1196,19 +1196,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="D15" t="n">
-        <v>1.038</v>
+        <v>1.018</v>
       </c>
       <c r="E15" t="n">
         <v>-2.3</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3</v>
+        <v>-1.3</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7</v>
+        <v>-0.4</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1224,22 +1224,22 @@
         <v>18174</v>
       </c>
       <c r="K15" t="n">
-        <v>13478</v>
+        <v>15895</v>
       </c>
       <c r="L15" t="n">
         <v>29.79</v>
       </c>
       <c r="M15" t="n">
-        <v>30.99</v>
+        <v>30.37</v>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BRUT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1248,50 +1248,50 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.03</v>
+        <v>0.95</v>
       </c>
       <c r="D16" t="n">
-        <v>0.989</v>
+        <v>1.067</v>
       </c>
       <c r="E16" t="n">
-        <v>3.6</v>
+        <v>-12.4</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5</v>
+        <v>-9</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3</v>
+        <v>-5.7</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>203013</v>
+        <v>35200</v>
       </c>
       <c r="K16" t="n">
-        <v>229936</v>
+        <v>24029</v>
       </c>
       <c r="L16" t="n">
-        <v>5.12</v>
+        <v>22.67</v>
       </c>
       <c r="M16" t="n">
-        <v>5.01</v>
+        <v>24.41</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.2</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CMDB</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1300,50 +1300,50 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.62</v>
+        <v>1.04</v>
       </c>
       <c r="D17" t="n">
-        <v>1.034</v>
+        <v>1.2</v>
       </c>
       <c r="E17" t="n">
-        <v>-2</v>
+        <v>-27.5</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7</v>
+        <v>-18</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7</v>
+        <v>-8.4</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>18716</v>
+        <v>214794</v>
       </c>
       <c r="K17" t="n">
-        <v>15152</v>
+        <v>60526</v>
       </c>
       <c r="L17" t="n">
-        <v>20.11</v>
+        <v>2.07</v>
       </c>
       <c r="M17" t="n">
-        <v>20.66</v>
+        <v>2.62</v>
       </c>
       <c r="N17" t="n">
-        <v>2.7</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1352,19 +1352,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.92</v>
+        <v>1.14</v>
       </c>
       <c r="D18" t="n">
-        <v>1.094</v>
+        <v>1.137</v>
       </c>
       <c r="E18" t="n">
-        <v>-12.4</v>
+        <v>-18.8</v>
       </c>
       <c r="F18" t="n">
-        <v>-7.6</v>
+        <v>-13.7</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.9</v>
+        <v>-8.6</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1373,50 +1373,50 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>35200</v>
+        <v>585846</v>
       </c>
       <c r="K18" t="n">
-        <v>19356</v>
+        <v>383020</v>
       </c>
       <c r="L18" t="n">
-        <v>22.67</v>
+        <v>15.97</v>
       </c>
       <c r="M18" t="n">
-        <v>25.13</v>
+        <v>17.98</v>
       </c>
       <c r="N18" t="n">
-        <v>9.5</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>whole-company</t>
+          <t>WHOLE-COMPANY (hybrid aggregation)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="D19" t="n">
-        <v>1.196</v>
+        <v>1.502</v>
       </c>
       <c r="E19" t="n">
-        <v>-18.8</v>
+        <v>-39.7</v>
       </c>
       <c r="F19" t="n">
-        <v>-11.5</v>
+        <v>-27.3</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.2</v>
+        <v>-14.9</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1425,29 +1425,29 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>585846</v>
+        <v>536654</v>
       </c>
       <c r="K19" t="n">
-        <v>296274</v>
+        <v>284074</v>
       </c>
       <c r="L19" t="n">
-        <v>15.97</v>
+        <v>59.59</v>
       </c>
       <c r="M19" t="n">
-        <v>18.84</v>
+        <v>84.09</v>
       </c>
       <c r="N19" t="n">
-        <v>14.6</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1456,19 +1456,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2</v>
+        <v>1.341</v>
       </c>
       <c r="E20" t="n">
-        <v>-27.5</v>
+        <v>-36.1</v>
       </c>
       <c r="F20" t="n">
-        <v>-17.9</v>
+        <v>-26.7</v>
       </c>
       <c r="G20" t="n">
-        <v>-8.4</v>
+        <v>-17.3</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1481,25 +1481,25 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>214768</v>
+        <v>281759</v>
       </c>
       <c r="K20" t="n">
-        <v>60522</v>
+        <v>135608</v>
       </c>
       <c r="L20" t="n">
-        <v>2.07</v>
+        <v>31.82</v>
       </c>
       <c r="M20" t="n">
-        <v>2.61</v>
+        <v>41.19</v>
       </c>
       <c r="N20" t="n">
-        <v>19.2</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1508,23 +1508,23 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.96</v>
+        <v>1.13</v>
       </c>
       <c r="D21" t="n">
-        <v>1.489</v>
+        <v>0.827</v>
       </c>
       <c r="E21" t="n">
-        <v>-36.1</v>
+        <v>11.9</v>
       </c>
       <c r="F21" t="n">
-        <v>-22.6</v>
+        <v>-3</v>
       </c>
       <c r="G21" t="n">
-        <v>-9.1</v>
+        <v>-18</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1533,46 +1533,46 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>281759</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>72178</v>
+        <v>57726</v>
       </c>
       <c r="L21" t="n">
-        <v>31.82</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>45.26</v>
+        <v>6.99</v>
       </c>
       <c r="N21" t="n">
-        <v>27</v>
+        <v>-29.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>WHOLE-COMPANY (hybrid aggregation)</t>
+          <t>whole-company</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="D22" t="n">
-        <v>1.554</v>
+        <v>1.208</v>
       </c>
       <c r="E22" t="n">
-        <v>-39.7</v>
+        <v>-37.1</v>
       </c>
       <c r="F22" t="n">
-        <v>-26</v>
+        <v>-29.1</v>
       </c>
       <c r="G22" t="n">
-        <v>-12.3</v>
+        <v>-21</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1585,25 +1585,25 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>536654</v>
+        <v>682553</v>
       </c>
       <c r="K22" t="n">
-        <v>257979</v>
+        <v>465663</v>
       </c>
       <c r="L22" t="n">
-        <v>59.59</v>
+        <v>27.79</v>
       </c>
       <c r="M22" t="n">
-        <v>86.62</v>
+        <v>34.92</v>
       </c>
       <c r="N22" t="n">
-        <v>27.4</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1612,19 +1612,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="D23" t="n">
-        <v>1.222</v>
+        <v>1.051</v>
       </c>
       <c r="E23" t="n">
-        <v>-37.1</v>
+        <v>-25.8</v>
       </c>
       <c r="F23" t="n">
-        <v>-28.5</v>
+        <v>-23.9</v>
       </c>
       <c r="G23" t="n">
-        <v>-19.9</v>
+        <v>-22.1</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1637,25 +1637,25 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>682553</v>
+        <v>36604</v>
       </c>
       <c r="K23" t="n">
-        <v>451717</v>
+        <v>33560</v>
       </c>
       <c r="L23" t="n">
-        <v>27.79</v>
+        <v>0.4</v>
       </c>
       <c r="M23" t="n">
-        <v>35.38</v>
+        <v>0.41</v>
       </c>
       <c r="N23" t="n">
-        <v>17.2</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BWLP</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="D24" t="n">
-        <v>1.273</v>
+        <v>0.899</v>
       </c>
       <c r="E24" t="n">
-        <v>-39.9</v>
+        <v>-6.4</v>
       </c>
       <c r="F24" t="n">
-        <v>-30.4</v>
+        <v>-14.3</v>
       </c>
       <c r="G24" t="n">
-        <v>-20.9</v>
+        <v>-22.2</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1689,25 +1689,25 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>253792</v>
+        <v>304350</v>
       </c>
       <c r="K24" t="n">
-        <v>138973</v>
+        <v>553442</v>
       </c>
       <c r="L24" t="n">
-        <v>14.46</v>
+        <v>29.47</v>
       </c>
       <c r="M24" t="n">
-        <v>19.02</v>
+        <v>24.51</v>
       </c>
       <c r="N24" t="n">
-        <v>18.9</v>
+        <v>-15.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>BWLP</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1716,19 +1716,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="D25" t="n">
-        <v>0.902</v>
+        <v>1.156</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.4</v>
+        <v>-39.9</v>
       </c>
       <c r="F25" t="n">
-        <v>-14</v>
+        <v>-34.4</v>
       </c>
       <c r="G25" t="n">
-        <v>-21.7</v>
+        <v>-29</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1741,19 +1741,19 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>304350</v>
+        <v>253816</v>
       </c>
       <c r="K25" t="n">
-        <v>546338</v>
+        <v>188145</v>
       </c>
       <c r="L25" t="n">
-        <v>29.47</v>
+        <v>14.46</v>
       </c>
       <c r="M25" t="n">
-        <v>24.65</v>
+        <v>17.07</v>
       </c>
       <c r="N25" t="n">
-        <v>-15.3</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="26">
@@ -1768,19 +1768,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="D26" t="n">
-        <v>1.206</v>
+        <v>1.118</v>
       </c>
       <c r="E26" t="n">
         <v>-37.6</v>
       </c>
       <c r="F26" t="n">
-        <v>-30.6</v>
+        <v>-33.6</v>
       </c>
       <c r="G26" t="n">
-        <v>-23.7</v>
+        <v>-29.6</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1796,16 +1796,16 @@
         <v>623698</v>
       </c>
       <c r="K26" t="n">
-        <v>450546</v>
+        <v>524309</v>
       </c>
       <c r="L26" t="n">
         <v>41.71</v>
       </c>
       <c r="M26" t="n">
-        <v>51.03</v>
+        <v>47.06</v>
       </c>
       <c r="N26" t="n">
-        <v>13.9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -1095,16 +1095,16 @@
         <v>0.62</v>
       </c>
       <c r="D13" t="n">
-        <v>1.034</v>
+        <v>1.032</v>
       </c>
       <c r="E13" t="n">
-        <v>-2</v>
+        <v>-4.8</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7</v>
+        <v>-3.6</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7</v>
+        <v>-2.4</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1117,19 +1117,19 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>18716</v>
+        <v>18156</v>
       </c>
       <c r="K13" t="n">
-        <v>15152</v>
+        <v>14901</v>
       </c>
       <c r="L13" t="n">
-        <v>20.11</v>
+        <v>19.53</v>
       </c>
       <c r="M13" t="n">
-        <v>20.66</v>
+        <v>20.02</v>
       </c>
       <c r="N13" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="14">
@@ -1147,16 +1147,16 @@
         <v>0.86</v>
       </c>
       <c r="D14" t="n">
-        <v>1.176</v>
+        <v>1.174</v>
       </c>
       <c r="E14" t="n">
-        <v>-21.5</v>
+        <v>-24.4</v>
       </c>
       <c r="F14" t="n">
-        <v>-10.4</v>
+        <v>-13.8</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6</v>
+        <v>-3.1</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1165,23 +1165,23 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>170829</v>
+        <v>169243</v>
       </c>
       <c r="K14" t="n">
-        <v>35323</v>
+        <v>35286</v>
       </c>
       <c r="L14" t="n">
-        <v>14.41</v>
+        <v>13.87</v>
       </c>
       <c r="M14" t="n">
-        <v>18.46</v>
+        <v>17.78</v>
       </c>
       <c r="N14" t="n">
-        <v>22.1</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="15">
@@ -1199,47 +1199,47 @@
         <v>0.91</v>
       </c>
       <c r="D15" t="n">
-        <v>1.018</v>
+        <v>1.016</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.3</v>
+        <v>-5.7</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3</v>
+        <v>-4.9</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4</v>
+        <v>-4.1</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>TRIM/SHORT (overvalued)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>HOLD (fairly valued)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>HOLD (fairly valued)</t>
-        </is>
-      </c>
       <c r="J15" t="n">
-        <v>18174</v>
+        <v>17725</v>
       </c>
       <c r="K15" t="n">
-        <v>15895</v>
+        <v>15759</v>
       </c>
       <c r="L15" t="n">
-        <v>29.79</v>
+        <v>28.74</v>
       </c>
       <c r="M15" t="n">
-        <v>30.37</v>
+        <v>29.23</v>
       </c>
       <c r="N15" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GNK</t>
+          <t>MPCC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1248,19 +1248,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.95</v>
+        <v>1.04</v>
       </c>
       <c r="D16" t="n">
-        <v>1.067</v>
+        <v>1.2</v>
       </c>
       <c r="E16" t="n">
-        <v>-12.4</v>
+        <v>-27.5</v>
       </c>
       <c r="F16" t="n">
-        <v>-9</v>
+        <v>-18</v>
       </c>
       <c r="G16" t="n">
-        <v>-5.7</v>
+        <v>-8.4</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1273,25 +1273,25 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>35200</v>
+        <v>214794</v>
       </c>
       <c r="K16" t="n">
-        <v>24029</v>
+        <v>60526</v>
       </c>
       <c r="L16" t="n">
-        <v>22.67</v>
+        <v>2.07</v>
       </c>
       <c r="M16" t="n">
-        <v>24.41</v>
+        <v>2.62</v>
       </c>
       <c r="N16" t="n">
-        <v>6.7</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MPCC</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1300,19 +1300,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2</v>
+        <v>1.137</v>
       </c>
       <c r="E17" t="n">
-        <v>-27.5</v>
+        <v>-18.8</v>
       </c>
       <c r="F17" t="n">
-        <v>-18</v>
+        <v>-13.7</v>
       </c>
       <c r="G17" t="n">
-        <v>-8.4</v>
+        <v>-8.6</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1325,25 +1325,25 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>214794</v>
+        <v>585846</v>
       </c>
       <c r="K17" t="n">
-        <v>60526</v>
+        <v>383020</v>
       </c>
       <c r="L17" t="n">
-        <v>2.07</v>
+        <v>15.97</v>
       </c>
       <c r="M17" t="n">
-        <v>2.62</v>
+        <v>17.98</v>
       </c>
       <c r="N17" t="n">
-        <v>19.2</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>GNK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1352,19 +1352,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.14</v>
+        <v>0.95</v>
       </c>
       <c r="D18" t="n">
-        <v>1.137</v>
+        <v>1.067</v>
       </c>
       <c r="E18" t="n">
-        <v>-18.8</v>
+        <v>-16.3</v>
       </c>
       <c r="F18" t="n">
-        <v>-13.7</v>
+        <v>-13.1</v>
       </c>
       <c r="G18" t="n">
-        <v>-8.6</v>
+        <v>-9.9</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>585846</v>
+        <v>34989</v>
       </c>
       <c r="K18" t="n">
-        <v>383020</v>
+        <v>23884</v>
       </c>
       <c r="L18" t="n">
-        <v>15.97</v>
+        <v>21.66</v>
       </c>
       <c r="M18" t="n">
-        <v>17.98</v>
+        <v>23.32</v>
       </c>
       <c r="N18" t="n">
-        <v>10.2</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="19">
@@ -1499,7 +1499,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1508,23 +1508,23 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="D21" t="n">
-        <v>0.827</v>
+        <v>1.208</v>
       </c>
       <c r="E21" t="n">
-        <v>11.9</v>
+        <v>-37.1</v>
       </c>
       <c r="F21" t="n">
-        <v>-3</v>
+        <v>-29.1</v>
       </c>
       <c r="G21" t="n">
-        <v>-18</v>
+        <v>-21</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1533,25 +1533,25 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>682553</v>
       </c>
       <c r="K21" t="n">
-        <v>57726</v>
+        <v>465663</v>
       </c>
       <c r="L21" t="n">
-        <v>9.529999999999999</v>
+        <v>27.79</v>
       </c>
       <c r="M21" t="n">
-        <v>6.99</v>
+        <v>34.92</v>
       </c>
       <c r="N21" t="n">
-        <v>-29.9</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1560,23 +1560,23 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="D22" t="n">
-        <v>1.208</v>
+        <v>0.824</v>
       </c>
       <c r="E22" t="n">
-        <v>-37.1</v>
+        <v>8.4</v>
       </c>
       <c r="F22" t="n">
-        <v>-29.1</v>
+        <v>-6.6</v>
       </c>
       <c r="G22" t="n">
-        <v>-21</v>
+        <v>-21.5</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1585,25 +1585,25 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>682553</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>465663</v>
+        <v>58110</v>
       </c>
       <c r="L22" t="n">
-        <v>27.79</v>
+        <v>9.23</v>
       </c>
       <c r="M22" t="n">
-        <v>34.92</v>
+        <v>6.69</v>
       </c>
       <c r="N22" t="n">
-        <v>16.1</v>
+        <v>-29.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1612,19 +1612,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="D23" t="n">
-        <v>1.051</v>
+        <v>0.899</v>
       </c>
       <c r="E23" t="n">
-        <v>-25.8</v>
+        <v>-6.4</v>
       </c>
       <c r="F23" t="n">
-        <v>-23.9</v>
+        <v>-14.3</v>
       </c>
       <c r="G23" t="n">
-        <v>-22.1</v>
+        <v>-22.2</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1637,25 +1637,25 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>36604</v>
+        <v>304350</v>
       </c>
       <c r="K23" t="n">
-        <v>33560</v>
+        <v>553442</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4</v>
+        <v>29.47</v>
       </c>
       <c r="M23" t="n">
-        <v>0.41</v>
+        <v>24.51</v>
       </c>
       <c r="N23" t="n">
-        <v>3.7</v>
+        <v>-15.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="D24" t="n">
-        <v>0.899</v>
+        <v>1.051</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.4</v>
+        <v>-29.2</v>
       </c>
       <c r="F24" t="n">
-        <v>-14.3</v>
+        <v>-27.5</v>
       </c>
       <c r="G24" t="n">
-        <v>-22.2</v>
+        <v>-25.7</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>304350</v>
+        <v>40554</v>
       </c>
       <c r="K24" t="n">
-        <v>553442</v>
+        <v>36892</v>
       </c>
       <c r="L24" t="n">
-        <v>29.47</v>
+        <v>0.38</v>
       </c>
       <c r="M24" t="n">
-        <v>24.51</v>
+        <v>0.4</v>
       </c>
       <c r="N24" t="n">
-        <v>-15.8</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="25">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>40554</v>
+        <v>40559</v>
       </c>
       <c r="K24" t="n">
-        <v>36892</v>
+        <v>36896</v>
       </c>
       <c r="L24" t="n">
         <v>0.38</v>

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -1251,16 +1251,16 @@
         <v>1.04</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2</v>
+        <v>1.193</v>
       </c>
       <c r="E16" t="n">
-        <v>-27.5</v>
+        <v>-24.8</v>
       </c>
       <c r="F16" t="n">
-        <v>-18</v>
+        <v>-16</v>
       </c>
       <c r="G16" t="n">
-        <v>-8.4</v>
+        <v>-7.1</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1273,19 +1273,19 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>214794</v>
+        <v>192190</v>
       </c>
       <c r="K16" t="n">
-        <v>60526</v>
+        <v>54836</v>
       </c>
       <c r="L16" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="M16" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="N16" t="n">
-        <v>19.2</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="17">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -887,16 +887,16 @@
         <v>0.85</v>
       </c>
       <c r="D9" t="n">
-        <v>2.325</v>
+        <v>2.398</v>
       </c>
       <c r="E9" t="n">
-        <v>-54.7</v>
+        <v>-55.8</v>
       </c>
       <c r="F9" t="n">
-        <v>-21.6</v>
+        <v>-22.2</v>
       </c>
       <c r="G9" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -909,19 +909,19 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>667460</v>
+        <v>678594</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>7.54</v>
+        <v>7.53</v>
       </c>
       <c r="N9" t="n">
-        <v>66.09999999999999</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -991,16 +991,16 @@
         <v>1.03</v>
       </c>
       <c r="D11" t="n">
-        <v>1.404</v>
+        <v>1.554</v>
       </c>
       <c r="E11" t="n">
-        <v>-22.6</v>
+        <v>-34</v>
       </c>
       <c r="F11" t="n">
-        <v>-8.1</v>
+        <v>-14.2</v>
       </c>
       <c r="G11" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>126841</v>
+        <v>159436</v>
       </c>
       <c r="K11" t="n">
-        <v>52720</v>
+        <v>53122</v>
       </c>
       <c r="L11" t="n">
-        <v>6.56</v>
+        <v>5.59</v>
       </c>
       <c r="M11" t="n">
-        <v>9.02</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>29</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="12">
@@ -1511,16 +1511,16 @@
         <v>1.33</v>
       </c>
       <c r="D21" t="n">
-        <v>1.208</v>
+        <v>1.196</v>
       </c>
       <c r="E21" t="n">
-        <v>-37.1</v>
+        <v>-36</v>
       </c>
       <c r="F21" t="n">
-        <v>-29.1</v>
+        <v>-28.6</v>
       </c>
       <c r="G21" t="n">
-        <v>-21</v>
+        <v>-21.3</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>682553</v>
+        <v>715733</v>
       </c>
       <c r="K21" t="n">
-        <v>465663</v>
+        <v>499366</v>
       </c>
       <c r="L21" t="n">
-        <v>27.79</v>
+        <v>28.29</v>
       </c>
       <c r="M21" t="n">
-        <v>34.92</v>
+        <v>34.78</v>
       </c>
       <c r="N21" t="n">
-        <v>16.1</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="22">
@@ -1719,16 +1719,16 @@
         <v>1.27</v>
       </c>
       <c r="D25" t="n">
-        <v>1.156</v>
+        <v>1.157</v>
       </c>
       <c r="E25" t="n">
-        <v>-39.9</v>
+        <v>-39.6</v>
       </c>
       <c r="F25" t="n">
-        <v>-34.4</v>
+        <v>-34.3</v>
       </c>
       <c r="G25" t="n">
-        <v>-29</v>
+        <v>-28.9</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1741,19 +1741,19 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>253816</v>
+        <v>252777</v>
       </c>
       <c r="K25" t="n">
-        <v>188145</v>
+        <v>187737</v>
       </c>
       <c r="L25" t="n">
-        <v>14.46</v>
+        <v>14.52</v>
       </c>
       <c r="M25" t="n">
-        <v>17.07</v>
+        <v>17.1</v>
       </c>
       <c r="N25" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="26">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -627,20 +627,20 @@
         <v>0.72</v>
       </c>
       <c r="D4" t="n">
-        <v>1.263</v>
+        <v>1.175</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.7</v>
+        <v>6.7</v>
       </c>
       <c r="F4" t="n">
-        <v>18.1</v>
+        <v>22.3</v>
       </c>
       <c r="G4" t="n">
-        <v>38.9</v>
+        <v>37.8</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -649,19 +649,19 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>207425</v>
+        <v>63532</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>16.02</v>
+        <v>17.56</v>
       </c>
       <c r="M4" t="n">
-        <v>22.86</v>
+        <v>22.69</v>
       </c>
       <c r="N4" t="n">
-        <v>41.5</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/broker_nav_sweep.xlsx
+++ b/outputs/broker_nav_sweep.xlsx
@@ -1095,17 +1095,17 @@
         <v>0.62</v>
       </c>
       <c r="D13" t="n">
-        <v>1.032</v>
+        <v>1.017</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.8</v>
+        <v>-4.9</v>
       </c>
       <c r="F13" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="G13" t="n">
         <v>-3.6</v>
       </c>
-      <c r="G13" t="n">
-        <v>-2.4</v>
-      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>HOLD (fairly valued)</t>
@@ -1117,19 +1117,19 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>18156</v>
+        <v>16931</v>
       </c>
       <c r="K13" t="n">
-        <v>14901</v>
+        <v>15108</v>
       </c>
       <c r="L13" t="n">
-        <v>19.53</v>
+        <v>19.51</v>
       </c>
       <c r="M13" t="n">
-        <v>20.02</v>
+        <v>19.78</v>
       </c>
       <c r="N13" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="14">
@@ -1147,16 +1147,16 @@
         <v>0.86</v>
       </c>
       <c r="D14" t="n">
-        <v>1.174</v>
+        <v>1.173</v>
       </c>
       <c r="E14" t="n">
-        <v>-24.4</v>
+        <v>-25.7</v>
       </c>
       <c r="F14" t="n">
-        <v>-13.8</v>
+        <v>-15.3</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.1</v>
+        <v>-4.8</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1169,19 +1169,19 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>169243</v>
+        <v>168098</v>
       </c>
       <c r="K14" t="n">
-        <v>35286</v>
+        <v>35260</v>
       </c>
       <c r="L14" t="n">
-        <v>13.87</v>
+        <v>13.63</v>
       </c>
       <c r="M14" t="n">
-        <v>17.78</v>
+        <v>17.47</v>
       </c>
       <c r="N14" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="15">
@@ -1199,16 +1199,16 @@
         <v>0.91</v>
       </c>
       <c r="D15" t="n">
-        <v>1.016</v>
+        <v>1.006</v>
       </c>
       <c r="E15" t="n">
-        <v>-5.7</v>
+        <v>-6.2</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.9</v>
+        <v>-5.9</v>
       </c>
       <c r="G15" t="n">
-        <v>-4.1</v>
+        <v>-5.6</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1217,23 +1217,23 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>HOLD (fairly valued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>17725</v>
+        <v>15280</v>
       </c>
       <c r="K15" t="n">
-        <v>15759</v>
+        <v>14279</v>
       </c>
       <c r="L15" t="n">
-        <v>28.74</v>
+        <v>28.59</v>
       </c>
       <c r="M15" t="n">
-        <v>29.23</v>
+        <v>28.77</v>
       </c>
       <c r="N15" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="16">
@@ -1355,16 +1355,16 @@
         <v>0.95</v>
       </c>
       <c r="D18" t="n">
-        <v>1.067</v>
+        <v>1.058</v>
       </c>
       <c r="E18" t="n">
-        <v>-16.3</v>
+        <v>-17.1</v>
       </c>
       <c r="F18" t="n">
-        <v>-13.1</v>
+        <v>-14.3</v>
       </c>
       <c r="G18" t="n">
-        <v>-9.9</v>
+        <v>-11.6</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>34989</v>
+        <v>34013</v>
       </c>
       <c r="K18" t="n">
-        <v>23884</v>
+        <v>24146</v>
       </c>
       <c r="L18" t="n">
-        <v>21.66</v>
+        <v>21.45</v>
       </c>
       <c r="M18" t="n">
-        <v>23.32</v>
+        <v>22.89</v>
       </c>
       <c r="N18" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="19">
@@ -1551,7 +1551,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SB</t>
+          <t>FLNG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1560,23 +1560,23 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="D22" t="n">
-        <v>0.824</v>
+        <v>0.899</v>
       </c>
       <c r="E22" t="n">
-        <v>8.4</v>
+        <v>-6.4</v>
       </c>
       <c r="F22" t="n">
-        <v>-6.6</v>
+        <v>-14.3</v>
       </c>
       <c r="G22" t="n">
-        <v>-21.5</v>
+        <v>-22.2</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>BUY (undervalued)</t>
+          <t>TRIM/SHORT (overvalued)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1585,25 +1585,25 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>304350</v>
       </c>
       <c r="K22" t="n">
-        <v>58110</v>
+        <v>553442</v>
       </c>
       <c r="L22" t="n">
-        <v>9.23</v>
+        <v>29.47</v>
       </c>
       <c r="M22" t="n">
-        <v>6.69</v>
+        <v>24.51</v>
       </c>
       <c r="N22" t="n">
-        <v>-29.9</v>
+        <v>-15.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FLNG</t>
+          <t>SB</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1612,23 +1612,23 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.44</v>
+        <v>1.13</v>
       </c>
       <c r="D23" t="n">
-        <v>0.899</v>
+        <v>0.821</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.4</v>
+        <v>6.7</v>
       </c>
       <c r="F23" t="n">
-        <v>-14.3</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>-22.2</v>
+        <v>-23.4</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>TRIM/SHORT (overvalued)</t>
+          <t>BUY (undervalued)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1637,19 +1637,19 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>304350</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>553442</v>
+        <v>59090</v>
       </c>
       <c r="L23" t="n">
-        <v>29.47</v>
+        <v>9.09</v>
       </c>
       <c r="M23" t="n">
-        <v>24.51</v>
+        <v>6.53</v>
       </c>
       <c r="N23" t="n">
-        <v>-15.8</v>
+        <v>-30.1</v>
       </c>
     </row>
     <row r="24">
@@ -1667,16 +1667,16 @@
         <v>1.24</v>
       </c>
       <c r="D24" t="n">
-        <v>1.051</v>
+        <v>1.041</v>
       </c>
       <c r="E24" t="n">
-        <v>-29.2</v>
+        <v>-29.4</v>
       </c>
       <c r="F24" t="n">
-        <v>-27.5</v>
+        <v>-28</v>
       </c>
       <c r="G24" t="n">
-        <v>-25.7</v>
+        <v>-26.6</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>40559</v>
+        <v>40189</v>
       </c>
       <c r="K24" t="n">
-        <v>36896</v>
+        <v>37148</v>
       </c>
       <c r="L24" t="n">
         <v>0.38</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="25">
